--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -652,10 +652,10 @@
     <t>['20']</t>
   </si>
   <si>
-    <t>['8', '54']</t>
+    <t>['4']</t>
   </si>
   <si>
-    <t>['4']</t>
+    <t>['8', '54']</t>
   </si>
   <si>
     <t>['77']</t>
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP178"/>
+  <dimension ref="A1:BP179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1934,7 +1934,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2140,7 +2140,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q5">
         <v>5.5</v>
@@ -2633,7 +2633,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ7">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ19">
         <v>2</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ22">
         <v>2.4</v>
@@ -7989,7 +7989,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ33">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR33">
         <v>0.7</v>
@@ -9016,7 +9016,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -11285,7 +11285,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ49">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR49">
         <v>1.18</v>
@@ -14372,7 +14372,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14993,7 +14993,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -18492,7 +18492,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ84">
         <v>0.3</v>
@@ -19113,7 +19113,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ87">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -21791,7 +21791,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ100">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR100">
         <v>1.37</v>
@@ -22406,7 +22406,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ103">
         <v>2.1</v>
@@ -25702,7 +25702,7 @@
         <v>0.33</v>
       </c>
       <c r="AP119">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ119">
         <v>0.33</v>
@@ -26941,7 +26941,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ125">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR125">
         <v>1.92</v>
@@ -30031,7 +30031,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ140">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR140">
         <v>1.81</v>
@@ -31058,7 +31058,7 @@
         <v>1.86</v>
       </c>
       <c r="AP145">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ145">
         <v>1.8</v>
@@ -34560,7 +34560,7 @@
         <v>0.33</v>
       </c>
       <c r="AP162">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ162">
         <v>0.55</v>
@@ -35590,7 +35590,7 @@
         <v>1.44</v>
       </c>
       <c r="AP167">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ167">
         <v>1.3</v>
@@ -35799,7 +35799,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ168">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR168">
         <v>1.26</v>
@@ -37871,22 +37871,22 @@
         <v>2.64</v>
       </c>
       <c r="AU178">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV178">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW178">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX178">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY178">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AZ178">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BA178">
         <v>5</v>
@@ -37935,6 +37935,212 @@
       </c>
       <c r="BP178">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7466237</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F179">
+        <v>21</v>
+      </c>
+      <c r="G179" t="s">
+        <v>87</v>
+      </c>
+      <c r="H179" t="s">
+        <v>84</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>1</v>
+      </c>
+      <c r="N179">
+        <v>2</v>
+      </c>
+      <c r="O179" t="s">
+        <v>212</v>
+      </c>
+      <c r="P179" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q179">
+        <v>2.5</v>
+      </c>
+      <c r="R179">
+        <v>2.25</v>
+      </c>
+      <c r="S179">
+        <v>4.33</v>
+      </c>
+      <c r="T179">
+        <v>1.36</v>
+      </c>
+      <c r="U179">
+        <v>3</v>
+      </c>
+      <c r="V179">
+        <v>2.63</v>
+      </c>
+      <c r="W179">
+        <v>1.44</v>
+      </c>
+      <c r="X179">
+        <v>7</v>
+      </c>
+      <c r="Y179">
+        <v>1.1</v>
+      </c>
+      <c r="Z179">
+        <v>1.73</v>
+      </c>
+      <c r="AA179">
+        <v>4.1</v>
+      </c>
+      <c r="AB179">
+        <v>3.94</v>
+      </c>
+      <c r="AC179">
+        <v>1.05</v>
+      </c>
+      <c r="AD179">
+        <v>12</v>
+      </c>
+      <c r="AE179">
+        <v>1.26</v>
+      </c>
+      <c r="AF179">
+        <v>3.67</v>
+      </c>
+      <c r="AG179">
+        <v>1.53</v>
+      </c>
+      <c r="AH179">
+        <v>2.29</v>
+      </c>
+      <c r="AI179">
+        <v>1.7</v>
+      </c>
+      <c r="AJ179">
+        <v>2.05</v>
+      </c>
+      <c r="AK179">
+        <v>1.26</v>
+      </c>
+      <c r="AL179">
+        <v>1.28</v>
+      </c>
+      <c r="AM179">
+        <v>1.82</v>
+      </c>
+      <c r="AN179">
+        <v>1.8</v>
+      </c>
+      <c r="AO179">
+        <v>0.78</v>
+      </c>
+      <c r="AP179">
+        <v>1.73</v>
+      </c>
+      <c r="AQ179">
+        <v>0.8</v>
+      </c>
+      <c r="AR179">
+        <v>1.35</v>
+      </c>
+      <c r="AS179">
+        <v>0.95</v>
+      </c>
+      <c r="AT179">
+        <v>2.3</v>
+      </c>
+      <c r="AU179">
+        <v>6</v>
+      </c>
+      <c r="AV179">
+        <v>7</v>
+      </c>
+      <c r="AW179">
+        <v>13</v>
+      </c>
+      <c r="AX179">
+        <v>6</v>
+      </c>
+      <c r="AY179">
+        <v>24</v>
+      </c>
+      <c r="AZ179">
+        <v>16</v>
+      </c>
+      <c r="BA179">
+        <v>4</v>
+      </c>
+      <c r="BB179">
+        <v>3</v>
+      </c>
+      <c r="BC179">
+        <v>7</v>
+      </c>
+      <c r="BD179">
+        <v>1.58</v>
+      </c>
+      <c r="BE179">
+        <v>6.75</v>
+      </c>
+      <c r="BF179">
+        <v>2.55</v>
+      </c>
+      <c r="BG179">
+        <v>1.23</v>
+      </c>
+      <c r="BH179">
+        <v>3.65</v>
+      </c>
+      <c r="BI179">
+        <v>1.41</v>
+      </c>
+      <c r="BJ179">
+        <v>2.65</v>
+      </c>
+      <c r="BK179">
+        <v>1.67</v>
+      </c>
+      <c r="BL179">
+        <v>2.05</v>
+      </c>
+      <c r="BM179">
+        <v>2.05</v>
+      </c>
+      <c r="BN179">
+        <v>1.67</v>
+      </c>
+      <c r="BO179">
+        <v>2.63</v>
+      </c>
+      <c r="BP179">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="307">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -655,6 +655,24 @@
     <t>['4']</t>
   </si>
   <si>
+    <t>['18', '44', '70']</t>
+  </si>
+  <si>
+    <t>['8', '82']</t>
+  </si>
+  <si>
+    <t>['66', '90', '90+5']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['37', '90+4']</t>
+  </si>
+  <si>
+    <t>['11', '90+1']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -749,9 +767,6 @@
   </si>
   <si>
     <t>['15', '22']</t>
-  </si>
-  <si>
-    <t>['11', '90+1']</t>
   </si>
   <si>
     <t>['15', '22', '44', '58', '77']</t>
@@ -905,6 +920,21 @@
   </si>
   <si>
     <t>['50']</t>
+  </si>
+  <si>
+    <t>['55', '59', '83']</t>
+  </si>
+  <si>
+    <t>['15', '90']</t>
+  </si>
+  <si>
+    <t>['52', '73', '76']</t>
+  </si>
+  <si>
+    <t>['58', '72', '85', '90+2']</t>
+  </si>
+  <si>
+    <t>['66', '67']</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP179"/>
+  <dimension ref="A1:BP185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1934,7 +1964,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2012,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ4">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2218,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ5">
         <v>1.8</v>
@@ -2346,7 +2376,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2427,7 +2457,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ6">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2964,7 +2994,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3042,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3248,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ10">
         <v>0.55</v>
@@ -3660,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ12">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4200,7 +4230,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4406,7 +4436,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4487,7 +4517,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4612,7 +4642,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4690,10 +4720,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ17">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5308,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ20">
         <v>0.8</v>
@@ -5436,7 +5466,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5514,10 +5544,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ21">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR21">
         <v>0.96</v>
@@ -5642,7 +5672,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5723,7 +5753,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ22">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR22">
         <v>0.79</v>
@@ -6260,7 +6290,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -6341,7 +6371,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ25">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR25">
         <v>1.08</v>
@@ -6544,10 +6574,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ26">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6672,7 +6702,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6956,7 +6986,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ28">
         <v>0.5</v>
@@ -7084,7 +7114,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7368,7 +7398,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ30">
         <v>0.7</v>
@@ -7496,7 +7526,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7702,7 +7732,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7783,7 +7813,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ32">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR32">
         <v>1.07</v>
@@ -7986,7 +8016,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ33">
         <v>0.8</v>
@@ -8732,7 +8762,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -8813,7 +8843,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ37">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR37">
         <v>1.07</v>
@@ -9144,7 +9174,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9350,7 +9380,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9637,7 +9667,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ41">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -10252,7 +10282,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10380,7 +10410,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10458,7 +10488,7 @@
         <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ45">
         <v>1.8</v>
@@ -10586,7 +10616,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10792,7 +10822,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -10998,7 +11028,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11076,7 +11106,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ48">
         <v>2</v>
@@ -11204,7 +11234,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11282,7 +11312,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ49">
         <v>0.8</v>
@@ -11410,7 +11440,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11488,7 +11518,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ50">
         <v>0.5</v>
@@ -11616,7 +11646,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11694,10 +11724,10 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ51">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR51">
         <v>0.82</v>
@@ -12028,7 +12058,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12109,7 +12139,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ53">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12234,7 +12264,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12440,7 +12470,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12521,7 +12551,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ55">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR55">
         <v>1.25</v>
@@ -12646,7 +12676,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -12724,10 +12754,10 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ56">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR56">
         <v>1.55</v>
@@ -13136,7 +13166,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ58">
         <v>0.33</v>
@@ -13676,7 +13706,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13882,7 +13912,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -13963,7 +13993,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ62">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR62">
         <v>2.58</v>
@@ -14166,7 +14196,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ63">
         <v>1.1</v>
@@ -14706,7 +14736,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14787,7 +14817,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ66">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR66">
         <v>1.08</v>
@@ -14912,7 +14942,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -14990,7 +15020,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ67">
         <v>0.8</v>
@@ -15199,7 +15229,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ68">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR68">
         <v>2.17</v>
@@ -15402,7 +15432,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ69">
         <v>0.8</v>
@@ -15530,7 +15560,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15608,7 +15638,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ70">
         <v>0.5</v>
@@ -15942,7 +15972,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16148,7 +16178,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16229,7 +16259,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ73">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR73">
         <v>2.44</v>
@@ -16432,7 +16462,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74">
         <v>0.55</v>
@@ -16560,7 +16590,7 @@
         <v>144</v>
       </c>
       <c r="P75" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="Q75">
         <v>6.5</v>
@@ -16641,7 +16671,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ75">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR75">
         <v>1.24</v>
@@ -16766,7 +16796,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -16844,10 +16874,10 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ76">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR76">
         <v>1.77</v>
@@ -17259,7 +17289,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ78">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR78">
         <v>1.07</v>
@@ -17384,7 +17414,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17590,7 +17620,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17668,7 +17698,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ80">
         <v>0.7</v>
@@ -17874,7 +17904,7 @@
         <v>0.75</v>
       </c>
       <c r="AP81">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18414,7 +18444,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18495,7 +18525,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ84">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR84">
         <v>1.12</v>
@@ -18698,7 +18728,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ85">
         <v>1.2</v>
@@ -18826,7 +18856,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18907,7 +18937,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ86">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19316,7 +19346,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ88">
         <v>1.1</v>
@@ -19444,7 +19474,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19650,7 +19680,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19937,7 +19967,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ91">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR91">
         <v>1.05</v>
@@ -20268,7 +20298,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20346,10 +20376,10 @@
         <v>3</v>
       </c>
       <c r="AP93">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ93">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR93">
         <v>2.04</v>
@@ -20474,7 +20504,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20886,7 +20916,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -20964,7 +20994,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ96">
         <v>0.8</v>
@@ -21170,7 +21200,7 @@
         <v>0.8</v>
       </c>
       <c r="AP97">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ97">
         <v>0.5</v>
@@ -21298,7 +21328,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21379,7 +21409,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ98">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR98">
         <v>1.7</v>
@@ -22200,7 +22230,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22328,7 +22358,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22409,7 +22439,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ103">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR103">
         <v>1.38</v>
@@ -22534,7 +22564,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22740,7 +22770,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22818,10 +22848,10 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ105">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR105">
         <v>1.24</v>
@@ -22946,7 +22976,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23230,7 +23260,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ107">
         <v>1.22</v>
@@ -23358,7 +23388,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23642,7 +23672,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ109">
         <v>0.33</v>
@@ -23976,7 +24006,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24057,7 +24087,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ111">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR111">
         <v>1.37</v>
@@ -24388,7 +24418,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24469,7 +24499,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ113">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR113">
         <v>1.21</v>
@@ -24594,7 +24624,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24672,10 +24702,10 @@
         <v>2.6</v>
       </c>
       <c r="AP114">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ114">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -24800,7 +24830,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25006,7 +25036,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25290,7 +25320,7 @@
         <v>0.5</v>
       </c>
       <c r="AP117">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ117">
         <v>0.8</v>
@@ -25496,10 +25526,10 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ118">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR118">
         <v>1.65</v>
@@ -26320,7 +26350,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ122">
         <v>1.2</v>
@@ -26448,7 +26478,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26529,7 +26559,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ123">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR123">
         <v>1.43</v>
@@ -26654,7 +26684,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27066,7 +27096,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27144,7 +27174,7 @@
         <v>1.83</v>
       </c>
       <c r="AP126">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ126">
         <v>2</v>
@@ -27272,7 +27302,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27350,10 +27380,10 @@
         <v>2.67</v>
       </c>
       <c r="AP127">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ127">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR127">
         <v>1.82</v>
@@ -27559,7 +27589,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ128">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR128">
         <v>2.46</v>
@@ -27762,7 +27792,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ129">
         <v>1</v>
@@ -27890,7 +27920,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28096,7 +28126,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28177,7 +28207,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ131">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28302,7 +28332,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28714,7 +28744,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29126,7 +29156,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29204,10 +29234,10 @@
         <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ136">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29332,7 +29362,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29410,7 +29440,7 @@
         <v>1.14</v>
       </c>
       <c r="AP137">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ137">
         <v>1.1</v>
@@ -29616,10 +29646,10 @@
         <v>2.63</v>
       </c>
       <c r="AP138">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ138">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR138">
         <v>1.59</v>
@@ -29744,7 +29774,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29825,7 +29855,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ139">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR139">
         <v>1.21</v>
@@ -29950,7 +29980,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30156,7 +30186,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30440,7 +30470,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ142">
         <v>1.2</v>
@@ -30852,7 +30882,7 @@
         <v>0.29</v>
       </c>
       <c r="AP144">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ144">
         <v>0.33</v>
@@ -30980,7 +31010,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31186,7 +31216,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31470,7 +31500,7 @@
         <v>0.88</v>
       </c>
       <c r="AP147">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ147">
         <v>0.7</v>
@@ -31676,7 +31706,7 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ148">
         <v>0.55</v>
@@ -31885,7 +31915,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ149">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR149">
         <v>1.83</v>
@@ -32010,7 +32040,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32297,7 +32327,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ151">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR151">
         <v>2.48</v>
@@ -32422,7 +32452,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32834,7 +32864,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33040,7 +33070,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33324,10 +33354,10 @@
         <v>0.25</v>
       </c>
       <c r="AP156">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ156">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR156">
         <v>1.73</v>
@@ -33452,7 +33482,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33530,7 +33560,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ157">
         <v>1</v>
@@ -33658,7 +33688,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33864,7 +33894,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34276,7 +34306,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34357,7 +34387,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ161">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR161">
         <v>1.8</v>
@@ -34482,7 +34512,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34688,7 +34718,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -34766,10 +34796,10 @@
         <v>2.33</v>
       </c>
       <c r="AP163">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ163">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AR163">
         <v>1.24</v>
@@ -35100,7 +35130,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35181,7 +35211,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ165">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR165">
         <v>1.19</v>
@@ -35384,7 +35414,7 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ166">
         <v>0.5</v>
@@ -35512,7 +35542,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35593,7 +35623,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ167">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR167">
         <v>1.33</v>
@@ -35718,7 +35748,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -35796,7 +35826,7 @@
         <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ168">
         <v>0.8</v>
@@ -35924,7 +35954,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36002,7 +36032,7 @@
         <v>1.89</v>
       </c>
       <c r="AP169">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ169">
         <v>2</v>
@@ -36130,7 +36160,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36208,7 +36238,7 @@
         <v>1.11</v>
       </c>
       <c r="AP170">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36417,7 +36447,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ171">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR171">
         <v>1.53</v>
@@ -36623,7 +36653,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ172">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AR172">
         <v>1.45</v>
@@ -36748,7 +36778,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37160,7 +37190,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37572,7 +37602,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37778,7 +37808,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38141,6 +38171,1242 @@
       </c>
       <c r="BP179">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7466238</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45689.61458333334</v>
+      </c>
+      <c r="F180">
+        <v>21</v>
+      </c>
+      <c r="G180" t="s">
+        <v>85</v>
+      </c>
+      <c r="H180" t="s">
+        <v>76</v>
+      </c>
+      <c r="I180">
+        <v>2</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>2</v>
+      </c>
+      <c r="L180">
+        <v>3</v>
+      </c>
+      <c r="M180">
+        <v>3</v>
+      </c>
+      <c r="N180">
+        <v>6</v>
+      </c>
+      <c r="O180" t="s">
+        <v>213</v>
+      </c>
+      <c r="P180" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q180">
+        <v>3.6</v>
+      </c>
+      <c r="R180">
+        <v>2.25</v>
+      </c>
+      <c r="S180">
+        <v>2.75</v>
+      </c>
+      <c r="T180">
+        <v>1.33</v>
+      </c>
+      <c r="U180">
+        <v>3.25</v>
+      </c>
+      <c r="V180">
+        <v>2.63</v>
+      </c>
+      <c r="W180">
+        <v>1.44</v>
+      </c>
+      <c r="X180">
+        <v>6.5</v>
+      </c>
+      <c r="Y180">
+        <v>1.11</v>
+      </c>
+      <c r="Z180">
+        <v>3.63</v>
+      </c>
+      <c r="AA180">
+        <v>3.85</v>
+      </c>
+      <c r="AB180">
+        <v>2</v>
+      </c>
+      <c r="AC180">
+        <v>1.03</v>
+      </c>
+      <c r="AD180">
+        <v>13</v>
+      </c>
+      <c r="AE180">
+        <v>1.22</v>
+      </c>
+      <c r="AF180">
+        <v>4.08</v>
+      </c>
+      <c r="AG180">
+        <v>1.57</v>
+      </c>
+      <c r="AH180">
+        <v>2.3</v>
+      </c>
+      <c r="AI180">
+        <v>1.62</v>
+      </c>
+      <c r="AJ180">
+        <v>2.2</v>
+      </c>
+      <c r="AK180">
+        <v>1.75</v>
+      </c>
+      <c r="AL180">
+        <v>1.28</v>
+      </c>
+      <c r="AM180">
+        <v>1.3</v>
+      </c>
+      <c r="AN180">
+        <v>1.5</v>
+      </c>
+      <c r="AO180">
+        <v>2.4</v>
+      </c>
+      <c r="AP180">
+        <v>1.45</v>
+      </c>
+      <c r="AQ180">
+        <v>2.27</v>
+      </c>
+      <c r="AR180">
+        <v>1.23</v>
+      </c>
+      <c r="AS180">
+        <v>1.34</v>
+      </c>
+      <c r="AT180">
+        <v>2.57</v>
+      </c>
+      <c r="AU180">
+        <v>7</v>
+      </c>
+      <c r="AV180">
+        <v>9</v>
+      </c>
+      <c r="AW180">
+        <v>7</v>
+      </c>
+      <c r="AX180">
+        <v>8</v>
+      </c>
+      <c r="AY180">
+        <v>18</v>
+      </c>
+      <c r="AZ180">
+        <v>18</v>
+      </c>
+      <c r="BA180">
+        <v>5</v>
+      </c>
+      <c r="BB180">
+        <v>3</v>
+      </c>
+      <c r="BC180">
+        <v>8</v>
+      </c>
+      <c r="BD180">
+        <v>2.65</v>
+      </c>
+      <c r="BE180">
+        <v>6.75</v>
+      </c>
+      <c r="BF180">
+        <v>1.58</v>
+      </c>
+      <c r="BG180">
+        <v>1.21</v>
+      </c>
+      <c r="BH180">
+        <v>3.8</v>
+      </c>
+      <c r="BI180">
+        <v>1.37</v>
+      </c>
+      <c r="BJ180">
+        <v>2.8</v>
+      </c>
+      <c r="BK180">
+        <v>1.63</v>
+      </c>
+      <c r="BL180">
+        <v>2.12</v>
+      </c>
+      <c r="BM180">
+        <v>1.98</v>
+      </c>
+      <c r="BN180">
+        <v>1.73</v>
+      </c>
+      <c r="BO180">
+        <v>2.48</v>
+      </c>
+      <c r="BP180">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7466239</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45689.66666666666</v>
+      </c>
+      <c r="F181">
+        <v>21</v>
+      </c>
+      <c r="G181" t="s">
+        <v>80</v>
+      </c>
+      <c r="H181" t="s">
+        <v>79</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181">
+        <v>1</v>
+      </c>
+      <c r="K181">
+        <v>2</v>
+      </c>
+      <c r="L181">
+        <v>2</v>
+      </c>
+      <c r="M181">
+        <v>2</v>
+      </c>
+      <c r="N181">
+        <v>4</v>
+      </c>
+      <c r="O181" t="s">
+        <v>214</v>
+      </c>
+      <c r="P181" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q181">
+        <v>2.75</v>
+      </c>
+      <c r="R181">
+        <v>2.2</v>
+      </c>
+      <c r="S181">
+        <v>4</v>
+      </c>
+      <c r="T181">
+        <v>1.36</v>
+      </c>
+      <c r="U181">
+        <v>3</v>
+      </c>
+      <c r="V181">
+        <v>2.75</v>
+      </c>
+      <c r="W181">
+        <v>1.4</v>
+      </c>
+      <c r="X181">
+        <v>8</v>
+      </c>
+      <c r="Y181">
+        <v>1.08</v>
+      </c>
+      <c r="Z181">
+        <v>1.98</v>
+      </c>
+      <c r="AA181">
+        <v>3.85</v>
+      </c>
+      <c r="AB181">
+        <v>3.69</v>
+      </c>
+      <c r="AC181">
+        <v>1.05</v>
+      </c>
+      <c r="AD181">
+        <v>12</v>
+      </c>
+      <c r="AE181">
+        <v>1.28</v>
+      </c>
+      <c r="AF181">
+        <v>3.52</v>
+      </c>
+      <c r="AG181">
+        <v>1.82</v>
+      </c>
+      <c r="AH181">
+        <v>2</v>
+      </c>
+      <c r="AI181">
+        <v>1.7</v>
+      </c>
+      <c r="AJ181">
+        <v>2.05</v>
+      </c>
+      <c r="AK181">
+        <v>1.3</v>
+      </c>
+      <c r="AL181">
+        <v>1.28</v>
+      </c>
+      <c r="AM181">
+        <v>1.73</v>
+      </c>
+      <c r="AN181">
+        <v>2</v>
+      </c>
+      <c r="AO181">
+        <v>1</v>
+      </c>
+      <c r="AP181">
+        <v>1.9</v>
+      </c>
+      <c r="AQ181">
+        <v>1</v>
+      </c>
+      <c r="AR181">
+        <v>1.53</v>
+      </c>
+      <c r="AS181">
+        <v>1.14</v>
+      </c>
+      <c r="AT181">
+        <v>2.67</v>
+      </c>
+      <c r="AU181">
+        <v>6</v>
+      </c>
+      <c r="AV181">
+        <v>5</v>
+      </c>
+      <c r="AW181">
+        <v>19</v>
+      </c>
+      <c r="AX181">
+        <v>2</v>
+      </c>
+      <c r="AY181">
+        <v>29</v>
+      </c>
+      <c r="AZ181">
+        <v>7</v>
+      </c>
+      <c r="BA181">
+        <v>12</v>
+      </c>
+      <c r="BB181">
+        <v>1</v>
+      </c>
+      <c r="BC181">
+        <v>13</v>
+      </c>
+      <c r="BD181">
+        <v>1.49</v>
+      </c>
+      <c r="BE181">
+        <v>7</v>
+      </c>
+      <c r="BF181">
+        <v>2.9</v>
+      </c>
+      <c r="BG181">
+        <v>1.2</v>
+      </c>
+      <c r="BH181">
+        <v>3.9</v>
+      </c>
+      <c r="BI181">
+        <v>1.36</v>
+      </c>
+      <c r="BJ181">
+        <v>2.85</v>
+      </c>
+      <c r="BK181">
+        <v>1.58</v>
+      </c>
+      <c r="BL181">
+        <v>2.18</v>
+      </c>
+      <c r="BM181">
+        <v>1.95</v>
+      </c>
+      <c r="BN181">
+        <v>1.75</v>
+      </c>
+      <c r="BO181">
+        <v>2.43</v>
+      </c>
+      <c r="BP181">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7466236</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45689.70833333334</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>72</v>
+      </c>
+      <c r="H182" t="s">
+        <v>74</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>3</v>
+      </c>
+      <c r="M182">
+        <v>3</v>
+      </c>
+      <c r="N182">
+        <v>6</v>
+      </c>
+      <c r="O182" t="s">
+        <v>215</v>
+      </c>
+      <c r="P182" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q182">
+        <v>5.5</v>
+      </c>
+      <c r="R182">
+        <v>2.63</v>
+      </c>
+      <c r="S182">
+        <v>1.91</v>
+      </c>
+      <c r="T182">
+        <v>1.25</v>
+      </c>
+      <c r="U182">
+        <v>3.75</v>
+      </c>
+      <c r="V182">
+        <v>2.1</v>
+      </c>
+      <c r="W182">
+        <v>1.67</v>
+      </c>
+      <c r="X182">
+        <v>4.5</v>
+      </c>
+      <c r="Y182">
+        <v>1.18</v>
+      </c>
+      <c r="Z182">
+        <v>8</v>
+      </c>
+      <c r="AA182">
+        <v>5.8</v>
+      </c>
+      <c r="AB182">
+        <v>1.36</v>
+      </c>
+      <c r="AC182">
+        <v>1.01</v>
+      </c>
+      <c r="AD182">
+        <v>23</v>
+      </c>
+      <c r="AE182">
+        <v>1.1</v>
+      </c>
+      <c r="AF182">
+        <v>6.39</v>
+      </c>
+      <c r="AG182">
+        <v>1.48</v>
+      </c>
+      <c r="AH182">
+        <v>2.54</v>
+      </c>
+      <c r="AI182">
+        <v>1.62</v>
+      </c>
+      <c r="AJ182">
+        <v>2.2</v>
+      </c>
+      <c r="AK182">
+        <v>2.85</v>
+      </c>
+      <c r="AL182">
+        <v>1.16</v>
+      </c>
+      <c r="AM182">
+        <v>1.11</v>
+      </c>
+      <c r="AN182">
+        <v>1.4</v>
+      </c>
+      <c r="AO182">
+        <v>2.1</v>
+      </c>
+      <c r="AP182">
+        <v>1.36</v>
+      </c>
+      <c r="AQ182">
+        <v>2</v>
+      </c>
+      <c r="AR182">
+        <v>1.6</v>
+      </c>
+      <c r="AS182">
+        <v>1.84</v>
+      </c>
+      <c r="AT182">
+        <v>3.44</v>
+      </c>
+      <c r="AU182">
+        <v>9</v>
+      </c>
+      <c r="AV182">
+        <v>7</v>
+      </c>
+      <c r="AW182">
+        <v>2</v>
+      </c>
+      <c r="AX182">
+        <v>9</v>
+      </c>
+      <c r="AY182">
+        <v>12</v>
+      </c>
+      <c r="AZ182">
+        <v>16</v>
+      </c>
+      <c r="BA182">
+        <v>4</v>
+      </c>
+      <c r="BB182">
+        <v>5</v>
+      </c>
+      <c r="BC182">
+        <v>9</v>
+      </c>
+      <c r="BD182">
+        <v>4.4</v>
+      </c>
+      <c r="BE182">
+        <v>8.5</v>
+      </c>
+      <c r="BF182">
+        <v>1.23</v>
+      </c>
+      <c r="BG182">
+        <v>1.16</v>
+      </c>
+      <c r="BH182">
+        <v>4.4</v>
+      </c>
+      <c r="BI182">
+        <v>1.29</v>
+      </c>
+      <c r="BJ182">
+        <v>3.15</v>
+      </c>
+      <c r="BK182">
+        <v>1.5</v>
+      </c>
+      <c r="BL182">
+        <v>2.4</v>
+      </c>
+      <c r="BM182">
+        <v>1.79</v>
+      </c>
+      <c r="BN182">
+        <v>1.9</v>
+      </c>
+      <c r="BO182">
+        <v>2.23</v>
+      </c>
+      <c r="BP182">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7466234</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45690.34375</v>
+      </c>
+      <c r="F183">
+        <v>21</v>
+      </c>
+      <c r="G183" t="s">
+        <v>73</v>
+      </c>
+      <c r="H183" t="s">
+        <v>83</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>1</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>4</v>
+      </c>
+      <c r="N183">
+        <v>5</v>
+      </c>
+      <c r="O183" t="s">
+        <v>216</v>
+      </c>
+      <c r="P183" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q183">
+        <v>2.88</v>
+      </c>
+      <c r="R183">
+        <v>2.1</v>
+      </c>
+      <c r="S183">
+        <v>3.75</v>
+      </c>
+      <c r="T183">
+        <v>1.4</v>
+      </c>
+      <c r="U183">
+        <v>2.75</v>
+      </c>
+      <c r="V183">
+        <v>3</v>
+      </c>
+      <c r="W183">
+        <v>1.36</v>
+      </c>
+      <c r="X183">
+        <v>8</v>
+      </c>
+      <c r="Y183">
+        <v>1.08</v>
+      </c>
+      <c r="Z183">
+        <v>2.18</v>
+      </c>
+      <c r="AA183">
+        <v>3.53</v>
+      </c>
+      <c r="AB183">
+        <v>3.4</v>
+      </c>
+      <c r="AC183">
+        <v>1.04</v>
+      </c>
+      <c r="AD183">
+        <v>10.06</v>
+      </c>
+      <c r="AE183">
+        <v>1.31</v>
+      </c>
+      <c r="AF183">
+        <v>3.35</v>
+      </c>
+      <c r="AG183">
+        <v>1.93</v>
+      </c>
+      <c r="AH183">
+        <v>1.88</v>
+      </c>
+      <c r="AI183">
+        <v>1.75</v>
+      </c>
+      <c r="AJ183">
+        <v>2</v>
+      </c>
+      <c r="AK183">
+        <v>1.33</v>
+      </c>
+      <c r="AL183">
+        <v>1.3</v>
+      </c>
+      <c r="AM183">
+        <v>1.66</v>
+      </c>
+      <c r="AN183">
+        <v>0.7</v>
+      </c>
+      <c r="AO183">
+        <v>0.3</v>
+      </c>
+      <c r="AP183">
+        <v>0.64</v>
+      </c>
+      <c r="AQ183">
+        <v>0.55</v>
+      </c>
+      <c r="AR183">
+        <v>1.31</v>
+      </c>
+      <c r="AS183">
+        <v>1.07</v>
+      </c>
+      <c r="AT183">
+        <v>2.38</v>
+      </c>
+      <c r="AU183">
+        <v>6</v>
+      </c>
+      <c r="AV183">
+        <v>14</v>
+      </c>
+      <c r="AW183">
+        <v>10</v>
+      </c>
+      <c r="AX183">
+        <v>14</v>
+      </c>
+      <c r="AY183">
+        <v>18</v>
+      </c>
+      <c r="AZ183">
+        <v>34</v>
+      </c>
+      <c r="BA183">
+        <v>5</v>
+      </c>
+      <c r="BB183">
+        <v>10</v>
+      </c>
+      <c r="BC183">
+        <v>15</v>
+      </c>
+      <c r="BD183">
+        <v>1.55</v>
+      </c>
+      <c r="BE183">
+        <v>6.75</v>
+      </c>
+      <c r="BF183">
+        <v>2.7</v>
+      </c>
+      <c r="BG183">
+        <v>1.2</v>
+      </c>
+      <c r="BH183">
+        <v>3.95</v>
+      </c>
+      <c r="BI183">
+        <v>1.36</v>
+      </c>
+      <c r="BJ183">
+        <v>2.8</v>
+      </c>
+      <c r="BK183">
+        <v>1.6</v>
+      </c>
+      <c r="BL183">
+        <v>2.17</v>
+      </c>
+      <c r="BM183">
+        <v>1.85</v>
+      </c>
+      <c r="BN183">
+        <v>1.85</v>
+      </c>
+      <c r="BO183">
+        <v>2.4</v>
+      </c>
+      <c r="BP183">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7466233</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45690.4375</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184" t="s">
+        <v>78</v>
+      </c>
+      <c r="H184" t="s">
+        <v>71</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184">
+        <v>2</v>
+      </c>
+      <c r="M184">
+        <v>1</v>
+      </c>
+      <c r="N184">
+        <v>3</v>
+      </c>
+      <c r="O184" t="s">
+        <v>217</v>
+      </c>
+      <c r="P184" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q184">
+        <v>2.88</v>
+      </c>
+      <c r="R184">
+        <v>2.3</v>
+      </c>
+      <c r="S184">
+        <v>3.4</v>
+      </c>
+      <c r="T184">
+        <v>1.33</v>
+      </c>
+      <c r="U184">
+        <v>3.25</v>
+      </c>
+      <c r="V184">
+        <v>2.5</v>
+      </c>
+      <c r="W184">
+        <v>1.5</v>
+      </c>
+      <c r="X184">
+        <v>6.5</v>
+      </c>
+      <c r="Y184">
+        <v>1.11</v>
+      </c>
+      <c r="Z184">
+        <v>2.31</v>
+      </c>
+      <c r="AA184">
+        <v>3.63</v>
+      </c>
+      <c r="AB184">
+        <v>3.07</v>
+      </c>
+      <c r="AC184">
+        <v>1.03</v>
+      </c>
+      <c r="AD184">
+        <v>15</v>
+      </c>
+      <c r="AE184">
+        <v>1.21</v>
+      </c>
+      <c r="AF184">
+        <v>4.25</v>
+      </c>
+      <c r="AG184">
+        <v>1.67</v>
+      </c>
+      <c r="AH184">
+        <v>2.1</v>
+      </c>
+      <c r="AI184">
+        <v>1.57</v>
+      </c>
+      <c r="AJ184">
+        <v>2.25</v>
+      </c>
+      <c r="AK184">
+        <v>1.39</v>
+      </c>
+      <c r="AL184">
+        <v>1.27</v>
+      </c>
+      <c r="AM184">
+        <v>1.62</v>
+      </c>
+      <c r="AN184">
+        <v>2.78</v>
+      </c>
+      <c r="AO184">
+        <v>1.9</v>
+      </c>
+      <c r="AP184">
+        <v>2.8</v>
+      </c>
+      <c r="AQ184">
+        <v>1.73</v>
+      </c>
+      <c r="AR184">
+        <v>1.78</v>
+      </c>
+      <c r="AS184">
+        <v>1.93</v>
+      </c>
+      <c r="AT184">
+        <v>3.71</v>
+      </c>
+      <c r="AU184">
+        <v>10</v>
+      </c>
+      <c r="AV184">
+        <v>7</v>
+      </c>
+      <c r="AW184">
+        <v>8</v>
+      </c>
+      <c r="AX184">
+        <v>7</v>
+      </c>
+      <c r="AY184">
+        <v>18</v>
+      </c>
+      <c r="AZ184">
+        <v>17</v>
+      </c>
+      <c r="BA184">
+        <v>7</v>
+      </c>
+      <c r="BB184">
+        <v>5</v>
+      </c>
+      <c r="BC184">
+        <v>12</v>
+      </c>
+      <c r="BD184">
+        <v>1.75</v>
+      </c>
+      <c r="BE184">
+        <v>6.4</v>
+      </c>
+      <c r="BF184">
+        <v>2.32</v>
+      </c>
+      <c r="BG184">
+        <v>1.3</v>
+      </c>
+      <c r="BH184">
+        <v>3.05</v>
+      </c>
+      <c r="BI184">
+        <v>1.54</v>
+      </c>
+      <c r="BJ184">
+        <v>2.3</v>
+      </c>
+      <c r="BK184">
+        <v>1.85</v>
+      </c>
+      <c r="BL184">
+        <v>1.85</v>
+      </c>
+      <c r="BM184">
+        <v>2.4</v>
+      </c>
+      <c r="BN184">
+        <v>1.5</v>
+      </c>
+      <c r="BO184">
+        <v>3.05</v>
+      </c>
+      <c r="BP184">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7466235</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45690.4375</v>
+      </c>
+      <c r="F185">
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>77</v>
+      </c>
+      <c r="H185" t="s">
+        <v>81</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>2</v>
+      </c>
+      <c r="M185">
+        <v>2</v>
+      </c>
+      <c r="N185">
+        <v>4</v>
+      </c>
+      <c r="O185" t="s">
+        <v>218</v>
+      </c>
+      <c r="P185" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q185">
+        <v>3.1</v>
+      </c>
+      <c r="R185">
+        <v>2.3</v>
+      </c>
+      <c r="S185">
+        <v>3.1</v>
+      </c>
+      <c r="T185">
+        <v>1.33</v>
+      </c>
+      <c r="U185">
+        <v>3.25</v>
+      </c>
+      <c r="V185">
+        <v>2.5</v>
+      </c>
+      <c r="W185">
+        <v>1.5</v>
+      </c>
+      <c r="X185">
+        <v>6</v>
+      </c>
+      <c r="Y185">
+        <v>1.13</v>
+      </c>
+      <c r="Z185">
+        <v>2.63</v>
+      </c>
+      <c r="AA185">
+        <v>3.79</v>
+      </c>
+      <c r="AB185">
+        <v>2.56</v>
+      </c>
+      <c r="AC185">
+        <v>1.03</v>
+      </c>
+      <c r="AD185">
+        <v>13</v>
+      </c>
+      <c r="AE185">
+        <v>1.21</v>
+      </c>
+      <c r="AF185">
+        <v>4.25</v>
+      </c>
+      <c r="AG185">
+        <v>1.55</v>
+      </c>
+      <c r="AH185">
+        <v>2.3</v>
+      </c>
+      <c r="AI185">
+        <v>1.53</v>
+      </c>
+      <c r="AJ185">
+        <v>2.38</v>
+      </c>
+      <c r="AK185">
+        <v>1.51</v>
+      </c>
+      <c r="AL185">
+        <v>1.28</v>
+      </c>
+      <c r="AM185">
+        <v>1.47</v>
+      </c>
+      <c r="AN185">
+        <v>2</v>
+      </c>
+      <c r="AO185">
+        <v>1.3</v>
+      </c>
+      <c r="AP185">
+        <v>1.91</v>
+      </c>
+      <c r="AQ185">
+        <v>1.27</v>
+      </c>
+      <c r="AR185">
+        <v>1.74</v>
+      </c>
+      <c r="AS185">
+        <v>1.67</v>
+      </c>
+      <c r="AT185">
+        <v>3.41</v>
+      </c>
+      <c r="AU185">
+        <v>2</v>
+      </c>
+      <c r="AV185">
+        <v>10</v>
+      </c>
+      <c r="AW185">
+        <v>8</v>
+      </c>
+      <c r="AX185">
+        <v>9</v>
+      </c>
+      <c r="AY185">
+        <v>10</v>
+      </c>
+      <c r="AZ185">
+        <v>20</v>
+      </c>
+      <c r="BA185">
+        <v>4</v>
+      </c>
+      <c r="BB185">
+        <v>8</v>
+      </c>
+      <c r="BC185">
+        <v>12</v>
+      </c>
+      <c r="BD185">
+        <v>2.05</v>
+      </c>
+      <c r="BE185">
+        <v>6.4</v>
+      </c>
+      <c r="BF185">
+        <v>1.95</v>
+      </c>
+      <c r="BG185">
+        <v>1.24</v>
+      </c>
+      <c r="BH185">
+        <v>3.55</v>
+      </c>
+      <c r="BI185">
+        <v>1.43</v>
+      </c>
+      <c r="BJ185">
+        <v>2.55</v>
+      </c>
+      <c r="BK185">
+        <v>1.72</v>
+      </c>
+      <c r="BL185">
+        <v>1.98</v>
+      </c>
+      <c r="BM185">
+        <v>1.95</v>
+      </c>
+      <c r="BN185">
+        <v>1.77</v>
+      </c>
+      <c r="BO185">
+        <v>2.7</v>
+      </c>
+      <c r="BP185">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="308">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -673,6 +673,9 @@
     <t>['11', '90+1']</t>
   </si>
   <si>
+    <t>['60']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -695,9 +698,6 @@
   </si>
   <si>
     <t>['90+1', '90+6']</t>
-  </si>
-  <si>
-    <t>['60']</t>
   </si>
   <si>
     <t>['31', '36', '87']</t>
@@ -935,6 +935,9 @@
   </si>
   <si>
     <t>['66', '67']</t>
+  </si>
+  <si>
+    <t>['28', '42']</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP185"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1964,7 +1967,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2251,7 +2254,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ5">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2376,7 +2379,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2660,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ7">
         <v>0.8</v>
@@ -2994,7 +2997,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -4230,7 +4233,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4311,7 +4314,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4436,7 +4439,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4642,7 +4645,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4926,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ18">
         <v>1.22</v>
@@ -5466,7 +5469,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5672,7 +5675,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5959,7 +5962,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ23">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR23">
         <v>1.65</v>
@@ -6290,7 +6293,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -6368,7 +6371,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ25">
         <v>1.73</v>
@@ -6783,7 +6786,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ27">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR27">
         <v>1.81</v>
@@ -6989,7 +6992,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR28">
         <v>0.73</v>
@@ -7604,7 +7607,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ31">
         <v>1.2</v>
@@ -9458,7 +9461,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ40">
         <v>1.22</v>
@@ -9664,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ41">
         <v>0.55</v>
@@ -10491,7 +10494,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ45">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -11521,7 +11524,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ50">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -12548,7 +12551,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ55">
         <v>2</v>
@@ -12960,7 +12963,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -15641,7 +15644,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ70">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR70">
         <v>2.32</v>
@@ -15847,7 +15850,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ71">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR71">
         <v>1.43</v>
@@ -16050,7 +16053,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ72">
         <v>0.33</v>
@@ -17080,7 +17083,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -18113,7 +18116,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR82">
         <v>1.34</v>
@@ -19964,7 +19967,7 @@
         <v>1.4</v>
       </c>
       <c r="AP91">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ91">
         <v>1.27</v>
@@ -20585,7 +20588,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ94">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR94">
         <v>1.67</v>
@@ -21203,7 +21206,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ97">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR97">
         <v>1.38</v>
@@ -21406,7 +21409,7 @@
         <v>2.5</v>
       </c>
       <c r="AP98">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ98">
         <v>2.27</v>
@@ -24293,7 +24296,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ112">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR112">
         <v>2.46</v>
@@ -24908,10 +24911,10 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ115">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR115">
         <v>1.6</v>
@@ -25114,7 +25117,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ116">
         <v>0.7</v>
@@ -27998,7 +28001,7 @@
         <v>0.57</v>
       </c>
       <c r="AP130">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ130">
         <v>0.7</v>
@@ -28822,7 +28825,7 @@
         <v>0</v>
       </c>
       <c r="AP134">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ134">
         <v>0.55</v>
@@ -30679,7 +30682,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ143">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR143">
         <v>2.08</v>
@@ -31091,7 +31094,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ145">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -32118,7 +32121,7 @@
         <v>1.75</v>
       </c>
       <c r="AP150">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ150">
         <v>2</v>
@@ -32736,7 +32739,7 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -33769,7 +33772,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ158">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR158">
         <v>2.37</v>
@@ -35005,7 +35008,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ164">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR164">
         <v>1.55</v>
@@ -35208,7 +35211,7 @@
         <v>2</v>
       </c>
       <c r="AP165">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ165">
         <v>1.73</v>
@@ -35417,7 +35420,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ166">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR166">
         <v>1.78</v>
@@ -35542,7 +35545,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -36444,7 +36447,7 @@
         <v>0.22</v>
       </c>
       <c r="AP171">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ171">
         <v>0.55</v>
@@ -37889,7 +37892,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ178">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR178">
         <v>1.43</v>
@@ -39407,6 +39410,418 @@
       </c>
       <c r="BP185">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7466240</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45690.53125</v>
+      </c>
+      <c r="F186">
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>75</v>
+      </c>
+      <c r="H186" t="s">
+        <v>70</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>1</v>
+      </c>
+      <c r="O186" t="s">
+        <v>219</v>
+      </c>
+      <c r="P186" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q186">
+        <v>2.38</v>
+      </c>
+      <c r="R186">
+        <v>2.2</v>
+      </c>
+      <c r="S186">
+        <v>5</v>
+      </c>
+      <c r="T186">
+        <v>1.4</v>
+      </c>
+      <c r="U186">
+        <v>2.75</v>
+      </c>
+      <c r="V186">
+        <v>3</v>
+      </c>
+      <c r="W186">
+        <v>1.36</v>
+      </c>
+      <c r="X186">
+        <v>8</v>
+      </c>
+      <c r="Y186">
+        <v>1.08</v>
+      </c>
+      <c r="Z186">
+        <v>1.85</v>
+      </c>
+      <c r="AA186">
+        <v>3.5</v>
+      </c>
+      <c r="AB186">
+        <v>4.8</v>
+      </c>
+      <c r="AC186">
+        <v>1.04</v>
+      </c>
+      <c r="AD186">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AE186">
+        <v>1.31</v>
+      </c>
+      <c r="AF186">
+        <v>3.35</v>
+      </c>
+      <c r="AG186">
+        <v>2.01</v>
+      </c>
+      <c r="AH186">
+        <v>1.81</v>
+      </c>
+      <c r="AI186">
+        <v>1.95</v>
+      </c>
+      <c r="AJ186">
+        <v>1.8</v>
+      </c>
+      <c r="AK186">
+        <v>1.2</v>
+      </c>
+      <c r="AL186">
+        <v>1.28</v>
+      </c>
+      <c r="AM186">
+        <v>1.95</v>
+      </c>
+      <c r="AN186">
+        <v>0.5</v>
+      </c>
+      <c r="AO186">
+        <v>0.5</v>
+      </c>
+      <c r="AP186">
+        <v>0.73</v>
+      </c>
+      <c r="AQ186">
+        <v>0.45</v>
+      </c>
+      <c r="AR186">
+        <v>1.58</v>
+      </c>
+      <c r="AS186">
+        <v>1.09</v>
+      </c>
+      <c r="AT186">
+        <v>2.67</v>
+      </c>
+      <c r="AU186">
+        <v>5</v>
+      </c>
+      <c r="AV186">
+        <v>4</v>
+      </c>
+      <c r="AW186">
+        <v>5</v>
+      </c>
+      <c r="AX186">
+        <v>4</v>
+      </c>
+      <c r="AY186">
+        <v>10</v>
+      </c>
+      <c r="AZ186">
+        <v>8</v>
+      </c>
+      <c r="BA186">
+        <v>4</v>
+      </c>
+      <c r="BB186">
+        <v>2</v>
+      </c>
+      <c r="BC186">
+        <v>6</v>
+      </c>
+      <c r="BD186">
+        <v>1.57</v>
+      </c>
+      <c r="BE186">
+        <v>6.75</v>
+      </c>
+      <c r="BF186">
+        <v>2.65</v>
+      </c>
+      <c r="BG186">
+        <v>1.23</v>
+      </c>
+      <c r="BH186">
+        <v>3.65</v>
+      </c>
+      <c r="BI186">
+        <v>1.41</v>
+      </c>
+      <c r="BJ186">
+        <v>2.65</v>
+      </c>
+      <c r="BK186">
+        <v>1.66</v>
+      </c>
+      <c r="BL186">
+        <v>2.06</v>
+      </c>
+      <c r="BM186">
+        <v>1.95</v>
+      </c>
+      <c r="BN186">
+        <v>1.7</v>
+      </c>
+      <c r="BO186">
+        <v>2.63</v>
+      </c>
+      <c r="BP186">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7466241</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45690.66666666666</v>
+      </c>
+      <c r="F187">
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>86</v>
+      </c>
+      <c r="H187" t="s">
+        <v>82</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>2</v>
+      </c>
+      <c r="K187">
+        <v>2</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>2</v>
+      </c>
+      <c r="N187">
+        <v>2</v>
+      </c>
+      <c r="O187" t="s">
+        <v>91</v>
+      </c>
+      <c r="P187" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q187">
+        <v>4.75</v>
+      </c>
+      <c r="R187">
+        <v>2.1</v>
+      </c>
+      <c r="S187">
+        <v>2.5</v>
+      </c>
+      <c r="T187">
+        <v>1.44</v>
+      </c>
+      <c r="U187">
+        <v>2.63</v>
+      </c>
+      <c r="V187">
+        <v>3</v>
+      </c>
+      <c r="W187">
+        <v>1.36</v>
+      </c>
+      <c r="X187">
+        <v>9</v>
+      </c>
+      <c r="Y187">
+        <v>1.07</v>
+      </c>
+      <c r="Z187">
+        <v>4.75</v>
+      </c>
+      <c r="AA187">
+        <v>3.81</v>
+      </c>
+      <c r="AB187">
+        <v>1.78</v>
+      </c>
+      <c r="AC187">
+        <v>1.05</v>
+      </c>
+      <c r="AD187">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AE187">
+        <v>1.33</v>
+      </c>
+      <c r="AF187">
+        <v>3.19</v>
+      </c>
+      <c r="AG187">
+        <v>1.89</v>
+      </c>
+      <c r="AH187">
+        <v>1.92</v>
+      </c>
+      <c r="AI187">
+        <v>1.91</v>
+      </c>
+      <c r="AJ187">
+        <v>1.91</v>
+      </c>
+      <c r="AK187">
+        <v>1.93</v>
+      </c>
+      <c r="AL187">
+        <v>1.28</v>
+      </c>
+      <c r="AM187">
+        <v>1.21</v>
+      </c>
+      <c r="AN187">
+        <v>1.2</v>
+      </c>
+      <c r="AO187">
+        <v>1.8</v>
+      </c>
+      <c r="AP187">
+        <v>1.09</v>
+      </c>
+      <c r="AQ187">
+        <v>1.91</v>
+      </c>
+      <c r="AR187">
+        <v>1.16</v>
+      </c>
+      <c r="AS187">
+        <v>1.44</v>
+      </c>
+      <c r="AT187">
+        <v>2.6</v>
+      </c>
+      <c r="AU187">
+        <v>2</v>
+      </c>
+      <c r="AV187">
+        <v>6</v>
+      </c>
+      <c r="AW187">
+        <v>2</v>
+      </c>
+      <c r="AX187">
+        <v>10</v>
+      </c>
+      <c r="AY187">
+        <v>4</v>
+      </c>
+      <c r="AZ187">
+        <v>20</v>
+      </c>
+      <c r="BA187">
+        <v>1</v>
+      </c>
+      <c r="BB187">
+        <v>10</v>
+      </c>
+      <c r="BC187">
+        <v>11</v>
+      </c>
+      <c r="BD187">
+        <v>3.2</v>
+      </c>
+      <c r="BE187">
+        <v>7</v>
+      </c>
+      <c r="BF187">
+        <v>1.42</v>
+      </c>
+      <c r="BG187">
+        <v>1.3</v>
+      </c>
+      <c r="BH187">
+        <v>3.05</v>
+      </c>
+      <c r="BI187">
+        <v>1.54</v>
+      </c>
+      <c r="BJ187">
+        <v>2.3</v>
+      </c>
+      <c r="BK187">
+        <v>1.8</v>
+      </c>
+      <c r="BL187">
+        <v>1.91</v>
+      </c>
+      <c r="BM187">
+        <v>2.33</v>
+      </c>
+      <c r="BN187">
+        <v>1.5</v>
+      </c>
+      <c r="BO187">
+        <v>3.05</v>
+      </c>
+      <c r="BP187">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="313">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,6 +676,15 @@
     <t>['60']</t>
   </si>
   <si>
+    <t>['39', '72', '76', '83']</t>
+  </si>
+  <si>
+    <t>['2', '31']</t>
+  </si>
+  <si>
+    <t>['35', '85', '90+2']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -938,6 +947,12 @@
   </si>
   <si>
     <t>['28', '42']</t>
+  </si>
+  <si>
+    <t>['31', '82']</t>
+  </si>
+  <si>
+    <t>['83']</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1633,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ2">
         <v>0.7</v>
@@ -1839,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1967,7 +1982,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2379,7 +2394,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2457,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ6">
         <v>0.55</v>
@@ -2997,7 +3012,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3902,7 +3917,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ13">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4108,7 +4123,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4233,7 +4248,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4439,7 +4454,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4517,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16">
         <v>2</v>
@@ -4645,7 +4660,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4932,7 +4947,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ18">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5469,7 +5484,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5675,7 +5690,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5959,7 +5974,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ23">
         <v>1.91</v>
@@ -6165,10 +6180,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -6705,7 +6720,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7117,7 +7132,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7198,7 +7213,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR29">
         <v>2.19</v>
@@ -7529,7 +7544,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7610,7 +7625,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ31">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR31">
         <v>0.77</v>
@@ -7735,7 +7750,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8225,10 +8240,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ34">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR34">
         <v>2.85</v>
@@ -8431,10 +8446,10 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR35">
         <v>2.65</v>
@@ -8765,7 +8780,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -8843,7 +8858,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ37">
         <v>1.73</v>
@@ -9177,7 +9192,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9383,7 +9398,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9464,7 +9479,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ40">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR40">
         <v>1.21</v>
@@ -9873,7 +9888,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42">
         <v>0.33</v>
@@ -10413,7 +10428,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10619,7 +10634,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10700,7 +10715,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ46">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR46">
         <v>1.08</v>
@@ -10825,7 +10840,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -10906,7 +10921,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ47">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR47">
         <v>1.15</v>
@@ -11031,7 +11046,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11237,7 +11252,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11443,7 +11458,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11649,7 +11664,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11933,7 +11948,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>0.7</v>
@@ -12061,7 +12076,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12267,7 +12282,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12345,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
         <v>0.55</v>
@@ -12473,7 +12488,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12679,7 +12694,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13581,10 +13596,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ60">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR60">
         <v>1.17</v>
@@ -13709,7 +13724,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13915,7 +13930,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14202,7 +14217,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ63">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR63">
         <v>1.02</v>
@@ -14408,7 +14423,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -14611,10 +14626,10 @@
         <v>2.33</v>
       </c>
       <c r="AP65">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ65">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR65">
         <v>2.79</v>
@@ -14739,7 +14754,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14945,7 +14960,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15229,7 +15244,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
         <v>1.27</v>
@@ -15563,7 +15578,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15975,7 +15990,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16181,7 +16196,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16799,7 +16814,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17289,7 +17304,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ78">
         <v>2.27</v>
@@ -17417,7 +17432,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17495,7 +17510,7 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ79">
         <v>2</v>
@@ -17623,7 +17638,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17910,7 +17925,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR81">
         <v>1.25</v>
@@ -18319,7 +18334,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ83">
         <v>0.8</v>
@@ -18447,7 +18462,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18734,7 +18749,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ85">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR85">
         <v>1.93</v>
@@ -18859,7 +18874,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19352,7 +19367,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ88">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR88">
         <v>2.16</v>
@@ -19477,7 +19492,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19558,7 +19573,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ89">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR89">
         <v>2.01</v>
@@ -19683,7 +19698,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19761,7 +19776,7 @@
         <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>2</v>
@@ -20173,7 +20188,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ92">
         <v>0.7</v>
@@ -20301,7 +20316,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20507,7 +20522,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20585,7 +20600,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>1.91</v>
@@ -20919,7 +20934,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21331,7 +21346,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22027,10 +22042,10 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ101">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR101">
         <v>1.12</v>
@@ -22361,7 +22376,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22567,7 +22582,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22648,7 +22663,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR104">
         <v>1.2</v>
@@ -22773,7 +22788,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22979,7 +22994,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23266,7 +23281,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ107">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR107">
         <v>1.85</v>
@@ -23391,7 +23406,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23472,7 +23487,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ108">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR108">
         <v>1.94</v>
@@ -23881,7 +23896,7 @@
         <v>0</v>
       </c>
       <c r="AP110">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>0.55</v>
@@ -24009,7 +24024,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24087,7 +24102,7 @@
         <v>0</v>
       </c>
       <c r="AP111">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ111">
         <v>0.55</v>
@@ -24293,7 +24308,7 @@
         <v>0.67</v>
       </c>
       <c r="AP112">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ112">
         <v>0.45</v>
@@ -24421,7 +24436,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24627,7 +24642,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24833,7 +24848,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25039,7 +25054,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25941,10 +25956,10 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ120">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR120">
         <v>1.14</v>
@@ -26147,7 +26162,7 @@
         <v>0.83</v>
       </c>
       <c r="AP121">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26356,7 +26371,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ122">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR122">
         <v>1.18</v>
@@ -26481,7 +26496,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26687,7 +26702,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26768,7 +26783,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ124">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR124">
         <v>1.98</v>
@@ -27099,7 +27114,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27305,7 +27320,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27589,7 +27604,7 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ128">
         <v>1.27</v>
@@ -27798,7 +27813,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ129">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -27923,7 +27938,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28129,7 +28144,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28335,7 +28350,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28413,7 +28428,7 @@
         <v>0.86</v>
       </c>
       <c r="AP132">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -28619,7 +28634,7 @@
         <v>0.43</v>
       </c>
       <c r="AP133">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ133">
         <v>0.8</v>
@@ -28747,7 +28762,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29159,7 +29174,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29365,7 +29380,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29446,7 +29461,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ137">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR137">
         <v>1.19</v>
@@ -29777,7 +29792,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29983,7 +29998,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30061,7 +30076,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ140">
         <v>0.8</v>
@@ -30189,7 +30204,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30270,7 +30285,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ141">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -30476,7 +30491,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ142">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR142">
         <v>1.53</v>
@@ -31013,7 +31028,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31219,7 +31234,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -32043,7 +32058,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32327,7 +32342,7 @@
         <v>2.25</v>
       </c>
       <c r="AP151">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ151">
         <v>1.73</v>
@@ -32455,7 +32470,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32742,7 +32757,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ153">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR153">
         <v>1.13</v>
@@ -32867,7 +32882,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -32948,7 +32963,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ154">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR154">
         <v>1.32</v>
@@ -33073,7 +33088,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33151,10 +33166,10 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ155">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR155">
         <v>1.47</v>
@@ -33485,7 +33500,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33566,7 +33581,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR157">
         <v>1.23</v>
@@ -33691,7 +33706,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33769,7 +33784,7 @@
         <v>2</v>
       </c>
       <c r="AP158">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ158">
         <v>1.91</v>
@@ -33897,7 +33912,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -33978,7 +33993,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ159">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR159">
         <v>1.99</v>
@@ -34181,7 +34196,7 @@
         <v>0.25</v>
       </c>
       <c r="AP160">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ160">
         <v>0.33</v>
@@ -34309,7 +34324,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34387,7 +34402,7 @@
         <v>2.5</v>
       </c>
       <c r="AP161">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ161">
         <v>2.27</v>
@@ -34515,7 +34530,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34721,7 +34736,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35133,7 +35148,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35545,7 +35560,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35751,7 +35766,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -35957,7 +35972,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36163,7 +36178,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36653,7 +36668,7 @@
         <v>2.56</v>
       </c>
       <c r="AP172">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ172">
         <v>2.27</v>
@@ -36781,7 +36796,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -36859,7 +36874,7 @@
         <v>0.78</v>
       </c>
       <c r="AP173">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ173">
         <v>0.7</v>
@@ -37065,7 +37080,7 @@
         <v>0.6</v>
       </c>
       <c r="AP174">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ174">
         <v>0.55</v>
@@ -37193,7 +37208,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37480,7 +37495,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ176">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR176">
         <v>1.2</v>
@@ -37605,7 +37620,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37686,7 +37701,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ177">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR177">
         <v>1.77</v>
@@ -37811,7 +37826,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37889,7 +37904,7 @@
         <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ178">
         <v>0.45</v>
@@ -38223,7 +38238,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38429,7 +38444,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38635,7 +38650,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38841,7 +38856,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39253,7 +39268,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39665,7 +39680,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39822,6 +39837,830 @@
       </c>
       <c r="BP187">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7466247</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45696.52083333334</v>
+      </c>
+      <c r="F188">
+        <v>22</v>
+      </c>
+      <c r="G188" t="s">
+        <v>84</v>
+      </c>
+      <c r="H188" t="s">
+        <v>77</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188">
+        <v>1</v>
+      </c>
+      <c r="K188">
+        <v>2</v>
+      </c>
+      <c r="L188">
+        <v>4</v>
+      </c>
+      <c r="M188">
+        <v>2</v>
+      </c>
+      <c r="N188">
+        <v>6</v>
+      </c>
+      <c r="O188" t="s">
+        <v>220</v>
+      </c>
+      <c r="P188" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q188">
+        <v>3.75</v>
+      </c>
+      <c r="R188">
+        <v>2.3</v>
+      </c>
+      <c r="S188">
+        <v>2.63</v>
+      </c>
+      <c r="T188">
+        <v>1.3</v>
+      </c>
+      <c r="U188">
+        <v>3.4</v>
+      </c>
+      <c r="V188">
+        <v>2.5</v>
+      </c>
+      <c r="W188">
+        <v>1.5</v>
+      </c>
+      <c r="X188">
+        <v>6</v>
+      </c>
+      <c r="Y188">
+        <v>1.13</v>
+      </c>
+      <c r="Z188">
+        <v>3.11</v>
+      </c>
+      <c r="AA188">
+        <v>3.47</v>
+      </c>
+      <c r="AB188">
+        <v>2.35</v>
+      </c>
+      <c r="AC188">
+        <v>1.03</v>
+      </c>
+      <c r="AD188">
+        <v>15</v>
+      </c>
+      <c r="AE188">
+        <v>1.21</v>
+      </c>
+      <c r="AF188">
+        <v>4.25</v>
+      </c>
+      <c r="AG188">
+        <v>1.57</v>
+      </c>
+      <c r="AH188">
+        <v>2.25</v>
+      </c>
+      <c r="AI188">
+        <v>1.53</v>
+      </c>
+      <c r="AJ188">
+        <v>2.38</v>
+      </c>
+      <c r="AK188">
+        <v>1.72</v>
+      </c>
+      <c r="AL188">
+        <v>1.28</v>
+      </c>
+      <c r="AM188">
+        <v>1.32</v>
+      </c>
+      <c r="AN188">
+        <v>1.18</v>
+      </c>
+      <c r="AO188">
+        <v>1.22</v>
+      </c>
+      <c r="AP188">
+        <v>1.33</v>
+      </c>
+      <c r="AQ188">
+        <v>1.1</v>
+      </c>
+      <c r="AR188">
+        <v>1.33</v>
+      </c>
+      <c r="AS188">
+        <v>1.17</v>
+      </c>
+      <c r="AT188">
+        <v>2.5</v>
+      </c>
+      <c r="AU188">
+        <v>8</v>
+      </c>
+      <c r="AV188">
+        <v>6</v>
+      </c>
+      <c r="AW188">
+        <v>13</v>
+      </c>
+      <c r="AX188">
+        <v>6</v>
+      </c>
+      <c r="AY188">
+        <v>29</v>
+      </c>
+      <c r="AZ188">
+        <v>17</v>
+      </c>
+      <c r="BA188">
+        <v>11</v>
+      </c>
+      <c r="BB188">
+        <v>5</v>
+      </c>
+      <c r="BC188">
+        <v>16</v>
+      </c>
+      <c r="BD188">
+        <v>1.98</v>
+      </c>
+      <c r="BE188">
+        <v>6.4</v>
+      </c>
+      <c r="BF188">
+        <v>2</v>
+      </c>
+      <c r="BG188">
+        <v>1.23</v>
+      </c>
+      <c r="BH188">
+        <v>3.65</v>
+      </c>
+      <c r="BI188">
+        <v>1.41</v>
+      </c>
+      <c r="BJ188">
+        <v>2.65</v>
+      </c>
+      <c r="BK188">
+        <v>1.67</v>
+      </c>
+      <c r="BL188">
+        <v>2.05</v>
+      </c>
+      <c r="BM188">
+        <v>1.91</v>
+      </c>
+      <c r="BN188">
+        <v>1.8</v>
+      </c>
+      <c r="BO188">
+        <v>2.63</v>
+      </c>
+      <c r="BP188">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7466248</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45696.61458333334</v>
+      </c>
+      <c r="F189">
+        <v>22</v>
+      </c>
+      <c r="G189" t="s">
+        <v>74</v>
+      </c>
+      <c r="H189" t="s">
+        <v>86</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>1</v>
+      </c>
+      <c r="N189">
+        <v>2</v>
+      </c>
+      <c r="O189" t="s">
+        <v>171</v>
+      </c>
+      <c r="P189" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q189">
+        <v>1.44</v>
+      </c>
+      <c r="R189">
+        <v>3.25</v>
+      </c>
+      <c r="S189">
+        <v>13</v>
+      </c>
+      <c r="T189">
+        <v>1.2</v>
+      </c>
+      <c r="U189">
+        <v>4.33</v>
+      </c>
+      <c r="V189">
+        <v>1.91</v>
+      </c>
+      <c r="W189">
+        <v>1.8</v>
+      </c>
+      <c r="X189">
+        <v>4</v>
+      </c>
+      <c r="Y189">
+        <v>1.22</v>
+      </c>
+      <c r="Z189">
+        <v>1.17</v>
+      </c>
+      <c r="AA189">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AB189">
+        <v>17</v>
+      </c>
+      <c r="AC189">
+        <v>1.01</v>
+      </c>
+      <c r="AD189">
+        <v>29</v>
+      </c>
+      <c r="AE189">
+        <v>1.07</v>
+      </c>
+      <c r="AF189">
+        <v>7.77</v>
+      </c>
+      <c r="AG189">
+        <v>1.33</v>
+      </c>
+      <c r="AH189">
+        <v>3</v>
+      </c>
+      <c r="AI189">
+        <v>2.1</v>
+      </c>
+      <c r="AJ189">
+        <v>1.67</v>
+      </c>
+      <c r="AK189">
+        <v>1.01</v>
+      </c>
+      <c r="AL189">
+        <v>1.06</v>
+      </c>
+      <c r="AM189">
+        <v>6</v>
+      </c>
+      <c r="AN189">
+        <v>2.8</v>
+      </c>
+      <c r="AO189">
+        <v>1.1</v>
+      </c>
+      <c r="AP189">
+        <v>2.64</v>
+      </c>
+      <c r="AQ189">
+        <v>1.09</v>
+      </c>
+      <c r="AR189">
+        <v>2.4</v>
+      </c>
+      <c r="AS189">
+        <v>0.89</v>
+      </c>
+      <c r="AT189">
+        <v>3.29</v>
+      </c>
+      <c r="AU189">
+        <v>7</v>
+      </c>
+      <c r="AV189">
+        <v>4</v>
+      </c>
+      <c r="AW189">
+        <v>9</v>
+      </c>
+      <c r="AX189">
+        <v>5</v>
+      </c>
+      <c r="AY189">
+        <v>16</v>
+      </c>
+      <c r="AZ189">
+        <v>10</v>
+      </c>
+      <c r="BA189">
+        <v>6</v>
+      </c>
+      <c r="BB189">
+        <v>2</v>
+      </c>
+      <c r="BC189">
+        <v>8</v>
+      </c>
+      <c r="BD189">
+        <v>1.06</v>
+      </c>
+      <c r="BE189">
+        <v>14</v>
+      </c>
+      <c r="BF189">
+        <v>9.5</v>
+      </c>
+      <c r="BG189">
+        <v>1.15</v>
+      </c>
+      <c r="BH189">
+        <v>4.6</v>
+      </c>
+      <c r="BI189">
+        <v>1.27</v>
+      </c>
+      <c r="BJ189">
+        <v>3.3</v>
+      </c>
+      <c r="BK189">
+        <v>1.47</v>
+      </c>
+      <c r="BL189">
+        <v>2.48</v>
+      </c>
+      <c r="BM189">
+        <v>1.85</v>
+      </c>
+      <c r="BN189">
+        <v>1.85</v>
+      </c>
+      <c r="BO189">
+        <v>2.08</v>
+      </c>
+      <c r="BP189">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7466243</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45696.66666666666</v>
+      </c>
+      <c r="F190">
+        <v>22</v>
+      </c>
+      <c r="G190" t="s">
+        <v>70</v>
+      </c>
+      <c r="H190" t="s">
+        <v>72</v>
+      </c>
+      <c r="I190">
+        <v>2</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>2</v>
+      </c>
+      <c r="L190">
+        <v>2</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>3</v>
+      </c>
+      <c r="O190" t="s">
+        <v>221</v>
+      </c>
+      <c r="P190" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q190">
+        <v>3.6</v>
+      </c>
+      <c r="R190">
+        <v>2.1</v>
+      </c>
+      <c r="S190">
+        <v>3.1</v>
+      </c>
+      <c r="T190">
+        <v>1.44</v>
+      </c>
+      <c r="U190">
+        <v>2.63</v>
+      </c>
+      <c r="V190">
+        <v>3</v>
+      </c>
+      <c r="W190">
+        <v>1.36</v>
+      </c>
+      <c r="X190">
+        <v>9</v>
+      </c>
+      <c r="Y190">
+        <v>1.07</v>
+      </c>
+      <c r="Z190">
+        <v>2.72</v>
+      </c>
+      <c r="AA190">
+        <v>3.33</v>
+      </c>
+      <c r="AB190">
+        <v>2.72</v>
+      </c>
+      <c r="AC190">
+        <v>1.05</v>
+      </c>
+      <c r="AD190">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AE190">
+        <v>1.33</v>
+      </c>
+      <c r="AF190">
+        <v>3.19</v>
+      </c>
+      <c r="AG190">
+        <v>1.96</v>
+      </c>
+      <c r="AH190">
+        <v>1.85</v>
+      </c>
+      <c r="AI190">
+        <v>1.8</v>
+      </c>
+      <c r="AJ190">
+        <v>1.95</v>
+      </c>
+      <c r="AK190">
+        <v>1.52</v>
+      </c>
+      <c r="AL190">
+        <v>1.32</v>
+      </c>
+      <c r="AM190">
+        <v>1.41</v>
+      </c>
+      <c r="AN190">
+        <v>1.6</v>
+      </c>
+      <c r="AO190">
+        <v>1</v>
+      </c>
+      <c r="AP190">
+        <v>1.73</v>
+      </c>
+      <c r="AQ190">
+        <v>0.9</v>
+      </c>
+      <c r="AR190">
+        <v>1.38</v>
+      </c>
+      <c r="AS190">
+        <v>1.26</v>
+      </c>
+      <c r="AT190">
+        <v>2.64</v>
+      </c>
+      <c r="AU190">
+        <v>7</v>
+      </c>
+      <c r="AV190">
+        <v>6</v>
+      </c>
+      <c r="AW190">
+        <v>12</v>
+      </c>
+      <c r="AX190">
+        <v>9</v>
+      </c>
+      <c r="AY190">
+        <v>24</v>
+      </c>
+      <c r="AZ190">
+        <v>18</v>
+      </c>
+      <c r="BA190">
+        <v>7</v>
+      </c>
+      <c r="BB190">
+        <v>6</v>
+      </c>
+      <c r="BC190">
+        <v>13</v>
+      </c>
+      <c r="BD190">
+        <v>1.93</v>
+      </c>
+      <c r="BE190">
+        <v>6.4</v>
+      </c>
+      <c r="BF190">
+        <v>2.07</v>
+      </c>
+      <c r="BG190">
+        <v>1.26</v>
+      </c>
+      <c r="BH190">
+        <v>3.4</v>
+      </c>
+      <c r="BI190">
+        <v>1.47</v>
+      </c>
+      <c r="BJ190">
+        <v>2.48</v>
+      </c>
+      <c r="BK190">
+        <v>1.75</v>
+      </c>
+      <c r="BL190">
+        <v>1.95</v>
+      </c>
+      <c r="BM190">
+        <v>2.05</v>
+      </c>
+      <c r="BN190">
+        <v>1.7</v>
+      </c>
+      <c r="BO190">
+        <v>2.8</v>
+      </c>
+      <c r="BP190">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7466245</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45696.70833333334</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>71</v>
+      </c>
+      <c r="H191" t="s">
+        <v>75</v>
+      </c>
+      <c r="I191">
+        <v>1</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191">
+        <v>3</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>3</v>
+      </c>
+      <c r="O191" t="s">
+        <v>222</v>
+      </c>
+      <c r="P191" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q191">
+        <v>1.83</v>
+      </c>
+      <c r="R191">
+        <v>2.6</v>
+      </c>
+      <c r="S191">
+        <v>7</v>
+      </c>
+      <c r="T191">
+        <v>1.29</v>
+      </c>
+      <c r="U191">
+        <v>3.5</v>
+      </c>
+      <c r="V191">
+        <v>2.25</v>
+      </c>
+      <c r="W191">
+        <v>1.57</v>
+      </c>
+      <c r="X191">
+        <v>5.5</v>
+      </c>
+      <c r="Y191">
+        <v>1.14</v>
+      </c>
+      <c r="Z191">
+        <v>1.29</v>
+      </c>
+      <c r="AA191">
+        <v>6.2</v>
+      </c>
+      <c r="AB191">
+        <v>10</v>
+      </c>
+      <c r="AC191">
+        <v>1.02</v>
+      </c>
+      <c r="AD191">
+        <v>19</v>
+      </c>
+      <c r="AE191">
+        <v>1.16</v>
+      </c>
+      <c r="AF191">
+        <v>4.87</v>
+      </c>
+      <c r="AG191">
+        <v>1.53</v>
+      </c>
+      <c r="AH191">
+        <v>2.35</v>
+      </c>
+      <c r="AI191">
+        <v>1.8</v>
+      </c>
+      <c r="AJ191">
+        <v>1.95</v>
+      </c>
+      <c r="AK191">
+        <v>1.09</v>
+      </c>
+      <c r="AL191">
+        <v>1.16</v>
+      </c>
+      <c r="AM191">
+        <v>3</v>
+      </c>
+      <c r="AN191">
+        <v>1.89</v>
+      </c>
+      <c r="AO191">
+        <v>1.2</v>
+      </c>
+      <c r="AP191">
+        <v>2</v>
+      </c>
+      <c r="AQ191">
+        <v>1.09</v>
+      </c>
+      <c r="AR191">
+        <v>1.85</v>
+      </c>
+      <c r="AS191">
+        <v>1.41</v>
+      </c>
+      <c r="AT191">
+        <v>3.26</v>
+      </c>
+      <c r="AU191">
+        <v>6</v>
+      </c>
+      <c r="AV191">
+        <v>5</v>
+      </c>
+      <c r="AW191">
+        <v>11</v>
+      </c>
+      <c r="AX191">
+        <v>10</v>
+      </c>
+      <c r="AY191">
+        <v>20</v>
+      </c>
+      <c r="AZ191">
+        <v>16</v>
+      </c>
+      <c r="BA191">
+        <v>6</v>
+      </c>
+      <c r="BB191">
+        <v>2</v>
+      </c>
+      <c r="BC191">
+        <v>8</v>
+      </c>
+      <c r="BD191">
+        <v>1.17</v>
+      </c>
+      <c r="BE191">
+        <v>9.5</v>
+      </c>
+      <c r="BF191">
+        <v>5.3</v>
+      </c>
+      <c r="BG191">
+        <v>1.16</v>
+      </c>
+      <c r="BH191">
+        <v>4.4</v>
+      </c>
+      <c r="BI191">
+        <v>1.29</v>
+      </c>
+      <c r="BJ191">
+        <v>3.2</v>
+      </c>
+      <c r="BK191">
+        <v>1.48</v>
+      </c>
+      <c r="BL191">
+        <v>2.43</v>
+      </c>
+      <c r="BM191">
+        <v>1.91</v>
+      </c>
+      <c r="BN191">
+        <v>1.8</v>
+      </c>
+      <c r="BO191">
+        <v>2.15</v>
+      </c>
+      <c r="BP191">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,15 @@
     <t>['35', '85', '90+2']</t>
   </si>
   <si>
+    <t>['6', '14', '28', '72', '89']</t>
+  </si>
+  <si>
+    <t>['41', '56']</t>
+  </si>
+  <si>
+    <t>['33', '53', '90+3']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -953,6 +962,12 @@
   </si>
   <si>
     <t>['83']</t>
+  </si>
+  <si>
+    <t>['68', '90+4']</t>
+  </si>
+  <si>
+    <t>['3', '23', '62']</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1651,7 +1666,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ2">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1982,7 +1997,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2063,7 +2078,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ4">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2394,7 +2409,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2884,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ8">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3012,7 +3027,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3502,10 +3517,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ11">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3708,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ12">
         <v>2.27</v>
@@ -4120,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ14">
         <v>0.9</v>
@@ -4248,7 +4263,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4326,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ15">
         <v>0.45</v>
@@ -4454,7 +4469,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4660,7 +4675,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5153,7 +5168,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ19">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5359,7 +5374,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR20">
         <v>1.11</v>
@@ -5484,7 +5499,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5690,7 +5705,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6720,7 +6735,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6798,7 +6813,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>1.91</v>
@@ -7132,7 +7147,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7210,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ29">
         <v>0.9</v>
@@ -7416,10 +7431,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ30">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR30">
         <v>2.4</v>
@@ -7544,7 +7559,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7750,7 +7765,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7828,10 +7843,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ32">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR32">
         <v>1.07</v>
@@ -8655,7 +8670,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ36">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR36">
         <v>1.72</v>
@@ -8780,7 +8795,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9192,7 +9207,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9270,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ39">
         <v>0.55</v>
@@ -9398,7 +9413,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9891,7 +9906,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR42">
         <v>1.23</v>
@@ -10428,7 +10443,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10634,7 +10649,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10712,7 +10727,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ46">
         <v>1.09</v>
@@ -10840,7 +10855,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -10918,7 +10933,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
         <v>1.09</v>
@@ -11046,7 +11061,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11127,7 +11142,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ48">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR48">
         <v>1.91</v>
@@ -11252,7 +11267,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11458,7 +11473,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11536,7 +11551,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ50">
         <v>0.45</v>
@@ -11664,7 +11679,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11745,7 +11760,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ51">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR51">
         <v>0.82</v>
@@ -11951,7 +11966,7 @@
         <v>2</v>
       </c>
       <c r="AQ52">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR52">
         <v>2.23</v>
@@ -12076,7 +12091,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12154,7 +12169,7 @@
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ53">
         <v>2</v>
@@ -12282,7 +12297,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12488,7 +12503,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12694,7 +12709,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13187,7 +13202,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ58">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR58">
         <v>1.08</v>
@@ -13393,7 +13408,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ59">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR59">
         <v>2.11</v>
@@ -13724,7 +13739,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13802,10 +13817,10 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR61">
         <v>1.5</v>
@@ -13930,7 +13945,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14008,7 +14023,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ62">
         <v>2.27</v>
@@ -14754,7 +14769,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14832,7 +14847,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ66">
         <v>0.55</v>
@@ -14960,7 +14975,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15247,7 +15262,7 @@
         <v>2</v>
       </c>
       <c r="AQ68">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR68">
         <v>2.17</v>
@@ -15450,10 +15465,10 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ69">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR69">
         <v>2.09</v>
@@ -15578,7 +15593,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15862,7 +15877,7 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71">
         <v>1.91</v>
@@ -15990,7 +16005,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16071,7 +16086,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ72">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -16196,7 +16211,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16274,7 +16289,7 @@
         <v>3</v>
       </c>
       <c r="AP73">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ73">
         <v>2</v>
@@ -16686,10 +16701,10 @@
         <v>1.5</v>
       </c>
       <c r="AP75">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ75">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR75">
         <v>1.24</v>
@@ -16814,7 +16829,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17432,7 +17447,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17513,7 +17528,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR79">
         <v>1.54</v>
@@ -17638,7 +17653,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17719,7 +17734,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ80">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR80">
         <v>1.12</v>
@@ -18128,7 +18143,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ82">
         <v>0.45</v>
@@ -18337,7 +18352,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ83">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR83">
         <v>2.49</v>
@@ -18462,7 +18477,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18746,7 +18761,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ85">
         <v>1.09</v>
@@ -18874,7 +18889,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18952,7 +18967,7 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ86">
         <v>1.73</v>
@@ -19492,7 +19507,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19570,7 +19585,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ89">
         <v>1.1</v>
@@ -19698,7 +19713,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19779,7 +19794,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR90">
         <v>1.77</v>
@@ -19985,7 +20000,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ91">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
         <v>1.05</v>
@@ -20191,7 +20206,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ92">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR92">
         <v>1.39</v>
@@ -20316,7 +20331,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20522,7 +20537,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20806,7 +20821,7 @@
         <v>0</v>
       </c>
       <c r="AP95">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95">
         <v>0.55</v>
@@ -20934,7 +20949,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21015,7 +21030,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ96">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21346,7 +21361,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21630,10 +21645,10 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21836,7 +21851,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ100">
         <v>0.8</v>
@@ -22376,7 +22391,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22582,7 +22597,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22660,7 +22675,7 @@
         <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ104">
         <v>0.9</v>
@@ -22788,7 +22803,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22994,7 +23009,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23075,7 +23090,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ106">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR106">
         <v>2.03</v>
@@ -23278,7 +23293,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ107">
         <v>1.1</v>
@@ -23406,7 +23421,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23484,7 +23499,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ108">
         <v>1.09</v>
@@ -23693,7 +23708,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ109">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -24024,7 +24039,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24436,7 +24451,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24514,10 +24529,10 @@
         <v>1.67</v>
       </c>
       <c r="AP113">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ113">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR113">
         <v>1.21</v>
@@ -24642,7 +24657,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24848,7 +24863,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25054,7 +25069,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25135,7 +25150,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ116">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR116">
         <v>1.02</v>
@@ -25341,7 +25356,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ117">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR117">
         <v>2.01</v>
@@ -25544,7 +25559,7 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ118">
         <v>0.55</v>
@@ -25753,7 +25768,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ119">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR119">
         <v>1.34</v>
@@ -26496,7 +26511,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26574,7 +26589,7 @@
         <v>2.57</v>
       </c>
       <c r="AP123">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ123">
         <v>2</v>
@@ -26702,7 +26717,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26986,7 +27001,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ125">
         <v>0.8</v>
@@ -27114,7 +27129,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27195,7 +27210,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ126">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR126">
         <v>1.45</v>
@@ -27320,7 +27335,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27607,7 +27622,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ128">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR128">
         <v>2.46</v>
@@ -27938,7 +27953,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28019,7 +28034,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ130">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR130">
         <v>1.55</v>
@@ -28144,7 +28159,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28222,7 +28237,7 @@
         <v>2.14</v>
       </c>
       <c r="AP131">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ131">
         <v>1.73</v>
@@ -28350,7 +28365,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28637,7 +28652,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ133">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR133">
         <v>1.23</v>
@@ -28762,7 +28777,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29046,10 +29061,10 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR135">
         <v>1.92</v>
@@ -29174,7 +29189,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29380,7 +29395,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29664,7 +29679,7 @@
         <v>2.63</v>
       </c>
       <c r="AP138">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ138">
         <v>2</v>
@@ -29792,7 +29807,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29870,7 +29885,7 @@
         <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ139">
         <v>0.55</v>
@@ -29998,7 +30013,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30204,7 +30219,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30282,7 +30297,7 @@
         <v>1</v>
       </c>
       <c r="AP141">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ141">
         <v>1.1</v>
@@ -30903,7 +30918,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ144">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR144">
         <v>1.74</v>
@@ -31028,7 +31043,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31234,7 +31249,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31312,10 +31327,10 @@
         <v>0.5</v>
       </c>
       <c r="AP146">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ146">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR146">
         <v>1.16</v>
@@ -31521,7 +31536,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ147">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR147">
         <v>1.7</v>
@@ -31930,10 +31945,10 @@
         <v>1.63</v>
       </c>
       <c r="AP149">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ149">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR149">
         <v>1.83</v>
@@ -32058,7 +32073,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32139,7 +32154,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ150">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR150">
         <v>1.58</v>
@@ -32470,7 +32485,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32548,7 +32563,7 @@
         <v>0.88</v>
       </c>
       <c r="AP152">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -32882,7 +32897,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -32960,7 +32975,7 @@
         <v>1</v>
       </c>
       <c r="AP154">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ154">
         <v>1.1</v>
@@ -33088,7 +33103,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33500,7 +33515,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33706,7 +33721,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33912,7 +33927,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34199,7 +34214,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ160">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR160">
         <v>1.27</v>
@@ -34324,7 +34339,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34530,7 +34545,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34736,7 +34751,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35020,7 +35035,7 @@
         <v>1.89</v>
       </c>
       <c r="AP164">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ164">
         <v>1.91</v>
@@ -35148,7 +35163,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35560,7 +35575,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35641,7 +35656,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ167">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR167">
         <v>1.33</v>
@@ -35766,7 +35781,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -35972,7 +35987,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36050,10 +36065,10 @@
         <v>1.89</v>
       </c>
       <c r="AP169">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ169">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR169">
         <v>1.56</v>
@@ -36178,7 +36193,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36796,7 +36811,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -36877,7 +36892,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ173">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR173">
         <v>2.35</v>
@@ -37208,7 +37223,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37286,10 +37301,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP175">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ175">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR175">
         <v>1.34</v>
@@ -37492,7 +37507,7 @@
         <v>1.22</v>
       </c>
       <c r="AP176">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ176">
         <v>1.09</v>
@@ -37620,7 +37635,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37698,7 +37713,7 @@
         <v>1</v>
       </c>
       <c r="AP177">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ177">
         <v>1.09</v>
@@ -37826,7 +37841,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38238,7 +38253,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38444,7 +38459,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38522,7 +38537,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ181">
         <v>1</v>
@@ -38650,7 +38665,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38856,7 +38871,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39268,7 +39283,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39349,7 +39364,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ185">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR185">
         <v>1.74</v>
@@ -39680,7 +39695,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39886,7 +39901,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40092,7 +40107,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40661,6 +40676,1036 @@
       </c>
       <c r="BP191">
         <v>1.61</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7466244</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45697.34375</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>76</v>
+      </c>
+      <c r="H192" t="s">
+        <v>73</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>1</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
+        <v>91</v>
+      </c>
+      <c r="P192" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q192">
+        <v>1.83</v>
+      </c>
+      <c r="R192">
+        <v>2.5</v>
+      </c>
+      <c r="S192">
+        <v>7</v>
+      </c>
+      <c r="T192">
+        <v>1.3</v>
+      </c>
+      <c r="U192">
+        <v>3.4</v>
+      </c>
+      <c r="V192">
+        <v>2.5</v>
+      </c>
+      <c r="W192">
+        <v>1.5</v>
+      </c>
+      <c r="X192">
+        <v>6</v>
+      </c>
+      <c r="Y192">
+        <v>1.13</v>
+      </c>
+      <c r="Z192">
+        <v>1.4</v>
+      </c>
+      <c r="AA192">
+        <v>5.1</v>
+      </c>
+      <c r="AB192">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC192">
+        <v>1.03</v>
+      </c>
+      <c r="AD192">
+        <v>15</v>
+      </c>
+      <c r="AE192">
+        <v>1.21</v>
+      </c>
+      <c r="AF192">
+        <v>4.25</v>
+      </c>
+      <c r="AG192">
+        <v>1.6</v>
+      </c>
+      <c r="AH192">
+        <v>2.2</v>
+      </c>
+      <c r="AI192">
+        <v>1.95</v>
+      </c>
+      <c r="AJ192">
+        <v>1.8</v>
+      </c>
+      <c r="AK192">
+        <v>1.08</v>
+      </c>
+      <c r="AL192">
+        <v>1.17</v>
+      </c>
+      <c r="AM192">
+        <v>3</v>
+      </c>
+      <c r="AN192">
+        <v>1.7</v>
+      </c>
+      <c r="AO192">
+        <v>0.33</v>
+      </c>
+      <c r="AP192">
+        <v>1.55</v>
+      </c>
+      <c r="AQ192">
+        <v>0.6</v>
+      </c>
+      <c r="AR192">
+        <v>1.52</v>
+      </c>
+      <c r="AS192">
+        <v>1.04</v>
+      </c>
+      <c r="AT192">
+        <v>2.56</v>
+      </c>
+      <c r="AU192">
+        <v>6</v>
+      </c>
+      <c r="AV192">
+        <v>8</v>
+      </c>
+      <c r="AW192">
+        <v>10</v>
+      </c>
+      <c r="AX192">
+        <v>9</v>
+      </c>
+      <c r="AY192">
+        <v>17</v>
+      </c>
+      <c r="AZ192">
+        <v>18</v>
+      </c>
+      <c r="BA192">
+        <v>8</v>
+      </c>
+      <c r="BB192">
+        <v>5</v>
+      </c>
+      <c r="BC192">
+        <v>13</v>
+      </c>
+      <c r="BD192">
+        <v>1.2</v>
+      </c>
+      <c r="BE192">
+        <v>9</v>
+      </c>
+      <c r="BF192">
+        <v>4.8</v>
+      </c>
+      <c r="BG192">
+        <v>1.2</v>
+      </c>
+      <c r="BH192">
+        <v>3.95</v>
+      </c>
+      <c r="BI192">
+        <v>1.35</v>
+      </c>
+      <c r="BJ192">
+        <v>2.88</v>
+      </c>
+      <c r="BK192">
+        <v>1.57</v>
+      </c>
+      <c r="BL192">
+        <v>2.23</v>
+      </c>
+      <c r="BM192">
+        <v>1.95</v>
+      </c>
+      <c r="BN192">
+        <v>1.77</v>
+      </c>
+      <c r="BO192">
+        <v>2.33</v>
+      </c>
+      <c r="BP192">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7466249</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45697.4375</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>83</v>
+      </c>
+      <c r="H193" t="s">
+        <v>87</v>
+      </c>
+      <c r="I193">
+        <v>3</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>3</v>
+      </c>
+      <c r="L193">
+        <v>5</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>5</v>
+      </c>
+      <c r="O193" t="s">
+        <v>223</v>
+      </c>
+      <c r="P193" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q193">
+        <v>3.2</v>
+      </c>
+      <c r="R193">
+        <v>2.25</v>
+      </c>
+      <c r="S193">
+        <v>3.1</v>
+      </c>
+      <c r="T193">
+        <v>1.33</v>
+      </c>
+      <c r="U193">
+        <v>3.25</v>
+      </c>
+      <c r="V193">
+        <v>2.63</v>
+      </c>
+      <c r="W193">
+        <v>1.44</v>
+      </c>
+      <c r="X193">
+        <v>6.5</v>
+      </c>
+      <c r="Y193">
+        <v>1.11</v>
+      </c>
+      <c r="Z193">
+        <v>2.75</v>
+      </c>
+      <c r="AA193">
+        <v>3.62</v>
+      </c>
+      <c r="AB193">
+        <v>2.53</v>
+      </c>
+      <c r="AC193">
+        <v>1.03</v>
+      </c>
+      <c r="AD193">
+        <v>15</v>
+      </c>
+      <c r="AE193">
+        <v>1.21</v>
+      </c>
+      <c r="AF193">
+        <v>4.25</v>
+      </c>
+      <c r="AG193">
+        <v>1.7</v>
+      </c>
+      <c r="AH193">
+        <v>2.05</v>
+      </c>
+      <c r="AI193">
+        <v>1.57</v>
+      </c>
+      <c r="AJ193">
+        <v>2.25</v>
+      </c>
+      <c r="AK193">
+        <v>1.5</v>
+      </c>
+      <c r="AL193">
+        <v>1.29</v>
+      </c>
+      <c r="AM193">
+        <v>1.46</v>
+      </c>
+      <c r="AN193">
+        <v>0.8</v>
+      </c>
+      <c r="AO193">
+        <v>0.7</v>
+      </c>
+      <c r="AP193">
+        <v>1</v>
+      </c>
+      <c r="AQ193">
+        <v>0.64</v>
+      </c>
+      <c r="AR193">
+        <v>1.22</v>
+      </c>
+      <c r="AS193">
+        <v>1.15</v>
+      </c>
+      <c r="AT193">
+        <v>2.37</v>
+      </c>
+      <c r="AU193">
+        <v>8</v>
+      </c>
+      <c r="AV193">
+        <v>3</v>
+      </c>
+      <c r="AW193">
+        <v>11</v>
+      </c>
+      <c r="AX193">
+        <v>12</v>
+      </c>
+      <c r="AY193">
+        <v>24</v>
+      </c>
+      <c r="AZ193">
+        <v>19</v>
+      </c>
+      <c r="BA193">
+        <v>7</v>
+      </c>
+      <c r="BB193">
+        <v>5</v>
+      </c>
+      <c r="BC193">
+        <v>12</v>
+      </c>
+      <c r="BD193">
+        <v>2.05</v>
+      </c>
+      <c r="BE193">
+        <v>6.4</v>
+      </c>
+      <c r="BF193">
+        <v>1.94</v>
+      </c>
+      <c r="BG193">
+        <v>1.27</v>
+      </c>
+      <c r="BH193">
+        <v>3.3</v>
+      </c>
+      <c r="BI193">
+        <v>1.46</v>
+      </c>
+      <c r="BJ193">
+        <v>2.48</v>
+      </c>
+      <c r="BK193">
+        <v>1.7</v>
+      </c>
+      <c r="BL193">
+        <v>2.05</v>
+      </c>
+      <c r="BM193">
+        <v>2.18</v>
+      </c>
+      <c r="BN193">
+        <v>1.58</v>
+      </c>
+      <c r="BO193">
+        <v>2.8</v>
+      </c>
+      <c r="BP193">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7466246</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45697.4375</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>79</v>
+      </c>
+      <c r="H194" t="s">
+        <v>78</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>2</v>
+      </c>
+      <c r="N194">
+        <v>2</v>
+      </c>
+      <c r="O194" t="s">
+        <v>91</v>
+      </c>
+      <c r="P194" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q194">
+        <v>5.5</v>
+      </c>
+      <c r="R194">
+        <v>2.4</v>
+      </c>
+      <c r="S194">
+        <v>2.05</v>
+      </c>
+      <c r="T194">
+        <v>1.3</v>
+      </c>
+      <c r="U194">
+        <v>3.4</v>
+      </c>
+      <c r="V194">
+        <v>2.5</v>
+      </c>
+      <c r="W194">
+        <v>1.5</v>
+      </c>
+      <c r="X194">
+        <v>6</v>
+      </c>
+      <c r="Y194">
+        <v>1.13</v>
+      </c>
+      <c r="Z194">
+        <v>6</v>
+      </c>
+      <c r="AA194">
+        <v>4.6</v>
+      </c>
+      <c r="AB194">
+        <v>1.53</v>
+      </c>
+      <c r="AC194">
+        <v>1.03</v>
+      </c>
+      <c r="AD194">
+        <v>17</v>
+      </c>
+      <c r="AE194">
+        <v>1.19</v>
+      </c>
+      <c r="AF194">
+        <v>4.45</v>
+      </c>
+      <c r="AG194">
+        <v>1.57</v>
+      </c>
+      <c r="AH194">
+        <v>2.3</v>
+      </c>
+      <c r="AI194">
+        <v>1.8</v>
+      </c>
+      <c r="AJ194">
+        <v>1.95</v>
+      </c>
+      <c r="AK194">
+        <v>2.55</v>
+      </c>
+      <c r="AL194">
+        <v>1.2</v>
+      </c>
+      <c r="AM194">
+        <v>1.12</v>
+      </c>
+      <c r="AN194">
+        <v>1.5</v>
+      </c>
+      <c r="AO194">
+        <v>2</v>
+      </c>
+      <c r="AP194">
+        <v>1.36</v>
+      </c>
+      <c r="AQ194">
+        <v>2.09</v>
+      </c>
+      <c r="AR194">
+        <v>1.36</v>
+      </c>
+      <c r="AS194">
+        <v>1.4</v>
+      </c>
+      <c r="AT194">
+        <v>2.76</v>
+      </c>
+      <c r="AU194">
+        <v>4</v>
+      </c>
+      <c r="AV194">
+        <v>7</v>
+      </c>
+      <c r="AW194">
+        <v>7</v>
+      </c>
+      <c r="AX194">
+        <v>2</v>
+      </c>
+      <c r="AY194">
+        <v>11</v>
+      </c>
+      <c r="AZ194">
+        <v>10</v>
+      </c>
+      <c r="BA194">
+        <v>5</v>
+      </c>
+      <c r="BB194">
+        <v>4</v>
+      </c>
+      <c r="BC194">
+        <v>9</v>
+      </c>
+      <c r="BD194">
+        <v>3.3</v>
+      </c>
+      <c r="BE194">
+        <v>7</v>
+      </c>
+      <c r="BF194">
+        <v>1.38</v>
+      </c>
+      <c r="BG194">
+        <v>1.32</v>
+      </c>
+      <c r="BH194">
+        <v>3.05</v>
+      </c>
+      <c r="BI194">
+        <v>1.55</v>
+      </c>
+      <c r="BJ194">
+        <v>2.25</v>
+      </c>
+      <c r="BK194">
+        <v>1.8</v>
+      </c>
+      <c r="BL194">
+        <v>1.91</v>
+      </c>
+      <c r="BM194">
+        <v>2.4</v>
+      </c>
+      <c r="BN194">
+        <v>1.5</v>
+      </c>
+      <c r="BO194">
+        <v>3.05</v>
+      </c>
+      <c r="BP194">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7466242</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45697.53125</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>82</v>
+      </c>
+      <c r="H195" t="s">
+        <v>85</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>1</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>2</v>
+      </c>
+      <c r="O195" t="s">
+        <v>224</v>
+      </c>
+      <c r="P195" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q195">
+        <v>1.91</v>
+      </c>
+      <c r="R195">
+        <v>2.5</v>
+      </c>
+      <c r="S195">
+        <v>7</v>
+      </c>
+      <c r="T195">
+        <v>1.3</v>
+      </c>
+      <c r="U195">
+        <v>3.4</v>
+      </c>
+      <c r="V195">
+        <v>2.5</v>
+      </c>
+      <c r="W195">
+        <v>1.5</v>
+      </c>
+      <c r="X195">
+        <v>6</v>
+      </c>
+      <c r="Y195">
+        <v>1.13</v>
+      </c>
+      <c r="Z195">
+        <v>1.41</v>
+      </c>
+      <c r="AA195">
+        <v>5</v>
+      </c>
+      <c r="AB195">
+        <v>7.7</v>
+      </c>
+      <c r="AC195">
+        <v>1.03</v>
+      </c>
+      <c r="AD195">
+        <v>15</v>
+      </c>
+      <c r="AE195">
+        <v>1.19</v>
+      </c>
+      <c r="AF195">
+        <v>4.45</v>
+      </c>
+      <c r="AG195">
+        <v>1.65</v>
+      </c>
+      <c r="AH195">
+        <v>2.2</v>
+      </c>
+      <c r="AI195">
+        <v>1.91</v>
+      </c>
+      <c r="AJ195">
+        <v>1.91</v>
+      </c>
+      <c r="AK195">
+        <v>1.1</v>
+      </c>
+      <c r="AL195">
+        <v>1.18</v>
+      </c>
+      <c r="AM195">
+        <v>2.85</v>
+      </c>
+      <c r="AN195">
+        <v>1.6</v>
+      </c>
+      <c r="AO195">
+        <v>0.8</v>
+      </c>
+      <c r="AP195">
+        <v>1.73</v>
+      </c>
+      <c r="AQ195">
+        <v>0.73</v>
+      </c>
+      <c r="AR195">
+        <v>1.82</v>
+      </c>
+      <c r="AS195">
+        <v>1.03</v>
+      </c>
+      <c r="AT195">
+        <v>2.85</v>
+      </c>
+      <c r="AU195">
+        <v>8</v>
+      </c>
+      <c r="AV195">
+        <v>3</v>
+      </c>
+      <c r="AW195">
+        <v>4</v>
+      </c>
+      <c r="AX195">
+        <v>8</v>
+      </c>
+      <c r="AY195">
+        <v>12</v>
+      </c>
+      <c r="AZ195">
+        <v>12</v>
+      </c>
+      <c r="BA195">
+        <v>3</v>
+      </c>
+      <c r="BB195">
+        <v>3</v>
+      </c>
+      <c r="BC195">
+        <v>6</v>
+      </c>
+      <c r="BD195">
+        <v>1.19</v>
+      </c>
+      <c r="BE195">
+        <v>9</v>
+      </c>
+      <c r="BF195">
+        <v>4.9</v>
+      </c>
+      <c r="BG195">
+        <v>1.17</v>
+      </c>
+      <c r="BH195">
+        <v>4.3</v>
+      </c>
+      <c r="BI195">
+        <v>1.3</v>
+      </c>
+      <c r="BJ195">
+        <v>3.05</v>
+      </c>
+      <c r="BK195">
+        <v>1.53</v>
+      </c>
+      <c r="BL195">
+        <v>2.32</v>
+      </c>
+      <c r="BM195">
+        <v>2.05</v>
+      </c>
+      <c r="BN195">
+        <v>1.7</v>
+      </c>
+      <c r="BO195">
+        <v>2.25</v>
+      </c>
+      <c r="BP195">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7466250</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45697.53125</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>80</v>
+      </c>
+      <c r="H196" t="s">
+        <v>81</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>2</v>
+      </c>
+      <c r="K196">
+        <v>3</v>
+      </c>
+      <c r="L196">
+        <v>3</v>
+      </c>
+      <c r="M196">
+        <v>3</v>
+      </c>
+      <c r="N196">
+        <v>6</v>
+      </c>
+      <c r="O196" t="s">
+        <v>225</v>
+      </c>
+      <c r="P196" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q196">
+        <v>4</v>
+      </c>
+      <c r="R196">
+        <v>2.3</v>
+      </c>
+      <c r="S196">
+        <v>2.5</v>
+      </c>
+      <c r="T196">
+        <v>1.3</v>
+      </c>
+      <c r="U196">
+        <v>3.4</v>
+      </c>
+      <c r="V196">
+        <v>2.5</v>
+      </c>
+      <c r="W196">
+        <v>1.5</v>
+      </c>
+      <c r="X196">
+        <v>6</v>
+      </c>
+      <c r="Y196">
+        <v>1.13</v>
+      </c>
+      <c r="Z196">
+        <v>3.89</v>
+      </c>
+      <c r="AA196">
+        <v>3.93</v>
+      </c>
+      <c r="AB196">
+        <v>1.91</v>
+      </c>
+      <c r="AC196">
+        <v>1.02</v>
+      </c>
+      <c r="AD196">
+        <v>17</v>
+      </c>
+      <c r="AE196">
+        <v>1.19</v>
+      </c>
+      <c r="AF196">
+        <v>4.45</v>
+      </c>
+      <c r="AG196">
+        <v>1.65</v>
+      </c>
+      <c r="AH196">
+        <v>2.15</v>
+      </c>
+      <c r="AI196">
+        <v>1.62</v>
+      </c>
+      <c r="AJ196">
+        <v>2.2</v>
+      </c>
+      <c r="AK196">
+        <v>1.85</v>
+      </c>
+      <c r="AL196">
+        <v>1.26</v>
+      </c>
+      <c r="AM196">
+        <v>1.27</v>
+      </c>
+      <c r="AN196">
+        <v>1.9</v>
+      </c>
+      <c r="AO196">
+        <v>1.27</v>
+      </c>
+      <c r="AP196">
+        <v>1.82</v>
+      </c>
+      <c r="AQ196">
+        <v>1.25</v>
+      </c>
+      <c r="AR196">
+        <v>1.64</v>
+      </c>
+      <c r="AS196">
+        <v>1.73</v>
+      </c>
+      <c r="AT196">
+        <v>3.37</v>
+      </c>
+      <c r="AU196">
+        <v>8</v>
+      </c>
+      <c r="AV196">
+        <v>4</v>
+      </c>
+      <c r="AW196">
+        <v>13</v>
+      </c>
+      <c r="AX196">
+        <v>1</v>
+      </c>
+      <c r="AY196">
+        <v>26</v>
+      </c>
+      <c r="AZ196">
+        <v>5</v>
+      </c>
+      <c r="BA196">
+        <v>9</v>
+      </c>
+      <c r="BB196">
+        <v>2</v>
+      </c>
+      <c r="BC196">
+        <v>11</v>
+      </c>
+      <c r="BD196">
+        <v>2.3</v>
+      </c>
+      <c r="BE196">
+        <v>6.4</v>
+      </c>
+      <c r="BF196">
+        <v>1.75</v>
+      </c>
+      <c r="BG196">
+        <v>1.25</v>
+      </c>
+      <c r="BH196">
+        <v>3.4</v>
+      </c>
+      <c r="BI196">
+        <v>1.44</v>
+      </c>
+      <c r="BJ196">
+        <v>2.55</v>
+      </c>
+      <c r="BK196">
+        <v>1.73</v>
+      </c>
+      <c r="BL196">
+        <v>1.96</v>
+      </c>
+      <c r="BM196">
+        <v>2.05</v>
+      </c>
+      <c r="BN196">
+        <v>1.7</v>
+      </c>
+      <c r="BO196">
+        <v>2.75</v>
+      </c>
+      <c r="BP196">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1329,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3932,7 +3932,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ13">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>0.55</v>
@@ -7640,7 +7640,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ31">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>0.77</v>
@@ -10936,7 +10936,7 @@
         <v>1</v>
       </c>
       <c r="AQ47">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.15</v>
@@ -11139,7 +11139,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
         <v>2.09</v>
@@ -14644,7 +14644,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ65">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>2.79</v>
@@ -15053,7 +15053,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>0.8</v>
@@ -16907,7 +16907,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
         <v>1.73</v>
@@ -18764,7 +18764,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ85">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR85">
         <v>1.93</v>
@@ -21027,7 +21027,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>0.73</v>
@@ -22060,7 +22060,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ101">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR101">
         <v>1.12</v>
@@ -23705,7 +23705,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
         <v>0.6</v>
@@ -26386,7 +26386,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ122">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.18</v>
@@ -27825,7 +27825,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ129">
         <v>0.9</v>
@@ -30506,7 +30506,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ142">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR142">
         <v>1.53</v>
@@ -31533,7 +31533,7 @@
         <v>0.88</v>
       </c>
       <c r="AP147">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ147">
         <v>0.64</v>
@@ -33184,7 +33184,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ155">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR155">
         <v>1.47</v>
@@ -35447,7 +35447,7 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ166">
         <v>0.45</v>
@@ -37716,7 +37716,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ177">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR177">
         <v>1.77</v>
@@ -39361,7 +39361,7 @@
         <v>1.3</v>
       </c>
       <c r="AP185">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ185">
         <v>1.25</v>
@@ -40600,7 +40600,7 @@
         <v>2</v>
       </c>
       <c r="AQ191">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR191">
         <v>1.85</v>
@@ -41706,6 +41706,212 @@
       </c>
       <c r="BP196">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7466254</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F197">
+        <v>23</v>
+      </c>
+      <c r="G197" t="s">
+        <v>77</v>
+      </c>
+      <c r="H197" t="s">
+        <v>75</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197" t="s">
+        <v>105</v>
+      </c>
+      <c r="P197" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q197">
+        <v>2.5</v>
+      </c>
+      <c r="R197">
+        <v>2.3</v>
+      </c>
+      <c r="S197">
+        <v>4</v>
+      </c>
+      <c r="T197">
+        <v>1.33</v>
+      </c>
+      <c r="U197">
+        <v>3.25</v>
+      </c>
+      <c r="V197">
+        <v>2.63</v>
+      </c>
+      <c r="W197">
+        <v>1.44</v>
+      </c>
+      <c r="X197">
+        <v>6.5</v>
+      </c>
+      <c r="Y197">
+        <v>1.11</v>
+      </c>
+      <c r="Z197">
+        <v>1.79</v>
+      </c>
+      <c r="AA197">
+        <v>4.1</v>
+      </c>
+      <c r="AB197">
+        <v>4.3</v>
+      </c>
+      <c r="AC197">
+        <v>1.03</v>
+      </c>
+      <c r="AD197">
+        <v>15</v>
+      </c>
+      <c r="AE197">
+        <v>1.21</v>
+      </c>
+      <c r="AF197">
+        <v>4.25</v>
+      </c>
+      <c r="AG197">
+        <v>1.7</v>
+      </c>
+      <c r="AH197">
+        <v>2.13</v>
+      </c>
+      <c r="AI197">
+        <v>1.67</v>
+      </c>
+      <c r="AJ197">
+        <v>2.1</v>
+      </c>
+      <c r="AK197">
+        <v>1.25</v>
+      </c>
+      <c r="AL197">
+        <v>1.25</v>
+      </c>
+      <c r="AM197">
+        <v>1.9</v>
+      </c>
+      <c r="AN197">
+        <v>1.91</v>
+      </c>
+      <c r="AO197">
+        <v>1.09</v>
+      </c>
+      <c r="AP197">
+        <v>2</v>
+      </c>
+      <c r="AQ197">
+        <v>1</v>
+      </c>
+      <c r="AR197">
+        <v>1.68</v>
+      </c>
+      <c r="AS197">
+        <v>1.42</v>
+      </c>
+      <c r="AT197">
+        <v>3.1</v>
+      </c>
+      <c r="AU197">
+        <v>4</v>
+      </c>
+      <c r="AV197">
+        <v>3</v>
+      </c>
+      <c r="AW197">
+        <v>11</v>
+      </c>
+      <c r="AX197">
+        <v>13</v>
+      </c>
+      <c r="AY197">
+        <v>17</v>
+      </c>
+      <c r="AZ197">
+        <v>19</v>
+      </c>
+      <c r="BA197">
+        <v>8</v>
+      </c>
+      <c r="BB197">
+        <v>3</v>
+      </c>
+      <c r="BC197">
+        <v>11</v>
+      </c>
+      <c r="BD197">
+        <v>1.49</v>
+      </c>
+      <c r="BE197">
+        <v>6.75</v>
+      </c>
+      <c r="BF197">
+        <v>2.9</v>
+      </c>
+      <c r="BG197">
+        <v>1.21</v>
+      </c>
+      <c r="BH197">
+        <v>3.8</v>
+      </c>
+      <c r="BI197">
+        <v>1.38</v>
+      </c>
+      <c r="BJ197">
+        <v>2.7</v>
+      </c>
+      <c r="BK197">
+        <v>1.63</v>
+      </c>
+      <c r="BL197">
+        <v>2.1</v>
+      </c>
+      <c r="BM197">
+        <v>2</v>
+      </c>
+      <c r="BN197">
+        <v>1.7</v>
+      </c>
+      <c r="BO197">
+        <v>2.55</v>
+      </c>
+      <c r="BP197">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="322">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -694,6 +694,12 @@
     <t>['33', '53', '90+3']</t>
   </si>
   <si>
+    <t>['11', '90+2']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -968,6 +974,12 @@
   </si>
   <si>
     <t>['3', '23', '62']</t>
+  </si>
+  <si>
+    <t>['16', '75']</t>
+  </si>
+  <si>
+    <t>['5', '17', '21']</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP197"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1997,7 +2009,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2409,7 +2421,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2487,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6">
         <v>0.55</v>
@@ -3027,7 +3039,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3726,7 +3738,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ12">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4263,7 +4275,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4344,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="AQ15">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4469,7 +4481,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4675,7 +4687,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4756,7 +4768,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ17">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4959,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
         <v>1.1</v>
@@ -5165,7 +5177,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19">
         <v>2.09</v>
@@ -5499,7 +5511,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5705,7 +5717,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5783,10 +5795,10 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR22">
         <v>0.79</v>
@@ -6404,7 +6416,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ25">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR25">
         <v>1.08</v>
@@ -6735,7 +6747,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7022,7 +7034,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ28">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR28">
         <v>0.73</v>
@@ -7147,7 +7159,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7559,7 +7571,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7637,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7765,7 +7777,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8255,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ34">
         <v>1.1</v>
@@ -8461,7 +8473,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ35">
         <v>0.9</v>
@@ -8795,7 +8807,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -8876,7 +8888,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ37">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR37">
         <v>1.07</v>
@@ -9079,7 +9091,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9207,7 +9219,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9413,7 +9425,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9697,7 +9709,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>0.55</v>
@@ -10443,7 +10455,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10649,7 +10661,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10855,7 +10867,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11061,7 +11073,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11267,7 +11279,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11473,7 +11485,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11554,7 +11566,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ50">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -11679,7 +11691,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12091,7 +12103,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12297,7 +12309,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12503,7 +12515,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12581,7 +12593,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
         <v>2</v>
@@ -12709,7 +12721,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -12790,7 +12802,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ56">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR56">
         <v>1.55</v>
@@ -13739,7 +13751,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13945,7 +13957,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14026,7 +14038,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ62">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR62">
         <v>2.58</v>
@@ -14435,7 +14447,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
         <v>0.9</v>
@@ -14641,7 +14653,7 @@
         <v>2.33</v>
       </c>
       <c r="AP65">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14769,7 +14781,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14975,7 +14987,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15593,7 +15605,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15674,7 +15686,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ70">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR70">
         <v>2.32</v>
@@ -16005,7 +16017,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16211,7 +16223,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16829,7 +16841,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -16910,7 +16922,7 @@
         <v>2</v>
       </c>
       <c r="AQ76">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR76">
         <v>1.77</v>
@@ -17113,7 +17125,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17322,7 +17334,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ78">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR78">
         <v>1.07</v>
@@ -17447,7 +17459,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17653,7 +17665,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18146,7 +18158,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ82">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR82">
         <v>1.34</v>
@@ -18349,7 +18361,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ83">
         <v>0.73</v>
@@ -18477,7 +18489,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18555,7 +18567,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
         <v>0.55</v>
@@ -18889,7 +18901,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18970,7 +18982,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ86">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19507,7 +19519,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19713,7 +19725,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19997,7 +20009,7 @@
         <v>1.4</v>
       </c>
       <c r="AP91">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ91">
         <v>1.25</v>
@@ -20331,7 +20343,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20537,7 +20549,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20949,7 +20961,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21236,7 +21248,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ97">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR97">
         <v>1.38</v>
@@ -21361,7 +21373,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21442,7 +21454,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ98">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR98">
         <v>1.7</v>
@@ -22391,7 +22403,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22469,7 +22481,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ103">
         <v>2</v>
@@ -22597,7 +22609,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22803,7 +22815,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22884,7 +22896,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ105">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR105">
         <v>1.24</v>
@@ -23009,7 +23021,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23421,7 +23433,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -24039,7 +24051,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24323,10 +24335,10 @@
         <v>0.67</v>
       </c>
       <c r="AP112">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ112">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR112">
         <v>2.46</v>
@@ -24451,7 +24463,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24657,7 +24669,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24738,7 +24750,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ114">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -24863,7 +24875,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25069,7 +25081,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25147,7 +25159,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ116">
         <v>0.64</v>
@@ -25765,7 +25777,7 @@
         <v>0.33</v>
       </c>
       <c r="AP119">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ119">
         <v>0.6</v>
@@ -26511,7 +26523,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26717,7 +26729,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27129,7 +27141,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27335,7 +27347,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27416,7 +27428,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ127">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR127">
         <v>1.82</v>
@@ -27619,7 +27631,7 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ128">
         <v>1.25</v>
@@ -27953,7 +27965,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28159,7 +28171,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28240,7 +28252,7 @@
         <v>1</v>
       </c>
       <c r="AQ131">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28365,7 +28377,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28777,7 +28789,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28855,7 +28867,7 @@
         <v>0</v>
       </c>
       <c r="AP134">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ134">
         <v>0.55</v>
@@ -29189,7 +29201,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29270,7 +29282,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ136">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29395,7 +29407,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29807,7 +29819,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30013,7 +30025,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30219,7 +30231,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30712,7 +30724,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ143">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR143">
         <v>2.08</v>
@@ -31043,7 +31055,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31121,7 +31133,7 @@
         <v>1.86</v>
       </c>
       <c r="AP145">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ145">
         <v>1.91</v>
@@ -31249,7 +31261,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -32073,7 +32085,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32357,10 +32369,10 @@
         <v>2.25</v>
       </c>
       <c r="AP151">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ151">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR151">
         <v>2.48</v>
@@ -32485,7 +32497,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32769,7 +32781,7 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ153">
         <v>0.9</v>
@@ -32897,7 +32909,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33103,7 +33115,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33515,7 +33527,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33721,7 +33733,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33799,7 +33811,7 @@
         <v>2</v>
       </c>
       <c r="AP158">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ158">
         <v>1.91</v>
@@ -33927,7 +33939,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34339,7 +34351,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34420,7 +34432,7 @@
         <v>2</v>
       </c>
       <c r="AQ161">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR161">
         <v>1.8</v>
@@ -34545,7 +34557,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34623,7 +34635,7 @@
         <v>0.33</v>
       </c>
       <c r="AP162">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ162">
         <v>0.55</v>
@@ -34751,7 +34763,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35163,7 +35175,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35241,10 +35253,10 @@
         <v>2</v>
       </c>
       <c r="AP165">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ165">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR165">
         <v>1.19</v>
@@ -35450,7 +35462,7 @@
         <v>2</v>
       </c>
       <c r="AQ166">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR166">
         <v>1.78</v>
@@ -35575,7 +35587,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35653,7 +35665,7 @@
         <v>1.44</v>
       </c>
       <c r="AP167">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ167">
         <v>1.25</v>
@@ -35781,7 +35793,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -35987,7 +35999,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36193,7 +36205,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36686,7 +36698,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ172">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR172">
         <v>1.45</v>
@@ -36811,7 +36823,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -36889,7 +36901,7 @@
         <v>0.78</v>
       </c>
       <c r="AP173">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ173">
         <v>0.64</v>
@@ -37223,7 +37235,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37635,7 +37647,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37841,7 +37853,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37922,7 +37934,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ178">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR178">
         <v>1.43</v>
@@ -38125,7 +38137,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ179">
         <v>0.8</v>
@@ -38253,7 +38265,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38334,7 +38346,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ180">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AR180">
         <v>1.23</v>
@@ -38459,7 +38471,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38665,7 +38677,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38871,7 +38883,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39158,7 +39170,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ184">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR184">
         <v>1.78</v>
@@ -39283,7 +39295,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39570,7 +39582,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ186">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR186">
         <v>1.58</v>
@@ -39695,7 +39707,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39773,7 +39785,7 @@
         <v>1.8</v>
       </c>
       <c r="AP187">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ187">
         <v>1.91</v>
@@ -39901,7 +39913,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40107,7 +40119,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40185,7 +40197,7 @@
         <v>1.1</v>
       </c>
       <c r="AP189">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ189">
         <v>1.09</v>
@@ -41137,7 +41149,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41549,7 +41561,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41912,6 +41924,624 @@
       </c>
       <c r="BP197">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7466258</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45703.52083333334</v>
+      </c>
+      <c r="F198">
+        <v>23</v>
+      </c>
+      <c r="G198" t="s">
+        <v>74</v>
+      </c>
+      <c r="H198" t="s">
+        <v>76</v>
+      </c>
+      <c r="I198">
+        <v>1</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>2</v>
+      </c>
+      <c r="L198">
+        <v>2</v>
+      </c>
+      <c r="M198">
+        <v>2</v>
+      </c>
+      <c r="N198">
+        <v>4</v>
+      </c>
+      <c r="O198" t="s">
+        <v>226</v>
+      </c>
+      <c r="P198" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q198">
+        <v>1.8</v>
+      </c>
+      <c r="R198">
+        <v>2.75</v>
+      </c>
+      <c r="S198">
+        <v>6.5</v>
+      </c>
+      <c r="T198">
+        <v>1.22</v>
+      </c>
+      <c r="U198">
+        <v>4</v>
+      </c>
+      <c r="V198">
+        <v>2</v>
+      </c>
+      <c r="W198">
+        <v>1.73</v>
+      </c>
+      <c r="X198">
+        <v>4.33</v>
+      </c>
+      <c r="Y198">
+        <v>1.2</v>
+      </c>
+      <c r="Z198">
+        <v>1.34</v>
+      </c>
+      <c r="AA198">
+        <v>6</v>
+      </c>
+      <c r="AB198">
+        <v>8.1</v>
+      </c>
+      <c r="AC198">
+        <v>1.01</v>
+      </c>
+      <c r="AD198">
+        <v>21</v>
+      </c>
+      <c r="AE198">
+        <v>1.11</v>
+      </c>
+      <c r="AF198">
+        <v>6.28</v>
+      </c>
+      <c r="AG198">
+        <v>1.37</v>
+      </c>
+      <c r="AH198">
+        <v>2.94</v>
+      </c>
+      <c r="AI198">
+        <v>1.62</v>
+      </c>
+      <c r="AJ198">
+        <v>2.2</v>
+      </c>
+      <c r="AK198">
+        <v>1.09</v>
+      </c>
+      <c r="AL198">
+        <v>1.14</v>
+      </c>
+      <c r="AM198">
+        <v>3.2</v>
+      </c>
+      <c r="AN198">
+        <v>2.64</v>
+      </c>
+      <c r="AO198">
+        <v>2.27</v>
+      </c>
+      <c r="AP198">
+        <v>2.5</v>
+      </c>
+      <c r="AQ198">
+        <v>2.17</v>
+      </c>
+      <c r="AR198">
+        <v>2.36</v>
+      </c>
+      <c r="AS198">
+        <v>1.4</v>
+      </c>
+      <c r="AT198">
+        <v>3.76</v>
+      </c>
+      <c r="AU198">
+        <v>17</v>
+      </c>
+      <c r="AV198">
+        <v>3</v>
+      </c>
+      <c r="AW198">
+        <v>18</v>
+      </c>
+      <c r="AX198">
+        <v>10</v>
+      </c>
+      <c r="AY198">
+        <v>41</v>
+      </c>
+      <c r="AZ198">
+        <v>15</v>
+      </c>
+      <c r="BA198">
+        <v>9</v>
+      </c>
+      <c r="BB198">
+        <v>5</v>
+      </c>
+      <c r="BC198">
+        <v>14</v>
+      </c>
+      <c r="BD198">
+        <v>1.18</v>
+      </c>
+      <c r="BE198">
+        <v>9</v>
+      </c>
+      <c r="BF198">
+        <v>5.3</v>
+      </c>
+      <c r="BG198">
+        <v>1.21</v>
+      </c>
+      <c r="BH198">
+        <v>3.8</v>
+      </c>
+      <c r="BI198">
+        <v>1.38</v>
+      </c>
+      <c r="BJ198">
+        <v>2.7</v>
+      </c>
+      <c r="BK198">
+        <v>1.63</v>
+      </c>
+      <c r="BL198">
+        <v>2.12</v>
+      </c>
+      <c r="BM198">
+        <v>1.98</v>
+      </c>
+      <c r="BN198">
+        <v>1.72</v>
+      </c>
+      <c r="BO198">
+        <v>2.48</v>
+      </c>
+      <c r="BP198">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7466256</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45703.61458333334</v>
+      </c>
+      <c r="F199">
+        <v>23</v>
+      </c>
+      <c r="G199" t="s">
+        <v>87</v>
+      </c>
+      <c r="H199" t="s">
+        <v>71</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="N199">
+        <v>0</v>
+      </c>
+      <c r="O199" t="s">
+        <v>91</v>
+      </c>
+      <c r="P199" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q199">
+        <v>5</v>
+      </c>
+      <c r="R199">
+        <v>2.4</v>
+      </c>
+      <c r="S199">
+        <v>2.2</v>
+      </c>
+      <c r="T199">
+        <v>1.3</v>
+      </c>
+      <c r="U199">
+        <v>3.4</v>
+      </c>
+      <c r="V199">
+        <v>2.5</v>
+      </c>
+      <c r="W199">
+        <v>1.5</v>
+      </c>
+      <c r="X199">
+        <v>6</v>
+      </c>
+      <c r="Y199">
+        <v>1.13</v>
+      </c>
+      <c r="Z199">
+        <v>6.2</v>
+      </c>
+      <c r="AA199">
+        <v>5</v>
+      </c>
+      <c r="AB199">
+        <v>1.48</v>
+      </c>
+      <c r="AC199">
+        <v>1.02</v>
+      </c>
+      <c r="AD199">
+        <v>17</v>
+      </c>
+      <c r="AE199">
+        <v>1.19</v>
+      </c>
+      <c r="AF199">
+        <v>4.45</v>
+      </c>
+      <c r="AG199">
+        <v>1.6</v>
+      </c>
+      <c r="AH199">
+        <v>2.25</v>
+      </c>
+      <c r="AI199">
+        <v>1.7</v>
+      </c>
+      <c r="AJ199">
+        <v>2.05</v>
+      </c>
+      <c r="AK199">
+        <v>2.2</v>
+      </c>
+      <c r="AL199">
+        <v>1.22</v>
+      </c>
+      <c r="AM199">
+        <v>1.18</v>
+      </c>
+      <c r="AN199">
+        <v>1.73</v>
+      </c>
+      <c r="AO199">
+        <v>1.73</v>
+      </c>
+      <c r="AP199">
+        <v>1.67</v>
+      </c>
+      <c r="AQ199">
+        <v>1.67</v>
+      </c>
+      <c r="AR199">
+        <v>1.41</v>
+      </c>
+      <c r="AS199">
+        <v>1.91</v>
+      </c>
+      <c r="AT199">
+        <v>3.32</v>
+      </c>
+      <c r="AU199">
+        <v>3</v>
+      </c>
+      <c r="AV199">
+        <v>7</v>
+      </c>
+      <c r="AW199">
+        <v>9</v>
+      </c>
+      <c r="AX199">
+        <v>18</v>
+      </c>
+      <c r="AY199">
+        <v>14</v>
+      </c>
+      <c r="AZ199">
+        <v>29</v>
+      </c>
+      <c r="BA199">
+        <v>6</v>
+      </c>
+      <c r="BB199">
+        <v>5</v>
+      </c>
+      <c r="BC199">
+        <v>11</v>
+      </c>
+      <c r="BD199">
+        <v>3.45</v>
+      </c>
+      <c r="BE199">
+        <v>7.5</v>
+      </c>
+      <c r="BF199">
+        <v>1.35</v>
+      </c>
+      <c r="BG199">
+        <v>1.21</v>
+      </c>
+      <c r="BH199">
+        <v>3.8</v>
+      </c>
+      <c r="BI199">
+        <v>1.38</v>
+      </c>
+      <c r="BJ199">
+        <v>2.7</v>
+      </c>
+      <c r="BK199">
+        <v>1.64</v>
+      </c>
+      <c r="BL199">
+        <v>2.1</v>
+      </c>
+      <c r="BM199">
+        <v>2</v>
+      </c>
+      <c r="BN199">
+        <v>1.71</v>
+      </c>
+      <c r="BO199">
+        <v>2.5</v>
+      </c>
+      <c r="BP199">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7466259</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45703.70833333334</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>86</v>
+      </c>
+      <c r="H200" t="s">
+        <v>70</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>3</v>
+      </c>
+      <c r="K200">
+        <v>3</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="M200">
+        <v>3</v>
+      </c>
+      <c r="N200">
+        <v>4</v>
+      </c>
+      <c r="O200" t="s">
+        <v>227</v>
+      </c>
+      <c r="P200" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q200">
+        <v>3.25</v>
+      </c>
+      <c r="R200">
+        <v>1.95</v>
+      </c>
+      <c r="S200">
+        <v>3.75</v>
+      </c>
+      <c r="T200">
+        <v>1.53</v>
+      </c>
+      <c r="U200">
+        <v>2.38</v>
+      </c>
+      <c r="V200">
+        <v>3.5</v>
+      </c>
+      <c r="W200">
+        <v>1.29</v>
+      </c>
+      <c r="X200">
+        <v>11</v>
+      </c>
+      <c r="Y200">
+        <v>1.05</v>
+      </c>
+      <c r="Z200">
+        <v>2.58</v>
+      </c>
+      <c r="AA200">
+        <v>3.21</v>
+      </c>
+      <c r="AB200">
+        <v>2.97</v>
+      </c>
+      <c r="AC200">
+        <v>1.07</v>
+      </c>
+      <c r="AD200">
+        <v>7.61</v>
+      </c>
+      <c r="AE200">
+        <v>1.43</v>
+      </c>
+      <c r="AF200">
+        <v>2.75</v>
+      </c>
+      <c r="AG200">
+        <v>2.1</v>
+      </c>
+      <c r="AH200">
+        <v>1.67</v>
+      </c>
+      <c r="AI200">
+        <v>2</v>
+      </c>
+      <c r="AJ200">
+        <v>1.75</v>
+      </c>
+      <c r="AK200">
+        <v>1.37</v>
+      </c>
+      <c r="AL200">
+        <v>1.34</v>
+      </c>
+      <c r="AM200">
+        <v>1.55</v>
+      </c>
+      <c r="AN200">
+        <v>1.09</v>
+      </c>
+      <c r="AO200">
+        <v>0.45</v>
+      </c>
+      <c r="AP200">
+        <v>1</v>
+      </c>
+      <c r="AQ200">
+        <v>0.67</v>
+      </c>
+      <c r="AR200">
+        <v>1.12</v>
+      </c>
+      <c r="AS200">
+        <v>1.09</v>
+      </c>
+      <c r="AT200">
+        <v>2.21</v>
+      </c>
+      <c r="AU200">
+        <v>8</v>
+      </c>
+      <c r="AV200">
+        <v>10</v>
+      </c>
+      <c r="AW200">
+        <v>7</v>
+      </c>
+      <c r="AX200">
+        <v>7</v>
+      </c>
+      <c r="AY200">
+        <v>16</v>
+      </c>
+      <c r="AZ200">
+        <v>19</v>
+      </c>
+      <c r="BA200">
+        <v>5</v>
+      </c>
+      <c r="BB200">
+        <v>5</v>
+      </c>
+      <c r="BC200">
+        <v>10</v>
+      </c>
+      <c r="BD200">
+        <v>1.9</v>
+      </c>
+      <c r="BE200">
+        <v>6.5</v>
+      </c>
+      <c r="BF200">
+        <v>2.08</v>
+      </c>
+      <c r="BG200">
+        <v>1.3</v>
+      </c>
+      <c r="BH200">
+        <v>3.15</v>
+      </c>
+      <c r="BI200">
+        <v>1.53</v>
+      </c>
+      <c r="BJ200">
+        <v>2.3</v>
+      </c>
+      <c r="BK200">
+        <v>1.86</v>
+      </c>
+      <c r="BL200">
+        <v>1.82</v>
+      </c>
+      <c r="BM200">
+        <v>2.33</v>
+      </c>
+      <c r="BN200">
+        <v>1.5</v>
+      </c>
+      <c r="BO200">
+        <v>3.05</v>
+      </c>
+      <c r="BP200">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="326">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -700,6 +700,18 @@
     <t>['49']</t>
   </si>
   <si>
+    <t>['3', '90+4']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['28', '83']</t>
+  </si>
+  <si>
+    <t>['17', '42', '56', '66']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -731,9 +743,6 @@
   </si>
   <si>
     <t>['48', '89']</t>
-  </si>
-  <si>
-    <t>['11']</t>
   </si>
   <si>
     <t>['33', '70']</t>
@@ -980,6 +989,9 @@
   </si>
   <si>
     <t>['5', '17', '21']</t>
+  </si>
+  <si>
+    <t>['45', '74']</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2009,7 +2021,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2087,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>1.25</v>
@@ -2421,7 +2433,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2502,7 +2514,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ6">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2708,7 +2720,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ7">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3039,7 +3051,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3323,10 +3335,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ10">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3532,7 +3544,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ11">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3941,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -4275,7 +4287,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4481,7 +4493,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4687,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4765,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ17">
         <v>1.67</v>
@@ -5383,7 +5395,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20">
         <v>0.73</v>
@@ -5511,7 +5523,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5717,7 +5729,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6622,7 +6634,7 @@
         <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6747,7 +6759,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7159,7 +7171,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7571,7 +7583,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7777,7 +7789,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8061,10 +8073,10 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ33">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR33">
         <v>0.7</v>
@@ -8679,7 +8691,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ36">
         <v>0.73</v>
@@ -8807,7 +8819,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9219,7 +9231,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9300,7 +9312,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ39">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR39">
         <v>1.82</v>
@@ -9425,7 +9437,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9712,7 +9724,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -9918,7 +9930,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR42">
         <v>1.23</v>
@@ -10121,10 +10133,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ43">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR43">
         <v>2.19</v>
@@ -10327,7 +10339,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10455,7 +10467,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10533,7 +10545,7 @@
         <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ45">
         <v>1.91</v>
@@ -10661,7 +10673,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10867,7 +10879,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11073,7 +11085,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11279,7 +11291,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11357,10 +11369,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ49">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR49">
         <v>1.18</v>
@@ -11485,7 +11497,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11691,7 +11703,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12103,7 +12115,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12309,7 +12321,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12390,7 +12402,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR54">
         <v>1.37</v>
@@ -12515,7 +12527,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12721,7 +12733,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -12799,7 +12811,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ56">
         <v>1.67</v>
@@ -13211,10 +13223,10 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ58">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR58">
         <v>1.08</v>
@@ -13417,7 +13429,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ59">
         <v>0.64</v>
@@ -13751,7 +13763,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13957,7 +13969,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14781,7 +14793,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14862,7 +14874,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ66">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR66">
         <v>1.08</v>
@@ -14987,7 +14999,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15068,7 +15080,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15605,7 +15617,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15683,7 +15695,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ70">
         <v>0.67</v>
@@ -16017,7 +16029,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16098,7 +16110,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ72">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -16223,7 +16235,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16507,10 +16519,10 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR74">
         <v>1.44</v>
@@ -16841,7 +16853,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17459,7 +17471,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17665,7 +17677,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17743,7 +17755,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ80">
         <v>0.64</v>
@@ -18489,7 +18501,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18570,7 +18582,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ84">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR84">
         <v>1.12</v>
@@ -18901,7 +18913,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19185,10 +19197,10 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ87">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -19391,7 +19403,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ88">
         <v>1.09</v>
@@ -19519,7 +19531,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19725,7 +19737,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -20343,7 +20355,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20421,7 +20433,7 @@
         <v>3</v>
       </c>
       <c r="AP93">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ93">
         <v>2</v>
@@ -20549,7 +20561,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20836,7 +20848,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ95">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR95">
         <v>1.29</v>
@@ -20961,7 +20973,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21245,7 +21257,7 @@
         <v>0.8</v>
       </c>
       <c r="AP97">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ97">
         <v>0.67</v>
@@ -21373,7 +21385,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21660,7 +21672,7 @@
         <v>1</v>
       </c>
       <c r="AQ99">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21866,7 +21878,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ100">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR100">
         <v>1.37</v>
@@ -22275,7 +22287,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22403,7 +22415,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22609,7 +22621,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22815,7 +22827,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23021,7 +23033,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23099,7 +23111,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ106">
         <v>2.09</v>
@@ -23433,7 +23445,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23720,7 +23732,7 @@
         <v>2</v>
       </c>
       <c r="AQ109">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -23926,7 +23938,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR110">
         <v>1.62</v>
@@ -24051,7 +24063,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24132,7 +24144,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ111">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR111">
         <v>1.37</v>
@@ -24463,7 +24475,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24669,7 +24681,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24747,7 +24759,7 @@
         <v>2.6</v>
       </c>
       <c r="AP114">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ114">
         <v>2.17</v>
@@ -24875,7 +24887,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25081,7 +25093,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25365,7 +25377,7 @@
         <v>0.5</v>
       </c>
       <c r="AP117">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ117">
         <v>0.73</v>
@@ -25574,7 +25586,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ118">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR118">
         <v>1.65</v>
@@ -25780,7 +25792,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ119">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR119">
         <v>1.34</v>
@@ -26395,7 +26407,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26523,7 +26535,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26729,7 +26741,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26807,7 +26819,7 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ124">
         <v>1.1</v>
@@ -27016,7 +27028,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ125">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR125">
         <v>1.92</v>
@@ -27141,7 +27153,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27219,7 +27231,7 @@
         <v>1.83</v>
       </c>
       <c r="AP126">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ126">
         <v>2.09</v>
@@ -27347,7 +27359,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27425,7 +27437,7 @@
         <v>2.67</v>
       </c>
       <c r="AP127">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ127">
         <v>2.17</v>
@@ -27965,7 +27977,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28171,7 +28183,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28377,7 +28389,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28789,7 +28801,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28870,7 +28882,7 @@
         <v>1</v>
       </c>
       <c r="AQ134">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR134">
         <v>1.12</v>
@@ -29201,7 +29213,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29407,7 +29419,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29485,7 +29497,7 @@
         <v>1.14</v>
       </c>
       <c r="AP137">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ137">
         <v>1.09</v>
@@ -29819,7 +29831,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29900,7 +29912,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ139">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR139">
         <v>1.21</v>
@@ -30025,7 +30037,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30106,7 +30118,7 @@
         <v>2</v>
       </c>
       <c r="AQ140">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR140">
         <v>1.81</v>
@@ -30231,7 +30243,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30515,7 +30527,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ142">
         <v>1</v>
@@ -30721,7 +30733,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ143">
         <v>0.67</v>
@@ -30927,10 +30939,10 @@
         <v>0.29</v>
       </c>
       <c r="AP144">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ144">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR144">
         <v>1.74</v>
@@ -31055,7 +31067,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31261,7 +31273,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31754,7 +31766,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ148">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR148">
         <v>1.21</v>
@@ -32085,7 +32097,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32497,7 +32509,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32909,7 +32921,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33115,7 +33127,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33399,10 +33411,10 @@
         <v>0.25</v>
       </c>
       <c r="AP156">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ156">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR156">
         <v>1.73</v>
@@ -33527,7 +33539,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33605,7 +33617,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ157">
         <v>0.9</v>
@@ -33733,7 +33745,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33939,7 +33951,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34017,7 +34029,7 @@
         <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ159">
         <v>1.09</v>
@@ -34226,7 +34238,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ160">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR160">
         <v>1.27</v>
@@ -34351,7 +34363,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34557,7 +34569,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34638,7 +34650,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ162">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR162">
         <v>1.26</v>
@@ -34763,7 +34775,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -34841,7 +34853,7 @@
         <v>2.33</v>
       </c>
       <c r="AP163">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ163">
         <v>2</v>
@@ -35175,7 +35187,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35587,7 +35599,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35793,7 +35805,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -35874,7 +35886,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ168">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR168">
         <v>1.26</v>
@@ -35999,7 +36011,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36205,7 +36217,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36283,7 +36295,7 @@
         <v>1.11</v>
       </c>
       <c r="AP170">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36492,7 +36504,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ171">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR171">
         <v>1.53</v>
@@ -36823,7 +36835,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37110,7 +37122,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ174">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR174">
         <v>1.36</v>
@@ -37235,7 +37247,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37647,7 +37659,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37853,7 +37865,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38140,7 +38152,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ179">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR179">
         <v>1.35</v>
@@ -38265,7 +38277,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38343,7 +38355,7 @@
         <v>2.4</v>
       </c>
       <c r="AP180">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ180">
         <v>2.17</v>
@@ -38471,7 +38483,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38677,7 +38689,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38755,7 +38767,7 @@
         <v>2.1</v>
       </c>
       <c r="AP182">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ182">
         <v>2</v>
@@ -38883,7 +38895,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -38964,7 +38976,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ183">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR183">
         <v>1.31</v>
@@ -39167,7 +39179,7 @@
         <v>1.9</v>
       </c>
       <c r="AP184">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ184">
         <v>1.67</v>
@@ -39295,7 +39307,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39707,7 +39719,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39913,7 +39925,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40119,7 +40131,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40818,7 +40830,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ192">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR192">
         <v>1.52</v>
@@ -41149,7 +41161,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41561,7 +41573,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41973,7 +41985,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42385,7 +42397,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42542,6 +42554,830 @@
       </c>
       <c r="BP200">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7466255</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45704.34375</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>72</v>
+      </c>
+      <c r="H201" t="s">
+        <v>73</v>
+      </c>
+      <c r="I201">
+        <v>1</v>
+      </c>
+      <c r="J201">
+        <v>1</v>
+      </c>
+      <c r="K201">
+        <v>2</v>
+      </c>
+      <c r="L201">
+        <v>2</v>
+      </c>
+      <c r="M201">
+        <v>2</v>
+      </c>
+      <c r="N201">
+        <v>4</v>
+      </c>
+      <c r="O201" t="s">
+        <v>228</v>
+      </c>
+      <c r="P201" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q201">
+        <v>2.1</v>
+      </c>
+      <c r="R201">
+        <v>2.3</v>
+      </c>
+      <c r="S201">
+        <v>6</v>
+      </c>
+      <c r="T201">
+        <v>1.36</v>
+      </c>
+      <c r="U201">
+        <v>3</v>
+      </c>
+      <c r="V201">
+        <v>2.75</v>
+      </c>
+      <c r="W201">
+        <v>1.4</v>
+      </c>
+      <c r="X201">
+        <v>7</v>
+      </c>
+      <c r="Y201">
+        <v>1.1</v>
+      </c>
+      <c r="Z201">
+        <v>1.54</v>
+      </c>
+      <c r="AA201">
+        <v>4.4</v>
+      </c>
+      <c r="AB201">
+        <v>6.3</v>
+      </c>
+      <c r="AC201">
+        <v>1.05</v>
+      </c>
+      <c r="AD201">
+        <v>12</v>
+      </c>
+      <c r="AE201">
+        <v>1.28</v>
+      </c>
+      <c r="AF201">
+        <v>3.52</v>
+      </c>
+      <c r="AG201">
+        <v>1.81</v>
+      </c>
+      <c r="AH201">
+        <v>2.01</v>
+      </c>
+      <c r="AI201">
+        <v>1.95</v>
+      </c>
+      <c r="AJ201">
+        <v>1.8</v>
+      </c>
+      <c r="AK201">
+        <v>1.13</v>
+      </c>
+      <c r="AL201">
+        <v>1.21</v>
+      </c>
+      <c r="AM201">
+        <v>2.45</v>
+      </c>
+      <c r="AN201">
+        <v>1.36</v>
+      </c>
+      <c r="AO201">
+        <v>0.6</v>
+      </c>
+      <c r="AP201">
+        <v>1.33</v>
+      </c>
+      <c r="AQ201">
+        <v>0.64</v>
+      </c>
+      <c r="AR201">
+        <v>1.59</v>
+      </c>
+      <c r="AS201">
+        <v>1.13</v>
+      </c>
+      <c r="AT201">
+        <v>2.72</v>
+      </c>
+      <c r="AU201">
+        <v>5</v>
+      </c>
+      <c r="AV201">
+        <v>6</v>
+      </c>
+      <c r="AW201">
+        <v>4</v>
+      </c>
+      <c r="AX201">
+        <v>8</v>
+      </c>
+      <c r="AY201">
+        <v>12</v>
+      </c>
+      <c r="AZ201">
+        <v>18</v>
+      </c>
+      <c r="BA201">
+        <v>4</v>
+      </c>
+      <c r="BB201">
+        <v>7</v>
+      </c>
+      <c r="BC201">
+        <v>11</v>
+      </c>
+      <c r="BD201">
+        <v>1.28</v>
+      </c>
+      <c r="BE201">
+        <v>7.5</v>
+      </c>
+      <c r="BF201">
+        <v>3.95</v>
+      </c>
+      <c r="BG201">
+        <v>1.17</v>
+      </c>
+      <c r="BH201">
+        <v>4.35</v>
+      </c>
+      <c r="BI201">
+        <v>1.3</v>
+      </c>
+      <c r="BJ201">
+        <v>3.05</v>
+      </c>
+      <c r="BK201">
+        <v>1.52</v>
+      </c>
+      <c r="BL201">
+        <v>2.33</v>
+      </c>
+      <c r="BM201">
+        <v>1.83</v>
+      </c>
+      <c r="BN201">
+        <v>1.85</v>
+      </c>
+      <c r="BO201">
+        <v>2.23</v>
+      </c>
+      <c r="BP201">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7466257</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45704.4375</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>85</v>
+      </c>
+      <c r="H202" t="s">
+        <v>80</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>1</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>2</v>
+      </c>
+      <c r="O202" t="s">
+        <v>229</v>
+      </c>
+      <c r="P202" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q202">
+        <v>2.88</v>
+      </c>
+      <c r="R202">
+        <v>2.25</v>
+      </c>
+      <c r="S202">
+        <v>3.5</v>
+      </c>
+      <c r="T202">
+        <v>1.36</v>
+      </c>
+      <c r="U202">
+        <v>3</v>
+      </c>
+      <c r="V202">
+        <v>2.63</v>
+      </c>
+      <c r="W202">
+        <v>1.44</v>
+      </c>
+      <c r="X202">
+        <v>7</v>
+      </c>
+      <c r="Y202">
+        <v>1.1</v>
+      </c>
+      <c r="Z202">
+        <v>2.35</v>
+      </c>
+      <c r="AA202">
+        <v>3.59</v>
+      </c>
+      <c r="AB202">
+        <v>3.03</v>
+      </c>
+      <c r="AC202">
+        <v>1.04</v>
+      </c>
+      <c r="AD202">
+        <v>13</v>
+      </c>
+      <c r="AE202">
+        <v>1.24</v>
+      </c>
+      <c r="AF202">
+        <v>3.89</v>
+      </c>
+      <c r="AG202">
+        <v>1.85</v>
+      </c>
+      <c r="AH202">
+        <v>1.96</v>
+      </c>
+      <c r="AI202">
+        <v>1.62</v>
+      </c>
+      <c r="AJ202">
+        <v>2.2</v>
+      </c>
+      <c r="AK202">
+        <v>1.37</v>
+      </c>
+      <c r="AL202">
+        <v>1.28</v>
+      </c>
+      <c r="AM202">
+        <v>1.62</v>
+      </c>
+      <c r="AN202">
+        <v>1.45</v>
+      </c>
+      <c r="AO202">
+        <v>0.55</v>
+      </c>
+      <c r="AP202">
+        <v>1.42</v>
+      </c>
+      <c r="AQ202">
+        <v>0.58</v>
+      </c>
+      <c r="AR202">
+        <v>1.27</v>
+      </c>
+      <c r="AS202">
+        <v>1.31</v>
+      </c>
+      <c r="AT202">
+        <v>2.58</v>
+      </c>
+      <c r="AU202">
+        <v>6</v>
+      </c>
+      <c r="AV202">
+        <v>4</v>
+      </c>
+      <c r="AW202">
+        <v>2</v>
+      </c>
+      <c r="AX202">
+        <v>9</v>
+      </c>
+      <c r="AY202">
+        <v>8</v>
+      </c>
+      <c r="AZ202">
+        <v>16</v>
+      </c>
+      <c r="BA202">
+        <v>3</v>
+      </c>
+      <c r="BB202">
+        <v>3</v>
+      </c>
+      <c r="BC202">
+        <v>6</v>
+      </c>
+      <c r="BD202">
+        <v>2.08</v>
+      </c>
+      <c r="BE202">
+        <v>6.5</v>
+      </c>
+      <c r="BF202">
+        <v>1.9</v>
+      </c>
+      <c r="BG202">
+        <v>1.24</v>
+      </c>
+      <c r="BH202">
+        <v>3.55</v>
+      </c>
+      <c r="BI202">
+        <v>1.41</v>
+      </c>
+      <c r="BJ202">
+        <v>2.63</v>
+      </c>
+      <c r="BK202">
+        <v>1.68</v>
+      </c>
+      <c r="BL202">
+        <v>2.02</v>
+      </c>
+      <c r="BM202">
+        <v>2.08</v>
+      </c>
+      <c r="BN202">
+        <v>1.65</v>
+      </c>
+      <c r="BO202">
+        <v>2.65</v>
+      </c>
+      <c r="BP202">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7466253</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45704.4375</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>81</v>
+      </c>
+      <c r="H203" t="s">
+        <v>83</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>1</v>
+      </c>
+      <c r="L203">
+        <v>2</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>2</v>
+      </c>
+      <c r="O203" t="s">
+        <v>230</v>
+      </c>
+      <c r="P203" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q203">
+        <v>1.83</v>
+      </c>
+      <c r="R203">
+        <v>2.63</v>
+      </c>
+      <c r="S203">
+        <v>6.5</v>
+      </c>
+      <c r="T203">
+        <v>1.25</v>
+      </c>
+      <c r="U203">
+        <v>3.75</v>
+      </c>
+      <c r="V203">
+        <v>2.1</v>
+      </c>
+      <c r="W203">
+        <v>1.67</v>
+      </c>
+      <c r="X203">
+        <v>5</v>
+      </c>
+      <c r="Y203">
+        <v>1.17</v>
+      </c>
+      <c r="Z203">
+        <v>1.38</v>
+      </c>
+      <c r="AA203">
+        <v>5.6</v>
+      </c>
+      <c r="AB203">
+        <v>7.5</v>
+      </c>
+      <c r="AC203">
+        <v>1.01</v>
+      </c>
+      <c r="AD203">
+        <v>21</v>
+      </c>
+      <c r="AE203">
+        <v>1.14</v>
+      </c>
+      <c r="AF203">
+        <v>5.38</v>
+      </c>
+      <c r="AG203">
+        <v>1.42</v>
+      </c>
+      <c r="AH203">
+        <v>2.74</v>
+      </c>
+      <c r="AI203">
+        <v>1.7</v>
+      </c>
+      <c r="AJ203">
+        <v>2.05</v>
+      </c>
+      <c r="AK203">
+        <v>1.1</v>
+      </c>
+      <c r="AL203">
+        <v>1.15</v>
+      </c>
+      <c r="AM203">
+        <v>3</v>
+      </c>
+      <c r="AN203">
+        <v>2.33</v>
+      </c>
+      <c r="AO203">
+        <v>0.55</v>
+      </c>
+      <c r="AP203">
+        <v>2.4</v>
+      </c>
+      <c r="AQ203">
+        <v>0.5</v>
+      </c>
+      <c r="AR203">
+        <v>2.08</v>
+      </c>
+      <c r="AS203">
+        <v>1.29</v>
+      </c>
+      <c r="AT203">
+        <v>3.37</v>
+      </c>
+      <c r="AU203">
+        <v>5</v>
+      </c>
+      <c r="AV203">
+        <v>5</v>
+      </c>
+      <c r="AW203">
+        <v>15</v>
+      </c>
+      <c r="AX203">
+        <v>8</v>
+      </c>
+      <c r="AY203">
+        <v>28</v>
+      </c>
+      <c r="AZ203">
+        <v>16</v>
+      </c>
+      <c r="BA203">
+        <v>8</v>
+      </c>
+      <c r="BB203">
+        <v>2</v>
+      </c>
+      <c r="BC203">
+        <v>10</v>
+      </c>
+      <c r="BD203">
+        <v>1.13</v>
+      </c>
+      <c r="BE203">
+        <v>10</v>
+      </c>
+      <c r="BF203">
+        <v>6.1</v>
+      </c>
+      <c r="BG203">
+        <v>1.14</v>
+      </c>
+      <c r="BH203">
+        <v>4.8</v>
+      </c>
+      <c r="BI203">
+        <v>1.26</v>
+      </c>
+      <c r="BJ203">
+        <v>3.4</v>
+      </c>
+      <c r="BK203">
+        <v>1.44</v>
+      </c>
+      <c r="BL203">
+        <v>2.55</v>
+      </c>
+      <c r="BM203">
+        <v>1.68</v>
+      </c>
+      <c r="BN203">
+        <v>2.04</v>
+      </c>
+      <c r="BO203">
+        <v>2.04</v>
+      </c>
+      <c r="BP203">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7466251</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45704.53125</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>78</v>
+      </c>
+      <c r="H204" t="s">
+        <v>84</v>
+      </c>
+      <c r="I204">
+        <v>2</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>2</v>
+      </c>
+      <c r="L204">
+        <v>4</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="N204">
+        <v>4</v>
+      </c>
+      <c r="O204" t="s">
+        <v>231</v>
+      </c>
+      <c r="P204" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q204">
+        <v>1.62</v>
+      </c>
+      <c r="R204">
+        <v>2.88</v>
+      </c>
+      <c r="S204">
+        <v>9</v>
+      </c>
+      <c r="T204">
+        <v>1.22</v>
+      </c>
+      <c r="U204">
+        <v>4</v>
+      </c>
+      <c r="V204">
+        <v>2.1</v>
+      </c>
+      <c r="W204">
+        <v>1.67</v>
+      </c>
+      <c r="X204">
+        <v>4.5</v>
+      </c>
+      <c r="Y204">
+        <v>1.18</v>
+      </c>
+      <c r="Z204">
+        <v>1.22</v>
+      </c>
+      <c r="AA204">
+        <v>7.9</v>
+      </c>
+      <c r="AB204">
+        <v>12</v>
+      </c>
+      <c r="AC204">
+        <v>1.01</v>
+      </c>
+      <c r="AD204">
+        <v>23</v>
+      </c>
+      <c r="AE204">
+        <v>1.11</v>
+      </c>
+      <c r="AF204">
+        <v>6.28</v>
+      </c>
+      <c r="AG204">
+        <v>1.4</v>
+      </c>
+      <c r="AH204">
+        <v>2.82</v>
+      </c>
+      <c r="AI204">
+        <v>1.95</v>
+      </c>
+      <c r="AJ204">
+        <v>1.8</v>
+      </c>
+      <c r="AK204">
+        <v>1.04</v>
+      </c>
+      <c r="AL204">
+        <v>1.11</v>
+      </c>
+      <c r="AM204">
+        <v>4.2</v>
+      </c>
+      <c r="AN204">
+        <v>2.8</v>
+      </c>
+      <c r="AO204">
+        <v>0.8</v>
+      </c>
+      <c r="AP204">
+        <v>2.82</v>
+      </c>
+      <c r="AQ204">
+        <v>0.73</v>
+      </c>
+      <c r="AR204">
+        <v>1.82</v>
+      </c>
+      <c r="AS204">
+        <v>1.02</v>
+      </c>
+      <c r="AT204">
+        <v>2.84</v>
+      </c>
+      <c r="AU204">
+        <v>7</v>
+      </c>
+      <c r="AV204">
+        <v>5</v>
+      </c>
+      <c r="AW204">
+        <v>5</v>
+      </c>
+      <c r="AX204">
+        <v>4</v>
+      </c>
+      <c r="AY204">
+        <v>13</v>
+      </c>
+      <c r="AZ204">
+        <v>11</v>
+      </c>
+      <c r="BA204">
+        <v>5</v>
+      </c>
+      <c r="BB204">
+        <v>4</v>
+      </c>
+      <c r="BC204">
+        <v>9</v>
+      </c>
+      <c r="BD204">
+        <v>1.14</v>
+      </c>
+      <c r="BE204">
+        <v>9.5</v>
+      </c>
+      <c r="BF204">
+        <v>6.1</v>
+      </c>
+      <c r="BG204">
+        <v>1.24</v>
+      </c>
+      <c r="BH204">
+        <v>3.55</v>
+      </c>
+      <c r="BI204">
+        <v>1.41</v>
+      </c>
+      <c r="BJ204">
+        <v>2.63</v>
+      </c>
+      <c r="BK204">
+        <v>1.68</v>
+      </c>
+      <c r="BL204">
+        <v>2.04</v>
+      </c>
+      <c r="BM204">
+        <v>2.06</v>
+      </c>
+      <c r="BN204">
+        <v>1.66</v>
+      </c>
+      <c r="BO204">
+        <v>2.55</v>
+      </c>
+      <c r="BP204">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -42078,22 +42078,22 @@
         <v>3.76</v>
       </c>
       <c r="AU198">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AV198">
+        <v>4</v>
+      </c>
+      <c r="AW198">
+        <v>10</v>
+      </c>
+      <c r="AX198">
         <v>3</v>
       </c>
-      <c r="AW198">
-        <v>18</v>
-      </c>
-      <c r="AX198">
-        <v>10</v>
-      </c>
       <c r="AY198">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AZ198">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA198">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="327">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -712,6 +712,9 @@
     <t>['17', '42', '56', '66']</t>
   </si>
   <si>
+    <t>['33', '90+1']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1353,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1893,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ3">
         <v>1.09</v>
@@ -2021,7 +2024,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2433,7 +2436,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -3051,7 +3054,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3544,7 +3547,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ11">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4287,7 +4290,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4493,7 +4496,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4699,7 +4702,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5523,7 +5526,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5729,7 +5732,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6759,7 +6762,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7171,7 +7174,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7583,7 +7586,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8819,7 +8822,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9231,7 +9234,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9437,7 +9440,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9930,7 +9933,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR42">
         <v>1.23</v>
@@ -10467,7 +10470,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10673,7 +10676,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10879,7 +10882,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11085,7 +11088,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11291,7 +11294,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11497,7 +11500,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11703,7 +11706,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11987,7 +11990,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ52">
         <v>0.64</v>
@@ -12115,7 +12118,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12321,7 +12324,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12527,7 +12530,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12733,7 +12736,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13226,7 +13229,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ58">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR58">
         <v>1.08</v>
@@ -13763,7 +13766,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13969,7 +13972,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14793,7 +14796,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14999,7 +15002,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15283,7 +15286,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ68">
         <v>1.25</v>
@@ -15617,7 +15620,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -16029,7 +16032,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16110,7 +16113,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ72">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -16235,7 +16238,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16853,7 +16856,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17471,7 +17474,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17677,7 +17680,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18501,7 +18504,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18913,7 +18916,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19531,7 +19534,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19737,7 +19740,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19815,7 +19818,7 @@
         <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ90">
         <v>2.09</v>
@@ -20355,7 +20358,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20561,7 +20564,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20639,7 +20642,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ94">
         <v>1.91</v>
@@ -20973,7 +20976,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21385,7 +21388,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21672,7 +21675,7 @@
         <v>1</v>
       </c>
       <c r="AQ99">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -22415,7 +22418,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22621,7 +22624,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22827,7 +22830,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23033,7 +23036,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23445,7 +23448,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23732,7 +23735,7 @@
         <v>2</v>
       </c>
       <c r="AQ109">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -23935,7 +23938,7 @@
         <v>0</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ110">
         <v>0.58</v>
@@ -24063,7 +24066,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24475,7 +24478,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24681,7 +24684,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24887,7 +24890,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25093,7 +25096,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25792,7 +25795,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ119">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR119">
         <v>1.34</v>
@@ -26201,7 +26204,7 @@
         <v>0.83</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26535,7 +26538,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26741,7 +26744,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27153,7 +27156,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27359,7 +27362,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27977,7 +27980,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28183,7 +28186,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28389,7 +28392,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28801,7 +28804,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29213,7 +29216,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29831,7 +29834,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30037,7 +30040,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30115,7 +30118,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ140">
         <v>0.73</v>
@@ -30243,7 +30246,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30942,7 +30945,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ144">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR144">
         <v>1.74</v>
@@ -31067,7 +31070,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31273,7 +31276,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -32097,7 +32100,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32509,7 +32512,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32921,7 +32924,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33127,7 +33130,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33539,7 +33542,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33745,7 +33748,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33951,7 +33954,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34238,7 +34241,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ160">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR160">
         <v>1.27</v>
@@ -34363,7 +34366,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34441,7 +34444,7 @@
         <v>2.5</v>
       </c>
       <c r="AP161">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ161">
         <v>2.17</v>
@@ -34569,7 +34572,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34775,7 +34778,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35187,7 +35190,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35599,7 +35602,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35805,7 +35808,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36011,7 +36014,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36217,7 +36220,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36835,7 +36838,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37247,7 +37250,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37659,7 +37662,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37865,7 +37868,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38277,7 +38280,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38483,7 +38486,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38689,7 +38692,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38895,7 +38898,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39307,7 +39310,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39719,7 +39722,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39925,7 +39928,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40131,7 +40134,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40621,7 +40624,7 @@
         <v>1.2</v>
       </c>
       <c r="AP191">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ191">
         <v>1</v>
@@ -40830,7 +40833,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ192">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR192">
         <v>1.52</v>
@@ -41161,7 +41164,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41573,7 +41576,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41985,7 +41988,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42397,7 +42400,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42603,7 +42606,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42684,7 +42687,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ201">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR201">
         <v>1.59</v>
@@ -43377,6 +43380,212 @@
         <v>2.55</v>
       </c>
       <c r="BP204">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7466228</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45710.66666666666</v>
+      </c>
+      <c r="F205">
+        <v>20</v>
+      </c>
+      <c r="G205" t="s">
+        <v>71</v>
+      </c>
+      <c r="H205" t="s">
+        <v>73</v>
+      </c>
+      <c r="I205">
+        <v>1</v>
+      </c>
+      <c r="J205">
+        <v>1</v>
+      </c>
+      <c r="K205">
+        <v>2</v>
+      </c>
+      <c r="L205">
+        <v>2</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>3</v>
+      </c>
+      <c r="O205" t="s">
+        <v>232</v>
+      </c>
+      <c r="P205" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q205">
+        <v>1.57</v>
+      </c>
+      <c r="R205">
+        <v>2.88</v>
+      </c>
+      <c r="S205">
+        <v>10</v>
+      </c>
+      <c r="T205">
+        <v>1.22</v>
+      </c>
+      <c r="U205">
+        <v>4</v>
+      </c>
+      <c r="V205">
+        <v>2.1</v>
+      </c>
+      <c r="W205">
+        <v>1.67</v>
+      </c>
+      <c r="X205">
+        <v>4.5</v>
+      </c>
+      <c r="Y205">
+        <v>1.18</v>
+      </c>
+      <c r="Z205">
+        <v>1.2</v>
+      </c>
+      <c r="AA205">
+        <v>7.1</v>
+      </c>
+      <c r="AB205">
+        <v>17</v>
+      </c>
+      <c r="AC205">
+        <v>1.01</v>
+      </c>
+      <c r="AD205">
+        <v>23</v>
+      </c>
+      <c r="AE205">
+        <v>1.11</v>
+      </c>
+      <c r="AF205">
+        <v>6.25</v>
+      </c>
+      <c r="AG205">
+        <v>1.4</v>
+      </c>
+      <c r="AH205">
+        <v>2.82</v>
+      </c>
+      <c r="AI205">
+        <v>1.95</v>
+      </c>
+      <c r="AJ205">
+        <v>1.8</v>
+      </c>
+      <c r="AK205">
+        <v>1.03</v>
+      </c>
+      <c r="AL205">
+        <v>1.09</v>
+      </c>
+      <c r="AM205">
+        <v>4.8</v>
+      </c>
+      <c r="AN205">
+        <v>2</v>
+      </c>
+      <c r="AO205">
+        <v>0.64</v>
+      </c>
+      <c r="AP205">
+        <v>2.09</v>
+      </c>
+      <c r="AQ205">
+        <v>0.58</v>
+      </c>
+      <c r="AR205">
+        <v>1.87</v>
+      </c>
+      <c r="AS205">
+        <v>1.19</v>
+      </c>
+      <c r="AT205">
+        <v>3.06</v>
+      </c>
+      <c r="AU205">
+        <v>9</v>
+      </c>
+      <c r="AV205">
+        <v>5</v>
+      </c>
+      <c r="AW205">
+        <v>11</v>
+      </c>
+      <c r="AX205">
+        <v>9</v>
+      </c>
+      <c r="AY205">
+        <v>23</v>
+      </c>
+      <c r="AZ205">
+        <v>14</v>
+      </c>
+      <c r="BA205">
+        <v>7</v>
+      </c>
+      <c r="BB205">
+        <v>2</v>
+      </c>
+      <c r="BC205">
+        <v>9</v>
+      </c>
+      <c r="BD205">
+        <v>1.1</v>
+      </c>
+      <c r="BE205">
+        <v>11.5</v>
+      </c>
+      <c r="BF205">
+        <v>7</v>
+      </c>
+      <c r="BG205">
+        <v>1.25</v>
+      </c>
+      <c r="BH205">
+        <v>3.45</v>
+      </c>
+      <c r="BI205">
+        <v>1.44</v>
+      </c>
+      <c r="BJ205">
+        <v>2.55</v>
+      </c>
+      <c r="BK205">
+        <v>1.7</v>
+      </c>
+      <c r="BL205">
+        <v>2.02</v>
+      </c>
+      <c r="BM205">
+        <v>2.07</v>
+      </c>
+      <c r="BN205">
+        <v>1.66</v>
+      </c>
+      <c r="BO205">
+        <v>2.55</v>
+      </c>
+      <c r="BP205">
         <v>1.43</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="329">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,15 @@
     <t>['33', '90+1']</t>
   </si>
   <si>
+    <t>['19', '80']</t>
+  </si>
+  <si>
+    <t>['56', '86']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -914,9 +923,6 @@
   </si>
   <si>
     <t>['27', '47', '87']</t>
-  </si>
-  <si>
-    <t>['52']</t>
   </si>
   <si>
     <t>['23']</t>
@@ -1356,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2024,7 +2030,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2436,7 +2442,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -3054,7 +3060,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3135,7 +3141,7 @@
         <v>2</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3338,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ10">
         <v>0.58</v>
@@ -3956,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -4162,10 +4168,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ14">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4290,7 +4296,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4496,7 +4502,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4702,7 +4708,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4989,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5526,7 +5532,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5732,7 +5738,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6762,7 +6768,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7174,7 +7180,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7255,7 +7261,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ29">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR29">
         <v>2.19</v>
@@ -7586,7 +7592,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8285,7 +8291,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ34">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>2.85</v>
@@ -8491,7 +8497,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ35">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR35">
         <v>2.65</v>
@@ -8694,7 +8700,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ36">
         <v>0.73</v>
@@ -8822,7 +8828,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9109,7 +9115,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR38">
         <v>0.83</v>
@@ -9234,7 +9240,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9312,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ39">
         <v>0.58</v>
@@ -9440,7 +9446,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9521,7 +9527,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ40">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>1.21</v>
@@ -10136,7 +10142,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ43">
         <v>0.58</v>
@@ -10342,10 +10348,10 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR44">
         <v>1.45</v>
@@ -10470,7 +10476,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10676,7 +10682,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10882,7 +10888,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11088,7 +11094,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11294,7 +11300,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11500,7 +11506,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11706,7 +11712,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12118,7 +12124,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12324,7 +12330,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12530,7 +12536,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12736,7 +12742,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13023,7 +13029,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13432,7 +13438,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ59">
         <v>0.64</v>
@@ -13641,7 +13647,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ60">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.17</v>
@@ -13766,7 +13772,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13972,7 +13978,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14050,7 +14056,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ62">
         <v>2.17</v>
@@ -14465,7 +14471,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -14796,7 +14802,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15002,7 +15008,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15620,7 +15626,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15698,7 +15704,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ70">
         <v>0.67</v>
@@ -16032,7 +16038,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16238,7 +16244,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16316,7 +16322,7 @@
         <v>3</v>
       </c>
       <c r="AP73">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ73">
         <v>2</v>
@@ -16856,7 +16862,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17143,7 +17149,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
         <v>1.05</v>
@@ -17474,7 +17480,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17680,7 +17686,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17967,7 +17973,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ81">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR81">
         <v>1.25</v>
@@ -18504,7 +18510,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18916,7 +18922,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19200,7 +19206,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ87">
         <v>0.73</v>
@@ -19406,7 +19412,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ88">
         <v>1.09</v>
@@ -19534,7 +19540,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19612,10 +19618,10 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ89">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>2.01</v>
@@ -19740,7 +19746,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -20358,7 +20364,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20436,7 +20442,7 @@
         <v>3</v>
       </c>
       <c r="AP93">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ93">
         <v>2</v>
@@ -20564,7 +20570,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20976,7 +20982,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21388,7 +21394,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22293,7 +22299,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR102">
         <v>1.15</v>
@@ -22418,7 +22424,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22624,7 +22630,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22705,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="AQ104">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR104">
         <v>1.2</v>
@@ -22830,7 +22836,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23036,7 +23042,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23114,7 +23120,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ106">
         <v>2.09</v>
@@ -23323,7 +23329,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ107">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR107">
         <v>1.85</v>
@@ -23448,7 +23454,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23526,7 +23532,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ108">
         <v>1.09</v>
@@ -24066,7 +24072,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24478,7 +24484,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24684,7 +24690,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24890,7 +24896,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25096,7 +25102,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25380,7 +25386,7 @@
         <v>0.5</v>
       </c>
       <c r="AP117">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ117">
         <v>0.73</v>
@@ -26207,7 +26213,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR121">
         <v>1.62</v>
@@ -26538,7 +26544,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26744,7 +26750,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26822,10 +26828,10 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ124">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.98</v>
@@ -27028,7 +27034,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ125">
         <v>0.73</v>
@@ -27156,7 +27162,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27362,7 +27368,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27440,7 +27446,7 @@
         <v>2.67</v>
       </c>
       <c r="AP127">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ127">
         <v>2.17</v>
@@ -27855,7 +27861,7 @@
         <v>2</v>
       </c>
       <c r="AQ129">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -27980,7 +27986,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28186,7 +28192,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28392,7 +28398,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28473,7 +28479,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ132">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28804,7 +28810,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29088,7 +29094,7 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ135">
         <v>2.09</v>
@@ -29216,7 +29222,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29834,7 +29840,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30040,7 +30046,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30246,7 +30252,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30327,7 +30333,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ141">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -30736,7 +30742,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ143">
         <v>0.67</v>
@@ -30942,7 +30948,7 @@
         <v>0.29</v>
       </c>
       <c r="AP144">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ144">
         <v>0.58</v>
@@ -31070,7 +31076,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31276,7 +31282,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31972,7 +31978,7 @@
         <v>1.63</v>
       </c>
       <c r="AP149">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ149">
         <v>1.25</v>
@@ -32100,7 +32106,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32512,7 +32518,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32593,7 +32599,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ152">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR152">
         <v>1.54</v>
@@ -32799,7 +32805,7 @@
         <v>1</v>
       </c>
       <c r="AQ153">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR153">
         <v>1.13</v>
@@ -32924,7 +32930,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33005,7 +33011,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ154">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR154">
         <v>1.32</v>
@@ -33130,7 +33136,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33414,7 +33420,7 @@
         <v>0.25</v>
       </c>
       <c r="AP156">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ156">
         <v>0.5</v>
@@ -33542,7 +33548,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33623,7 +33629,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ157">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR157">
         <v>1.23</v>
@@ -33748,7 +33754,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33954,7 +33960,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34032,7 +34038,7 @@
         <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ159">
         <v>1.09</v>
@@ -34366,7 +34372,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34572,7 +34578,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34778,7 +34784,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35190,7 +35196,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35602,7 +35608,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35808,7 +35814,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36014,7 +36020,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36220,7 +36226,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36301,7 +36307,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ170">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR170">
         <v>1.58</v>
@@ -36838,7 +36844,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37250,7 +37256,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37662,7 +37668,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37740,7 +37746,7 @@
         <v>1</v>
       </c>
       <c r="AP177">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ177">
         <v>1</v>
@@ -37868,7 +37874,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38280,7 +38286,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38486,7 +38492,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38567,7 +38573,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ181">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR181">
         <v>1.53</v>
@@ -38692,7 +38698,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38898,7 +38904,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39182,7 +39188,7 @@
         <v>1.9</v>
       </c>
       <c r="AP184">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ184">
         <v>1.67</v>
@@ -39310,7 +39316,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39722,7 +39728,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39928,7 +39934,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40009,7 +40015,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ188">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR188">
         <v>1.33</v>
@@ -40134,7 +40140,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40421,7 +40427,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ190">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR190">
         <v>1.38</v>
@@ -41164,7 +41170,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41448,7 +41454,7 @@
         <v>0.8</v>
       </c>
       <c r="AP195">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ195">
         <v>0.73</v>
@@ -41576,7 +41582,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41988,7 +41994,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42400,7 +42406,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42606,7 +42612,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43096,7 +43102,7 @@
         <v>0.55</v>
       </c>
       <c r="AP203">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ203">
         <v>0.5</v>
@@ -43302,7 +43308,7 @@
         <v>0.8</v>
       </c>
       <c r="AP204">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ204">
         <v>0.73</v>
@@ -43587,6 +43593,624 @@
       </c>
       <c r="BP205">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7466227</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45711.4375</v>
+      </c>
+      <c r="F206">
+        <v>20</v>
+      </c>
+      <c r="G206" t="s">
+        <v>81</v>
+      </c>
+      <c r="H206" t="s">
+        <v>72</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>1</v>
+      </c>
+      <c r="L206">
+        <v>2</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>2</v>
+      </c>
+      <c r="O206" t="s">
+        <v>233</v>
+      </c>
+      <c r="P206" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q206">
+        <v>2.1</v>
+      </c>
+      <c r="R206">
+        <v>2.4</v>
+      </c>
+      <c r="S206">
+        <v>5.5</v>
+      </c>
+      <c r="T206">
+        <v>1.3</v>
+      </c>
+      <c r="U206">
+        <v>3.4</v>
+      </c>
+      <c r="V206">
+        <v>2.5</v>
+      </c>
+      <c r="W206">
+        <v>1.5</v>
+      </c>
+      <c r="X206">
+        <v>6</v>
+      </c>
+      <c r="Y206">
+        <v>1.13</v>
+      </c>
+      <c r="Z206">
+        <v>1.63</v>
+      </c>
+      <c r="AA206">
+        <v>4.33</v>
+      </c>
+      <c r="AB206">
+        <v>5.2</v>
+      </c>
+      <c r="AC206">
+        <v>1.03</v>
+      </c>
+      <c r="AD206">
+        <v>17</v>
+      </c>
+      <c r="AE206">
+        <v>1.19</v>
+      </c>
+      <c r="AF206">
+        <v>4.45</v>
+      </c>
+      <c r="AG206">
+        <v>1.61</v>
+      </c>
+      <c r="AH206">
+        <v>2.23</v>
+      </c>
+      <c r="AI206">
+        <v>1.7</v>
+      </c>
+      <c r="AJ206">
+        <v>2.05</v>
+      </c>
+      <c r="AK206">
+        <v>1.16</v>
+      </c>
+      <c r="AL206">
+        <v>1.22</v>
+      </c>
+      <c r="AM206">
+        <v>2.3</v>
+      </c>
+      <c r="AN206">
+        <v>2.4</v>
+      </c>
+      <c r="AO206">
+        <v>0.9</v>
+      </c>
+      <c r="AP206">
+        <v>2.45</v>
+      </c>
+      <c r="AQ206">
+        <v>0.82</v>
+      </c>
+      <c r="AR206">
+        <v>2.08</v>
+      </c>
+      <c r="AS206">
+        <v>1.31</v>
+      </c>
+      <c r="AT206">
+        <v>3.39</v>
+      </c>
+      <c r="AU206">
+        <v>7</v>
+      </c>
+      <c r="AV206">
+        <v>4</v>
+      </c>
+      <c r="AW206">
+        <v>5</v>
+      </c>
+      <c r="AX206">
+        <v>9</v>
+      </c>
+      <c r="AY206">
+        <v>12</v>
+      </c>
+      <c r="AZ206">
+        <v>18</v>
+      </c>
+      <c r="BA206">
+        <v>2</v>
+      </c>
+      <c r="BB206">
+        <v>4</v>
+      </c>
+      <c r="BC206">
+        <v>6</v>
+      </c>
+      <c r="BD206">
+        <v>1.29</v>
+      </c>
+      <c r="BE206">
+        <v>7.5</v>
+      </c>
+      <c r="BF206">
+        <v>3.9</v>
+      </c>
+      <c r="BG206">
+        <v>1.2</v>
+      </c>
+      <c r="BH206">
+        <v>3.9</v>
+      </c>
+      <c r="BI206">
+        <v>1.37</v>
+      </c>
+      <c r="BJ206">
+        <v>2.8</v>
+      </c>
+      <c r="BK206">
+        <v>1.58</v>
+      </c>
+      <c r="BL206">
+        <v>2.18</v>
+      </c>
+      <c r="BM206">
+        <v>1.95</v>
+      </c>
+      <c r="BN206">
+        <v>1.75</v>
+      </c>
+      <c r="BO206">
+        <v>2.4</v>
+      </c>
+      <c r="BP206">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7466224</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45711.4375</v>
+      </c>
+      <c r="F207">
+        <v>20</v>
+      </c>
+      <c r="G207" t="s">
+        <v>78</v>
+      </c>
+      <c r="H207" t="s">
+        <v>77</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>2</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>2</v>
+      </c>
+      <c r="O207" t="s">
+        <v>234</v>
+      </c>
+      <c r="P207" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q207">
+        <v>1.95</v>
+      </c>
+      <c r="R207">
+        <v>2.6</v>
+      </c>
+      <c r="S207">
+        <v>5.5</v>
+      </c>
+      <c r="T207">
+        <v>1.25</v>
+      </c>
+      <c r="U207">
+        <v>3.75</v>
+      </c>
+      <c r="V207">
+        <v>2.2</v>
+      </c>
+      <c r="W207">
+        <v>1.62</v>
+      </c>
+      <c r="X207">
+        <v>5</v>
+      </c>
+      <c r="Y207">
+        <v>1.17</v>
+      </c>
+      <c r="Z207">
+        <v>1.53</v>
+      </c>
+      <c r="AA207">
+        <v>4.8</v>
+      </c>
+      <c r="AB207">
+        <v>5.8</v>
+      </c>
+      <c r="AC207">
+        <v>1.01</v>
+      </c>
+      <c r="AD207">
+        <v>23</v>
+      </c>
+      <c r="AE207">
+        <v>1.14</v>
+      </c>
+      <c r="AF207">
+        <v>5.38</v>
+      </c>
+      <c r="AG207">
+        <v>1.48</v>
+      </c>
+      <c r="AH207">
+        <v>2.54</v>
+      </c>
+      <c r="AI207">
+        <v>1.62</v>
+      </c>
+      <c r="AJ207">
+        <v>2.2</v>
+      </c>
+      <c r="AK207">
+        <v>1.13</v>
+      </c>
+      <c r="AL207">
+        <v>1.19</v>
+      </c>
+      <c r="AM207">
+        <v>2.55</v>
+      </c>
+      <c r="AN207">
+        <v>2.82</v>
+      </c>
+      <c r="AO207">
+        <v>1.1</v>
+      </c>
+      <c r="AP207">
+        <v>2.83</v>
+      </c>
+      <c r="AQ207">
+        <v>1</v>
+      </c>
+      <c r="AR207">
+        <v>1.8</v>
+      </c>
+      <c r="AS207">
+        <v>1.19</v>
+      </c>
+      <c r="AT207">
+        <v>2.99</v>
+      </c>
+      <c r="AU207">
+        <v>7</v>
+      </c>
+      <c r="AV207">
+        <v>3</v>
+      </c>
+      <c r="AW207">
+        <v>15</v>
+      </c>
+      <c r="AX207">
+        <v>5</v>
+      </c>
+      <c r="AY207">
+        <v>27</v>
+      </c>
+      <c r="AZ207">
+        <v>11</v>
+      </c>
+      <c r="BA207">
+        <v>3</v>
+      </c>
+      <c r="BB207">
+        <v>3</v>
+      </c>
+      <c r="BC207">
+        <v>6</v>
+      </c>
+      <c r="BD207">
+        <v>1.24</v>
+      </c>
+      <c r="BE207">
+        <v>7.5</v>
+      </c>
+      <c r="BF207">
+        <v>4.4</v>
+      </c>
+      <c r="BG207">
+        <v>1.29</v>
+      </c>
+      <c r="BH207">
+        <v>3.2</v>
+      </c>
+      <c r="BI207">
+        <v>1.49</v>
+      </c>
+      <c r="BJ207">
+        <v>2.4</v>
+      </c>
+      <c r="BK207">
+        <v>1.81</v>
+      </c>
+      <c r="BL207">
+        <v>1.88</v>
+      </c>
+      <c r="BM207">
+        <v>2.25</v>
+      </c>
+      <c r="BN207">
+        <v>1.55</v>
+      </c>
+      <c r="BO207">
+        <v>2.9</v>
+      </c>
+      <c r="BP207">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7466252</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45711.53125</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>82</v>
+      </c>
+      <c r="H208" t="s">
+        <v>79</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>1</v>
+      </c>
+      <c r="O208" t="s">
+        <v>235</v>
+      </c>
+      <c r="P208" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q208">
+        <v>1.91</v>
+      </c>
+      <c r="R208">
+        <v>2.5</v>
+      </c>
+      <c r="S208">
+        <v>7</v>
+      </c>
+      <c r="T208">
+        <v>1.3</v>
+      </c>
+      <c r="U208">
+        <v>3.4</v>
+      </c>
+      <c r="V208">
+        <v>2.5</v>
+      </c>
+      <c r="W208">
+        <v>1.5</v>
+      </c>
+      <c r="X208">
+        <v>6</v>
+      </c>
+      <c r="Y208">
+        <v>1.13</v>
+      </c>
+      <c r="Z208">
+        <v>1.39</v>
+      </c>
+      <c r="AA208">
+        <v>5.2</v>
+      </c>
+      <c r="AB208">
+        <v>7.9</v>
+      </c>
+      <c r="AC208">
+        <v>1.03</v>
+      </c>
+      <c r="AD208">
+        <v>15</v>
+      </c>
+      <c r="AE208">
+        <v>1.21</v>
+      </c>
+      <c r="AF208">
+        <v>4.25</v>
+      </c>
+      <c r="AG208">
+        <v>1.57</v>
+      </c>
+      <c r="AH208">
+        <v>2.25</v>
+      </c>
+      <c r="AI208">
+        <v>1.95</v>
+      </c>
+      <c r="AJ208">
+        <v>1.8</v>
+      </c>
+      <c r="AK208">
+        <v>1.09</v>
+      </c>
+      <c r="AL208">
+        <v>1.17</v>
+      </c>
+      <c r="AM208">
+        <v>2.95</v>
+      </c>
+      <c r="AN208">
+        <v>1.73</v>
+      </c>
+      <c r="AO208">
+        <v>1</v>
+      </c>
+      <c r="AP208">
+        <v>1.83</v>
+      </c>
+      <c r="AQ208">
+        <v>0.92</v>
+      </c>
+      <c r="AR208">
+        <v>1.81</v>
+      </c>
+      <c r="AS208">
+        <v>1.13</v>
+      </c>
+      <c r="AT208">
+        <v>2.94</v>
+      </c>
+      <c r="AU208">
+        <v>6</v>
+      </c>
+      <c r="AV208">
+        <v>4</v>
+      </c>
+      <c r="AW208">
+        <v>8</v>
+      </c>
+      <c r="AX208">
+        <v>5</v>
+      </c>
+      <c r="AY208">
+        <v>17</v>
+      </c>
+      <c r="AZ208">
+        <v>10</v>
+      </c>
+      <c r="BA208">
+        <v>9</v>
+      </c>
+      <c r="BB208">
+        <v>1</v>
+      </c>
+      <c r="BC208">
+        <v>10</v>
+      </c>
+      <c r="BD208">
+        <v>1.3</v>
+      </c>
+      <c r="BE208">
+        <v>7.5</v>
+      </c>
+      <c r="BF208">
+        <v>3.95</v>
+      </c>
+      <c r="BG208">
+        <v>1.3</v>
+      </c>
+      <c r="BH208">
+        <v>3.15</v>
+      </c>
+      <c r="BI208">
+        <v>1.52</v>
+      </c>
+      <c r="BJ208">
+        <v>2.33</v>
+      </c>
+      <c r="BK208">
+        <v>1.84</v>
+      </c>
+      <c r="BL208">
+        <v>1.84</v>
+      </c>
+      <c r="BM208">
+        <v>2.32</v>
+      </c>
+      <c r="BN208">
+        <v>1.53</v>
+      </c>
+      <c r="BO208">
+        <v>2.95</v>
+      </c>
+      <c r="BP208">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -1696,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ2">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AQ3">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2108,10 +2108,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ4">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2314,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ5">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2726,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ7">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2932,10 +2932,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ8">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3138,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ9">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3344,10 +3344,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ10">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3544,25 +3544,25 @@
         <v>2</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AU11">
         <v>10</v>
@@ -3753,22 +3753,22 @@
         <v>0</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AQ12">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AU12">
         <v>8</v>
@@ -3956,25 +3956,25 @@
         <v>2.55</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP13">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AU13">
         <v>4</v>
@@ -4162,25 +4162,25 @@
         <v>2.75</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ14">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4371,22 +4371,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AU15">
         <v>8</v>
@@ -4574,25 +4574,25 @@
         <v>1.02</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4783,22 +4783,22 @@
         <v>0</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ17">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4986,25 +4986,25 @@
         <v>1.36</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO18">
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AU18">
         <v>4</v>
@@ -5195,22 +5195,22 @@
         <v>0</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU19">
         <v>4</v>
@@ -5404,19 +5404,19 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ20">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR20">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="AS20">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="AT20">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AU20">
         <v>3</v>
@@ -5610,19 +5610,19 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR21">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="AS21">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="AT21">
-        <v>3.23</v>
+        <v>3.61</v>
       </c>
       <c r="AU21">
         <v>2</v>
@@ -5810,25 +5810,25 @@
         <v>1.22</v>
       </c>
       <c r="AN22">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP22">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ22">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR22">
         <v>0.79</v>
       </c>
       <c r="AS22">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AU22">
         <v>4</v>
@@ -6022,19 +6022,19 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ23">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR23">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AS23">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AT23">
-        <v>2.89</v>
+        <v>3.23</v>
       </c>
       <c r="AU23">
         <v>2</v>
@@ -6222,25 +6222,25 @@
         <v>1.57</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ24">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR24">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AS24">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AT24">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6431,22 +6431,22 @@
         <v>1</v>
       </c>
       <c r="AO25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP25">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ25">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AS25">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AT25">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="AU25">
         <v>7</v>
@@ -6640,19 +6640,19 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ26">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR26">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AS26">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="AT26">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AU26">
         <v>7</v>
@@ -6843,22 +6843,22 @@
         <v>0</v>
       </c>
       <c r="AO27">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ27">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR27">
-        <v>1.81</v>
+        <v>1.21</v>
       </c>
       <c r="AS27">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AT27">
-        <v>3.09</v>
+        <v>2.67</v>
       </c>
       <c r="AU27">
         <v>2</v>
@@ -7049,22 +7049,22 @@
         <v>0</v>
       </c>
       <c r="AO28">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ28">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="AS28">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="AT28">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="AU28">
         <v>3</v>
@@ -7255,22 +7255,22 @@
         <v>3</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ29">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR29">
-        <v>2.19</v>
+        <v>1.64</v>
       </c>
       <c r="AS29">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="AT29">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="AU29">
         <v>2</v>
@@ -7458,25 +7458,25 @@
         <v>2.15</v>
       </c>
       <c r="AN30">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AQ30">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR30">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="AS30">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="AT30">
-        <v>3.19</v>
+        <v>2.46</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7664,25 +7664,25 @@
         <v>1.47</v>
       </c>
       <c r="AN31">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AO31">
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR31">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS31">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AT31">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AU31">
         <v>6</v>
@@ -7870,25 +7870,25 @@
         <v>1.4</v>
       </c>
       <c r="AN32">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP32">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ32">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR32">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AS32">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AT32">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="AU32">
         <v>5</v>
@@ -8079,22 +8079,22 @@
         <v>0</v>
       </c>
       <c r="AO33">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP33">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ33">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR33">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="AS33">
-        <v>0.91</v>
+        <v>1.12</v>
       </c>
       <c r="AT33">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="AU33">
         <v>6</v>
@@ -8285,22 +8285,22 @@
         <v>3</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP34">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR34">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="AS34">
-        <v>0.86</v>
+        <v>1.56</v>
       </c>
       <c r="AT34">
-        <v>3.71</v>
+        <v>4.13</v>
       </c>
       <c r="AU34">
         <v>9</v>
@@ -8494,19 +8494,19 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ35">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR35">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="AS35">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AT35">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="AU35">
         <v>12</v>
@@ -8694,25 +8694,25 @@
         <v>3.75</v>
       </c>
       <c r="AN36">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO36">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AP36">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ36">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR36">
         <v>1.72</v>
       </c>
       <c r="AS36">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT36">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="AU36">
         <v>13</v>
@@ -8903,22 +8903,22 @@
         <v>2</v>
       </c>
       <c r="AO37">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP37">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR37">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AS37">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AT37">
-        <v>2.96</v>
+        <v>3.31</v>
       </c>
       <c r="AU37">
         <v>6</v>
@@ -9106,25 +9106,25 @@
         <v>1.4</v>
       </c>
       <c r="AN38">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ38">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR38">
         <v>0.83</v>
       </c>
       <c r="AS38">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="AT38">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9312,25 +9312,25 @@
         <v>2.8</v>
       </c>
       <c r="AN39">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AO39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP39">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ39">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR39">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AS39">
-        <v>0.89</v>
+        <v>1.74</v>
       </c>
       <c r="AT39">
-        <v>2.71</v>
+        <v>3.41</v>
       </c>
       <c r="AU39">
         <v>20</v>
@@ -9518,25 +9518,25 @@
         <v>1.74</v>
       </c>
       <c r="AN40">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO40">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AP40">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR40">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AS40">
-        <v>0.82</v>
+        <v>1.37</v>
       </c>
       <c r="AT40">
-        <v>2.03</v>
+        <v>2.57</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9724,22 +9724,22 @@
         <v>1.9</v>
       </c>
       <c r="AN41">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ41">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR41">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AS41">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="AT41">
         <v>1.99</v>
@@ -9933,22 +9933,22 @@
         <v>0.5</v>
       </c>
       <c r="AO42">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP42">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ42">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR42">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AS42">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="AT42">
-        <v>2.37</v>
+        <v>2.01</v>
       </c>
       <c r="AU42">
         <v>3</v>
@@ -10136,25 +10136,25 @@
         <v>2.8</v>
       </c>
       <c r="AN43">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP43">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ43">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR43">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="AS43">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AT43">
-        <v>3.44</v>
+        <v>3.67</v>
       </c>
       <c r="AU43">
         <v>10</v>
@@ -10342,25 +10342,25 @@
         <v>2.7</v>
       </c>
       <c r="AN44">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO44">
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ44">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR44">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AS44">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AT44">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="AU44">
         <v>15</v>
@@ -10548,25 +10548,25 @@
         <v>1.12</v>
       </c>
       <c r="AN45">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO45">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AP45">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ45">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR45">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="AS45">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="AT45">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="AU45">
         <v>3</v>
@@ -10754,25 +10754,25 @@
         <v>2.4</v>
       </c>
       <c r="AN46">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AO46">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AP46">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ46">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR46">
+        <v>1.22</v>
+      </c>
+      <c r="AS46">
         <v>1.08</v>
       </c>
-      <c r="AS46">
-        <v>0.84</v>
-      </c>
       <c r="AT46">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AU46">
         <v>3</v>
@@ -10963,22 +10963,22 @@
         <v>0</v>
       </c>
       <c r="AO47">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR47">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AS47">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AT47">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AU47">
         <v>11</v>
@@ -11166,25 +11166,25 @@
         <v>1.28</v>
       </c>
       <c r="AN48">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AO48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ48">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR48">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AS48">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AT48">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="AU48">
         <v>5</v>
@@ -11372,25 +11372,25 @@
         <v>2.4</v>
       </c>
       <c r="AN49">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AO49">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP49">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ49">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR49">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="AS49">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AT49">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AU49">
         <v>10</v>
@@ -11578,25 +11578,25 @@
         <v>1.55</v>
       </c>
       <c r="AN50">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AO50">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AP50">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AQ50">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR50">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="AS50">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AT50">
-        <v>3.68</v>
+        <v>2.91</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11784,25 +11784,25 @@
         <v>1.14</v>
       </c>
       <c r="AN51">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AO51">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP51">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ51">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR51">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AS51">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AT51">
-        <v>2.55</v>
+        <v>2.91</v>
       </c>
       <c r="AU51">
         <v>5</v>
@@ -11990,25 +11990,25 @@
         <v>5.45</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AP52">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AQ52">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR52">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AS52">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="AT52">
-        <v>3.05</v>
+        <v>2.81</v>
       </c>
       <c r="AU52">
         <v>6</v>
@@ -12196,25 +12196,25 @@
         <v>1.06</v>
       </c>
       <c r="AN53">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AO53">
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR53">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="AS53">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="AT53">
-        <v>4.08</v>
+        <v>3.91</v>
       </c>
       <c r="AU53">
         <v>5</v>
@@ -12402,25 +12402,25 @@
         <v>1.48</v>
       </c>
       <c r="AN54">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO54">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ54">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR54">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AS54">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AT54">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="AU54">
         <v>10</v>
@@ -12608,25 +12608,25 @@
         <v>1.05</v>
       </c>
       <c r="AN55">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR55">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AS55">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="AT55">
-        <v>3.51</v>
+        <v>3.59</v>
       </c>
       <c r="AU55">
         <v>0</v>
@@ -12817,22 +12817,22 @@
         <v>1</v>
       </c>
       <c r="AO56">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AP56">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ56">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR56">
-        <v>1.55</v>
+        <v>1.19</v>
       </c>
       <c r="AS56">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AT56">
-        <v>3.39</v>
+        <v>3.16</v>
       </c>
       <c r="AU56">
         <v>5</v>
@@ -13020,25 +13020,25 @@
         <v>1.95</v>
       </c>
       <c r="AN57">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO57">
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ57">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR57">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AS57">
-        <v>0.99</v>
+        <v>1.21</v>
       </c>
       <c r="AT57">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="AU57">
         <v>7</v>
@@ -13226,25 +13226,25 @@
         <v>1.77</v>
       </c>
       <c r="AN58">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO58">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ58">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR58">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AS58">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AT58">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13432,25 +13432,25 @@
         <v>4.33</v>
       </c>
       <c r="AN59">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AO59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP59">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ59">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR59">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AS59">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AT59">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13638,25 +13638,25 @@
         <v>1.72</v>
       </c>
       <c r="AN60">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP60">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR60">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AS60">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AT60">
-        <v>2.17</v>
+        <v>2.51</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13847,22 +13847,22 @@
         <v>0</v>
       </c>
       <c r="AO61">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ61">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR61">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AS61">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AT61">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AU61">
         <v>2</v>
@@ -14050,25 +14050,25 @@
         <v>2.4</v>
       </c>
       <c r="AN62">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AO62">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AP62">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ62">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR62">
-        <v>2.58</v>
+        <v>1.95</v>
       </c>
       <c r="AS62">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AT62">
-        <v>3.93</v>
+        <v>3.14</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14256,25 +14256,25 @@
         <v>1.44</v>
       </c>
       <c r="AN63">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AO63">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="AP63">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ63">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR63">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AS63">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="AT63">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="AU63">
         <v>8</v>
@@ -14462,25 +14462,25 @@
         <v>1.38</v>
       </c>
       <c r="AN64">
-        <v>2</v>
+        <v>0.86</v>
       </c>
       <c r="AO64">
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ64">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR64">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AS64">
-        <v>0.82</v>
+        <v>1.18</v>
       </c>
       <c r="AT64">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AU64">
         <v>7</v>
@@ -14671,22 +14671,22 @@
         <v>3</v>
       </c>
       <c r="AO65">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP65">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR65">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="AS65">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AT65">
-        <v>4.1</v>
+        <v>3.87</v>
       </c>
       <c r="AU65">
         <v>7</v>
@@ -14874,25 +14874,25 @@
         <v>3</v>
       </c>
       <c r="AN66">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AO66">
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ66">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR66">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AS66">
-        <v>0.92</v>
+        <v>1.1</v>
       </c>
       <c r="AT66">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AU66">
         <v>9</v>
@@ -15080,25 +15080,25 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO67">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ67">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR67">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AS67">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AT67">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="AU67">
         <v>10</v>
@@ -15286,25 +15286,25 @@
         <v>2.15</v>
       </c>
       <c r="AN68">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO68">
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AQ68">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR68">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AS68">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AT68">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15492,25 +15492,25 @@
         <v>2.18</v>
       </c>
       <c r="AN69">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AO69">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AQ69">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR69">
-        <v>2.09</v>
+        <v>1.64</v>
       </c>
       <c r="AS69">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AT69">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15698,25 +15698,25 @@
         <v>3.08</v>
       </c>
       <c r="AN70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO70">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP70">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ70">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR70">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="AS70">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AT70">
-        <v>3.51</v>
+        <v>3.02</v>
       </c>
       <c r="AU70">
         <v>9</v>
@@ -15907,22 +15907,22 @@
         <v>1</v>
       </c>
       <c r="AO71">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AP71">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ71">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR71">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AS71">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AT71">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="AU71">
         <v>4</v>
@@ -16110,25 +16110,25 @@
         <v>0</v>
       </c>
       <c r="AN72">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AO72">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ72">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR72">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AS72">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT72">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16322,19 +16322,19 @@
         <v>3</v>
       </c>
       <c r="AP73">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ73">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR73">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="AS73">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AT73">
-        <v>4.51</v>
+        <v>4.17</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16522,25 +16522,25 @@
         <v>1.92</v>
       </c>
       <c r="AN74">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ74">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR74">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AS74">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="AT74">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="AU74">
         <v>6</v>
@@ -16731,22 +16731,22 @@
         <v>0</v>
       </c>
       <c r="AO75">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ75">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR75">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AS75">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AT75">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16934,25 +16934,25 @@
         <v>1.17</v>
       </c>
       <c r="AN76">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO76">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ76">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR76">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AS76">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AT76">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17140,25 +17140,25 @@
         <v>1.68</v>
       </c>
       <c r="AN77">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AO77">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ77">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR77">
-        <v>1.05</v>
+        <v>0.93</v>
       </c>
       <c r="AS77">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AT77">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AU77">
         <v>0</v>
@@ -17346,25 +17346,25 @@
         <v>1.32</v>
       </c>
       <c r="AN78">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AO78">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AP78">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ78">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR78">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AS78">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AT78">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="AU78">
         <v>5</v>
@@ -17552,25 +17552,25 @@
         <v>1.1</v>
       </c>
       <c r="AN79">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AO79">
-        <v>1.33</v>
+        <v>2.17</v>
       </c>
       <c r="AP79">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ79">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR79">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AS79">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AT79">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17758,25 +17758,25 @@
         <v>1.88</v>
       </c>
       <c r="AN80">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO80">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AP80">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ80">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR80">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AS80">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT80">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17964,25 +17964,25 @@
         <v>1.4</v>
       </c>
       <c r="AN81">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AO81">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="AP81">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ81">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR81">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AS81">
-        <v>0.9</v>
+        <v>1.16</v>
       </c>
       <c r="AT81">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -18170,25 +18170,25 @@
         <v>1.65</v>
       </c>
       <c r="AN82">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AO82">
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ82">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR82">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AS82">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AT82">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AU82">
         <v>4</v>
@@ -18379,22 +18379,22 @@
         <v>3</v>
       </c>
       <c r="AO83">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AP83">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ83">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR83">
-        <v>2.49</v>
+        <v>2.21</v>
       </c>
       <c r="AS83">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="AT83">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="AU83">
         <v>10</v>
@@ -18582,25 +18582,25 @@
         <v>1.85</v>
       </c>
       <c r="AN84">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO84">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AP84">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ84">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR84">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS84">
-        <v>0.83</v>
+        <v>1.04</v>
       </c>
       <c r="AT84">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AU84">
         <v>12</v>
@@ -18788,25 +18788,25 @@
         <v>1.55</v>
       </c>
       <c r="AN85">
-        <v>2</v>
+        <v>0.89</v>
       </c>
       <c r="AO85">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AP85">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR85">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AS85">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AT85">
-        <v>3.26</v>
+        <v>3.07</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18994,25 +18994,25 @@
         <v>1.28</v>
       </c>
       <c r="AN86">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AO86">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AP86">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ86">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR86">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AS86">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AT86">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="AU86">
         <v>3</v>
@@ -19200,25 +19200,25 @@
         <v>4.2</v>
       </c>
       <c r="AN87">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO87">
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ87">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR87">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AS87">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AT87">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="AU87">
         <v>10</v>
@@ -19406,25 +19406,25 @@
         <v>3.3</v>
       </c>
       <c r="AN88">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AO88">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ88">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR88">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="AS88">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="AT88">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="AU88">
         <v>8</v>
@@ -19612,25 +19612,25 @@
         <v>2.55</v>
       </c>
       <c r="AN89">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AO89">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP89">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR89">
-        <v>2.01</v>
+        <v>1.76</v>
       </c>
       <c r="AS89">
-        <v>1.06</v>
+        <v>1.37</v>
       </c>
       <c r="AT89">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="AU89">
         <v>7</v>
@@ -19818,25 +19818,25 @@
         <v>2.45</v>
       </c>
       <c r="AN90">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="AO90">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AP90">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AQ90">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR90">
+        <v>1.83</v>
+      </c>
+      <c r="AS90">
         <v>1.77</v>
       </c>
-      <c r="AS90">
-        <v>1.51</v>
-      </c>
       <c r="AT90">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -20024,22 +20024,22 @@
         <v>1.17</v>
       </c>
       <c r="AN91">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AO91">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AP91">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ91">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR91">
-        <v>1.05</v>
+        <v>0.89</v>
       </c>
       <c r="AS91">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AT91">
         <v>2.76</v>
@@ -20230,25 +20230,25 @@
         <v>1.63</v>
       </c>
       <c r="AN92">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AO92">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP92">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ92">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR92">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AS92">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="AT92">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AU92">
         <v>4</v>
@@ -20436,25 +20436,25 @@
         <v>1.36</v>
       </c>
       <c r="AN93">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="AO93">
         <v>3</v>
       </c>
       <c r="AP93">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ93">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR93">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="AS93">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="AT93">
-        <v>4.03</v>
+        <v>3.91</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20642,25 +20642,25 @@
         <v>2.5</v>
       </c>
       <c r="AN94">
+        <v>1.9</v>
+      </c>
+      <c r="AO94">
+        <v>1.7</v>
+      </c>
+      <c r="AP94">
+        <v>1.87</v>
+      </c>
+      <c r="AQ94">
+        <v>1.87</v>
+      </c>
+      <c r="AR94">
+        <v>1.79</v>
+      </c>
+      <c r="AS94">
         <v>1.75</v>
       </c>
-      <c r="AO94">
-        <v>2</v>
-      </c>
-      <c r="AP94">
-        <v>2.09</v>
-      </c>
-      <c r="AQ94">
-        <v>1.91</v>
-      </c>
-      <c r="AR94">
-        <v>1.67</v>
-      </c>
-      <c r="AS94">
-        <v>1.56</v>
-      </c>
       <c r="AT94">
-        <v>3.23</v>
+        <v>3.54</v>
       </c>
       <c r="AU94">
         <v>5</v>
@@ -20848,25 +20848,25 @@
         <v>1.7</v>
       </c>
       <c r="AN95">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO95">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AP95">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ95">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR95">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AS95">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AT95">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -21057,22 +21057,22 @@
         <v>1.4</v>
       </c>
       <c r="AO96">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ96">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR96">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AS96">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="AT96">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AU96">
         <v>8</v>
@@ -21260,25 +21260,25 @@
         <v>1.96</v>
       </c>
       <c r="AN97">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO97">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AP97">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ97">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR97">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AS97">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AT97">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="AU97">
         <v>7</v>
@@ -21466,25 +21466,25 @@
         <v>1.5</v>
       </c>
       <c r="AN98">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AO98">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AP98">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ98">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR98">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AS98">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AT98">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="AU98">
         <v>4</v>
@@ -21672,25 +21672,25 @@
         <v>1.48</v>
       </c>
       <c r="AN99">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AO99">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ99">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR99">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AS99">
         <v>1.24</v>
       </c>
       <c r="AT99">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AU99">
         <v>4</v>
@@ -21878,25 +21878,25 @@
         <v>2.85</v>
       </c>
       <c r="AN100">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AO100">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="AP100">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ100">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR100">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AS100">
-        <v>0.95</v>
+        <v>1.18</v>
       </c>
       <c r="AT100">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="AU100">
         <v>7</v>
@@ -22084,25 +22084,25 @@
         <v>1.48</v>
       </c>
       <c r="AN101">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AO101">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR101">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AS101">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AT101">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AU101">
         <v>6</v>
@@ -22290,25 +22290,25 @@
         <v>1.47</v>
       </c>
       <c r="AN102">
-        <v>1.2</v>
+        <v>0.82</v>
       </c>
       <c r="AO102">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AP102">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ102">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR102">
+        <v>0.99</v>
+      </c>
+      <c r="AS102">
         <v>1.15</v>
       </c>
-      <c r="AS102">
-        <v>1.05</v>
-      </c>
       <c r="AT102">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AU102">
         <v>5</v>
@@ -22496,25 +22496,25 @@
         <v>1.06</v>
       </c>
       <c r="AN103">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AO103">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AP103">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ103">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR103">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AS103">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="AT103">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22702,25 +22702,25 @@
         <v>1.2</v>
       </c>
       <c r="AN104">
-        <v>0.67</v>
+        <v>0.36</v>
       </c>
       <c r="AO104">
-        <v>0.6</v>
+        <v>1.18</v>
       </c>
       <c r="AP104">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ104">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR104">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AS104">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="AT104">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AU104">
         <v>4</v>
@@ -22908,25 +22908,25 @@
         <v>1.01</v>
       </c>
       <c r="AN105">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="AO105">
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ105">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR105">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AS105">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AT105">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AU105">
         <v>5</v>
@@ -23114,25 +23114,25 @@
         <v>1.48</v>
       </c>
       <c r="AN106">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AO106">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP106">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ106">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR106">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AS106">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AT106">
-        <v>3.43</v>
+        <v>3.56</v>
       </c>
       <c r="AU106">
         <v>8</v>
@@ -23320,25 +23320,25 @@
         <v>1.48</v>
       </c>
       <c r="AN107">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="AO107">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AP107">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AQ107">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR107">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AS107">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AT107">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="AU107">
         <v>2</v>
@@ -23526,25 +23526,25 @@
         <v>2.85</v>
       </c>
       <c r="AN108">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AO108">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AP108">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ108">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR108">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AS108">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AT108">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23732,25 +23732,25 @@
         <v>2.5</v>
       </c>
       <c r="AN109">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO109">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ109">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR109">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AS109">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AT109">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="AU109">
         <v>4</v>
@@ -23938,25 +23938,25 @@
         <v>3.6</v>
       </c>
       <c r="AN110">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AO110">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AP110">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AQ110">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR110">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AS110">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AT110">
-        <v>2.82</v>
+        <v>3.24</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24144,25 +24144,25 @@
         <v>2.05</v>
       </c>
       <c r="AN111">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO111">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP111">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ111">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR111">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AS111">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="AT111">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AU111">
         <v>4</v>
@@ -24350,25 +24350,25 @@
         <v>5.5</v>
       </c>
       <c r="AN112">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AO112">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP112">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ112">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR112">
-        <v>2.46</v>
+        <v>2.13</v>
       </c>
       <c r="AS112">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AT112">
-        <v>3.52</v>
+        <v>3.23</v>
       </c>
       <c r="AU112">
         <v>7</v>
@@ -24556,25 +24556,25 @@
         <v>1.22</v>
       </c>
       <c r="AN113">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AO113">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AP113">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ113">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR113">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AS113">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AT113">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="AU113">
         <v>0</v>
@@ -24762,25 +24762,25 @@
         <v>1.65</v>
       </c>
       <c r="AN114">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AO114">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AP114">
+        <v>1.09</v>
+      </c>
+      <c r="AQ114">
+        <v>1.87</v>
+      </c>
+      <c r="AR114">
+        <v>1.3</v>
+      </c>
+      <c r="AS114">
         <v>1.33</v>
       </c>
-      <c r="AQ114">
-        <v>2.17</v>
-      </c>
-      <c r="AR114">
-        <v>1.43</v>
-      </c>
-      <c r="AS114">
-        <v>1.21</v>
-      </c>
       <c r="AT114">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24968,25 +24968,25 @@
         <v>1.33</v>
       </c>
       <c r="AN115">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="AO115">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AP115">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ115">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR115">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AS115">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AT115">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AU115">
         <v>5</v>
@@ -25174,25 +25174,25 @@
         <v>1.65</v>
       </c>
       <c r="AN116">
+        <v>1.25</v>
+      </c>
+      <c r="AO116">
+        <v>1.25</v>
+      </c>
+      <c r="AP116">
+        <v>1.04</v>
+      </c>
+      <c r="AQ116">
         <v>1.17</v>
       </c>
-      <c r="AO116">
-        <v>0.5</v>
-      </c>
-      <c r="AP116">
-        <v>1</v>
-      </c>
-      <c r="AQ116">
-        <v>0.64</v>
-      </c>
       <c r="AR116">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AS116">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AT116">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AU116">
         <v>5</v>
@@ -25380,25 +25380,25 @@
         <v>5.75</v>
       </c>
       <c r="AN117">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="AO117">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP117">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ117">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR117">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="AS117">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="AT117">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="AU117">
         <v>0</v>
@@ -25586,25 +25586,25 @@
         <v>2.5</v>
       </c>
       <c r="AN118">
-        <v>2.33</v>
+        <v>1.08</v>
       </c>
       <c r="AO118">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AP118">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AQ118">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR118">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AS118">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="AT118">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AU118">
         <v>5</v>
@@ -25792,25 +25792,25 @@
         <v>1.83</v>
       </c>
       <c r="AN119">
-        <v>2</v>
+        <v>1.23</v>
       </c>
       <c r="AO119">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="AP119">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ119">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR119">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="AS119">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AT119">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25998,25 +25998,25 @@
         <v>1.75</v>
       </c>
       <c r="AN120">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AO120">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AP120">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ120">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR120">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AS120">
-        <v>0.77</v>
+        <v>0.95</v>
       </c>
       <c r="AT120">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AU120">
         <v>8</v>
@@ -26204,25 +26204,25 @@
         <v>3.75</v>
       </c>
       <c r="AN121">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AO121">
-        <v>0.83</v>
+        <v>1.31</v>
       </c>
       <c r="AP121">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AQ121">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR121">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AS121">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AT121">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="AU121">
         <v>11</v>
@@ -26410,25 +26410,25 @@
         <v>1.48</v>
       </c>
       <c r="AN122">
-        <v>1.5</v>
+        <v>0.92</v>
       </c>
       <c r="AO122">
-        <v>1.17</v>
+        <v>0.85</v>
       </c>
       <c r="AP122">
+        <v>1.09</v>
+      </c>
+      <c r="AQ122">
+        <v>0.87</v>
+      </c>
+      <c r="AR122">
+        <v>1.06</v>
+      </c>
+      <c r="AS122">
         <v>1.42</v>
       </c>
-      <c r="AQ122">
-        <v>1</v>
-      </c>
-      <c r="AR122">
-        <v>1.18</v>
-      </c>
-      <c r="AS122">
-        <v>1.26</v>
-      </c>
       <c r="AT122">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26616,25 +26616,25 @@
         <v>1.16</v>
       </c>
       <c r="AN123">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AO123">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="AP123">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ123">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR123">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AS123">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="AT123">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="AU123">
         <v>4</v>
@@ -26822,25 +26822,25 @@
         <v>2.4</v>
       </c>
       <c r="AN124">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AO124">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AP124">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR124">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AS124">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AT124">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -27028,25 +27028,25 @@
         <v>3.3</v>
       </c>
       <c r="AN125">
+        <v>1.54</v>
+      </c>
+      <c r="AO125">
+        <v>1</v>
+      </c>
+      <c r="AP125">
+        <v>1.87</v>
+      </c>
+      <c r="AQ125">
+        <v>1.04</v>
+      </c>
+      <c r="AR125">
+        <v>1.65</v>
+      </c>
+      <c r="AS125">
         <v>1.17</v>
       </c>
-      <c r="AO125">
-        <v>0.67</v>
-      </c>
-      <c r="AP125">
-        <v>1.83</v>
-      </c>
-      <c r="AQ125">
-        <v>0.73</v>
-      </c>
-      <c r="AR125">
-        <v>1.92</v>
-      </c>
-      <c r="AS125">
-        <v>0.96</v>
-      </c>
       <c r="AT125">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27234,25 +27234,25 @@
         <v>1.22</v>
       </c>
       <c r="AN126">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AO126">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AP126">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ126">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR126">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS126">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AT126">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AU126">
         <v>9</v>
@@ -27440,25 +27440,25 @@
         <v>2.24</v>
       </c>
       <c r="AN127">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="AO127">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="AP127">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ127">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR127">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AS127">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AT127">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="AU127">
         <v>2</v>
@@ -27646,25 +27646,25 @@
         <v>2.8</v>
       </c>
       <c r="AN128">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="AO128">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP128">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ128">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR128">
-        <v>2.46</v>
+        <v>2.11</v>
       </c>
       <c r="AS128">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AT128">
-        <v>4.18</v>
+        <v>4.02</v>
       </c>
       <c r="AU128">
         <v>13</v>
@@ -27852,25 +27852,25 @@
         <v>1.78</v>
       </c>
       <c r="AN129">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AO129">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AP129">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ129">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR129">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="AS129">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AT129">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AU129">
         <v>10</v>
@@ -28058,25 +28058,25 @@
         <v>2</v>
       </c>
       <c r="AN130">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="AO130">
-        <v>0.57</v>
+        <v>1.36</v>
       </c>
       <c r="AP130">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ130">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR130">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AS130">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="AT130">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AU130">
         <v>6</v>
@@ -28264,25 +28264,25 @@
         <v>1.02</v>
       </c>
       <c r="AN131">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="AO131">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AP131">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ131">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR131">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AS131">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AT131">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28470,25 +28470,25 @@
         <v>1.5</v>
       </c>
       <c r="AN132">
+        <v>0.93</v>
+      </c>
+      <c r="AO132">
         <v>1.29</v>
       </c>
-      <c r="AO132">
-        <v>0.86</v>
-      </c>
       <c r="AP132">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ132">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR132">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AS132">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AT132">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AU132">
         <v>9</v>
@@ -28676,25 +28676,25 @@
         <v>1.77</v>
       </c>
       <c r="AN133">
-        <v>1.57</v>
+        <v>1.07</v>
       </c>
       <c r="AO133">
-        <v>0.43</v>
+        <v>1.07</v>
       </c>
       <c r="AP133">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ133">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR133">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AS133">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="AT133">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AU133">
         <v>7</v>
@@ -28885,22 +28885,22 @@
         <v>1.14</v>
       </c>
       <c r="AO134">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AP134">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ134">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR134">
-        <v>1.12</v>
+        <v>0.93</v>
       </c>
       <c r="AS134">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AT134">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AU134">
         <v>4</v>
@@ -29088,25 +29088,25 @@
         <v>1.4</v>
       </c>
       <c r="AN135">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AO135">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AP135">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ135">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR135">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AS135">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AT135">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="AU135">
         <v>5</v>
@@ -29294,25 +29294,25 @@
         <v>1.2</v>
       </c>
       <c r="AN136">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="AO136">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="AP136">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ136">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR136">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AS136">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AT136">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29500,25 +29500,25 @@
         <v>1.63</v>
       </c>
       <c r="AN137">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="AO137">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AP137">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ137">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR137">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AS137">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT137">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AU137">
         <v>3</v>
@@ -29706,25 +29706,25 @@
         <v>1.05</v>
       </c>
       <c r="AN138">
+        <v>1.2</v>
+      </c>
+      <c r="AO138">
+        <v>2.8</v>
+      </c>
+      <c r="AP138">
+        <v>1.17</v>
+      </c>
+      <c r="AQ138">
+        <v>2.26</v>
+      </c>
+      <c r="AR138">
+        <v>1.42</v>
+      </c>
+      <c r="AS138">
         <v>2.14</v>
       </c>
-      <c r="AO138">
-        <v>2.63</v>
-      </c>
-      <c r="AP138">
-        <v>1.82</v>
-      </c>
-      <c r="AQ138">
-        <v>2</v>
-      </c>
-      <c r="AR138">
-        <v>1.59</v>
-      </c>
-      <c r="AS138">
-        <v>1.89</v>
-      </c>
       <c r="AT138">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="AU138">
         <v>6</v>
@@ -29912,25 +29912,25 @@
         <v>2.35</v>
       </c>
       <c r="AN139">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="AO139">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="AP139">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ139">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR139">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AS139">
-        <v>0.82</v>
+        <v>1.01</v>
       </c>
       <c r="AT139">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AU139">
         <v>9</v>
@@ -30118,25 +30118,25 @@
         <v>4.75</v>
       </c>
       <c r="AN140">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AO140">
-        <v>0.57</v>
+        <v>0.93</v>
       </c>
       <c r="AP140">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AQ140">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR140">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AS140">
-        <v>0.9399999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="AT140">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AU140">
         <v>8</v>
@@ -30324,25 +30324,25 @@
         <v>1.78</v>
       </c>
       <c r="AN141">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AO141">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AP141">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR141">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AS141">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AT141">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="AU141">
         <v>9</v>
@@ -30530,25 +30530,25 @@
         <v>1.8</v>
       </c>
       <c r="AN142">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AO142">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AP142">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ142">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR142">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AS142">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AT142">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AU142">
         <v>8</v>
@@ -30736,25 +30736,25 @@
         <v>3.1</v>
       </c>
       <c r="AN143">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AO143">
-        <v>0.57</v>
+        <v>1.07</v>
       </c>
       <c r="AP143">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ143">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR143">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AS143">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AT143">
-        <v>3.14</v>
+        <v>3.03</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30942,25 +30942,25 @@
         <v>6.5</v>
       </c>
       <c r="AN144">
+        <v>2.2</v>
+      </c>
+      <c r="AO144">
+        <v>0.4</v>
+      </c>
+      <c r="AP144">
+        <v>2.48</v>
+      </c>
+      <c r="AQ144">
+        <v>0.61</v>
+      </c>
+      <c r="AR144">
+        <v>1.52</v>
+      </c>
+      <c r="AS144">
+        <v>1.19</v>
+      </c>
+      <c r="AT144">
         <v>2.71</v>
-      </c>
-      <c r="AO144">
-        <v>0.29</v>
-      </c>
-      <c r="AP144">
-        <v>2.83</v>
-      </c>
-      <c r="AQ144">
-        <v>0.58</v>
-      </c>
-      <c r="AR144">
-        <v>1.74</v>
-      </c>
-      <c r="AS144">
-        <v>1.18</v>
-      </c>
-      <c r="AT144">
-        <v>2.92</v>
       </c>
       <c r="AU144">
         <v>9</v>
@@ -31148,25 +31148,25 @@
         <v>1.33</v>
       </c>
       <c r="AN145">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="AO145">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AP145">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ145">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR145">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AS145">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AT145">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AU145">
         <v>3</v>
@@ -31354,25 +31354,25 @@
         <v>1.44</v>
       </c>
       <c r="AN146">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AO146">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP146">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ146">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR146">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AS146">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="AT146">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AU146">
         <v>8</v>
@@ -31560,25 +31560,25 @@
         <v>2.3</v>
       </c>
       <c r="AN147">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AO147">
-        <v>0.88</v>
+        <v>1.38</v>
       </c>
       <c r="AP147">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ147">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR147">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AS147">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AT147">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31766,25 +31766,25 @@
         <v>1.36</v>
       </c>
       <c r="AN148">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AO148">
-        <v>0.38</v>
+        <v>1.31</v>
       </c>
       <c r="AP148">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ148">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR148">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AS148">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AT148">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AU148">
         <v>9</v>
@@ -31972,25 +31972,25 @@
         <v>1.65</v>
       </c>
       <c r="AN149">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AO149">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AP149">
+        <v>1.87</v>
+      </c>
+      <c r="AQ149">
         <v>1.83</v>
       </c>
-      <c r="AQ149">
-        <v>1.25</v>
-      </c>
       <c r="AR149">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AS149">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AT149">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="AU149">
         <v>6</v>
@@ -32178,25 +32178,25 @@
         <v>1.19</v>
       </c>
       <c r="AN150">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO150">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AP150">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ150">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR150">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AS150">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AT150">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AU150">
         <v>4</v>
@@ -32384,25 +32384,25 @@
         <v>2.25</v>
       </c>
       <c r="AN151">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AO151">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AP151">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ151">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR151">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="AS151">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AT151">
-        <v>4.5</v>
+        <v>3.99</v>
       </c>
       <c r="AU151">
         <v>8</v>
@@ -32590,25 +32590,25 @@
         <v>2.25</v>
       </c>
       <c r="AN152">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO152">
-        <v>0.88</v>
+        <v>1.38</v>
       </c>
       <c r="AP152">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ152">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR152">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS152">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AT152">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AU152">
         <v>7</v>
@@ -32796,25 +32796,25 @@
         <v>1.45</v>
       </c>
       <c r="AN153">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AO153">
-        <v>0.86</v>
+        <v>1.06</v>
       </c>
       <c r="AP153">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ153">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR153">
-        <v>1.13</v>
+        <v>0.97</v>
       </c>
       <c r="AS153">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AT153">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AU153">
         <v>9</v>
@@ -33002,25 +33002,25 @@
         <v>1.4</v>
       </c>
       <c r="AN154">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="AO154">
-        <v>1</v>
+        <v>1.47</v>
       </c>
       <c r="AP154">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ154">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR154">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AS154">
-        <v>1.08</v>
+        <v>1.45</v>
       </c>
       <c r="AT154">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="AU154">
         <v>4</v>
@@ -33208,25 +33208,25 @@
         <v>1.44</v>
       </c>
       <c r="AN155">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AO155">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP155">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR155">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AS155">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AT155">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="AU155">
         <v>4</v>
@@ -33414,25 +33414,25 @@
         <v>6</v>
       </c>
       <c r="AN156">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="AO156">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="AP156">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ156">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR156">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AS156">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="AT156">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="AU156">
         <v>7</v>
@@ -33620,25 +33620,25 @@
         <v>1.46</v>
       </c>
       <c r="AN157">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO157">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP157">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ157">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR157">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AS157">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AT157">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="AU157">
         <v>4</v>
@@ -33826,25 +33826,25 @@
         <v>2.75</v>
       </c>
       <c r="AN158">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AO158">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AP158">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ158">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR158">
-        <v>2.37</v>
+        <v>2.06</v>
       </c>
       <c r="AS158">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AT158">
-        <v>3.83</v>
+        <v>3.68</v>
       </c>
       <c r="AU158">
         <v>4</v>
@@ -34032,25 +34032,25 @@
         <v>2.85</v>
       </c>
       <c r="AN159">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AO159">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AP159">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ159">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR159">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AS159">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="AT159">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="AU159">
         <v>13</v>
@@ -34238,22 +34238,22 @@
         <v>1.95</v>
       </c>
       <c r="AN160">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO160">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="AP160">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ160">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR160">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AS160">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AT160">
         <v>2.36</v>
@@ -34444,25 +34444,25 @@
         <v>2.45</v>
       </c>
       <c r="AN161">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AO161">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AP161">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AQ161">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR161">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AS161">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AT161">
-        <v>3.06</v>
+        <v>3.27</v>
       </c>
       <c r="AU161">
         <v>5</v>
@@ -34650,25 +34650,25 @@
         <v>1.62</v>
       </c>
       <c r="AN162">
-        <v>1.88</v>
+        <v>1.29</v>
       </c>
       <c r="AO162">
-        <v>0.33</v>
+        <v>1.24</v>
       </c>
       <c r="AP162">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ162">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR162">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AS162">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AT162">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AU162">
         <v>8</v>
@@ -34856,25 +34856,25 @@
         <v>1.06</v>
       </c>
       <c r="AN163">
-        <v>1.33</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO163">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="AP163">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ163">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AR163">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AS163">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="AT163">
-        <v>3.06</v>
+        <v>3.19</v>
       </c>
       <c r="AU163">
         <v>5</v>
@@ -35062,25 +35062,25 @@
         <v>1.46</v>
       </c>
       <c r="AN164">
-        <v>1.78</v>
+        <v>2.17</v>
       </c>
       <c r="AO164">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AP164">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ164">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR164">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AS164">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AT164">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="AU164">
         <v>4</v>
@@ -35271,22 +35271,22 @@
         <v>1.22</v>
       </c>
       <c r="AO165">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AP165">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ165">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR165">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AS165">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AT165">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AU165">
         <v>2</v>
@@ -35474,25 +35474,25 @@
         <v>2.25</v>
       </c>
       <c r="AN166">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="AO166">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ166">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR166">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AS166">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AT166">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="AU166">
         <v>5</v>
@@ -35680,25 +35680,25 @@
         <v>1.19</v>
       </c>
       <c r="AN167">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AO167">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AP167">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ167">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR167">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AS167">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="AT167">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35886,25 +35886,25 @@
         <v>1.57</v>
       </c>
       <c r="AN168">
-        <v>0.78</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO168">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AP168">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ168">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR168">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AS168">
-        <v>0.91</v>
+        <v>1.18</v>
       </c>
       <c r="AT168">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AU168">
         <v>4</v>
@@ -36092,25 +36092,25 @@
         <v>1.16</v>
       </c>
       <c r="AN169">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO169">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AP169">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AQ169">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR169">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AS169">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AT169">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="AU169">
         <v>3</v>
@@ -36298,25 +36298,25 @@
         <v>1.93</v>
       </c>
       <c r="AN170">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AO170">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AP170">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ170">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR170">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AS170">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT170">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="AU170">
         <v>8</v>
@@ -36504,25 +36504,25 @@
         <v>2.45</v>
       </c>
       <c r="AN171">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="AO171">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="AP171">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ171">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR171">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AS171">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="AT171">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AU171">
         <v>6</v>
@@ -36710,25 +36710,25 @@
         <v>1.27</v>
       </c>
       <c r="AN172">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AO172">
-        <v>2.56</v>
+        <v>2.11</v>
       </c>
       <c r="AP172">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ172">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR172">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AS172">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AT172">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="AU172">
         <v>4</v>
@@ -36916,25 +36916,25 @@
         <v>7.5</v>
       </c>
       <c r="AN173">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="AO173">
-        <v>0.78</v>
+        <v>1.32</v>
       </c>
       <c r="AP173">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ173">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR173">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AS173">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AT173">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AU173">
         <v>10</v>
@@ -37122,25 +37122,25 @@
         <v>1.62</v>
       </c>
       <c r="AN174">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO174">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="AP174">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ174">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR174">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AS174">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AT174">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="AU174">
         <v>8</v>
@@ -37328,25 +37328,25 @@
         <v>1.73</v>
       </c>
       <c r="AN175">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AO175">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AP175">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ175">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR175">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AS175">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AT175">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AU175">
         <v>2</v>
@@ -37534,25 +37534,25 @@
         <v>1.46</v>
       </c>
       <c r="AN176">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="AO176">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AP176">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ176">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR176">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AS176">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="AT176">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AU176">
         <v>4</v>
@@ -37740,25 +37740,25 @@
         <v>2.3</v>
       </c>
       <c r="AN177">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AO177">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AP177">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ177">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR177">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AS177">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AT177">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AU177">
         <v>6</v>
@@ -37946,25 +37946,25 @@
         <v>1.6</v>
       </c>
       <c r="AN178">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO178">
-        <v>0.44</v>
+        <v>1.05</v>
       </c>
       <c r="AP178">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ178">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR178">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AS178">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AT178">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AU178">
         <v>0</v>
@@ -38152,25 +38152,25 @@
         <v>1.82</v>
       </c>
       <c r="AN179">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO179">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AP179">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ179">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR179">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AS179">
-        <v>0.95</v>
+        <v>1.15</v>
       </c>
       <c r="AT179">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AU179">
         <v>6</v>
@@ -38358,25 +38358,25 @@
         <v>1.3</v>
       </c>
       <c r="AN180">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AO180">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AP180">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ180">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR180">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AS180">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AT180">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AU180">
         <v>7</v>
@@ -38564,25 +38564,25 @@
         <v>1.73</v>
       </c>
       <c r="AN181">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AO181">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AP181">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AQ181">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR181">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AS181">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AT181">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AU181">
         <v>6</v>
@@ -38770,25 +38770,25 @@
         <v>1.11</v>
       </c>
       <c r="AN182">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AO182">
+        <v>2.45</v>
+      </c>
+      <c r="AP182">
+        <v>1.09</v>
+      </c>
+      <c r="AQ182">
+        <v>2.26</v>
+      </c>
+      <c r="AR182">
+        <v>1.44</v>
+      </c>
+      <c r="AS182">
         <v>2.1</v>
       </c>
-      <c r="AP182">
-        <v>1.33</v>
-      </c>
-      <c r="AQ182">
-        <v>2</v>
-      </c>
-      <c r="AR182">
-        <v>1.6</v>
-      </c>
-      <c r="AS182">
-        <v>1.84</v>
-      </c>
       <c r="AT182">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="AU182">
         <v>9</v>
@@ -38976,25 +38976,25 @@
         <v>1.66</v>
       </c>
       <c r="AN183">
-        <v>0.7</v>
+        <v>0.53</v>
       </c>
       <c r="AO183">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AP183">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AQ183">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR183">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS183">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AT183">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AU183">
         <v>6</v>
@@ -39182,25 +39182,25 @@
         <v>1.62</v>
       </c>
       <c r="AN184">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="AO184">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AP184">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ184">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR184">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AS184">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AT184">
-        <v>3.71</v>
+        <v>3.47</v>
       </c>
       <c r="AU184">
         <v>10</v>
@@ -39388,25 +39388,25 @@
         <v>1.47</v>
       </c>
       <c r="AN185">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AO185">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="AP185">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ185">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AR185">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="AS185">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AT185">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="AU185">
         <v>2</v>
@@ -39594,25 +39594,25 @@
         <v>1.95</v>
       </c>
       <c r="AN186">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="AO186">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AP186">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="AQ186">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR186">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AS186">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AT186">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AU186">
         <v>5</v>
@@ -39800,25 +39800,25 @@
         <v>1.21</v>
       </c>
       <c r="AN187">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AO187">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AP187">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ187">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AR187">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AS187">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AT187">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AU187">
         <v>2</v>
@@ -40006,25 +40006,25 @@
         <v>1.32</v>
       </c>
       <c r="AN188">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AO188">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AP188">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AQ188">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR188">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AS188">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AT188">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AU188">
         <v>8</v>
@@ -40212,25 +40212,25 @@
         <v>6</v>
       </c>
       <c r="AN189">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AO189">
         <v>1.1</v>
       </c>
       <c r="AP189">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ189">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AR189">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AS189">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AT189">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="AU189">
         <v>7</v>
@@ -40418,25 +40418,25 @@
         <v>1.41</v>
       </c>
       <c r="AN190">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AO190">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP190">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AQ190">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR190">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AS190">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AT190">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AU190">
         <v>7</v>
@@ -40624,25 +40624,25 @@
         <v>3</v>
       </c>
       <c r="AN191">
+        <v>1.8</v>
+      </c>
+      <c r="AO191">
+        <v>0.95</v>
+      </c>
+      <c r="AP191">
+        <v>1.87</v>
+      </c>
+      <c r="AQ191">
+        <v>0.87</v>
+      </c>
+      <c r="AR191">
         <v>1.89</v>
       </c>
-      <c r="AO191">
-        <v>1.2</v>
-      </c>
-      <c r="AP191">
-        <v>2.09</v>
-      </c>
-      <c r="AQ191">
-        <v>1</v>
-      </c>
-      <c r="AR191">
-        <v>1.85</v>
-      </c>
       <c r="AS191">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AT191">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="AU191">
         <v>6</v>
@@ -40830,25 +40830,25 @@
         <v>3</v>
       </c>
       <c r="AN192">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AO192">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP192">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AQ192">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR192">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AS192">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AT192">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="AU192">
         <v>6</v>
@@ -41036,25 +41036,25 @@
         <v>1.46</v>
       </c>
       <c r="AN193">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AO193">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AP193">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ193">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="AR193">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AS193">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AT193">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="AU193">
         <v>8</v>
@@ -41242,25 +41242,25 @@
         <v>1.12</v>
       </c>
       <c r="AN194">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AO194">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AP194">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AQ194">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AR194">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AS194">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AT194">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="AU194">
         <v>4</v>
@@ -41448,25 +41448,25 @@
         <v>2.85</v>
       </c>
       <c r="AN195">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AO195">
-        <v>0.8</v>
+        <v>1.14</v>
       </c>
       <c r="AP195">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ195">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="AR195">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AS195">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AT195">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="AU195">
         <v>8</v>
@@ -41654,22 +41654,22 @@
         <v>1.27</v>
       </c>
       <c r="AN196">
+        <v>1.19</v>
+      </c>
+      <c r="AO196">
+        <v>1.75</v>
+      </c>
+      <c r="AP196">
+        <v>1.17</v>
+      </c>
+      <c r="AQ196">
+        <v>1.83</v>
+      </c>
+      <c r="AR196">
+        <v>1.47</v>
+      </c>
+      <c r="AS196">
         <v>1.9</v>
-      </c>
-      <c r="AO196">
-        <v>1.27</v>
-      </c>
-      <c r="AP196">
-        <v>1.82</v>
-      </c>
-      <c r="AQ196">
-        <v>1.25</v>
-      </c>
-      <c r="AR196">
-        <v>1.64</v>
-      </c>
-      <c r="AS196">
-        <v>1.73</v>
       </c>
       <c r="AT196">
         <v>3.37</v>
@@ -41860,25 +41860,25 @@
         <v>1.9</v>
       </c>
       <c r="AN197">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AO197">
-        <v>1.09</v>
+        <v>0.91</v>
       </c>
       <c r="AP197">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ197">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AR197">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AS197">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AT197">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AU197">
         <v>4</v>
@@ -42066,25 +42066,25 @@
         <v>3.2</v>
       </c>
       <c r="AN198">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="AO198">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="AP198">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AQ198">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AR198">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AS198">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AT198">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AU198">
         <v>20</v>
@@ -42272,25 +42272,25 @@
         <v>1.18</v>
       </c>
       <c r="AN199">
-        <v>1.73</v>
+        <v>1.18</v>
       </c>
       <c r="AO199">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AP199">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AQ199">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR199">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS199">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AT199">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="AU199">
         <v>3</v>
@@ -42481,22 +42481,22 @@
         <v>1.09</v>
       </c>
       <c r="AO200">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="AP200">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AQ200">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR200">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AS200">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AT200">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AU200">
         <v>8</v>
@@ -42684,25 +42684,25 @@
         <v>2.45</v>
       </c>
       <c r="AN201">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AO201">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="AP201">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AQ201">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR201">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS201">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AT201">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AU201">
         <v>5</v>
@@ -42890,25 +42890,25 @@
         <v>1.62</v>
       </c>
       <c r="AN202">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AO202">
-        <v>0.55</v>
+        <v>1.18</v>
       </c>
       <c r="AP202">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AQ202">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AR202">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AS202">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AT202">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="AU202">
         <v>6</v>
@@ -43096,25 +43096,25 @@
         <v>3</v>
       </c>
       <c r="AN203">
-        <v>2.33</v>
+        <v>1.71</v>
       </c>
       <c r="AO203">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="AP203">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ203">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="AR203">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AS203">
         <v>1.29</v>
       </c>
       <c r="AT203">
-        <v>3.37</v>
+        <v>3.13</v>
       </c>
       <c r="AU203">
         <v>5</v>
@@ -43302,25 +43302,25 @@
         <v>4.2</v>
       </c>
       <c r="AN204">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="AO204">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="AP204">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ204">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="AR204">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AS204">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="AT204">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AU204">
         <v>7</v>
@@ -43508,25 +43508,25 @@
         <v>4.8</v>
       </c>
       <c r="AN205">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AO205">
         <v>0.64</v>
       </c>
       <c r="AP205">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AQ205">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AR205">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AS205">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AT205">
-        <v>3.06</v>
+        <v>3.19</v>
       </c>
       <c r="AU205">
         <v>9</v>
@@ -43714,25 +43714,25 @@
         <v>2.3</v>
       </c>
       <c r="AN206">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="AO206">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="AP206">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AQ206">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR206">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AS206">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AT206">
-        <v>3.39</v>
+        <v>3.29</v>
       </c>
       <c r="AU206">
         <v>7</v>
@@ -43920,25 +43920,25 @@
         <v>2.55</v>
       </c>
       <c r="AN207">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="AO207">
-        <v>1.1</v>
+        <v>1.59</v>
       </c>
       <c r="AP207">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AQ207">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AR207">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AS207">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AT207">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AU207">
         <v>7</v>
@@ -44126,25 +44126,25 @@
         <v>2.95</v>
       </c>
       <c r="AN208">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AO208">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AP208">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AQ208">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="AR208">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AS208">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AT208">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AU208">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -1696,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AQ2">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ3">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2108,10 +2108,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2314,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ5">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2726,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ7">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2932,10 +2932,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ8">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3138,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3344,10 +3344,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ10">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3544,25 +3544,25 @@
         <v>2</v>
       </c>
       <c r="AN11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ11">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR11">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>10</v>
@@ -3753,22 +3753,22 @@
         <v>0</v>
       </c>
       <c r="AO12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ12">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR12">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>8</v>
@@ -3956,25 +3956,25 @@
         <v>2.55</v>
       </c>
       <c r="AN13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ13">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR13">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>4</v>
@@ -4162,25 +4162,25 @@
         <v>2.75</v>
       </c>
       <c r="AN14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ14">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR14">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4371,22 +4371,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ15">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AU15">
         <v>8</v>
@@ -4574,25 +4574,25 @@
         <v>1.02</v>
       </c>
       <c r="AN16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR16">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4783,22 +4783,22 @@
         <v>0</v>
       </c>
       <c r="AO17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ17">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR17">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4986,25 +4986,25 @@
         <v>1.36</v>
       </c>
       <c r="AN18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR18">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AU18">
         <v>4</v>
@@ -5195,22 +5195,22 @@
         <v>0</v>
       </c>
       <c r="AO19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR19">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AS19">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AU19">
         <v>4</v>
@@ -5404,19 +5404,19 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR20">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="AS20">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AT20">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AU20">
         <v>3</v>
@@ -5610,19 +5610,19 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ21">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR21">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="AS21">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="AT21">
-        <v>3.61</v>
+        <v>3.23</v>
       </c>
       <c r="AU21">
         <v>2</v>
@@ -5810,25 +5810,25 @@
         <v>1.22</v>
       </c>
       <c r="AN22">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR22">
         <v>0.79</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="AT22">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AU22">
         <v>4</v>
@@ -6022,19 +6022,19 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AQ23">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR23">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AS23">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AT23">
-        <v>3.23</v>
+        <v>2.89</v>
       </c>
       <c r="AU23">
         <v>2</v>
@@ -6222,25 +6222,25 @@
         <v>1.57</v>
       </c>
       <c r="AN24">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR24">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="AS24">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="AT24">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -6431,22 +6431,22 @@
         <v>1</v>
       </c>
       <c r="AO25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP25">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ25">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR25">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AS25">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AT25">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU25">
         <v>7</v>
@@ -6640,19 +6640,19 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR26">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AS26">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AU26">
         <v>7</v>
@@ -6843,22 +6843,22 @@
         <v>0</v>
       </c>
       <c r="AO27">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR27">
-        <v>1.21</v>
+        <v>1.81</v>
       </c>
       <c r="AS27">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AT27">
-        <v>2.67</v>
+        <v>3.09</v>
       </c>
       <c r="AU27">
         <v>2</v>
@@ -7049,22 +7049,22 @@
         <v>0</v>
       </c>
       <c r="AO28">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR28">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="AS28">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="AT28">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="AU28">
         <v>3</v>
@@ -7255,22 +7255,22 @@
         <v>3</v>
       </c>
       <c r="AO29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ29">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR29">
-        <v>1.64</v>
+        <v>2.19</v>
       </c>
       <c r="AS29">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="AT29">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="AU29">
         <v>2</v>
@@ -7458,25 +7458,25 @@
         <v>2.15</v>
       </c>
       <c r="AN30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ30">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR30">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="AS30">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AT30">
-        <v>2.46</v>
+        <v>3.19</v>
       </c>
       <c r="AU30">
         <v>9</v>
@@ -7664,25 +7664,25 @@
         <v>1.47</v>
       </c>
       <c r="AN31">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AO31">
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR31">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="AS31">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AT31">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AU31">
         <v>6</v>
@@ -7870,25 +7870,25 @@
         <v>1.4</v>
       </c>
       <c r="AN32">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ32">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR32">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AS32">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AT32">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AU32">
         <v>5</v>
@@ -8079,22 +8079,22 @@
         <v>0</v>
       </c>
       <c r="AO33">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ33">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR33">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="AS33">
-        <v>1.12</v>
+        <v>0.91</v>
       </c>
       <c r="AT33">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="AU33">
         <v>6</v>
@@ -8285,22 +8285,22 @@
         <v>3</v>
       </c>
       <c r="AO34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ34">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR34">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="AS34">
-        <v>1.56</v>
+        <v>0.86</v>
       </c>
       <c r="AT34">
-        <v>4.13</v>
+        <v>3.71</v>
       </c>
       <c r="AU34">
         <v>9</v>
@@ -8494,19 +8494,19 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ35">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR35">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="AS35">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AT35">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="AU35">
         <v>12</v>
@@ -8694,25 +8694,25 @@
         <v>3.75</v>
       </c>
       <c r="AN36">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ36">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR36">
         <v>1.72</v>
       </c>
       <c r="AS36">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="AT36">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AU36">
         <v>13</v>
@@ -8903,22 +8903,22 @@
         <v>2</v>
       </c>
       <c r="AO37">
+        <v>2</v>
+      </c>
+      <c r="AP37">
+        <v>1.73</v>
+      </c>
+      <c r="AQ37">
         <v>1.67</v>
       </c>
-      <c r="AP37">
-        <v>1.17</v>
-      </c>
-      <c r="AQ37">
-        <v>1.87</v>
-      </c>
       <c r="AR37">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AS37">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="AT37">
-        <v>3.31</v>
+        <v>2.96</v>
       </c>
       <c r="AU37">
         <v>6</v>
@@ -9106,25 +9106,25 @@
         <v>1.4</v>
       </c>
       <c r="AN38">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR38">
         <v>0.83</v>
       </c>
       <c r="AS38">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="AT38">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9312,25 +9312,25 @@
         <v>2.8</v>
       </c>
       <c r="AN39">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AO39">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ39">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR39">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AS39">
-        <v>1.74</v>
+        <v>0.89</v>
       </c>
       <c r="AT39">
-        <v>3.41</v>
+        <v>2.71</v>
       </c>
       <c r="AU39">
         <v>20</v>
@@ -9518,25 +9518,25 @@
         <v>1.74</v>
       </c>
       <c r="AN40">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO40">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP40">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ40">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR40">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AS40">
-        <v>1.37</v>
+        <v>0.82</v>
       </c>
       <c r="AT40">
-        <v>2.57</v>
+        <v>2.03</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9724,22 +9724,22 @@
         <v>1.9</v>
       </c>
       <c r="AN41">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR41">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AS41">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="AT41">
         <v>1.99</v>
@@ -9933,22 +9933,22 @@
         <v>0.5</v>
       </c>
       <c r="AO42">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR42">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AS42">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="AT42">
-        <v>2.01</v>
+        <v>2.37</v>
       </c>
       <c r="AU42">
         <v>3</v>
@@ -10136,25 +10136,25 @@
         <v>2.8</v>
       </c>
       <c r="AN43">
+        <v>1</v>
+      </c>
+      <c r="AO43">
+        <v>0</v>
+      </c>
+      <c r="AP43">
+        <v>2.45</v>
+      </c>
+      <c r="AQ43">
+        <v>0.58</v>
+      </c>
+      <c r="AR43">
+        <v>2.19</v>
+      </c>
+      <c r="AS43">
         <v>1.25</v>
       </c>
-      <c r="AO43">
-        <v>1</v>
-      </c>
-      <c r="AP43">
-        <v>1.83</v>
-      </c>
-      <c r="AQ43">
-        <v>1.17</v>
-      </c>
-      <c r="AR43">
-        <v>1.96</v>
-      </c>
-      <c r="AS43">
-        <v>1.71</v>
-      </c>
       <c r="AT43">
-        <v>3.67</v>
+        <v>3.44</v>
       </c>
       <c r="AU43">
         <v>10</v>
@@ -10342,25 +10342,25 @@
         <v>2.7</v>
       </c>
       <c r="AN44">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO44">
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ44">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR44">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AS44">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AT44">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AU44">
         <v>15</v>
@@ -10548,25 +10548,25 @@
         <v>1.12</v>
       </c>
       <c r="AN45">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ45">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR45">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AS45">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AT45">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="AU45">
         <v>3</v>
@@ -10754,25 +10754,25 @@
         <v>2.4</v>
       </c>
       <c r="AN46">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ46">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR46">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AS46">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AT46">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AU46">
         <v>3</v>
@@ -10963,22 +10963,22 @@
         <v>0</v>
       </c>
       <c r="AO47">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AP47">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR47">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AS47">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AT47">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AU47">
         <v>11</v>
@@ -11166,25 +11166,25 @@
         <v>1.28</v>
       </c>
       <c r="AN48">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AO48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR48">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AS48">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AT48">
-        <v>3.46</v>
+        <v>3.56</v>
       </c>
       <c r="AU48">
         <v>5</v>
@@ -11372,25 +11372,25 @@
         <v>2.4</v>
       </c>
       <c r="AN49">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AO49">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ49">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR49">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="AS49">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AT49">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AU49">
         <v>10</v>
@@ -11578,25 +11578,25 @@
         <v>1.55</v>
       </c>
       <c r="AN50">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="AO50">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ50">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR50">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="AS50">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AT50">
-        <v>2.91</v>
+        <v>3.68</v>
       </c>
       <c r="AU50">
         <v>7</v>
@@ -11784,25 +11784,25 @@
         <v>1.14</v>
       </c>
       <c r="AN51">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AO51">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ51">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR51">
-        <v>0.95</v>
+        <v>0.82</v>
       </c>
       <c r="AS51">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AT51">
-        <v>2.91</v>
+        <v>2.55</v>
       </c>
       <c r="AU51">
         <v>5</v>
@@ -11990,25 +11990,25 @@
         <v>5.45</v>
       </c>
       <c r="AN52">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ52">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR52">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AS52">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AT52">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="AU52">
         <v>6</v>
@@ -12196,25 +12196,25 @@
         <v>1.06</v>
       </c>
       <c r="AN53">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AO53">
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ53">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR53">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="AS53">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AT53">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="AU53">
         <v>5</v>
@@ -12402,25 +12402,25 @@
         <v>1.48</v>
       </c>
       <c r="AN54">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO54">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR54">
+        <v>1.37</v>
+      </c>
+      <c r="AS54">
         <v>1.22</v>
       </c>
-      <c r="AS54">
-        <v>1.65</v>
-      </c>
       <c r="AT54">
-        <v>2.87</v>
+        <v>2.59</v>
       </c>
       <c r="AU54">
         <v>10</v>
@@ -12608,25 +12608,25 @@
         <v>1.05</v>
       </c>
       <c r="AN55">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO55">
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
+        <v>2</v>
+      </c>
+      <c r="AR55">
+        <v>1.25</v>
+      </c>
+      <c r="AS55">
         <v>2.26</v>
       </c>
-      <c r="AR55">
-        <v>1.06</v>
-      </c>
-      <c r="AS55">
-        <v>2.53</v>
-      </c>
       <c r="AT55">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
       <c r="AU55">
         <v>0</v>
@@ -12817,22 +12817,22 @@
         <v>1</v>
       </c>
       <c r="AO56">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ56">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR56">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="AS56">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AT56">
-        <v>3.16</v>
+        <v>3.39</v>
       </c>
       <c r="AU56">
         <v>5</v>
@@ -13020,25 +13020,25 @@
         <v>1.95</v>
       </c>
       <c r="AN57">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO57">
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ57">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR57">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AS57">
-        <v>1.21</v>
+        <v>0.99</v>
       </c>
       <c r="AT57">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="AU57">
         <v>7</v>
@@ -13226,25 +13226,25 @@
         <v>1.77</v>
       </c>
       <c r="AN58">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO58">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ58">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR58">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AS58">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AT58">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13432,25 +13432,25 @@
         <v>4.33</v>
       </c>
       <c r="AN59">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ59">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR59">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="AS59">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="AT59">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="AU59">
         <v>6</v>
@@ -13638,25 +13638,25 @@
         <v>1.72</v>
       </c>
       <c r="AN60">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO60">
+        <v>1</v>
+      </c>
+      <c r="AP60">
+        <v>1.73</v>
+      </c>
+      <c r="AQ60">
+        <v>1</v>
+      </c>
+      <c r="AR60">
         <v>1.17</v>
       </c>
-      <c r="AP60">
-        <v>1.17</v>
-      </c>
-      <c r="AQ60">
-        <v>1.52</v>
-      </c>
-      <c r="AR60">
-        <v>1.18</v>
-      </c>
       <c r="AS60">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AT60">
-        <v>2.51</v>
+        <v>2.17</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13847,22 +13847,22 @@
         <v>0</v>
       </c>
       <c r="AO61">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR61">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AS61">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AT61">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AU61">
         <v>2</v>
@@ -14050,25 +14050,25 @@
         <v>2.4</v>
       </c>
       <c r="AN62">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AO62">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ62">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR62">
-        <v>1.95</v>
+        <v>2.58</v>
       </c>
       <c r="AS62">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AT62">
-        <v>3.14</v>
+        <v>3.93</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14256,25 +14256,25 @@
         <v>1.44</v>
       </c>
       <c r="AN63">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AO63">
-        <v>1.14</v>
+        <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ63">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR63">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AS63">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
       <c r="AT63">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AU63">
         <v>8</v>
@@ -14462,25 +14462,25 @@
         <v>1.38</v>
       </c>
       <c r="AN64">
-        <v>0.86</v>
+        <v>2</v>
       </c>
       <c r="AO64">
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR64">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AS64">
-        <v>1.18</v>
+        <v>0.82</v>
       </c>
       <c r="AT64">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AU64">
         <v>7</v>
@@ -14671,22 +14671,22 @@
         <v>3</v>
       </c>
       <c r="AO65">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="AP65">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ65">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR65">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="AS65">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AT65">
-        <v>3.87</v>
+        <v>4.1</v>
       </c>
       <c r="AU65">
         <v>7</v>
@@ -14874,25 +14874,25 @@
         <v>3</v>
       </c>
       <c r="AN66">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AO66">
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ66">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR66">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AS66">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="AT66">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AU66">
         <v>9</v>
@@ -15080,25 +15080,25 @@
         <v>2.2</v>
       </c>
       <c r="AN67">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AO67">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR67">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AS67">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AT67">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="AU67">
         <v>10</v>
@@ -15286,25 +15286,25 @@
         <v>2.15</v>
       </c>
       <c r="AN68">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO68">
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ68">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR68">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AS68">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AT68">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="AU68">
         <v>3</v>
@@ -15492,25 +15492,25 @@
         <v>2.18</v>
       </c>
       <c r="AN69">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AO69">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ69">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR69">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="AS69">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="AT69">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15698,25 +15698,25 @@
         <v>3.08</v>
       </c>
       <c r="AN70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO70">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ70">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR70">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="AS70">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AT70">
-        <v>3.02</v>
+        <v>3.51</v>
       </c>
       <c r="AU70">
         <v>9</v>
@@ -15907,22 +15907,22 @@
         <v>1</v>
       </c>
       <c r="AO71">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR71">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AS71">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AT71">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="AU71">
         <v>4</v>
@@ -16110,25 +16110,25 @@
         <v>0</v>
       </c>
       <c r="AN72">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="AO72">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ72">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR72">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AS72">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT72">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16322,19 +16322,19 @@
         <v>3</v>
       </c>
       <c r="AP73">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ73">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR73">
-        <v>1.89</v>
+        <v>2.44</v>
       </c>
       <c r="AS73">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AT73">
-        <v>4.17</v>
+        <v>4.51</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16522,25 +16522,25 @@
         <v>1.92</v>
       </c>
       <c r="AN74">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR74">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AS74">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AT74">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="AU74">
         <v>6</v>
@@ -16731,22 +16731,22 @@
         <v>0</v>
       </c>
       <c r="AO75">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP75">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ75">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR75">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AS75">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AT75">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16934,25 +16934,25 @@
         <v>1.17</v>
       </c>
       <c r="AN76">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO76">
+        <v>1.5</v>
+      </c>
+      <c r="AP76">
+        <v>2</v>
+      </c>
+      <c r="AQ76">
+        <v>1.67</v>
+      </c>
+      <c r="AR76">
+        <v>1.77</v>
+      </c>
+      <c r="AS76">
         <v>1.86</v>
       </c>
-      <c r="AP76">
-        <v>1.52</v>
-      </c>
-      <c r="AQ76">
-        <v>1.87</v>
-      </c>
-      <c r="AR76">
-        <v>1.41</v>
-      </c>
-      <c r="AS76">
-        <v>1.82</v>
-      </c>
       <c r="AT76">
-        <v>3.23</v>
+        <v>3.63</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17140,25 +17140,25 @@
         <v>1.68</v>
       </c>
       <c r="AN77">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AO77">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="AS77">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AT77">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AU77">
         <v>0</v>
@@ -17346,25 +17346,25 @@
         <v>1.32</v>
       </c>
       <c r="AN78">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AO78">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AQ78">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR78">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AS78">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AT78">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="AU78">
         <v>5</v>
@@ -17552,25 +17552,25 @@
         <v>1.1</v>
       </c>
       <c r="AN79">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AO79">
-        <v>2.17</v>
+        <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ79">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR79">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AS79">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AT79">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17758,25 +17758,25 @@
         <v>1.88</v>
       </c>
       <c r="AN80">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO80">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ80">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR80">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="AS80">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="AT80">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AU80">
         <v>5</v>
@@ -17964,25 +17964,25 @@
         <v>1.4</v>
       </c>
       <c r="AN81">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="AO81">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="AP81">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ81">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR81">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AS81">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="AT81">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -18170,25 +18170,25 @@
         <v>1.65</v>
       </c>
       <c r="AN82">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AO82">
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ82">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR82">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AS82">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AT82">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AU82">
         <v>4</v>
@@ -18379,22 +18379,22 @@
         <v>3</v>
       </c>
       <c r="AO83">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ83">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR83">
-        <v>2.21</v>
+        <v>2.49</v>
       </c>
       <c r="AS83">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="AT83">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="AU83">
         <v>10</v>
@@ -18582,25 +18582,25 @@
         <v>1.85</v>
       </c>
       <c r="AN84">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AO84">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR84">
-        <v>0.9399999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AS84">
-        <v>1.04</v>
+        <v>0.83</v>
       </c>
       <c r="AT84">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AU84">
         <v>12</v>
@@ -18788,25 +18788,25 @@
         <v>1.55</v>
       </c>
       <c r="AN85">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="AO85">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AP85">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ85">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR85">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AS85">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AT85">
-        <v>3.07</v>
+        <v>3.26</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18994,25 +18994,25 @@
         <v>1.28</v>
       </c>
       <c r="AN86">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AO86">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ86">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR86">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AS86">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AT86">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="AU86">
         <v>3</v>
@@ -19200,25 +19200,25 @@
         <v>4.2</v>
       </c>
       <c r="AN87">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO87">
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ87">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR87">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AS87">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AT87">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AU87">
         <v>10</v>
@@ -19406,25 +19406,25 @@
         <v>3.3</v>
       </c>
       <c r="AN88">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AO88">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ88">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR88">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="AS88">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="AT88">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="AU88">
         <v>8</v>
@@ -19612,25 +19612,25 @@
         <v>2.55</v>
       </c>
       <c r="AN89">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AO89">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ89">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR89">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="AS89">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
       <c r="AT89">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="AU89">
         <v>7</v>
@@ -19818,25 +19818,25 @@
         <v>2.45</v>
       </c>
       <c r="AN90">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="AO90">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ90">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR90">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AS90">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AT90">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AU90">
         <v>3</v>
@@ -20024,22 +20024,22 @@
         <v>1.17</v>
       </c>
       <c r="AN91">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AO91">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP91">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ91">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="AS91">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AT91">
         <v>2.76</v>
@@ -20230,25 +20230,25 @@
         <v>1.63</v>
       </c>
       <c r="AN92">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AO92">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ92">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR92">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AS92">
-        <v>1.09</v>
+        <v>0.8</v>
       </c>
       <c r="AT92">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AU92">
         <v>4</v>
@@ -20436,25 +20436,25 @@
         <v>1.36</v>
       </c>
       <c r="AN93">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="AO93">
         <v>3</v>
       </c>
       <c r="AP93">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ93">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR93">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AS93">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="AT93">
-        <v>3.91</v>
+        <v>4.03</v>
       </c>
       <c r="AU93">
         <v>9</v>
@@ -20642,25 +20642,25 @@
         <v>2.5</v>
       </c>
       <c r="AN94">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AO94">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ94">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR94">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AS94">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AT94">
-        <v>3.54</v>
+        <v>3.23</v>
       </c>
       <c r="AU94">
         <v>5</v>
@@ -20848,25 +20848,25 @@
         <v>1.7</v>
       </c>
       <c r="AN95">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AO95">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AP95">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR95">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AS95">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AT95">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AU95">
         <v>4</v>
@@ -21057,22 +21057,22 @@
         <v>1.4</v>
       </c>
       <c r="AO96">
+        <v>0.4</v>
+      </c>
+      <c r="AP96">
+        <v>2</v>
+      </c>
+      <c r="AQ96">
+        <v>0.73</v>
+      </c>
+      <c r="AR96">
+        <v>1.62</v>
+      </c>
+      <c r="AS96">
         <v>0.8</v>
       </c>
-      <c r="AP96">
-        <v>1.52</v>
-      </c>
-      <c r="AQ96">
-        <v>1.09</v>
-      </c>
-      <c r="AR96">
-        <v>1.35</v>
-      </c>
-      <c r="AS96">
-        <v>0.98</v>
-      </c>
       <c r="AT96">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AU96">
         <v>8</v>
@@ -21260,25 +21260,25 @@
         <v>1.96</v>
       </c>
       <c r="AN97">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO97">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AP97">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ97">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR97">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AS97">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AT97">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="AU97">
         <v>7</v>
@@ -21466,25 +21466,25 @@
         <v>1.5</v>
       </c>
       <c r="AN98">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AO98">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AP98">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ98">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR98">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AS98">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AT98">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="AU98">
         <v>4</v>
@@ -21672,25 +21672,25 @@
         <v>1.48</v>
       </c>
       <c r="AN99">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AO99">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR99">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AS99">
         <v>1.24</v>
       </c>
       <c r="AT99">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AU99">
         <v>4</v>
@@ -21878,25 +21878,25 @@
         <v>2.85</v>
       </c>
       <c r="AN100">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AO100">
-        <v>1.09</v>
+        <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ100">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR100">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AS100">
-        <v>1.18</v>
+        <v>0.95</v>
       </c>
       <c r="AT100">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="AU100">
         <v>7</v>
@@ -22084,25 +22084,25 @@
         <v>1.48</v>
       </c>
       <c r="AN101">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AO101">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AQ101">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR101">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AS101">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AT101">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AU101">
         <v>6</v>
@@ -22290,25 +22290,25 @@
         <v>1.47</v>
       </c>
       <c r="AN102">
-        <v>0.82</v>
+        <v>1.2</v>
       </c>
       <c r="AO102">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ102">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR102">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="AS102">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AT102">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AU102">
         <v>5</v>
@@ -22496,25 +22496,25 @@
         <v>1.06</v>
       </c>
       <c r="AN103">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AO103">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ103">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR103">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AS103">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AT103">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22702,25 +22702,25 @@
         <v>1.2</v>
       </c>
       <c r="AN104">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="AO104">
-        <v>1.18</v>
+        <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ104">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR104">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AS104">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AT104">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AU104">
         <v>4</v>
@@ -22908,25 +22908,25 @@
         <v>1.01</v>
       </c>
       <c r="AN105">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AO105">
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ105">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR105">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AS105">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AT105">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AU105">
         <v>5</v>
@@ -23114,25 +23114,25 @@
         <v>1.48</v>
       </c>
       <c r="AN106">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AO106">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AP106">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ106">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR106">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AS106">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AT106">
-        <v>3.56</v>
+        <v>3.43</v>
       </c>
       <c r="AU106">
         <v>8</v>
@@ -23320,25 +23320,25 @@
         <v>1.48</v>
       </c>
       <c r="AN107">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="AO107">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ107">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR107">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AS107">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AT107">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="AU107">
         <v>2</v>
@@ -23526,25 +23526,25 @@
         <v>2.85</v>
       </c>
       <c r="AN108">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AO108">
+        <v>1</v>
+      </c>
+      <c r="AP108">
+        <v>1.83</v>
+      </c>
+      <c r="AQ108">
         <v>1.09</v>
       </c>
-      <c r="AP108">
-        <v>1.87</v>
-      </c>
-      <c r="AQ108">
-        <v>1.04</v>
-      </c>
       <c r="AR108">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AS108">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
       <c r="AT108">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23732,25 +23732,25 @@
         <v>2.5</v>
       </c>
       <c r="AN109">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO109">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR109">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AS109">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AT109">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="AU109">
         <v>4</v>
@@ -23938,25 +23938,25 @@
         <v>3.6</v>
       </c>
       <c r="AN110">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AO110">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AP110">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ110">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR110">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AS110">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AT110">
-        <v>3.24</v>
+        <v>2.82</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24144,25 +24144,25 @@
         <v>2.05</v>
       </c>
       <c r="AN111">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO111">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP111">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ111">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR111">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AS111">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT111">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AU111">
         <v>4</v>
@@ -24350,25 +24350,25 @@
         <v>5.5</v>
       </c>
       <c r="AN112">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AO112">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP112">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ112">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR112">
-        <v>2.13</v>
+        <v>2.46</v>
       </c>
       <c r="AS112">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AT112">
-        <v>3.23</v>
+        <v>3.52</v>
       </c>
       <c r="AU112">
         <v>7</v>
@@ -24556,25 +24556,25 @@
         <v>1.22</v>
       </c>
       <c r="AN113">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AO113">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AP113">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ113">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR113">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AS113">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AT113">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="AU113">
         <v>0</v>
@@ -24762,25 +24762,25 @@
         <v>1.65</v>
       </c>
       <c r="AN114">
+        <v>1.67</v>
+      </c>
+      <c r="AO114">
+        <v>2.6</v>
+      </c>
+      <c r="AP114">
         <v>1.33</v>
       </c>
-      <c r="AO114">
-        <v>2.55</v>
-      </c>
-      <c r="AP114">
-        <v>1.09</v>
-      </c>
       <c r="AQ114">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR114">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AS114">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AT114">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24968,25 +24968,25 @@
         <v>1.33</v>
       </c>
       <c r="AN115">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="AO115">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ115">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR115">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AS115">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AT115">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AU115">
         <v>5</v>
@@ -25174,25 +25174,25 @@
         <v>1.65</v>
       </c>
       <c r="AN116">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AO116">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ116">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR116">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="AS116">
-        <v>1.11</v>
+        <v>0.88</v>
       </c>
       <c r="AT116">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AU116">
         <v>5</v>
@@ -25380,25 +25380,25 @@
         <v>5.75</v>
       </c>
       <c r="AN117">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="AO117">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP117">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ117">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR117">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AS117">
-        <v>1.01</v>
+        <v>0.84</v>
       </c>
       <c r="AT117">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="AU117">
         <v>0</v>
@@ -25586,25 +25586,25 @@
         <v>2.5</v>
       </c>
       <c r="AN118">
-        <v>1.08</v>
+        <v>2.33</v>
       </c>
       <c r="AO118">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ118">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR118">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AS118">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT118">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AU118">
         <v>5</v>
@@ -25792,25 +25792,25 @@
         <v>1.83</v>
       </c>
       <c r="AN119">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AO119">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="AP119">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ119">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR119">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="AS119">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AT119">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25998,25 +25998,25 @@
         <v>1.75</v>
       </c>
       <c r="AN120">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AO120">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AQ120">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR120">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AS120">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="AT120">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AU120">
         <v>8</v>
@@ -26204,25 +26204,25 @@
         <v>3.75</v>
       </c>
       <c r="AN121">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AO121">
-        <v>1.31</v>
+        <v>0.83</v>
       </c>
       <c r="AP121">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ121">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR121">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AS121">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AT121">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="AU121">
         <v>11</v>
@@ -26410,25 +26410,25 @@
         <v>1.48</v>
       </c>
       <c r="AN122">
-        <v>0.92</v>
+        <v>1.5</v>
       </c>
       <c r="AO122">
-        <v>0.85</v>
+        <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ122">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR122">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AS122">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AT122">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="AU122">
         <v>4</v>
@@ -26616,25 +26616,25 @@
         <v>1.16</v>
       </c>
       <c r="AN123">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AO123">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="AP123">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ123">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR123">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AS123">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AT123">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="AU123">
         <v>4</v>
@@ -26822,25 +26822,25 @@
         <v>2.4</v>
       </c>
       <c r="AN124">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AO124">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ124">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR124">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AS124">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AT124">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="AU124">
         <v>7</v>
@@ -27028,25 +27028,25 @@
         <v>3.3</v>
       </c>
       <c r="AN125">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="AO125">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ125">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR125">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AS125">
-        <v>1.17</v>
+        <v>0.96</v>
       </c>
       <c r="AT125">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27234,25 +27234,25 @@
         <v>1.22</v>
       </c>
       <c r="AN126">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="AO126">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AP126">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ126">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR126">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AS126">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AT126">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="AU126">
         <v>9</v>
@@ -27440,25 +27440,25 @@
         <v>2.24</v>
       </c>
       <c r="AN127">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="AO127">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="AP127">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ127">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR127">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AS127">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AT127">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="AU127">
         <v>2</v>
@@ -27646,25 +27646,25 @@
         <v>2.8</v>
       </c>
       <c r="AN128">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="AO128">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ128">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR128">
-        <v>2.11</v>
+        <v>2.46</v>
       </c>
       <c r="AS128">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AT128">
-        <v>4.02</v>
+        <v>4.18</v>
       </c>
       <c r="AU128">
         <v>13</v>
@@ -27852,25 +27852,25 @@
         <v>1.78</v>
       </c>
       <c r="AN129">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AO129">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP129">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ129">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR129">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="AS129">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="AT129">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AU129">
         <v>10</v>
@@ -28058,25 +28058,25 @@
         <v>2</v>
       </c>
       <c r="AN130">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="AO130">
-        <v>1.36</v>
+        <v>0.57</v>
       </c>
       <c r="AP130">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ130">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR130">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AS130">
-        <v>1.11</v>
+        <v>0.9</v>
       </c>
       <c r="AT130">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AU130">
         <v>6</v>
@@ -28264,25 +28264,25 @@
         <v>1.02</v>
       </c>
       <c r="AN131">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AO131">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AP131">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ131">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR131">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AS131">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AT131">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28470,25 +28470,25 @@
         <v>1.5</v>
       </c>
       <c r="AN132">
-        <v>0.93</v>
+        <v>1.29</v>
       </c>
       <c r="AO132">
-        <v>1.29</v>
+        <v>0.86</v>
       </c>
       <c r="AP132">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ132">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR132">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="AS132">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AT132">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AU132">
         <v>9</v>
@@ -28676,25 +28676,25 @@
         <v>1.77</v>
       </c>
       <c r="AN133">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="AO133">
-        <v>1.07</v>
+        <v>0.43</v>
       </c>
       <c r="AP133">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AQ133">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR133">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AS133">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="AT133">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AU133">
         <v>7</v>
@@ -28885,22 +28885,22 @@
         <v>1.14</v>
       </c>
       <c r="AO134">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AP134">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ134">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR134">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="AS134">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AT134">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AU134">
         <v>4</v>
@@ -29088,25 +29088,25 @@
         <v>1.4</v>
       </c>
       <c r="AN135">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AO135">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ135">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR135">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AS135">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AT135">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="AU135">
         <v>5</v>
@@ -29294,25 +29294,25 @@
         <v>1.2</v>
       </c>
       <c r="AN136">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="AO136">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ136">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR136">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AS136">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AT136">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29500,25 +29500,25 @@
         <v>1.63</v>
       </c>
       <c r="AN137">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="AO137">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AP137">
+        <v>1.42</v>
+      </c>
+      <c r="AQ137">
         <v>1.09</v>
       </c>
-      <c r="AQ137">
-        <v>1.04</v>
-      </c>
       <c r="AR137">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AS137">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="AT137">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AU137">
         <v>3</v>
@@ -29706,25 +29706,25 @@
         <v>1.05</v>
       </c>
       <c r="AN138">
-        <v>1.2</v>
+        <v>2.14</v>
       </c>
       <c r="AO138">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AP138">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ138">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR138">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AS138">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="AT138">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="AU138">
         <v>6</v>
@@ -29912,25 +29912,25 @@
         <v>2.35</v>
       </c>
       <c r="AN139">
-        <v>1.27</v>
+        <v>1.71</v>
       </c>
       <c r="AO139">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ139">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR139">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AS139">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="AT139">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AU139">
         <v>9</v>
@@ -30118,25 +30118,25 @@
         <v>4.75</v>
       </c>
       <c r="AN140">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AO140">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ140">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR140">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AS140">
-        <v>1.21</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT140">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AU140">
         <v>8</v>
@@ -30324,25 +30324,25 @@
         <v>1.78</v>
       </c>
       <c r="AN141">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AO141">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AP141">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ141">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR141">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AS141">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="AT141">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU141">
         <v>9</v>
@@ -30530,25 +30530,25 @@
         <v>1.8</v>
       </c>
       <c r="AN142">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AO142">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ142">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR142">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AS142">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AT142">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="AU142">
         <v>8</v>
@@ -30736,25 +30736,25 @@
         <v>3.1</v>
       </c>
       <c r="AN143">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="AO143">
-        <v>1.07</v>
+        <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ143">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR143">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AS143">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AT143">
-        <v>3.03</v>
+        <v>3.14</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30942,25 +30942,25 @@
         <v>6.5</v>
       </c>
       <c r="AN144">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="AO144">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="AP144">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ144">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR144">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="AS144">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AT144">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="AU144">
         <v>9</v>
@@ -31148,25 +31148,25 @@
         <v>1.33</v>
       </c>
       <c r="AN145">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="AO145">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AP145">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ145">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR145">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AS145">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AT145">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AU145">
         <v>3</v>
@@ -31354,25 +31354,25 @@
         <v>1.44</v>
       </c>
       <c r="AN146">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="AO146">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP146">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ146">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR146">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AS146">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="AT146">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AU146">
         <v>8</v>
@@ -31560,25 +31560,25 @@
         <v>2.3</v>
       </c>
       <c r="AN147">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AO147">
-        <v>1.38</v>
+        <v>0.88</v>
       </c>
       <c r="AP147">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ147">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR147">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AS147">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AT147">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31766,25 +31766,25 @@
         <v>1.36</v>
       </c>
       <c r="AN148">
+        <v>0.5</v>
+      </c>
+      <c r="AO148">
         <v>0.38</v>
       </c>
-      <c r="AO148">
-        <v>1.31</v>
-      </c>
       <c r="AP148">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ148">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR148">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AS148">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AT148">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AU148">
         <v>9</v>
@@ -31972,25 +31972,25 @@
         <v>1.65</v>
       </c>
       <c r="AN149">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="AO149">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AP149">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ149">
+        <v>1.25</v>
+      </c>
+      <c r="AR149">
         <v>1.83</v>
       </c>
-      <c r="AR149">
-        <v>1.64</v>
-      </c>
       <c r="AS149">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AT149">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AU149">
         <v>6</v>
@@ -32178,25 +32178,25 @@
         <v>1.19</v>
       </c>
       <c r="AN150">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO150">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AP150">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ150">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR150">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AS150">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AT150">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="AU150">
         <v>4</v>
@@ -32384,25 +32384,25 @@
         <v>2.25</v>
       </c>
       <c r="AN151">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AO151">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AP151">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ151">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR151">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="AS151">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AT151">
-        <v>3.99</v>
+        <v>4.5</v>
       </c>
       <c r="AU151">
         <v>8</v>
@@ -32590,25 +32590,25 @@
         <v>2.25</v>
       </c>
       <c r="AN152">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO152">
-        <v>1.38</v>
+        <v>0.88</v>
       </c>
       <c r="AP152">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ152">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR152">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AS152">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AT152">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AU152">
         <v>7</v>
@@ -32796,25 +32796,25 @@
         <v>1.45</v>
       </c>
       <c r="AN153">
+        <v>1</v>
+      </c>
+      <c r="AO153">
+        <v>0.86</v>
+      </c>
+      <c r="AP153">
+        <v>1</v>
+      </c>
+      <c r="AQ153">
+        <v>0.82</v>
+      </c>
+      <c r="AR153">
+        <v>1.13</v>
+      </c>
+      <c r="AS153">
         <v>1.19</v>
       </c>
-      <c r="AO153">
-        <v>1.06</v>
-      </c>
-      <c r="AP153">
-        <v>1.04</v>
-      </c>
-      <c r="AQ153">
-        <v>1.09</v>
-      </c>
-      <c r="AR153">
-        <v>0.97</v>
-      </c>
-      <c r="AS153">
-        <v>1.41</v>
-      </c>
       <c r="AT153">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AU153">
         <v>9</v>
@@ -33002,25 +33002,25 @@
         <v>1.4</v>
       </c>
       <c r="AN154">
-        <v>1.47</v>
+        <v>1.88</v>
       </c>
       <c r="AO154">
-        <v>1.47</v>
+        <v>1</v>
       </c>
       <c r="AP154">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ154">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR154">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AS154">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="AT154">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AU154">
         <v>4</v>
@@ -33208,25 +33208,25 @@
         <v>1.44</v>
       </c>
       <c r="AN155">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AO155">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ155">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR155">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AS155">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT155">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="AU155">
         <v>4</v>
@@ -33414,25 +33414,25 @@
         <v>6</v>
       </c>
       <c r="AN156">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="AO156">
-        <v>0.41</v>
+        <v>0.25</v>
       </c>
       <c r="AP156">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ156">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR156">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AS156">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="AT156">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="AU156">
         <v>7</v>
@@ -33620,25 +33620,25 @@
         <v>1.46</v>
       </c>
       <c r="AN157">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO157">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP157">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ157">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR157">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AS157">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AT157">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="AU157">
         <v>4</v>
@@ -33826,25 +33826,25 @@
         <v>2.75</v>
       </c>
       <c r="AN158">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AO158">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AP158">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ158">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR158">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="AS158">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AT158">
-        <v>3.68</v>
+        <v>3.83</v>
       </c>
       <c r="AU158">
         <v>4</v>
@@ -34032,25 +34032,25 @@
         <v>2.85</v>
       </c>
       <c r="AN159">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AO159">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ159">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR159">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AS159">
-        <v>1.01</v>
+        <v>0.83</v>
       </c>
       <c r="AT159">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="AU159">
         <v>13</v>
@@ -34238,22 +34238,22 @@
         <v>1.95</v>
       </c>
       <c r="AN160">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO160">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="AP160">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AQ160">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR160">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AS160">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AT160">
         <v>2.36</v>
@@ -34444,25 +34444,25 @@
         <v>2.45</v>
       </c>
       <c r="AN161">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AO161">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AP161">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ161">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR161">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AS161">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AT161">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="AU161">
         <v>5</v>
@@ -34650,25 +34650,25 @@
         <v>1.62</v>
       </c>
       <c r="AN162">
-        <v>1.29</v>
+        <v>1.88</v>
       </c>
       <c r="AO162">
-        <v>1.24</v>
+        <v>0.33</v>
       </c>
       <c r="AP162">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ162">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR162">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AS162">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AT162">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AU162">
         <v>8</v>
@@ -34856,25 +34856,25 @@
         <v>1.06</v>
       </c>
       <c r="AN163">
-        <v>0.9399999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="AO163">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="AP163">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ163">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR163">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AS163">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AT163">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="AU163">
         <v>5</v>
@@ -35062,25 +35062,25 @@
         <v>1.46</v>
       </c>
       <c r="AN164">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="AO164">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AP164">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ164">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR164">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AS164">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AT164">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="AU164">
         <v>4</v>
@@ -35271,22 +35271,22 @@
         <v>1.22</v>
       </c>
       <c r="AO165">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AP165">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ165">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR165">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AS165">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AT165">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AU165">
         <v>2</v>
@@ -35474,25 +35474,25 @@
         <v>2.25</v>
       </c>
       <c r="AN166">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="AO166">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ166">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR166">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AS166">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AT166">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="AU166">
         <v>5</v>
@@ -35680,25 +35680,25 @@
         <v>1.19</v>
       </c>
       <c r="AN167">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AO167">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AP167">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ167">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR167">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AS167">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AT167">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35886,25 +35886,25 @@
         <v>1.57</v>
       </c>
       <c r="AN168">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="AO168">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ168">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR168">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AS168">
-        <v>1.18</v>
+        <v>0.91</v>
       </c>
       <c r="AT168">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="AU168">
         <v>4</v>
@@ -36092,25 +36092,25 @@
         <v>1.16</v>
       </c>
       <c r="AN169">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AO169">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="AP169">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ169">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR169">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AS169">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AT169">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="AU169">
         <v>3</v>
@@ -36298,25 +36298,25 @@
         <v>1.93</v>
       </c>
       <c r="AN170">
+        <v>1.22</v>
+      </c>
+      <c r="AO170">
         <v>1.11</v>
       </c>
-      <c r="AO170">
-        <v>1.39</v>
-      </c>
       <c r="AP170">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ170">
+        <v>0.92</v>
+      </c>
+      <c r="AR170">
+        <v>1.58</v>
+      </c>
+      <c r="AS170">
         <v>1.13</v>
       </c>
-      <c r="AR170">
-        <v>1.42</v>
-      </c>
-      <c r="AS170">
-        <v>1.23</v>
-      </c>
       <c r="AT170">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="AU170">
         <v>8</v>
@@ -36504,25 +36504,25 @@
         <v>2.45</v>
       </c>
       <c r="AN171">
-        <v>0.72</v>
+        <v>0.44</v>
       </c>
       <c r="AO171">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
       <c r="AP171">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ171">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR171">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AS171">
-        <v>1.09</v>
+        <v>0.97</v>
       </c>
       <c r="AT171">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AU171">
         <v>6</v>
@@ -36710,25 +36710,25 @@
         <v>1.27</v>
       </c>
       <c r="AN172">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AO172">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="AP172">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ172">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR172">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AS172">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AT172">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="AU172">
         <v>4</v>
@@ -36916,25 +36916,25 @@
         <v>7.5</v>
       </c>
       <c r="AN173">
-        <v>2.42</v>
+        <v>2.78</v>
       </c>
       <c r="AO173">
-        <v>1.32</v>
+        <v>0.78</v>
       </c>
       <c r="AP173">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ173">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR173">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="AS173">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AT173">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AU173">
         <v>10</v>
@@ -37122,25 +37122,25 @@
         <v>1.62</v>
       </c>
       <c r="AN174">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="AO174">
-        <v>1.26</v>
+        <v>0.6</v>
       </c>
       <c r="AP174">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AQ174">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR174">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AS174">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AT174">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="AU174">
         <v>8</v>
@@ -37328,25 +37328,25 @@
         <v>1.73</v>
       </c>
       <c r="AN175">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AO175">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP175">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ175">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR175">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AS175">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AT175">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AU175">
         <v>2</v>
@@ -37534,25 +37534,25 @@
         <v>1.46</v>
       </c>
       <c r="AN176">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO176">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AP176">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ176">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR176">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AS176">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="AT176">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AU176">
         <v>4</v>
@@ -37740,25 +37740,25 @@
         <v>2.3</v>
       </c>
       <c r="AN177">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AO177">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AP177">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ177">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR177">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AS177">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AT177">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AU177">
         <v>6</v>
@@ -37946,25 +37946,25 @@
         <v>1.6</v>
       </c>
       <c r="AN178">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO178">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ178">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR178">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AS178">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AT178">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AU178">
         <v>0</v>
@@ -38152,25 +38152,25 @@
         <v>1.82</v>
       </c>
       <c r="AN179">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO179">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ179">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR179">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AS179">
-        <v>1.15</v>
+        <v>0.95</v>
       </c>
       <c r="AT179">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AU179">
         <v>6</v>
@@ -38358,25 +38358,25 @@
         <v>1.3</v>
       </c>
       <c r="AN180">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AO180">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AP180">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ180">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR180">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AS180">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AT180">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AU180">
         <v>7</v>
@@ -38564,25 +38564,25 @@
         <v>1.73</v>
       </c>
       <c r="AN181">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AO181">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ181">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="AR181">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AS181">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AT181">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="AU181">
         <v>6</v>
@@ -38770,25 +38770,25 @@
         <v>1.11</v>
       </c>
       <c r="AN182">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AO182">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AP182">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ182">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AR182">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AS182">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AT182">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="AU182">
         <v>9</v>
@@ -38976,25 +38976,25 @@
         <v>1.66</v>
       </c>
       <c r="AN183">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="AO183">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="AP183">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AQ183">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR183">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AS183">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AT183">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AU183">
         <v>6</v>
@@ -39182,25 +39182,25 @@
         <v>1.62</v>
       </c>
       <c r="AN184">
-        <v>2.37</v>
+        <v>2.78</v>
       </c>
       <c r="AO184">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AP184">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ184">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR184">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AS184">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AT184">
-        <v>3.47</v>
+        <v>3.71</v>
       </c>
       <c r="AU184">
         <v>10</v>
@@ -39388,25 +39388,25 @@
         <v>1.47</v>
       </c>
       <c r="AN185">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AO185">
-        <v>1.79</v>
+        <v>1.3</v>
       </c>
       <c r="AP185">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ185">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR185">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="AS185">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AT185">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="AU185">
         <v>2</v>
@@ -39594,25 +39594,25 @@
         <v>1.95</v>
       </c>
       <c r="AN186">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="AO186">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AP186">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AQ186">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AR186">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AS186">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AT186">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AU186">
         <v>5</v>
@@ -39800,25 +39800,25 @@
         <v>1.21</v>
       </c>
       <c r="AN187">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AO187">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AP187">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AQ187">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR187">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AS187">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AT187">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AU187">
         <v>2</v>
@@ -40006,25 +40006,25 @@
         <v>1.32</v>
       </c>
       <c r="AN188">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AO188">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AQ188">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR188">
+        <v>1.33</v>
+      </c>
+      <c r="AS188">
         <v>1.17</v>
       </c>
-      <c r="AS188">
-        <v>1.45</v>
-      </c>
       <c r="AT188">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AU188">
         <v>8</v>
@@ -40212,25 +40212,25 @@
         <v>6</v>
       </c>
       <c r="AN189">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AO189">
         <v>1.1</v>
       </c>
       <c r="AP189">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ189">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR189">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AS189">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AT189">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="AU189">
         <v>7</v>
@@ -40418,25 +40418,25 @@
         <v>1.41</v>
       </c>
       <c r="AN190">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AO190">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AQ190">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR190">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AS190">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AT190">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AU190">
         <v>7</v>
@@ -40624,25 +40624,25 @@
         <v>3</v>
       </c>
       <c r="AN191">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AO191">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="AP191">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AQ191">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR191">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AS191">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AT191">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="AU191">
         <v>6</v>
@@ -40830,25 +40830,25 @@
         <v>3</v>
       </c>
       <c r="AN192">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AO192">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP192">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AQ192">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR192">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AS192">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AT192">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="AU192">
         <v>6</v>
@@ -41036,25 +41036,25 @@
         <v>1.46</v>
       </c>
       <c r="AN193">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AO193">
-        <v>1.24</v>
+        <v>0.7</v>
       </c>
       <c r="AP193">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="AQ193">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AR193">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AS193">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AT193">
-        <v>2.54</v>
+        <v>2.37</v>
       </c>
       <c r="AU193">
         <v>8</v>
@@ -41242,25 +41242,25 @@
         <v>1.12</v>
       </c>
       <c r="AN194">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AO194">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AP194">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AQ194">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="AR194">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AS194">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AT194">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AU194">
         <v>4</v>
@@ -41448,25 +41448,25 @@
         <v>2.85</v>
       </c>
       <c r="AN195">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AO195">
-        <v>1.14</v>
+        <v>0.8</v>
       </c>
       <c r="AP195">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ195">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="AR195">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AS195">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AT195">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="AU195">
         <v>8</v>
@@ -41654,22 +41654,22 @@
         <v>1.27</v>
       </c>
       <c r="AN196">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="AO196">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AP196">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AQ196">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AR196">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AS196">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AT196">
         <v>3.37</v>
@@ -41860,25 +41860,25 @@
         <v>1.9</v>
       </c>
       <c r="AN197">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AO197">
-        <v>0.91</v>
+        <v>1.09</v>
       </c>
       <c r="AP197">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AQ197">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR197">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="AS197">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AT197">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AU197">
         <v>4</v>
@@ -42066,25 +42066,25 @@
         <v>3.2</v>
       </c>
       <c r="AN198">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="AO198">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="AP198">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AQ198">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AR198">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AS198">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AT198">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AU198">
         <v>20</v>
@@ -42272,25 +42272,25 @@
         <v>1.18</v>
       </c>
       <c r="AN199">
-        <v>1.18</v>
+        <v>1.73</v>
       </c>
       <c r="AO199">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AP199">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AQ199">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AR199">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS199">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AT199">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="AU199">
         <v>3</v>
@@ -42481,22 +42481,22 @@
         <v>1.09</v>
       </c>
       <c r="AO200">
+        <v>0.45</v>
+      </c>
+      <c r="AP200">
+        <v>1</v>
+      </c>
+      <c r="AQ200">
+        <v>0.67</v>
+      </c>
+      <c r="AR200">
+        <v>1.12</v>
+      </c>
+      <c r="AS200">
         <v>1.09</v>
       </c>
-      <c r="AP200">
-        <v>1.04</v>
-      </c>
-      <c r="AQ200">
-        <v>1.17</v>
-      </c>
-      <c r="AR200">
-        <v>1.01</v>
-      </c>
-      <c r="AS200">
-        <v>1.27</v>
-      </c>
       <c r="AT200">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AU200">
         <v>8</v>
@@ -42684,25 +42684,25 @@
         <v>2.45</v>
       </c>
       <c r="AN201">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AO201">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AP201">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AQ201">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AR201">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AS201">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AT201">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="AU201">
         <v>5</v>
@@ -42890,25 +42890,25 @@
         <v>1.62</v>
       </c>
       <c r="AN202">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AO202">
-        <v>1.18</v>
+        <v>0.55</v>
       </c>
       <c r="AP202">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AQ202">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AR202">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AS202">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AT202">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="AU202">
         <v>6</v>
@@ -43096,25 +43096,25 @@
         <v>3</v>
       </c>
       <c r="AN203">
-        <v>1.71</v>
+        <v>2.33</v>
       </c>
       <c r="AO203">
-        <v>0.77</v>
+        <v>0.55</v>
       </c>
       <c r="AP203">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ203">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="AR203">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AS203">
         <v>1.29</v>
       </c>
       <c r="AT203">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="AU203">
         <v>5</v>
@@ -43302,25 +43302,25 @@
         <v>4.2</v>
       </c>
       <c r="AN204">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AO204">
-        <v>1.09</v>
+        <v>0.8</v>
       </c>
       <c r="AP204">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ204">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="AR204">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AS204">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="AT204">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AU204">
         <v>7</v>
@@ -43508,25 +43508,25 @@
         <v>4.8</v>
       </c>
       <c r="AN205">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AO205">
         <v>0.64</v>
       </c>
       <c r="AP205">
+        <v>2.09</v>
+      </c>
+      <c r="AQ205">
+        <v>0.58</v>
+      </c>
+      <c r="AR205">
         <v>1.87</v>
       </c>
-      <c r="AQ205">
-        <v>0.61</v>
-      </c>
-      <c r="AR205">
-        <v>1.92</v>
-      </c>
       <c r="AS205">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AT205">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="AU205">
         <v>9</v>
@@ -43714,25 +43714,25 @@
         <v>2.3</v>
       </c>
       <c r="AN206">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="AO206">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="AP206">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ206">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="AR206">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AS206">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT206">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="AU206">
         <v>7</v>
@@ -43920,25 +43920,25 @@
         <v>2.55</v>
       </c>
       <c r="AN207">
-        <v>2.45</v>
+        <v>2.82</v>
       </c>
       <c r="AO207">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="AP207">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AQ207">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AR207">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AS207">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AT207">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AU207">
         <v>7</v>
@@ -44126,25 +44126,25 @@
         <v>2.95</v>
       </c>
       <c r="AN208">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AO208">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AP208">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AQ208">
+        <v>0.92</v>
+      </c>
+      <c r="AR208">
+        <v>1.81</v>
+      </c>
+      <c r="AS208">
         <v>1.13</v>
       </c>
-      <c r="AR208">
-        <v>1.64</v>
-      </c>
-      <c r="AS208">
-        <v>1.24</v>
-      </c>
       <c r="AT208">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AU208">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1002,6 +1002,9 @@
   <si>
     <t>['45', '74']</t>
   </si>
+  <si>
+    <t>['8', '90+4']</t>
+  </si>
 </sst>
 </file>
 
@@ -1362,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3141,7 +3144,7 @@
         <v>2</v>
       </c>
       <c r="AQ9">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -4374,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -6846,7 +6849,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ27">
         <v>1.91</v>
@@ -9115,7 +9118,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ38">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR38">
         <v>0.83</v>
@@ -10351,7 +10354,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ44">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR44">
         <v>1.45</v>
@@ -10966,7 +10969,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -13029,7 +13032,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ57">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13850,7 +13853,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ61">
         <v>2.09</v>
@@ -16734,7 +16737,7 @@
         <v>1.5</v>
       </c>
       <c r="AP75">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ75">
         <v>1.25</v>
@@ -17149,7 +17152,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR77">
         <v>1.05</v>
@@ -21678,7 +21681,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ99">
         <v>0.58</v>
@@ -22299,7 +22302,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ102">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR102">
         <v>1.15</v>
@@ -22708,7 +22711,7 @@
         <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ104">
         <v>0.82</v>
@@ -26213,7 +26216,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ121">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR121">
         <v>1.62</v>
@@ -28270,7 +28273,7 @@
         <v>2.14</v>
       </c>
       <c r="AP131">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ131">
         <v>1.67</v>
@@ -28479,7 +28482,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ132">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -31360,7 +31363,7 @@
         <v>0.5</v>
       </c>
       <c r="AP146">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ146">
         <v>0.73</v>
@@ -32599,7 +32602,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ152">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR152">
         <v>1.54</v>
@@ -36307,7 +36310,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ170">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR170">
         <v>1.58</v>
@@ -37540,7 +37543,7 @@
         <v>1.22</v>
       </c>
       <c r="AP176">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ176">
         <v>1.09</v>
@@ -38573,7 +38576,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ181">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR181">
         <v>1.53</v>
@@ -41042,7 +41045,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ193">
         <v>0.64</v>
@@ -44135,7 +44138,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ208">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR208">
         <v>1.81</v>
@@ -44211,6 +44214,212 @@
       </c>
       <c r="BP208">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7466266</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F209">
+        <v>24</v>
+      </c>
+      <c r="G209" t="s">
+        <v>83</v>
+      </c>
+      <c r="H209" t="s">
+        <v>79</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>2</v>
+      </c>
+      <c r="N209">
+        <v>3</v>
+      </c>
+      <c r="O209" t="s">
+        <v>160</v>
+      </c>
+      <c r="P209" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q209">
+        <v>2.6</v>
+      </c>
+      <c r="R209">
+        <v>2.38</v>
+      </c>
+      <c r="S209">
+        <v>3.75</v>
+      </c>
+      <c r="T209">
+        <v>1.3</v>
+      </c>
+      <c r="U209">
+        <v>3.4</v>
+      </c>
+      <c r="V209">
+        <v>2.38</v>
+      </c>
+      <c r="W209">
+        <v>1.53</v>
+      </c>
+      <c r="X209">
+        <v>6</v>
+      </c>
+      <c r="Y209">
+        <v>1.13</v>
+      </c>
+      <c r="Z209">
+        <v>2.34</v>
+      </c>
+      <c r="AA209">
+        <v>3.99</v>
+      </c>
+      <c r="AB209">
+        <v>2.8</v>
+      </c>
+      <c r="AC209">
+        <v>1.03</v>
+      </c>
+      <c r="AD209">
+        <v>15</v>
+      </c>
+      <c r="AE209">
+        <v>1.18</v>
+      </c>
+      <c r="AF209">
+        <v>4.65</v>
+      </c>
+      <c r="AG209">
+        <v>1.63</v>
+      </c>
+      <c r="AH209">
+        <v>2.19</v>
+      </c>
+      <c r="AI209">
+        <v>1.53</v>
+      </c>
+      <c r="AJ209">
+        <v>2.38</v>
+      </c>
+      <c r="AK209">
+        <v>1.33</v>
+      </c>
+      <c r="AL209">
+        <v>1.25</v>
+      </c>
+      <c r="AM209">
+        <v>1.75</v>
+      </c>
+      <c r="AN209">
+        <v>1</v>
+      </c>
+      <c r="AO209">
+        <v>0.92</v>
+      </c>
+      <c r="AP209">
+        <v>0.92</v>
+      </c>
+      <c r="AQ209">
+        <v>1.08</v>
+      </c>
+      <c r="AR209">
+        <v>1.29</v>
+      </c>
+      <c r="AS209">
+        <v>1.12</v>
+      </c>
+      <c r="AT209">
+        <v>2.41</v>
+      </c>
+      <c r="AU209">
+        <v>2</v>
+      </c>
+      <c r="AV209">
+        <v>3</v>
+      </c>
+      <c r="AW209">
+        <v>17</v>
+      </c>
+      <c r="AX209">
+        <v>4</v>
+      </c>
+      <c r="AY209">
+        <v>20</v>
+      </c>
+      <c r="AZ209">
+        <v>7</v>
+      </c>
+      <c r="BA209">
+        <v>8</v>
+      </c>
+      <c r="BB209">
+        <v>1</v>
+      </c>
+      <c r="BC209">
+        <v>9</v>
+      </c>
+      <c r="BD209">
+        <v>1.95</v>
+      </c>
+      <c r="BE209">
+        <v>6.75</v>
+      </c>
+      <c r="BF209">
+        <v>2.02</v>
+      </c>
+      <c r="BG209">
+        <v>1.16</v>
+      </c>
+      <c r="BH209">
+        <v>4.4</v>
+      </c>
+      <c r="BI209">
+        <v>1.29</v>
+      </c>
+      <c r="BJ209">
+        <v>3.2</v>
+      </c>
+      <c r="BK209">
+        <v>1.48</v>
+      </c>
+      <c r="BL209">
+        <v>2.43</v>
+      </c>
+      <c r="BM209">
+        <v>1.76</v>
+      </c>
+      <c r="BN209">
+        <v>1.93</v>
+      </c>
+      <c r="BO209">
+        <v>2.18</v>
+      </c>
+      <c r="BP209">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="333">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,13 +715,19 @@
     <t>['33', '90+1']</t>
   </si>
   <si>
+    <t>['56', '86']</t>
+  </si>
+  <si>
     <t>['19', '80']</t>
   </si>
   <si>
-    <t>['56', '86']</t>
+    <t>['52']</t>
   </si>
   <si>
-    <t>['52']</t>
+    <t>['59']</t>
+  </si>
+  <si>
+    <t>['23', '74', '87']</t>
   </si>
   <si>
     <t>['8', '54']</t>
@@ -788,9 +794,6 @@
   </si>
   <si>
     <t>['16', '68', '72']</t>
-  </si>
-  <si>
-    <t>['59']</t>
   </si>
   <si>
     <t>['49', '64']</t>
@@ -1004,6 +1007,12 @@
   </si>
   <si>
     <t>['8', '90+4']</t>
+  </si>
+  <si>
+    <t>['30', '34']</t>
+  </si>
+  <si>
+    <t>['45+4']</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1699,10 +1708,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ2">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1905,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>1.09</v>
@@ -2033,7 +2042,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2114,7 +2123,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2445,7 +2454,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2935,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8">
         <v>0.73</v>
@@ -3063,7 +3072,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3141,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ9">
         <v>1.08</v>
@@ -4174,7 +4183,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ14">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4299,7 +4308,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4505,7 +4514,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4586,7 +4595,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4711,7 +4720,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5535,7 +5544,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5616,7 +5625,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR21">
         <v>0.96</v>
@@ -5741,7 +5750,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6025,7 +6034,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ23">
         <v>1.91</v>
@@ -6643,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6771,7 +6780,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7183,7 +7192,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7264,7 +7273,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ29">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR29">
         <v>2.19</v>
@@ -7470,7 +7479,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ30">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR30">
         <v>2.4</v>
@@ -7595,7 +7604,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7879,10 +7888,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ32">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR32">
         <v>1.07</v>
@@ -8500,7 +8509,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ35">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR35">
         <v>2.65</v>
@@ -8831,7 +8840,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -8909,7 +8918,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37">
         <v>1.67</v>
@@ -9243,7 +9252,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9449,7 +9458,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -10479,7 +10488,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10685,7 +10694,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10763,7 +10772,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ46">
         <v>1.09</v>
@@ -10891,7 +10900,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11097,7 +11106,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11175,7 +11184,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ48">
         <v>2.09</v>
@@ -11303,7 +11312,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11509,7 +11518,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11715,7 +11724,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11796,7 +11805,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ51">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR51">
         <v>0.82</v>
@@ -11999,10 +12008,10 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR52">
         <v>2.23</v>
@@ -12127,7 +12136,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12208,7 +12217,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12333,7 +12342,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12539,7 +12548,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12620,7 +12629,7 @@
         <v>1</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR55">
         <v>1.25</v>
@@ -12745,7 +12754,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13444,7 +13453,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ59">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR59">
         <v>2.11</v>
@@ -13647,7 +13656,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13775,7 +13784,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13981,7 +13990,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14474,7 +14483,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -14805,7 +14814,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14883,7 +14892,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ66">
         <v>0.5</v>
@@ -15011,7 +15020,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15089,7 +15098,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ67">
         <v>0.73</v>
@@ -15295,10 +15304,10 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR68">
         <v>2.17</v>
@@ -15629,7 +15638,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -16041,7 +16050,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16247,7 +16256,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16328,7 +16337,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ73">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR73">
         <v>2.44</v>
@@ -16740,7 +16749,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ75">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR75">
         <v>1.24</v>
@@ -16865,7 +16874,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -16943,7 +16952,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ76">
         <v>1.67</v>
@@ -17355,7 +17364,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78">
         <v>2.17</v>
@@ -17483,7 +17492,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17689,7 +17698,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17770,7 +17779,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ80">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR80">
         <v>1.12</v>
@@ -17976,7 +17985,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ81">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR81">
         <v>1.25</v>
@@ -18513,7 +18522,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18925,7 +18934,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19003,7 +19012,7 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ86">
         <v>1.67</v>
@@ -19543,7 +19552,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19749,7 +19758,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19827,7 +19836,7 @@
         <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>2.09</v>
@@ -20036,7 +20045,7 @@
         <v>1</v>
       </c>
       <c r="AQ91">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR91">
         <v>1.05</v>
@@ -20242,7 +20251,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ92">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR92">
         <v>1.39</v>
@@ -20367,7 +20376,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20448,7 +20457,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ93">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR93">
         <v>2.04</v>
@@ -20573,7 +20582,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20651,7 +20660,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>1.91</v>
@@ -20985,7 +20994,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21063,7 +21072,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ96">
         <v>0.73</v>
@@ -21397,7 +21406,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21887,7 +21896,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
         <v>0.73</v>
@@ -22093,7 +22102,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22427,7 +22436,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22508,7 +22517,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ103">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR103">
         <v>1.38</v>
@@ -22633,7 +22642,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22714,7 +22723,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ104">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR104">
         <v>1.2</v>
@@ -22839,7 +22848,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23045,7 +23054,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23457,7 +23466,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23741,7 +23750,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ109">
         <v>0.58</v>
@@ -23947,7 +23956,7 @@
         <v>0</v>
       </c>
       <c r="AP110">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>0.58</v>
@@ -24075,7 +24084,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24487,7 +24496,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24568,7 +24577,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ113">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR113">
         <v>1.21</v>
@@ -24693,7 +24702,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24899,7 +24908,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25105,7 +25114,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25186,7 +25195,7 @@
         <v>1</v>
       </c>
       <c r="AQ116">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR116">
         <v>1.02</v>
@@ -26007,7 +26016,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120">
         <v>1.09</v>
@@ -26213,7 +26222,7 @@
         <v>0.83</v>
       </c>
       <c r="AP121">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
         <v>1.08</v>
@@ -26547,7 +26556,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26625,10 +26634,10 @@
         <v>2.57</v>
       </c>
       <c r="AP123">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ123">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR123">
         <v>1.43</v>
@@ -26753,7 +26762,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27165,7 +27174,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27371,7 +27380,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27658,7 +27667,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ128">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR128">
         <v>2.46</v>
@@ -27861,10 +27870,10 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ129">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -27989,7 +27998,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28070,7 +28079,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ130">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR130">
         <v>1.55</v>
@@ -28195,7 +28204,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28401,7 +28410,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28685,7 +28694,7 @@
         <v>0.43</v>
       </c>
       <c r="AP133">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ133">
         <v>0.73</v>
@@ -28813,7 +28822,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29225,7 +29234,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29718,7 +29727,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ138">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR138">
         <v>1.59</v>
@@ -29843,7 +29852,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30049,7 +30058,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30127,7 +30136,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ140">
         <v>0.73</v>
@@ -30255,7 +30264,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30333,7 +30342,7 @@
         <v>1</v>
       </c>
       <c r="AP141">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -31079,7 +31088,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31285,7 +31294,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31569,10 +31578,10 @@
         <v>0.88</v>
       </c>
       <c r="AP147">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ147">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR147">
         <v>1.7</v>
@@ -31984,7 +31993,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ149">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR149">
         <v>1.83</v>
@@ -32109,7 +32118,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32521,7 +32530,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32599,7 +32608,7 @@
         <v>0.88</v>
       </c>
       <c r="AP152">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ152">
         <v>1.08</v>
@@ -32808,7 +32817,7 @@
         <v>1</v>
       </c>
       <c r="AQ153">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR153">
         <v>1.13</v>
@@ -32933,7 +32942,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33551,7 +33560,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33632,7 +33641,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ157">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR157">
         <v>1.23</v>
@@ -33757,7 +33766,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33963,7 +33972,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34247,7 +34256,7 @@
         <v>0.25</v>
       </c>
       <c r="AP160">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ160">
         <v>0.58</v>
@@ -34375,7 +34384,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34453,7 +34462,7 @@
         <v>2.5</v>
       </c>
       <c r="AP161">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ161">
         <v>2.17</v>
@@ -34581,7 +34590,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34787,7 +34796,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -34868,7 +34877,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ163">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR163">
         <v>1.24</v>
@@ -35071,7 +35080,7 @@
         <v>1.89</v>
       </c>
       <c r="AP164">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ164">
         <v>1.91</v>
@@ -35199,7 +35208,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35483,7 +35492,7 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ166">
         <v>0.67</v>
@@ -35611,7 +35620,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35692,7 +35701,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ167">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR167">
         <v>1.33</v>
@@ -35817,7 +35826,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36023,7 +36032,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36229,7 +36238,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36847,7 +36856,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -36928,7 +36937,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ173">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR173">
         <v>2.35</v>
@@ -37131,7 +37140,7 @@
         <v>0.6</v>
       </c>
       <c r="AP174">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ174">
         <v>0.58</v>
@@ -37259,7 +37268,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37671,7 +37680,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37877,7 +37886,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38289,7 +38298,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38495,7 +38504,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38701,7 +38710,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38782,7 +38791,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ182">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR182">
         <v>1.6</v>
@@ -38907,7 +38916,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39319,7 +39328,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39397,10 +39406,10 @@
         <v>1.3</v>
       </c>
       <c r="AP185">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ185">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR185">
         <v>1.74</v>
@@ -39731,7 +39740,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39937,7 +39946,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40143,7 +40152,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40427,10 +40436,10 @@
         <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ190">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR190">
         <v>1.38</v>
@@ -40633,7 +40642,7 @@
         <v>1.2</v>
       </c>
       <c r="AP191">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ191">
         <v>1</v>
@@ -40839,7 +40848,7 @@
         <v>0.33</v>
       </c>
       <c r="AP192">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ192">
         <v>0.58</v>
@@ -41048,7 +41057,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ193">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR193">
         <v>1.22</v>
@@ -41173,7 +41182,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41585,7 +41594,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41666,7 +41675,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ196">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR196">
         <v>1.64</v>
@@ -41869,7 +41878,7 @@
         <v>1.09</v>
       </c>
       <c r="AP197">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ197">
         <v>1</v>
@@ -41997,7 +42006,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42409,7 +42418,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42615,7 +42624,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43517,7 +43526,7 @@
         <v>0.64</v>
       </c>
       <c r="AP205">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ205">
         <v>0.58</v>
@@ -43603,7 +43612,7 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>7466227</v>
+        <v>7466224</v>
       </c>
       <c r="C206" t="s">
         <v>68</v>
@@ -43618,19 +43627,19 @@
         <v>20</v>
       </c>
       <c r="G206" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H206" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206">
         <v>0</v>
       </c>
       <c r="K206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L206">
         <v>2</v>
@@ -43648,160 +43657,160 @@
         <v>91</v>
       </c>
       <c r="Q206">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="R206">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S206">
         <v>5.5</v>
       </c>
       <c r="T206">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="U206">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="V206">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="W206">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="X206">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y206">
+        <v>1.17</v>
+      </c>
+      <c r="Z206">
+        <v>1.53</v>
+      </c>
+      <c r="AA206">
+        <v>4.8</v>
+      </c>
+      <c r="AB206">
+        <v>5.8</v>
+      </c>
+      <c r="AC206">
+        <v>1.01</v>
+      </c>
+      <c r="AD206">
+        <v>23</v>
+      </c>
+      <c r="AE206">
+        <v>1.14</v>
+      </c>
+      <c r="AF206">
+        <v>5.38</v>
+      </c>
+      <c r="AG206">
+        <v>1.48</v>
+      </c>
+      <c r="AH206">
+        <v>2.54</v>
+      </c>
+      <c r="AI206">
+        <v>1.62</v>
+      </c>
+      <c r="AJ206">
+        <v>2.2</v>
+      </c>
+      <c r="AK206">
         <v>1.13</v>
       </c>
-      <c r="Z206">
-        <v>1.63</v>
-      </c>
-      <c r="AA206">
-        <v>4.33</v>
-      </c>
-      <c r="AB206">
-        <v>5.2</v>
-      </c>
-      <c r="AC206">
-        <v>1.03</v>
-      </c>
-      <c r="AD206">
-        <v>17</v>
-      </c>
-      <c r="AE206">
+      <c r="AL206">
         <v>1.19</v>
       </c>
-      <c r="AF206">
-        <v>4.45</v>
-      </c>
-      <c r="AG206">
-        <v>1.61</v>
-      </c>
-      <c r="AH206">
-        <v>2.23</v>
-      </c>
-      <c r="AI206">
-        <v>1.7</v>
-      </c>
-      <c r="AJ206">
-        <v>2.05</v>
-      </c>
-      <c r="AK206">
-        <v>1.16</v>
-      </c>
-      <c r="AL206">
-        <v>1.22</v>
-      </c>
       <c r="AM206">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AN206">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="AO206">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AP206">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AQ206">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR206">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AS206">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AT206">
-        <v>3.39</v>
+        <v>2.99</v>
       </c>
       <c r="AU206">
         <v>7</v>
       </c>
       <c r="AV206">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW206">
+        <v>15</v>
+      </c>
+      <c r="AX206">
         <v>5</v>
       </c>
-      <c r="AX206">
-        <v>9</v>
-      </c>
       <c r="AY206">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="AZ206">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB206">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC206">
         <v>6</v>
       </c>
       <c r="BD206">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BE206">
         <v>7.5</v>
       </c>
       <c r="BF206">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BG206">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BH206">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="BI206">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="BJ206">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="BK206">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="BL206">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="BM206">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="BN206">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="BO206">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="BP206">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="207" spans="1:68">
@@ -43809,7 +43818,7 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>7466224</v>
+        <v>7466227</v>
       </c>
       <c r="C207" t="s">
         <v>68</v>
@@ -43824,19 +43833,19 @@
         <v>20</v>
       </c>
       <c r="G207" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H207" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207">
         <v>0</v>
       </c>
       <c r="K207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L207">
         <v>2</v>
@@ -43854,160 +43863,160 @@
         <v>91</v>
       </c>
       <c r="Q207">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R207">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S207">
         <v>5.5</v>
       </c>
       <c r="T207">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="U207">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="V207">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="W207">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="X207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y207">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z207">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AA207">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AB207">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AC207">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD207">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE207">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF207">
-        <v>5.38</v>
+        <v>4.45</v>
       </c>
       <c r="AG207">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AH207">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="AI207">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AJ207">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK207">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AL207">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AM207">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AN207">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AO207">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AP207">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="AQ207">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR207">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AS207">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AT207">
-        <v>2.99</v>
+        <v>3.39</v>
       </c>
       <c r="AU207">
         <v>7</v>
       </c>
       <c r="AV207">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW207">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AX207">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY207">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AZ207">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BA207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB207">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC207">
         <v>6</v>
       </c>
       <c r="BD207">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BE207">
         <v>7.5</v>
       </c>
       <c r="BF207">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BG207">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BH207">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="BI207">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="BJ207">
+        <v>2.8</v>
+      </c>
+      <c r="BK207">
+        <v>1.58</v>
+      </c>
+      <c r="BL207">
+        <v>2.18</v>
+      </c>
+      <c r="BM207">
+        <v>1.95</v>
+      </c>
+      <c r="BN207">
+        <v>1.75</v>
+      </c>
+      <c r="BO207">
         <v>2.4</v>
       </c>
-      <c r="BK207">
-        <v>1.81</v>
-      </c>
-      <c r="BL207">
-        <v>1.88</v>
-      </c>
-      <c r="BM207">
-        <v>2.25</v>
-      </c>
-      <c r="BN207">
-        <v>1.55</v>
-      </c>
-      <c r="BO207">
-        <v>2.9</v>
-      </c>
       <c r="BP207">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="208" spans="1:68">
@@ -44263,7 +44272,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44420,6 +44429,830 @@
       </c>
       <c r="BP209">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7466262</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45717.52083333334</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>76</v>
+      </c>
+      <c r="H210" t="s">
+        <v>87</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>1</v>
+      </c>
+      <c r="O210" t="s">
+        <v>236</v>
+      </c>
+      <c r="P210" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q210">
+        <v>2.05</v>
+      </c>
+      <c r="R210">
+        <v>2.4</v>
+      </c>
+      <c r="S210">
+        <v>5.5</v>
+      </c>
+      <c r="T210">
+        <v>1.3</v>
+      </c>
+      <c r="U210">
+        <v>3.4</v>
+      </c>
+      <c r="V210">
+        <v>2.38</v>
+      </c>
+      <c r="W210">
+        <v>1.53</v>
+      </c>
+      <c r="X210">
+        <v>6</v>
+      </c>
+      <c r="Y210">
+        <v>1.13</v>
+      </c>
+      <c r="Z210">
+        <v>1.56</v>
+      </c>
+      <c r="AA210">
+        <v>4.5</v>
+      </c>
+      <c r="AB210">
+        <v>5.8</v>
+      </c>
+      <c r="AC210">
+        <v>1.02</v>
+      </c>
+      <c r="AD210">
+        <v>17</v>
+      </c>
+      <c r="AE210">
+        <v>1.19</v>
+      </c>
+      <c r="AF210">
+        <v>4.45</v>
+      </c>
+      <c r="AG210">
+        <v>1.57</v>
+      </c>
+      <c r="AH210">
+        <v>2.3</v>
+      </c>
+      <c r="AI210">
+        <v>1.7</v>
+      </c>
+      <c r="AJ210">
+        <v>2.05</v>
+      </c>
+      <c r="AK210">
+        <v>1.15</v>
+      </c>
+      <c r="AL210">
+        <v>1.2</v>
+      </c>
+      <c r="AM210">
+        <v>2.4</v>
+      </c>
+      <c r="AN210">
+        <v>1.55</v>
+      </c>
+      <c r="AO210">
+        <v>0.64</v>
+      </c>
+      <c r="AP210">
+        <v>1.67</v>
+      </c>
+      <c r="AQ210">
+        <v>0.58</v>
+      </c>
+      <c r="AR210">
+        <v>1.55</v>
+      </c>
+      <c r="AS210">
+        <v>1.17</v>
+      </c>
+      <c r="AT210">
+        <v>2.72</v>
+      </c>
+      <c r="AU210">
+        <v>8</v>
+      </c>
+      <c r="AV210">
+        <v>4</v>
+      </c>
+      <c r="AW210">
+        <v>13</v>
+      </c>
+      <c r="AX210">
+        <v>5</v>
+      </c>
+      <c r="AY210">
+        <v>24</v>
+      </c>
+      <c r="AZ210">
+        <v>9</v>
+      </c>
+      <c r="BA210">
+        <v>6</v>
+      </c>
+      <c r="BB210">
+        <v>2</v>
+      </c>
+      <c r="BC210">
+        <v>8</v>
+      </c>
+      <c r="BD210">
+        <v>1.27</v>
+      </c>
+      <c r="BE210">
+        <v>7.5</v>
+      </c>
+      <c r="BF210">
+        <v>4</v>
+      </c>
+      <c r="BG210">
+        <v>1.17</v>
+      </c>
+      <c r="BH210">
+        <v>4.3</v>
+      </c>
+      <c r="BI210">
+        <v>1.3</v>
+      </c>
+      <c r="BJ210">
+        <v>3.05</v>
+      </c>
+      <c r="BK210">
+        <v>1.52</v>
+      </c>
+      <c r="BL210">
+        <v>2.32</v>
+      </c>
+      <c r="BM210">
+        <v>1.84</v>
+      </c>
+      <c r="BN210">
+        <v>1.84</v>
+      </c>
+      <c r="BO210">
+        <v>2.28</v>
+      </c>
+      <c r="BP210">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7466264</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45717.61458333334</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>77</v>
+      </c>
+      <c r="H211" t="s">
+        <v>74</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211">
+        <v>2</v>
+      </c>
+      <c r="K211">
+        <v>3</v>
+      </c>
+      <c r="L211">
+        <v>3</v>
+      </c>
+      <c r="M211">
+        <v>2</v>
+      </c>
+      <c r="N211">
+        <v>5</v>
+      </c>
+      <c r="O211" t="s">
+        <v>237</v>
+      </c>
+      <c r="P211" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q211">
+        <v>4.75</v>
+      </c>
+      <c r="R211">
+        <v>2.6</v>
+      </c>
+      <c r="S211">
+        <v>2.1</v>
+      </c>
+      <c r="T211">
+        <v>1.25</v>
+      </c>
+      <c r="U211">
+        <v>3.75</v>
+      </c>
+      <c r="V211">
+        <v>2.1</v>
+      </c>
+      <c r="W211">
+        <v>1.67</v>
+      </c>
+      <c r="X211">
+        <v>4.5</v>
+      </c>
+      <c r="Y211">
+        <v>1.18</v>
+      </c>
+      <c r="Z211">
+        <v>6.8</v>
+      </c>
+      <c r="AA211">
+        <v>5.2</v>
+      </c>
+      <c r="AB211">
+        <v>1.43</v>
+      </c>
+      <c r="AC211">
+        <v>1.01</v>
+      </c>
+      <c r="AD211">
+        <v>17</v>
+      </c>
+      <c r="AE211">
+        <v>1.12</v>
+      </c>
+      <c r="AF211">
+        <v>5.87</v>
+      </c>
+      <c r="AG211">
+        <v>1.41</v>
+      </c>
+      <c r="AH211">
+        <v>2.69</v>
+      </c>
+      <c r="AI211">
+        <v>1.5</v>
+      </c>
+      <c r="AJ211">
+        <v>2.5</v>
+      </c>
+      <c r="AK211">
+        <v>2.4</v>
+      </c>
+      <c r="AL211">
+        <v>1.18</v>
+      </c>
+      <c r="AM211">
+        <v>1.17</v>
+      </c>
+      <c r="AN211">
+        <v>2</v>
+      </c>
+      <c r="AO211">
+        <v>2</v>
+      </c>
+      <c r="AP211">
+        <v>2.08</v>
+      </c>
+      <c r="AQ211">
+        <v>1.83</v>
+      </c>
+      <c r="AR211">
+        <v>1.68</v>
+      </c>
+      <c r="AS211">
+        <v>1.86</v>
+      </c>
+      <c r="AT211">
+        <v>3.54</v>
+      </c>
+      <c r="AU211">
+        <v>6</v>
+      </c>
+      <c r="AV211">
+        <v>7</v>
+      </c>
+      <c r="AW211">
+        <v>4</v>
+      </c>
+      <c r="AX211">
+        <v>11</v>
+      </c>
+      <c r="AY211">
+        <v>10</v>
+      </c>
+      <c r="AZ211">
+        <v>21</v>
+      </c>
+      <c r="BA211">
+        <v>2</v>
+      </c>
+      <c r="BB211">
+        <v>5</v>
+      </c>
+      <c r="BC211">
+        <v>7</v>
+      </c>
+      <c r="BD211">
+        <v>3.9</v>
+      </c>
+      <c r="BE211">
+        <v>7.5</v>
+      </c>
+      <c r="BF211">
+        <v>1.29</v>
+      </c>
+      <c r="BG211">
+        <v>1.21</v>
+      </c>
+      <c r="BH211">
+        <v>3.8</v>
+      </c>
+      <c r="BI211">
+        <v>1.38</v>
+      </c>
+      <c r="BJ211">
+        <v>2.7</v>
+      </c>
+      <c r="BK211">
+        <v>1.64</v>
+      </c>
+      <c r="BL211">
+        <v>2.1</v>
+      </c>
+      <c r="BM211">
+        <v>1.98</v>
+      </c>
+      <c r="BN211">
+        <v>1.72</v>
+      </c>
+      <c r="BO211">
+        <v>2.5</v>
+      </c>
+      <c r="BP211">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7466261</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45717.66666666666</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>70</v>
+      </c>
+      <c r="H212" t="s">
+        <v>81</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>2</v>
+      </c>
+      <c r="L212">
+        <v>1</v>
+      </c>
+      <c r="M212">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>2</v>
+      </c>
+      <c r="O212" t="s">
+        <v>128</v>
+      </c>
+      <c r="P212" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q212">
+        <v>4.33</v>
+      </c>
+      <c r="R212">
+        <v>2.2</v>
+      </c>
+      <c r="S212">
+        <v>2.6</v>
+      </c>
+      <c r="T212">
+        <v>1.4</v>
+      </c>
+      <c r="U212">
+        <v>2.75</v>
+      </c>
+      <c r="V212">
+        <v>2.75</v>
+      </c>
+      <c r="W212">
+        <v>1.4</v>
+      </c>
+      <c r="X212">
+        <v>8</v>
+      </c>
+      <c r="Y212">
+        <v>1.08</v>
+      </c>
+      <c r="Z212">
+        <v>4.6</v>
+      </c>
+      <c r="AA212">
+        <v>4</v>
+      </c>
+      <c r="AB212">
+        <v>1.75</v>
+      </c>
+      <c r="AC212">
+        <v>1.05</v>
+      </c>
+      <c r="AD212">
+        <v>11</v>
+      </c>
+      <c r="AE212">
+        <v>1.31</v>
+      </c>
+      <c r="AF212">
+        <v>3.35</v>
+      </c>
+      <c r="AG212">
+        <v>1.6</v>
+      </c>
+      <c r="AH212">
+        <v>2.25</v>
+      </c>
+      <c r="AI212">
+        <v>1.75</v>
+      </c>
+      <c r="AJ212">
+        <v>2</v>
+      </c>
+      <c r="AK212">
+        <v>1.8</v>
+      </c>
+      <c r="AL212">
+        <v>1.29</v>
+      </c>
+      <c r="AM212">
+        <v>1.27</v>
+      </c>
+      <c r="AN212">
+        <v>1.73</v>
+      </c>
+      <c r="AO212">
+        <v>1.25</v>
+      </c>
+      <c r="AP212">
+        <v>1.67</v>
+      </c>
+      <c r="AQ212">
+        <v>1.23</v>
+      </c>
+      <c r="AR212">
+        <v>1.44</v>
+      </c>
+      <c r="AS212">
+        <v>1.64</v>
+      </c>
+      <c r="AT212">
+        <v>3.08</v>
+      </c>
+      <c r="AU212">
+        <v>4</v>
+      </c>
+      <c r="AV212">
+        <v>3</v>
+      </c>
+      <c r="AW212">
+        <v>3</v>
+      </c>
+      <c r="AX212">
+        <v>10</v>
+      </c>
+      <c r="AY212">
+        <v>9</v>
+      </c>
+      <c r="AZ212">
+        <v>15</v>
+      </c>
+      <c r="BA212">
+        <v>2</v>
+      </c>
+      <c r="BB212">
+        <v>3</v>
+      </c>
+      <c r="BC212">
+        <v>5</v>
+      </c>
+      <c r="BD212">
+        <v>2.4</v>
+      </c>
+      <c r="BE212">
+        <v>6.4</v>
+      </c>
+      <c r="BF212">
+        <v>1.7</v>
+      </c>
+      <c r="BG212">
+        <v>1.32</v>
+      </c>
+      <c r="BH212">
+        <v>3</v>
+      </c>
+      <c r="BI212">
+        <v>1.56</v>
+      </c>
+      <c r="BJ212">
+        <v>2.23</v>
+      </c>
+      <c r="BK212">
+        <v>1.9</v>
+      </c>
+      <c r="BL212">
+        <v>1.78</v>
+      </c>
+      <c r="BM212">
+        <v>2.4</v>
+      </c>
+      <c r="BN212">
+        <v>1.49</v>
+      </c>
+      <c r="BO212">
+        <v>3.15</v>
+      </c>
+      <c r="BP212">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7466263</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45717.70833333334</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>71</v>
+      </c>
+      <c r="H213" t="s">
+        <v>72</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="N213">
+        <v>0</v>
+      </c>
+      <c r="O213" t="s">
+        <v>91</v>
+      </c>
+      <c r="P213" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q213">
+        <v>1.95</v>
+      </c>
+      <c r="R213">
+        <v>2.5</v>
+      </c>
+      <c r="S213">
+        <v>6</v>
+      </c>
+      <c r="T213">
+        <v>1.29</v>
+      </c>
+      <c r="U213">
+        <v>3.5</v>
+      </c>
+      <c r="V213">
+        <v>2.25</v>
+      </c>
+      <c r="W213">
+        <v>1.57</v>
+      </c>
+      <c r="X213">
+        <v>5.5</v>
+      </c>
+      <c r="Y213">
+        <v>1.14</v>
+      </c>
+      <c r="Z213">
+        <v>1.31</v>
+      </c>
+      <c r="AA213">
+        <v>6.3</v>
+      </c>
+      <c r="AB213">
+        <v>9</v>
+      </c>
+      <c r="AC213">
+        <v>1.01</v>
+      </c>
+      <c r="AD213">
+        <v>21</v>
+      </c>
+      <c r="AE213">
+        <v>1.14</v>
+      </c>
+      <c r="AF213">
+        <v>5.31</v>
+      </c>
+      <c r="AG213">
+        <v>1.57</v>
+      </c>
+      <c r="AH213">
+        <v>2.31</v>
+      </c>
+      <c r="AI213">
+        <v>1.7</v>
+      </c>
+      <c r="AJ213">
+        <v>2.05</v>
+      </c>
+      <c r="AK213">
+        <v>1.12</v>
+      </c>
+      <c r="AL213">
+        <v>1.19</v>
+      </c>
+      <c r="AM213">
+        <v>2.6</v>
+      </c>
+      <c r="AN213">
+        <v>2.09</v>
+      </c>
+      <c r="AO213">
+        <v>0.82</v>
+      </c>
+      <c r="AP213">
+        <v>2</v>
+      </c>
+      <c r="AQ213">
+        <v>0.83</v>
+      </c>
+      <c r="AR213">
+        <v>1.91</v>
+      </c>
+      <c r="AS213">
+        <v>1.31</v>
+      </c>
+      <c r="AT213">
+        <v>3.22</v>
+      </c>
+      <c r="AU213">
+        <v>8</v>
+      </c>
+      <c r="AV213">
+        <v>4</v>
+      </c>
+      <c r="AW213">
+        <v>12</v>
+      </c>
+      <c r="AX213">
+        <v>3</v>
+      </c>
+      <c r="AY213">
+        <v>23</v>
+      </c>
+      <c r="AZ213">
+        <v>7</v>
+      </c>
+      <c r="BA213">
+        <v>10</v>
+      </c>
+      <c r="BB213">
+        <v>3</v>
+      </c>
+      <c r="BC213">
+        <v>13</v>
+      </c>
+      <c r="BD213">
+        <v>1.17</v>
+      </c>
+      <c r="BE213">
+        <v>9.5</v>
+      </c>
+      <c r="BF213">
+        <v>5.1</v>
+      </c>
+      <c r="BG213">
+        <v>1.16</v>
+      </c>
+      <c r="BH213">
+        <v>4.3</v>
+      </c>
+      <c r="BI213">
+        <v>1.3</v>
+      </c>
+      <c r="BJ213">
+        <v>3.05</v>
+      </c>
+      <c r="BK213">
+        <v>1.53</v>
+      </c>
+      <c r="BL213">
+        <v>2.32</v>
+      </c>
+      <c r="BM213">
+        <v>1.83</v>
+      </c>
+      <c r="BN213">
+        <v>1.85</v>
+      </c>
+      <c r="BO213">
+        <v>2.23</v>
+      </c>
+      <c r="BP213">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="334">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -730,6 +730,9 @@
     <t>['23', '74', '87']</t>
   </si>
   <si>
+    <t>['5', '57', '90+4']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1374,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2042,7 +2045,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2329,7 +2332,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ5">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2454,7 +2457,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -3072,7 +3075,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3768,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12">
         <v>2.17</v>
@@ -4308,7 +4311,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4514,7 +4517,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4720,7 +4723,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5544,7 +5547,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5750,7 +5753,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6037,7 +6040,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ23">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR23">
         <v>1.65</v>
@@ -6780,7 +6783,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6861,7 +6864,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ27">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR27">
         <v>1.81</v>
@@ -7192,7 +7195,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7476,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ30">
         <v>0.58</v>
@@ -7604,7 +7607,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8840,7 +8843,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9252,7 +9255,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9458,7 +9461,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -10488,7 +10491,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10569,7 +10572,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ45">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -10694,7 +10697,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10900,7 +10903,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11106,7 +11109,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11312,7 +11315,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11518,7 +11521,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11596,7 +11599,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ50">
         <v>0.67</v>
@@ -11724,7 +11727,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12136,7 +12139,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12548,7 +12551,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12754,7 +12757,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13784,7 +13787,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13990,7 +13993,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14814,7 +14817,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15020,7 +15023,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15510,7 +15513,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ69">
         <v>0.73</v>
@@ -15638,7 +15641,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15925,7 +15928,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ71">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR71">
         <v>1.43</v>
@@ -16050,7 +16053,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16256,7 +16259,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16874,7 +16877,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17492,7 +17495,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17698,7 +17701,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18522,7 +18525,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18806,7 +18809,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -18934,7 +18937,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19552,7 +19555,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19758,7 +19761,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -20376,7 +20379,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20582,7 +20585,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20663,7 +20666,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR94">
         <v>1.67</v>
@@ -20994,7 +20997,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21406,7 +21409,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22436,7 +22439,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22642,7 +22645,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22848,7 +22851,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23054,7 +23057,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23338,7 +23341,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23466,7 +23469,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -24084,7 +24087,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24496,7 +24499,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24702,7 +24705,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24908,7 +24911,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -24989,7 +24992,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ115">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR115">
         <v>1.6</v>
@@ -25114,7 +25117,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25604,7 +25607,7 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ118">
         <v>0.5</v>
@@ -26556,7 +26559,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26762,7 +26765,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27174,7 +27177,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27380,7 +27383,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27998,7 +28001,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28204,7 +28207,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28410,7 +28413,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28822,7 +28825,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29234,7 +29237,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29724,7 +29727,7 @@
         <v>2.63</v>
       </c>
       <c r="AP138">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ138">
         <v>1.83</v>
@@ -29852,7 +29855,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30058,7 +30061,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30264,7 +30267,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -31088,7 +31091,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31169,7 +31172,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ145">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -31294,7 +31297,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -32118,7 +32121,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32530,7 +32533,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32942,7 +32945,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33560,7 +33563,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33766,7 +33769,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33847,7 +33850,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ158">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR158">
         <v>2.37</v>
@@ -33972,7 +33975,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34384,7 +34387,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34590,7 +34593,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34796,7 +34799,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35083,7 +35086,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ164">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR164">
         <v>1.55</v>
@@ -35208,7 +35211,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35620,7 +35623,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35826,7 +35829,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36032,7 +36035,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36110,7 +36113,7 @@
         <v>1.89</v>
       </c>
       <c r="AP169">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ169">
         <v>2.09</v>
@@ -36238,7 +36241,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36856,7 +36859,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37268,7 +37271,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37680,7 +37683,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37886,7 +37889,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38298,7 +38301,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38504,7 +38507,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38582,7 +38585,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ181">
         <v>1.08</v>
@@ -38710,7 +38713,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38916,7 +38919,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39328,7 +39331,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39740,7 +39743,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39821,7 +39824,7 @@
         <v>1</v>
       </c>
       <c r="AQ187">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR187">
         <v>1.16</v>
@@ -39946,7 +39949,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40152,7 +40155,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -41182,7 +41185,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41594,7 +41597,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41672,7 +41675,7 @@
         <v>1.27</v>
       </c>
       <c r="AP196">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ196">
         <v>1.23</v>
@@ -42006,7 +42009,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42418,7 +42421,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42624,7 +42627,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -44272,7 +44275,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44684,7 +44687,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44890,7 +44893,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45253,6 +45256,212 @@
       </c>
       <c r="BP213">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7466267</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45718.34375</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>80</v>
+      </c>
+      <c r="H214" t="s">
+        <v>82</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>3</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>4</v>
+      </c>
+      <c r="O214" t="s">
+        <v>238</v>
+      </c>
+      <c r="P214" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q214">
+        <v>4</v>
+      </c>
+      <c r="R214">
+        <v>2.1</v>
+      </c>
+      <c r="S214">
+        <v>2.75</v>
+      </c>
+      <c r="T214">
+        <v>1.4</v>
+      </c>
+      <c r="U214">
+        <v>2.75</v>
+      </c>
+      <c r="V214">
+        <v>3</v>
+      </c>
+      <c r="W214">
+        <v>1.36</v>
+      </c>
+      <c r="X214">
+        <v>8</v>
+      </c>
+      <c r="Y214">
+        <v>1.08</v>
+      </c>
+      <c r="Z214">
+        <v>3.69</v>
+      </c>
+      <c r="AA214">
+        <v>3.55</v>
+      </c>
+      <c r="AB214">
+        <v>2.07</v>
+      </c>
+      <c r="AC214">
+        <v>1.04</v>
+      </c>
+      <c r="AD214">
+        <v>10.06</v>
+      </c>
+      <c r="AE214">
+        <v>1.31</v>
+      </c>
+      <c r="AF214">
+        <v>3.35</v>
+      </c>
+      <c r="AG214">
+        <v>1.82</v>
+      </c>
+      <c r="AH214">
+        <v>2</v>
+      </c>
+      <c r="AI214">
+        <v>1.75</v>
+      </c>
+      <c r="AJ214">
+        <v>2</v>
+      </c>
+      <c r="AK214">
+        <v>1.73</v>
+      </c>
+      <c r="AL214">
+        <v>1.3</v>
+      </c>
+      <c r="AM214">
+        <v>1.29</v>
+      </c>
+      <c r="AN214">
+        <v>1.82</v>
+      </c>
+      <c r="AO214">
+        <v>1.91</v>
+      </c>
+      <c r="AP214">
+        <v>1.92</v>
+      </c>
+      <c r="AQ214">
+        <v>1.75</v>
+      </c>
+      <c r="AR214">
+        <v>1.72</v>
+      </c>
+      <c r="AS214">
+        <v>1.47</v>
+      </c>
+      <c r="AT214">
+        <v>3.19</v>
+      </c>
+      <c r="AU214">
+        <v>8</v>
+      </c>
+      <c r="AV214">
+        <v>4</v>
+      </c>
+      <c r="AW214">
+        <v>1</v>
+      </c>
+      <c r="AX214">
+        <v>9</v>
+      </c>
+      <c r="AY214">
+        <v>10</v>
+      </c>
+      <c r="AZ214">
+        <v>15</v>
+      </c>
+      <c r="BA214">
+        <v>3</v>
+      </c>
+      <c r="BB214">
+        <v>6</v>
+      </c>
+      <c r="BC214">
+        <v>9</v>
+      </c>
+      <c r="BD214">
+        <v>2.18</v>
+      </c>
+      <c r="BE214">
+        <v>6.4</v>
+      </c>
+      <c r="BF214">
+        <v>1.82</v>
+      </c>
+      <c r="BG214">
+        <v>1.33</v>
+      </c>
+      <c r="BH214">
+        <v>2.95</v>
+      </c>
+      <c r="BI214">
+        <v>1.57</v>
+      </c>
+      <c r="BJ214">
+        <v>2.23</v>
+      </c>
+      <c r="BK214">
+        <v>1.95</v>
+      </c>
+      <c r="BL214">
+        <v>1.75</v>
+      </c>
+      <c r="BM214">
+        <v>2.45</v>
+      </c>
+      <c r="BN214">
+        <v>1.48</v>
+      </c>
+      <c r="BO214">
+        <v>3.2</v>
+      </c>
+      <c r="BP214">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="337">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,12 @@
     <t>['5', '57', '90+4']</t>
   </si>
   <si>
+    <t>['8', '44', '58', '63']</t>
+  </si>
+  <si>
+    <t>['20', '63', '68', '90']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1016,6 +1022,9 @@
   </si>
   <si>
     <t>['45+4']</t>
+  </si>
+  <si>
+    <t>['9', '32']</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP214"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1920,7 +1929,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2045,7 +2054,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2329,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ5">
         <v>1.75</v>
@@ -2457,7 +2466,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2741,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ7">
         <v>0.73</v>
@@ -2950,7 +2959,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ8">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3075,7 +3084,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -4311,7 +4320,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4517,7 +4526,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4595,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ16">
         <v>1.83</v>
@@ -4723,7 +4732,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5216,7 +5225,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ19">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5422,7 +5431,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ20">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR20">
         <v>1.11</v>
@@ -5547,7 +5556,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5625,7 +5634,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ21">
         <v>1.83</v>
@@ -5753,7 +5762,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6243,10 +6252,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ24">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -6449,7 +6458,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ25">
         <v>1.67</v>
@@ -6783,7 +6792,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7067,7 +7076,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ28">
         <v>0.67</v>
@@ -7195,7 +7204,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7607,7 +7616,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8718,7 +8727,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ36">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR36">
         <v>1.72</v>
@@ -8843,7 +8852,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9255,7 +9264,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9461,7 +9470,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9539,7 +9548,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -9951,7 +9960,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ42">
         <v>0.58</v>
@@ -10491,7 +10500,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10697,7 +10706,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10778,7 +10787,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ46">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>1.08</v>
@@ -10903,7 +10912,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11109,7 +11118,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11190,7 +11199,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ48">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR48">
         <v>1.91</v>
@@ -11315,7 +11324,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11521,7 +11530,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11727,7 +11736,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11805,7 +11814,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ51">
         <v>1.23</v>
@@ -12139,7 +12148,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12423,7 +12432,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ54">
         <v>0.58</v>
@@ -12551,7 +12560,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12757,7 +12766,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13041,7 +13050,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ57">
         <v>1.08</v>
@@ -13787,7 +13796,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13868,7 +13877,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ61">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR61">
         <v>1.5</v>
@@ -13993,7 +14002,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14277,10 +14286,10 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ63">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR63">
         <v>1.02</v>
@@ -14817,7 +14826,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15023,7 +15032,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15516,7 +15525,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ69">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR69">
         <v>2.09</v>
@@ -15641,7 +15650,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -16053,7 +16062,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16131,7 +16140,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ72">
         <v>0.58</v>
@@ -16259,7 +16268,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16877,7 +16886,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17495,7 +17504,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17573,10 +17582,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ79">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR79">
         <v>1.54</v>
@@ -17701,7 +17710,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17985,7 +17994,7 @@
         <v>0.75</v>
       </c>
       <c r="AP81">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ81">
         <v>0.83</v>
@@ -18400,7 +18409,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ83">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR83">
         <v>2.49</v>
@@ -18525,7 +18534,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18937,7 +18946,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19430,7 +19439,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ88">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>2.16</v>
@@ -19555,7 +19564,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19761,7 +19770,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19842,7 +19851,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR90">
         <v>1.77</v>
@@ -20251,7 +20260,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ92">
         <v>0.58</v>
@@ -20379,7 +20388,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20585,7 +20594,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20997,7 +21006,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21078,7 +21087,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ96">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21409,7 +21418,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21487,7 +21496,7 @@
         <v>2.5</v>
       </c>
       <c r="AP98">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ98">
         <v>2.17</v>
@@ -22439,7 +22448,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22645,7 +22654,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22851,7 +22860,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22929,7 +22938,7 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ105">
         <v>1.67</v>
@@ -23057,7 +23066,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23138,7 +23147,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ106">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR106">
         <v>2.03</v>
@@ -23469,7 +23478,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23550,7 +23559,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ108">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.94</v>
@@ -24087,7 +24096,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24165,7 +24174,7 @@
         <v>0</v>
       </c>
       <c r="AP111">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ111">
         <v>0.5</v>
@@ -24499,7 +24508,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24705,7 +24714,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24911,7 +24920,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -24989,7 +24998,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ115">
         <v>1.75</v>
@@ -25117,7 +25126,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25404,7 +25413,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ117">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR117">
         <v>2.01</v>
@@ -26022,7 +26031,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ120">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR120">
         <v>1.14</v>
@@ -26559,7 +26568,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26765,7 +26774,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27177,7 +27186,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27258,7 +27267,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ126">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR126">
         <v>1.45</v>
@@ -27383,7 +27392,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -28001,7 +28010,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28079,7 +28088,7 @@
         <v>0.57</v>
       </c>
       <c r="AP130">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ130">
         <v>0.58</v>
@@ -28207,7 +28216,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28413,7 +28422,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28491,7 +28500,7 @@
         <v>0.86</v>
       </c>
       <c r="AP132">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ132">
         <v>1.08</v>
@@ -28700,7 +28709,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ133">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR133">
         <v>1.23</v>
@@ -28825,7 +28834,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29112,7 +29121,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ135">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR135">
         <v>1.92</v>
@@ -29237,7 +29246,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29315,7 +29324,7 @@
         <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ136">
         <v>2.17</v>
@@ -29524,7 +29533,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ137">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR137">
         <v>1.19</v>
@@ -29855,7 +29864,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30061,7 +30070,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30267,7 +30276,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -31091,7 +31100,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31297,7 +31306,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31378,7 +31387,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ146">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR146">
         <v>1.16</v>
@@ -31787,7 +31796,7 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ148">
         <v>0.58</v>
@@ -32121,7 +32130,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32199,10 +32208,10 @@
         <v>1.75</v>
       </c>
       <c r="AP150">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ150">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR150">
         <v>1.58</v>
@@ -32533,7 +32542,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32945,7 +32954,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33229,7 +33238,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ155">
         <v>1</v>
@@ -33563,7 +33572,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33769,7 +33778,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33975,7 +33984,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34056,7 +34065,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ159">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR159">
         <v>1.99</v>
@@ -34387,7 +34396,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34593,7 +34602,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34799,7 +34808,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35211,7 +35220,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35623,7 +35632,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35829,7 +35838,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -35907,7 +35916,7 @@
         <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ168">
         <v>0.73</v>
@@ -36035,7 +36044,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36116,7 +36125,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ169">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR169">
         <v>1.56</v>
@@ -36241,7 +36250,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36525,7 +36534,7 @@
         <v>0.22</v>
       </c>
       <c r="AP171">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ171">
         <v>0.5</v>
@@ -36731,7 +36740,7 @@
         <v>2.56</v>
       </c>
       <c r="AP172">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ172">
         <v>2.17</v>
@@ -36859,7 +36868,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37271,7 +37280,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37352,7 +37361,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ175">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR175">
         <v>1.34</v>
@@ -37558,7 +37567,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ176">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR176">
         <v>1.2</v>
@@ -37683,7 +37692,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37889,7 +37898,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37967,7 +37976,7 @@
         <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ178">
         <v>0.67</v>
@@ -38301,7 +38310,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38507,7 +38516,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38713,7 +38722,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38919,7 +38928,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -38997,7 +39006,7 @@
         <v>0.3</v>
       </c>
       <c r="AP183">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ183">
         <v>0.5</v>
@@ -39331,7 +39340,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39615,7 +39624,7 @@
         <v>0.5</v>
       </c>
       <c r="AP186">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ186">
         <v>0.67</v>
@@ -39743,7 +39752,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39949,7 +39958,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40027,7 +40036,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ188">
         <v>1</v>
@@ -40155,7 +40164,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40236,7 +40245,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ189">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR189">
         <v>2.4</v>
@@ -41185,7 +41194,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41266,7 +41275,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ194">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AR194">
         <v>1.36</v>
@@ -41472,7 +41481,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ195">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR195">
         <v>1.82</v>
@@ -41597,7 +41606,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -42009,7 +42018,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42421,7 +42430,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42627,7 +42636,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -44275,7 +44284,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44687,7 +44696,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44893,7 +44902,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45462,6 +45471,624 @@
       </c>
       <c r="BP214">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7466265</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45718.4375</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>84</v>
+      </c>
+      <c r="H215" t="s">
+        <v>85</v>
+      </c>
+      <c r="I215">
+        <v>2</v>
+      </c>
+      <c r="J215">
+        <v>2</v>
+      </c>
+      <c r="K215">
+        <v>4</v>
+      </c>
+      <c r="L215">
+        <v>4</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
+      </c>
+      <c r="N215">
+        <v>6</v>
+      </c>
+      <c r="O215" t="s">
+        <v>239</v>
+      </c>
+      <c r="P215" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q215">
+        <v>2.75</v>
+      </c>
+      <c r="R215">
+        <v>2.2</v>
+      </c>
+      <c r="S215">
+        <v>3.75</v>
+      </c>
+      <c r="T215">
+        <v>1.36</v>
+      </c>
+      <c r="U215">
+        <v>3</v>
+      </c>
+      <c r="V215">
+        <v>2.75</v>
+      </c>
+      <c r="W215">
+        <v>1.4</v>
+      </c>
+      <c r="X215">
+        <v>7</v>
+      </c>
+      <c r="Y215">
+        <v>1.1</v>
+      </c>
+      <c r="Z215">
+        <v>2.23</v>
+      </c>
+      <c r="AA215">
+        <v>3.3</v>
+      </c>
+      <c r="AB215">
+        <v>3.55</v>
+      </c>
+      <c r="AC215">
+        <v>1.04</v>
+      </c>
+      <c r="AD215">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AE215">
+        <v>1.26</v>
+      </c>
+      <c r="AF215">
+        <v>3.67</v>
+      </c>
+      <c r="AG215">
+        <v>1.81</v>
+      </c>
+      <c r="AH215">
+        <v>2.01</v>
+      </c>
+      <c r="AI215">
+        <v>1.67</v>
+      </c>
+      <c r="AJ215">
+        <v>2.1</v>
+      </c>
+      <c r="AK215">
+        <v>1.33</v>
+      </c>
+      <c r="AL215">
+        <v>1.29</v>
+      </c>
+      <c r="AM215">
+        <v>1.66</v>
+      </c>
+      <c r="AN215">
+        <v>1.33</v>
+      </c>
+      <c r="AO215">
+        <v>0.73</v>
+      </c>
+      <c r="AP215">
+        <v>1.46</v>
+      </c>
+      <c r="AQ215">
+        <v>0.67</v>
+      </c>
+      <c r="AR215">
+        <v>1.42</v>
+      </c>
+      <c r="AS215">
+        <v>1.04</v>
+      </c>
+      <c r="AT215">
+        <v>2.46</v>
+      </c>
+      <c r="AU215">
+        <v>5</v>
+      </c>
+      <c r="AV215">
+        <v>4</v>
+      </c>
+      <c r="AW215">
+        <v>11</v>
+      </c>
+      <c r="AX215">
+        <v>2</v>
+      </c>
+      <c r="AY215">
+        <v>19</v>
+      </c>
+      <c r="AZ215">
+        <v>6</v>
+      </c>
+      <c r="BA215">
+        <v>7</v>
+      </c>
+      <c r="BB215">
+        <v>1</v>
+      </c>
+      <c r="BC215">
+        <v>8</v>
+      </c>
+      <c r="BD215">
+        <v>1.49</v>
+      </c>
+      <c r="BE215">
+        <v>6.75</v>
+      </c>
+      <c r="BF215">
+        <v>2.9</v>
+      </c>
+      <c r="BG215">
+        <v>1.2</v>
+      </c>
+      <c r="BH215">
+        <v>3.9</v>
+      </c>
+      <c r="BI215">
+        <v>1.36</v>
+      </c>
+      <c r="BJ215">
+        <v>2.8</v>
+      </c>
+      <c r="BK215">
+        <v>1.6</v>
+      </c>
+      <c r="BL215">
+        <v>2.17</v>
+      </c>
+      <c r="BM215">
+        <v>1.95</v>
+      </c>
+      <c r="BN215">
+        <v>1.74</v>
+      </c>
+      <c r="BO215">
+        <v>2.43</v>
+      </c>
+      <c r="BP215">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7466260</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45718.4375</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>73</v>
+      </c>
+      <c r="H216" t="s">
+        <v>78</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>1</v>
+      </c>
+      <c r="O216" t="s">
+        <v>91</v>
+      </c>
+      <c r="P216" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q216">
+        <v>6.5</v>
+      </c>
+      <c r="R216">
+        <v>2.5</v>
+      </c>
+      <c r="S216">
+        <v>1.91</v>
+      </c>
+      <c r="T216">
+        <v>1.3</v>
+      </c>
+      <c r="U216">
+        <v>3.4</v>
+      </c>
+      <c r="V216">
+        <v>2.5</v>
+      </c>
+      <c r="W216">
+        <v>1.5</v>
+      </c>
+      <c r="X216">
+        <v>6</v>
+      </c>
+      <c r="Y216">
+        <v>1.13</v>
+      </c>
+      <c r="Z216">
+        <v>6.4</v>
+      </c>
+      <c r="AA216">
+        <v>5.1</v>
+      </c>
+      <c r="AB216">
+        <v>1.46</v>
+      </c>
+      <c r="AC216">
+        <v>1.02</v>
+      </c>
+      <c r="AD216">
+        <v>19</v>
+      </c>
+      <c r="AE216">
+        <v>1.18</v>
+      </c>
+      <c r="AF216">
+        <v>4.65</v>
+      </c>
+      <c r="AG216">
+        <v>1.61</v>
+      </c>
+      <c r="AH216">
+        <v>2.23</v>
+      </c>
+      <c r="AI216">
+        <v>1.91</v>
+      </c>
+      <c r="AJ216">
+        <v>1.91</v>
+      </c>
+      <c r="AK216">
+        <v>2.75</v>
+      </c>
+      <c r="AL216">
+        <v>1.18</v>
+      </c>
+      <c r="AM216">
+        <v>1.11</v>
+      </c>
+      <c r="AN216">
+        <v>0.64</v>
+      </c>
+      <c r="AO216">
+        <v>2.09</v>
+      </c>
+      <c r="AP216">
+        <v>0.58</v>
+      </c>
+      <c r="AQ216">
+        <v>2.17</v>
+      </c>
+      <c r="AR216">
+        <v>1.35</v>
+      </c>
+      <c r="AS216">
+        <v>1.39</v>
+      </c>
+      <c r="AT216">
+        <v>2.74</v>
+      </c>
+      <c r="AU216">
+        <v>2</v>
+      </c>
+      <c r="AV216">
+        <v>4</v>
+      </c>
+      <c r="AW216">
+        <v>13</v>
+      </c>
+      <c r="AX216">
+        <v>3</v>
+      </c>
+      <c r="AY216">
+        <v>18</v>
+      </c>
+      <c r="AZ216">
+        <v>9</v>
+      </c>
+      <c r="BA216">
+        <v>3</v>
+      </c>
+      <c r="BB216">
+        <v>0</v>
+      </c>
+      <c r="BC216">
+        <v>3</v>
+      </c>
+      <c r="BD216">
+        <v>4.6</v>
+      </c>
+      <c r="BE216">
+        <v>8.5</v>
+      </c>
+      <c r="BF216">
+        <v>1.22</v>
+      </c>
+      <c r="BG216">
+        <v>1.24</v>
+      </c>
+      <c r="BH216">
+        <v>3.55</v>
+      </c>
+      <c r="BI216">
+        <v>1.41</v>
+      </c>
+      <c r="BJ216">
+        <v>2.63</v>
+      </c>
+      <c r="BK216">
+        <v>1.68</v>
+      </c>
+      <c r="BL216">
+        <v>2.04</v>
+      </c>
+      <c r="BM216">
+        <v>2.04</v>
+      </c>
+      <c r="BN216">
+        <v>1.67</v>
+      </c>
+      <c r="BO216">
+        <v>2.55</v>
+      </c>
+      <c r="BP216">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7466268</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45718.53125</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>75</v>
+      </c>
+      <c r="H217" t="s">
+        <v>86</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+      <c r="L217">
+        <v>4</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>4</v>
+      </c>
+      <c r="O217" t="s">
+        <v>240</v>
+      </c>
+      <c r="P217" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q217">
+        <v>2.3</v>
+      </c>
+      <c r="R217">
+        <v>2.2</v>
+      </c>
+      <c r="S217">
+        <v>5.5</v>
+      </c>
+      <c r="T217">
+        <v>1.4</v>
+      </c>
+      <c r="U217">
+        <v>2.75</v>
+      </c>
+      <c r="V217">
+        <v>3</v>
+      </c>
+      <c r="W217">
+        <v>1.36</v>
+      </c>
+      <c r="X217">
+        <v>8</v>
+      </c>
+      <c r="Y217">
+        <v>1.08</v>
+      </c>
+      <c r="Z217">
+        <v>1.69</v>
+      </c>
+      <c r="AA217">
+        <v>3.96</v>
+      </c>
+      <c r="AB217">
+        <v>5.2</v>
+      </c>
+      <c r="AC217">
+        <v>1.05</v>
+      </c>
+      <c r="AD217">
+        <v>11</v>
+      </c>
+      <c r="AE217">
+        <v>1.31</v>
+      </c>
+      <c r="AF217">
+        <v>3.35</v>
+      </c>
+      <c r="AG217">
+        <v>1.97</v>
+      </c>
+      <c r="AH217">
+        <v>1.84</v>
+      </c>
+      <c r="AI217">
+        <v>1.95</v>
+      </c>
+      <c r="AJ217">
+        <v>1.8</v>
+      </c>
+      <c r="AK217">
+        <v>1.16</v>
+      </c>
+      <c r="AL217">
+        <v>1.26</v>
+      </c>
+      <c r="AM217">
+        <v>2.15</v>
+      </c>
+      <c r="AN217">
+        <v>0.73</v>
+      </c>
+      <c r="AO217">
+        <v>1.09</v>
+      </c>
+      <c r="AP217">
+        <v>0.92</v>
+      </c>
+      <c r="AQ217">
+        <v>1</v>
+      </c>
+      <c r="AR217">
+        <v>1.56</v>
+      </c>
+      <c r="AS217">
+        <v>0.91</v>
+      </c>
+      <c r="AT217">
+        <v>2.47</v>
+      </c>
+      <c r="AU217">
+        <v>13</v>
+      </c>
+      <c r="AV217">
+        <v>4</v>
+      </c>
+      <c r="AW217">
+        <v>10</v>
+      </c>
+      <c r="AX217">
+        <v>6</v>
+      </c>
+      <c r="AY217">
+        <v>25</v>
+      </c>
+      <c r="AZ217">
+        <v>11</v>
+      </c>
+      <c r="BA217">
+        <v>9</v>
+      </c>
+      <c r="BB217">
+        <v>5</v>
+      </c>
+      <c r="BC217">
+        <v>14</v>
+      </c>
+      <c r="BD217">
+        <v>1.32</v>
+      </c>
+      <c r="BE217">
+        <v>8</v>
+      </c>
+      <c r="BF217">
+        <v>3.65</v>
+      </c>
+      <c r="BG217">
+        <v>1.18</v>
+      </c>
+      <c r="BH217">
+        <v>4.1</v>
+      </c>
+      <c r="BI217">
+        <v>1.33</v>
+      </c>
+      <c r="BJ217">
+        <v>2.95</v>
+      </c>
+      <c r="BK217">
+        <v>1.54</v>
+      </c>
+      <c r="BL217">
+        <v>2.28</v>
+      </c>
+      <c r="BM217">
+        <v>1.86</v>
+      </c>
+      <c r="BN217">
+        <v>1.82</v>
+      </c>
+      <c r="BO217">
+        <v>2.32</v>
+      </c>
+      <c r="BP217">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="339">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -739,6 +739,9 @@
     <t>['20', '63', '68', '90']</t>
   </si>
   <si>
+    <t>['40', '57']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1025,6 +1028,9 @@
   </si>
   <si>
     <t>['9', '32']</t>
+  </si>
+  <si>
+    <t>['72']</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2054,7 +2060,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2466,7 +2472,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2544,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ6">
         <v>0.5</v>
@@ -2753,7 +2759,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ7">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3084,7 +3090,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3371,7 +3377,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ10">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3574,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
         <v>0.58</v>
@@ -4320,7 +4326,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4526,7 +4532,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4732,7 +4738,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5222,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ19">
         <v>2.17</v>
@@ -5556,7 +5562,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5762,7 +5768,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5840,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ22">
         <v>2.17</v>
@@ -6792,7 +6798,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7204,7 +7210,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7282,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>0.83</v>
@@ -7616,7 +7622,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8109,7 +8115,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ33">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR33">
         <v>0.7</v>
@@ -8312,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8518,7 +8524,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ35">
         <v>0.83</v>
@@ -8852,7 +8858,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9136,7 +9142,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ38">
         <v>1.08</v>
@@ -9264,7 +9270,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9345,7 +9351,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ39">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR39">
         <v>1.82</v>
@@ -9470,7 +9476,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -10169,7 +10175,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ43">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR43">
         <v>2.19</v>
@@ -10500,7 +10506,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10706,7 +10712,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10912,7 +10918,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11118,7 +11124,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11324,7 +11330,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11405,7 +11411,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ49">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR49">
         <v>1.18</v>
@@ -11530,7 +11536,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11736,7 +11742,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12148,7 +12154,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12226,7 +12232,7 @@
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ53">
         <v>1.83</v>
@@ -12435,7 +12441,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ54">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR54">
         <v>1.37</v>
@@ -12560,7 +12566,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12766,7 +12772,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13796,7 +13802,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -14002,7 +14008,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14492,7 +14498,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ64">
         <v>0.83</v>
@@ -14698,7 +14704,7 @@
         <v>2.33</v>
       </c>
       <c r="AP65">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14826,7 +14832,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15032,7 +15038,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15113,7 +15119,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ67">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15650,7 +15656,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15934,7 +15940,7 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ71">
         <v>1.75</v>
@@ -16062,7 +16068,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16268,7 +16274,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16555,7 +16561,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR74">
         <v>1.44</v>
@@ -16886,7 +16892,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17504,7 +17510,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17710,7 +17716,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18200,7 +18206,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82">
         <v>0.67</v>
@@ -18406,7 +18412,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ83">
         <v>0.67</v>
@@ -18534,7 +18540,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18612,7 +18618,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ84">
         <v>0.5</v>
@@ -18946,7 +18952,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19233,7 +19239,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ87">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -19564,7 +19570,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19770,7 +19776,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -20388,7 +20394,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20594,7 +20600,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20878,10 +20884,10 @@
         <v>0</v>
       </c>
       <c r="AP95">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ95">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR95">
         <v>1.29</v>
@@ -21006,7 +21012,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21418,7 +21424,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21911,7 +21917,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR100">
         <v>1.37</v>
@@ -22448,7 +22454,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22526,7 +22532,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ103">
         <v>1.83</v>
@@ -22654,7 +22660,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22860,7 +22866,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23066,7 +23072,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23478,7 +23484,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23971,7 +23977,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR110">
         <v>1.62</v>
@@ -24096,7 +24102,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24380,7 +24386,7 @@
         <v>0.67</v>
       </c>
       <c r="AP112">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ112">
         <v>0.67</v>
@@ -24508,7 +24514,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24586,7 +24592,7 @@
         <v>1.67</v>
       </c>
       <c r="AP113">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ113">
         <v>1.23</v>
@@ -24714,7 +24720,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24920,7 +24926,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25126,7 +25132,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25822,7 +25828,7 @@
         <v>0.33</v>
       </c>
       <c r="AP119">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ119">
         <v>0.58</v>
@@ -26568,7 +26574,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26774,7 +26780,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27061,7 +27067,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ125">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR125">
         <v>1.92</v>
@@ -27186,7 +27192,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27392,7 +27398,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27676,7 +27682,7 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ128">
         <v>1.23</v>
@@ -28010,7 +28016,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28216,7 +28222,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28422,7 +28428,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28834,7 +28840,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28915,7 +28921,7 @@
         <v>1</v>
       </c>
       <c r="AQ134">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR134">
         <v>1.12</v>
@@ -29246,7 +29252,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29864,7 +29870,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29942,7 +29948,7 @@
         <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ139">
         <v>0.5</v>
@@ -30070,7 +30076,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30151,7 +30157,7 @@
         <v>2</v>
       </c>
       <c r="AQ140">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR140">
         <v>1.81</v>
@@ -30276,7 +30282,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -31100,7 +31106,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31178,7 +31184,7 @@
         <v>1.86</v>
       </c>
       <c r="AP145">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ145">
         <v>1.75</v>
@@ -31306,7 +31312,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31799,7 +31805,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ148">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR148">
         <v>1.21</v>
@@ -32130,7 +32136,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32414,7 +32420,7 @@
         <v>2.25</v>
       </c>
       <c r="AP151">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ151">
         <v>1.67</v>
@@ -32542,7 +32548,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32954,7 +32960,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33032,7 +33038,7 @@
         <v>1</v>
       </c>
       <c r="AP154">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ154">
         <v>1</v>
@@ -33572,7 +33578,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33778,7 +33784,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33856,7 +33862,7 @@
         <v>2</v>
       </c>
       <c r="AP158">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ158">
         <v>1.75</v>
@@ -33984,7 +33990,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34396,7 +34402,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34602,7 +34608,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34680,10 +34686,10 @@
         <v>0.33</v>
       </c>
       <c r="AP162">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ162">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR162">
         <v>1.26</v>
@@ -34808,7 +34814,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35220,7 +35226,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35632,7 +35638,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35710,7 +35716,7 @@
         <v>1.44</v>
       </c>
       <c r="AP167">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ167">
         <v>1.23</v>
@@ -35838,7 +35844,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -35919,7 +35925,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ168">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR168">
         <v>1.26</v>
@@ -36044,7 +36050,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36250,7 +36256,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36868,7 +36874,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -36946,7 +36952,7 @@
         <v>0.78</v>
       </c>
       <c r="AP173">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ173">
         <v>0.58</v>
@@ -37155,7 +37161,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ174">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR174">
         <v>1.36</v>
@@ -37280,7 +37286,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37358,7 +37364,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP175">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ175">
         <v>0.67</v>
@@ -37692,7 +37698,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37898,7 +37904,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38182,10 +38188,10 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ179">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR179">
         <v>1.35</v>
@@ -38310,7 +38316,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38516,7 +38522,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38722,7 +38728,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38928,7 +38934,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39340,7 +39346,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39752,7 +39758,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39958,7 +39964,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40164,7 +40170,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40242,7 +40248,7 @@
         <v>1.1</v>
       </c>
       <c r="AP189">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ189">
         <v>1</v>
@@ -41194,7 +41200,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41272,7 +41278,7 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ194">
         <v>2.17</v>
@@ -41606,7 +41612,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -42018,7 +42024,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42096,7 +42102,7 @@
         <v>2.27</v>
       </c>
       <c r="AP198">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ198">
         <v>2.17</v>
@@ -42302,7 +42308,7 @@
         <v>1.73</v>
       </c>
       <c r="AP199">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ199">
         <v>1.67</v>
@@ -42430,7 +42436,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42636,7 +42642,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42923,7 +42929,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ202">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR202">
         <v>1.27</v>
@@ -43335,7 +43341,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ204">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR204">
         <v>1.82</v>
@@ -44284,7 +44290,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44696,7 +44702,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44902,7 +44908,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45520,7 +45526,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46089,6 +46095,624 @@
       </c>
       <c r="BP217">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7466274</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>87</v>
+      </c>
+      <c r="H218" t="s">
+        <v>75</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+      <c r="L218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>2</v>
+      </c>
+      <c r="O218" t="s">
+        <v>115</v>
+      </c>
+      <c r="P218" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q218">
+        <v>3.25</v>
+      </c>
+      <c r="R218">
+        <v>2.2</v>
+      </c>
+      <c r="S218">
+        <v>3.2</v>
+      </c>
+      <c r="T218">
+        <v>1.4</v>
+      </c>
+      <c r="U218">
+        <v>2.75</v>
+      </c>
+      <c r="V218">
+        <v>2.75</v>
+      </c>
+      <c r="W218">
+        <v>1.4</v>
+      </c>
+      <c r="X218">
+        <v>8</v>
+      </c>
+      <c r="Y218">
+        <v>1.08</v>
+      </c>
+      <c r="Z218">
+        <v>2.41</v>
+      </c>
+      <c r="AA218">
+        <v>3.51</v>
+      </c>
+      <c r="AB218">
+        <v>2.98</v>
+      </c>
+      <c r="AC218">
+        <v>1.04</v>
+      </c>
+      <c r="AD218">
+        <v>13</v>
+      </c>
+      <c r="AE218">
+        <v>1.24</v>
+      </c>
+      <c r="AF218">
+        <v>3.92</v>
+      </c>
+      <c r="AG218">
+        <v>1.85</v>
+      </c>
+      <c r="AH218">
+        <v>1.96</v>
+      </c>
+      <c r="AI218">
+        <v>1.7</v>
+      </c>
+      <c r="AJ218">
+        <v>2.05</v>
+      </c>
+      <c r="AK218">
+        <v>1.3</v>
+      </c>
+      <c r="AL218">
+        <v>1.31</v>
+      </c>
+      <c r="AM218">
+        <v>1.68</v>
+      </c>
+      <c r="AN218">
+        <v>1.67</v>
+      </c>
+      <c r="AO218">
+        <v>1</v>
+      </c>
+      <c r="AP218">
+        <v>1.62</v>
+      </c>
+      <c r="AQ218">
+        <v>1</v>
+      </c>
+      <c r="AR218">
+        <v>1.39</v>
+      </c>
+      <c r="AS218">
+        <v>1.44</v>
+      </c>
+      <c r="AT218">
+        <v>2.83</v>
+      </c>
+      <c r="AU218">
+        <v>6</v>
+      </c>
+      <c r="AV218">
+        <v>4</v>
+      </c>
+      <c r="AW218">
+        <v>7</v>
+      </c>
+      <c r="AX218">
+        <v>13</v>
+      </c>
+      <c r="AY218">
+        <v>17</v>
+      </c>
+      <c r="AZ218">
+        <v>25</v>
+      </c>
+      <c r="BA218">
+        <v>5</v>
+      </c>
+      <c r="BB218">
+        <v>7</v>
+      </c>
+      <c r="BC218">
+        <v>12</v>
+      </c>
+      <c r="BD218">
+        <v>1.98</v>
+      </c>
+      <c r="BE218">
+        <v>6.4</v>
+      </c>
+      <c r="BF218">
+        <v>2</v>
+      </c>
+      <c r="BG218">
+        <v>1.2</v>
+      </c>
+      <c r="BH218">
+        <v>3.9</v>
+      </c>
+      <c r="BI218">
+        <v>1.36</v>
+      </c>
+      <c r="BJ218">
+        <v>2.8</v>
+      </c>
+      <c r="BK218">
+        <v>1.6</v>
+      </c>
+      <c r="BL218">
+        <v>2.17</v>
+      </c>
+      <c r="BM218">
+        <v>1.96</v>
+      </c>
+      <c r="BN218">
+        <v>1.73</v>
+      </c>
+      <c r="BO218">
+        <v>2.48</v>
+      </c>
+      <c r="BP218">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7466272</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45724.52083333334</v>
+      </c>
+      <c r="F219">
+        <v>25</v>
+      </c>
+      <c r="G219" t="s">
+        <v>79</v>
+      </c>
+      <c r="H219" t="s">
+        <v>84</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>0</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>0</v>
+      </c>
+      <c r="N219">
+        <v>1</v>
+      </c>
+      <c r="O219" t="s">
+        <v>123</v>
+      </c>
+      <c r="P219" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q219">
+        <v>2.88</v>
+      </c>
+      <c r="R219">
+        <v>2.2</v>
+      </c>
+      <c r="S219">
+        <v>3.6</v>
+      </c>
+      <c r="T219">
+        <v>1.4</v>
+      </c>
+      <c r="U219">
+        <v>2.75</v>
+      </c>
+      <c r="V219">
+        <v>2.75</v>
+      </c>
+      <c r="W219">
+        <v>1.4</v>
+      </c>
+      <c r="X219">
+        <v>8</v>
+      </c>
+      <c r="Y219">
+        <v>1.08</v>
+      </c>
+      <c r="Z219">
+        <v>2.11</v>
+      </c>
+      <c r="AA219">
+        <v>3.85</v>
+      </c>
+      <c r="AB219">
+        <v>3.32</v>
+      </c>
+      <c r="AC219">
+        <v>1.03</v>
+      </c>
+      <c r="AD219">
+        <v>15</v>
+      </c>
+      <c r="AE219">
+        <v>1.18</v>
+      </c>
+      <c r="AF219">
+        <v>4.65</v>
+      </c>
+      <c r="AG219">
+        <v>1.6</v>
+      </c>
+      <c r="AH219">
+        <v>2.2</v>
+      </c>
+      <c r="AI219">
+        <v>1.75</v>
+      </c>
+      <c r="AJ219">
+        <v>2</v>
+      </c>
+      <c r="AK219">
+        <v>1.34</v>
+      </c>
+      <c r="AL219">
+        <v>1.3</v>
+      </c>
+      <c r="AM219">
+        <v>1.63</v>
+      </c>
+      <c r="AN219">
+        <v>1.36</v>
+      </c>
+      <c r="AO219">
+        <v>0.73</v>
+      </c>
+      <c r="AP219">
+        <v>1.5</v>
+      </c>
+      <c r="AQ219">
+        <v>0.67</v>
+      </c>
+      <c r="AR219">
+        <v>1.35</v>
+      </c>
+      <c r="AS219">
+        <v>1.03</v>
+      </c>
+      <c r="AT219">
+        <v>2.38</v>
+      </c>
+      <c r="AU219">
+        <v>6</v>
+      </c>
+      <c r="AV219">
+        <v>0</v>
+      </c>
+      <c r="AW219">
+        <v>6</v>
+      </c>
+      <c r="AX219">
+        <v>7</v>
+      </c>
+      <c r="AY219">
+        <v>15</v>
+      </c>
+      <c r="AZ219">
+        <v>11</v>
+      </c>
+      <c r="BA219">
+        <v>2</v>
+      </c>
+      <c r="BB219">
+        <v>6</v>
+      </c>
+      <c r="BC219">
+        <v>8</v>
+      </c>
+      <c r="BD219">
+        <v>1.55</v>
+      </c>
+      <c r="BE219">
+        <v>6.75</v>
+      </c>
+      <c r="BF219">
+        <v>2.65</v>
+      </c>
+      <c r="BG219">
+        <v>1.2</v>
+      </c>
+      <c r="BH219">
+        <v>3.9</v>
+      </c>
+      <c r="BI219">
+        <v>1.37</v>
+      </c>
+      <c r="BJ219">
+        <v>2.8</v>
+      </c>
+      <c r="BK219">
+        <v>1.61</v>
+      </c>
+      <c r="BL219">
+        <v>2.15</v>
+      </c>
+      <c r="BM219">
+        <v>1.96</v>
+      </c>
+      <c r="BN219">
+        <v>1.73</v>
+      </c>
+      <c r="BO219">
+        <v>2.48</v>
+      </c>
+      <c r="BP219">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7466276</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45724.66666666666</v>
+      </c>
+      <c r="F220">
+        <v>25</v>
+      </c>
+      <c r="G220" t="s">
+        <v>74</v>
+      </c>
+      <c r="H220" t="s">
+        <v>80</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>1</v>
+      </c>
+      <c r="L220">
+        <v>2</v>
+      </c>
+      <c r="M220">
+        <v>1</v>
+      </c>
+      <c r="N220">
+        <v>3</v>
+      </c>
+      <c r="O220" t="s">
+        <v>241</v>
+      </c>
+      <c r="P220" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q220">
+        <v>1.62</v>
+      </c>
+      <c r="R220">
+        <v>3</v>
+      </c>
+      <c r="S220">
+        <v>8</v>
+      </c>
+      <c r="T220">
+        <v>1.2</v>
+      </c>
+      <c r="U220">
+        <v>4.33</v>
+      </c>
+      <c r="V220">
+        <v>1.91</v>
+      </c>
+      <c r="W220">
+        <v>1.8</v>
+      </c>
+      <c r="X220">
+        <v>4</v>
+      </c>
+      <c r="Y220">
+        <v>1.22</v>
+      </c>
+      <c r="Z220">
+        <v>1.19</v>
+      </c>
+      <c r="AA220">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AB220">
+        <v>14</v>
+      </c>
+      <c r="AC220">
+        <v>1.01</v>
+      </c>
+      <c r="AD220">
+        <v>26</v>
+      </c>
+      <c r="AE220">
+        <v>1.09</v>
+      </c>
+      <c r="AF220">
+        <v>6.83</v>
+      </c>
+      <c r="AG220">
+        <v>1.3</v>
+      </c>
+      <c r="AH220">
+        <v>3.33</v>
+      </c>
+      <c r="AI220">
+        <v>1.7</v>
+      </c>
+      <c r="AJ220">
+        <v>2.05</v>
+      </c>
+      <c r="AK220">
+        <v>1.06</v>
+      </c>
+      <c r="AL220">
+        <v>1.11</v>
+      </c>
+      <c r="AM220">
+        <v>4</v>
+      </c>
+      <c r="AN220">
+        <v>2.5</v>
+      </c>
+      <c r="AO220">
+        <v>0.58</v>
+      </c>
+      <c r="AP220">
+        <v>2.54</v>
+      </c>
+      <c r="AQ220">
+        <v>0.54</v>
+      </c>
+      <c r="AR220">
+        <v>2.5</v>
+      </c>
+      <c r="AS220">
+        <v>1.33</v>
+      </c>
+      <c r="AT220">
+        <v>3.83</v>
+      </c>
+      <c r="AU220">
+        <v>12</v>
+      </c>
+      <c r="AV220">
+        <v>4</v>
+      </c>
+      <c r="AW220">
+        <v>13</v>
+      </c>
+      <c r="AX220">
+        <v>4</v>
+      </c>
+      <c r="AY220">
+        <v>28</v>
+      </c>
+      <c r="AZ220">
+        <v>8</v>
+      </c>
+      <c r="BA220">
+        <v>8</v>
+      </c>
+      <c r="BB220">
+        <v>4</v>
+      </c>
+      <c r="BC220">
+        <v>12</v>
+      </c>
+      <c r="BD220">
+        <v>1.1</v>
+      </c>
+      <c r="BE220">
+        <v>11</v>
+      </c>
+      <c r="BF220">
+        <v>7</v>
+      </c>
+      <c r="BG220">
+        <v>1.14</v>
+      </c>
+      <c r="BH220">
+        <v>4.8</v>
+      </c>
+      <c r="BI220">
+        <v>1.26</v>
+      </c>
+      <c r="BJ220">
+        <v>3.4</v>
+      </c>
+      <c r="BK220">
+        <v>1.44</v>
+      </c>
+      <c r="BL220">
+        <v>2.55</v>
+      </c>
+      <c r="BM220">
+        <v>1.68</v>
+      </c>
+      <c r="BN220">
+        <v>2.04</v>
+      </c>
+      <c r="BO220">
+        <v>2.02</v>
+      </c>
+      <c r="BP220">
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="344">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -742,6 +742,15 @@
     <t>['40', '57']</t>
   </si>
   <si>
+    <t>['17', '83']</t>
+  </si>
+  <si>
+    <t>['69', '90+1']</t>
+  </si>
+  <si>
+    <t>['19']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -776,9 +785,6 @@
   </si>
   <si>
     <t>['33', '70']</t>
-  </si>
-  <si>
-    <t>['19']</t>
   </si>
   <si>
     <t>['21', '53']</t>
@@ -1031,6 +1037,15 @@
   </si>
   <si>
     <t>['72']</t>
+  </si>
+  <si>
+    <t>['67', '75', '85']</t>
+  </si>
+  <si>
+    <t>['61']</t>
+  </si>
+  <si>
+    <t>['41', '66', '75']</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP220"/>
+  <dimension ref="A1:BP224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2060,7 +2075,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2138,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ4">
         <v>1.23</v>
@@ -2472,7 +2487,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -3090,7 +3105,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3583,7 +3598,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3789,7 +3804,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ12">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3992,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -4326,7 +4341,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4532,7 +4547,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4738,7 +4753,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4816,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ17">
         <v>1.67</v>
@@ -5022,10 +5037,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5231,7 +5246,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ19">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5434,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ20">
         <v>0.67</v>
@@ -5562,7 +5577,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5768,7 +5783,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5849,7 +5864,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ22">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR22">
         <v>0.79</v>
@@ -6798,7 +6813,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7210,7 +7225,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7622,7 +7637,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7700,7 +7715,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -8112,7 +8127,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ33">
         <v>0.67</v>
@@ -8321,7 +8336,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR34">
         <v>2.85</v>
@@ -8730,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ36">
         <v>0.67</v>
@@ -8858,7 +8873,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9270,7 +9285,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9476,7 +9491,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9557,7 +9572,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR40">
         <v>1.21</v>
@@ -9760,7 +9775,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ41">
         <v>0.5</v>
@@ -9969,7 +9984,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ42">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR42">
         <v>1.23</v>
@@ -10172,7 +10187,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ43">
         <v>0.54</v>
@@ -10506,7 +10521,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10584,7 +10599,7 @@
         <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ45">
         <v>1.75</v>
@@ -10712,7 +10727,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10918,7 +10933,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11124,7 +11139,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11205,7 +11220,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ48">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR48">
         <v>1.91</v>
@@ -11330,7 +11345,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11408,7 +11423,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ49">
         <v>0.67</v>
@@ -11536,7 +11551,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11742,7 +11757,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12154,7 +12169,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12566,7 +12581,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12644,7 +12659,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ55">
         <v>1.83</v>
@@ -12772,7 +12787,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -12850,7 +12865,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ56">
         <v>1.67</v>
@@ -13262,10 +13277,10 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ58">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR58">
         <v>1.08</v>
@@ -13468,7 +13483,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ59">
         <v>0.58</v>
@@ -13677,7 +13692,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR60">
         <v>1.17</v>
@@ -13802,7 +13817,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13883,7 +13898,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ61">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR61">
         <v>1.5</v>
@@ -14008,7 +14023,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14089,7 +14104,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ62">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR62">
         <v>2.58</v>
@@ -14832,7 +14847,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15038,7 +15053,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15656,7 +15671,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -16068,7 +16083,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16149,7 +16164,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ72">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -16274,7 +16289,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16558,7 +16573,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ74">
         <v>0.54</v>
@@ -16892,7 +16907,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17176,7 +17191,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ77">
         <v>1.08</v>
@@ -17385,7 +17400,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ78">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR78">
         <v>1.07</v>
@@ -17510,7 +17525,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17591,7 +17606,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ79">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR79">
         <v>1.54</v>
@@ -17716,7 +17731,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17794,7 +17809,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ80">
         <v>0.58</v>
@@ -18540,7 +18555,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18952,7 +18967,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19236,7 +19251,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ87">
         <v>0.67</v>
@@ -19570,7 +19585,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19651,7 +19666,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR89">
         <v>2.01</v>
@@ -19776,7 +19791,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19857,7 +19872,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR90">
         <v>1.77</v>
@@ -20060,7 +20075,7 @@
         <v>1.4</v>
       </c>
       <c r="AP91">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ91">
         <v>1.23</v>
@@ -20394,7 +20409,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20600,7 +20615,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -21012,7 +21027,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21296,7 +21311,7 @@
         <v>0.8</v>
       </c>
       <c r="AP97">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ97">
         <v>0.67</v>
@@ -21424,7 +21439,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21505,7 +21520,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ98">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR98">
         <v>1.7</v>
@@ -21711,7 +21726,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ99">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -22326,7 +22341,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ102">
         <v>1.08</v>
@@ -22454,7 +22469,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22660,7 +22675,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22866,7 +22881,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23072,7 +23087,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23150,10 +23165,10 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ106">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR106">
         <v>2.03</v>
@@ -23359,7 +23374,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ107">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR107">
         <v>1.85</v>
@@ -23484,7 +23499,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23771,7 +23786,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ109">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -24102,7 +24117,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24514,7 +24529,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24720,7 +24735,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24798,10 +24813,10 @@
         <v>2.6</v>
       </c>
       <c r="AP114">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ114">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -24926,7 +24941,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25132,7 +25147,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25210,7 +25225,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ116">
         <v>0.58</v>
@@ -25831,7 +25846,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ119">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR119">
         <v>1.34</v>
@@ -26446,7 +26461,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26574,7 +26589,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26780,7 +26795,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26858,10 +26873,10 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR124">
         <v>1.98</v>
@@ -27192,7 +27207,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27270,10 +27285,10 @@
         <v>1.83</v>
       </c>
       <c r="AP126">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ126">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR126">
         <v>1.45</v>
@@ -27398,7 +27413,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27479,7 +27494,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ127">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR127">
         <v>1.82</v>
@@ -28016,7 +28031,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28222,7 +28237,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28428,7 +28443,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28840,7 +28855,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28918,7 +28933,7 @@
         <v>0</v>
       </c>
       <c r="AP134">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ134">
         <v>0.54</v>
@@ -29127,7 +29142,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ135">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR135">
         <v>1.92</v>
@@ -29252,7 +29267,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29333,7 +29348,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ136">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29536,7 +29551,7 @@
         <v>1.14</v>
       </c>
       <c r="AP137">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ137">
         <v>1</v>
@@ -29870,7 +29885,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30076,7 +30091,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30282,7 +30297,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30363,7 +30378,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -30566,7 +30581,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ142">
         <v>1</v>
@@ -30772,7 +30787,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ143">
         <v>0.67</v>
@@ -30981,7 +30996,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ144">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR144">
         <v>1.74</v>
@@ -31106,7 +31121,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31312,7 +31327,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -32136,7 +32151,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32217,7 +32232,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ150">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR150">
         <v>1.58</v>
@@ -32548,7 +32563,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32832,7 +32847,7 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ153">
         <v>0.83</v>
@@ -32960,7 +32975,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33041,7 +33056,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ154">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR154">
         <v>1.32</v>
@@ -33578,7 +33593,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33656,7 +33671,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ157">
         <v>0.83</v>
@@ -33784,7 +33799,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33990,7 +34005,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34068,7 +34083,7 @@
         <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ159">
         <v>1</v>
@@ -34277,7 +34292,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ160">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR160">
         <v>1.27</v>
@@ -34402,7 +34417,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34483,7 +34498,7 @@
         <v>2</v>
       </c>
       <c r="AQ161">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR161">
         <v>1.8</v>
@@ -34608,7 +34623,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34814,7 +34829,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -34892,7 +34907,7 @@
         <v>2.33</v>
       </c>
       <c r="AP163">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ163">
         <v>1.83</v>
@@ -35226,7 +35241,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35304,7 +35319,7 @@
         <v>2</v>
       </c>
       <c r="AP165">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ165">
         <v>1.67</v>
@@ -35638,7 +35653,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35844,7 +35859,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36050,7 +36065,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36131,7 +36146,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ169">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR169">
         <v>1.56</v>
@@ -36256,7 +36271,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36334,7 +36349,7 @@
         <v>1.11</v>
       </c>
       <c r="AP170">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ170">
         <v>1.08</v>
@@ -36749,7 +36764,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ172">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR172">
         <v>1.45</v>
@@ -36874,7 +36889,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37286,7 +37301,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37698,7 +37713,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37904,7 +37919,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38316,7 +38331,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38394,10 +38409,10 @@
         <v>2.4</v>
       </c>
       <c r="AP180">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ180">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR180">
         <v>1.23</v>
@@ -38522,7 +38537,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38728,7 +38743,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38806,7 +38821,7 @@
         <v>2.1</v>
       </c>
       <c r="AP182">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ182">
         <v>1.83</v>
@@ -38934,7 +38949,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39346,7 +39361,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39758,7 +39773,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39836,7 +39851,7 @@
         <v>1.8</v>
       </c>
       <c r="AP187">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ187">
         <v>1.75</v>
@@ -39964,7 +39979,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40045,7 +40060,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ188">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR188">
         <v>1.33</v>
@@ -40170,7 +40185,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40869,7 +40884,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ192">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR192">
         <v>1.52</v>
@@ -41200,7 +41215,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41281,7 +41296,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ194">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR194">
         <v>1.36</v>
@@ -41612,7 +41627,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -42024,7 +42039,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42105,7 +42120,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ198">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR198">
         <v>2.36</v>
@@ -42436,7 +42451,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42514,7 +42529,7 @@
         <v>0.45</v>
       </c>
       <c r="AP200">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ200">
         <v>0.67</v>
@@ -42642,7 +42657,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42720,10 +42735,10 @@
         <v>0.6</v>
       </c>
       <c r="AP201">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ201">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR201">
         <v>1.59</v>
@@ -42926,7 +42941,7 @@
         <v>0.55</v>
       </c>
       <c r="AP202">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ202">
         <v>0.54</v>
@@ -43132,7 +43147,7 @@
         <v>0.55</v>
       </c>
       <c r="AP203">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ203">
         <v>0.5</v>
@@ -43547,7 +43562,7 @@
         <v>2</v>
       </c>
       <c r="AQ205">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR205">
         <v>1.87</v>
@@ -43753,7 +43768,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ206">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR206">
         <v>1.8</v>
@@ -43956,7 +43971,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ207">
         <v>0.83</v>
@@ -44290,7 +44305,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44702,7 +44717,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44908,7 +44923,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45526,7 +45541,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45813,7 +45828,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ216">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR216">
         <v>1.35</v>
@@ -46556,7 +46571,7 @@
         <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q220">
         <v>1.62</v>
@@ -46713,6 +46728,830 @@
       </c>
       <c r="BP220">
         <v>1.68</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7466277</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45725.34375</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>86</v>
+      </c>
+      <c r="H221" t="s">
+        <v>76</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221">
+        <v>2</v>
+      </c>
+      <c r="M221">
+        <v>3</v>
+      </c>
+      <c r="N221">
+        <v>5</v>
+      </c>
+      <c r="O221" t="s">
+        <v>242</v>
+      </c>
+      <c r="P221" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q221">
+        <v>4.33</v>
+      </c>
+      <c r="R221">
+        <v>2.2</v>
+      </c>
+      <c r="S221">
+        <v>2.6</v>
+      </c>
+      <c r="T221">
+        <v>1.4</v>
+      </c>
+      <c r="U221">
+        <v>2.75</v>
+      </c>
+      <c r="V221">
+        <v>3</v>
+      </c>
+      <c r="W221">
+        <v>1.36</v>
+      </c>
+      <c r="X221">
+        <v>8</v>
+      </c>
+      <c r="Y221">
+        <v>1.08</v>
+      </c>
+      <c r="Z221">
+        <v>3.84</v>
+      </c>
+      <c r="AA221">
+        <v>3.51</v>
+      </c>
+      <c r="AB221">
+        <v>2.04</v>
+      </c>
+      <c r="AC221">
+        <v>1.03</v>
+      </c>
+      <c r="AD221">
+        <v>15</v>
+      </c>
+      <c r="AE221">
+        <v>1.18</v>
+      </c>
+      <c r="AF221">
+        <v>4.65</v>
+      </c>
+      <c r="AG221">
+        <v>2</v>
+      </c>
+      <c r="AH221">
+        <v>1.82</v>
+      </c>
+      <c r="AI221">
+        <v>1.75</v>
+      </c>
+      <c r="AJ221">
+        <v>2</v>
+      </c>
+      <c r="AK221">
+        <v>1.78</v>
+      </c>
+      <c r="AL221">
+        <v>1.29</v>
+      </c>
+      <c r="AM221">
+        <v>1.27</v>
+      </c>
+      <c r="AN221">
+        <v>1</v>
+      </c>
+      <c r="AO221">
+        <v>2.17</v>
+      </c>
+      <c r="AP221">
+        <v>0.92</v>
+      </c>
+      <c r="AQ221">
+        <v>2.23</v>
+      </c>
+      <c r="AR221">
+        <v>1.2</v>
+      </c>
+      <c r="AS221">
+        <v>1.37</v>
+      </c>
+      <c r="AT221">
+        <v>2.57</v>
+      </c>
+      <c r="AU221">
+        <v>7</v>
+      </c>
+      <c r="AV221">
+        <v>7</v>
+      </c>
+      <c r="AW221">
+        <v>6</v>
+      </c>
+      <c r="AX221">
+        <v>9</v>
+      </c>
+      <c r="AY221">
+        <v>14</v>
+      </c>
+      <c r="AZ221">
+        <v>19</v>
+      </c>
+      <c r="BA221">
+        <v>4</v>
+      </c>
+      <c r="BB221">
+        <v>5</v>
+      </c>
+      <c r="BC221">
+        <v>9</v>
+      </c>
+      <c r="BD221">
+        <v>2.65</v>
+      </c>
+      <c r="BE221">
+        <v>6.75</v>
+      </c>
+      <c r="BF221">
+        <v>1.56</v>
+      </c>
+      <c r="BG221">
+        <v>1.25</v>
+      </c>
+      <c r="BH221">
+        <v>3.45</v>
+      </c>
+      <c r="BI221">
+        <v>1.44</v>
+      </c>
+      <c r="BJ221">
+        <v>2.55</v>
+      </c>
+      <c r="BK221">
+        <v>1.72</v>
+      </c>
+      <c r="BL221">
+        <v>1.98</v>
+      </c>
+      <c r="BM221">
+        <v>2.14</v>
+      </c>
+      <c r="BN221">
+        <v>1.61</v>
+      </c>
+      <c r="BO221">
+        <v>2.7</v>
+      </c>
+      <c r="BP221">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7466275</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45725.4375</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>85</v>
+      </c>
+      <c r="H222" t="s">
+        <v>78</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>91</v>
+      </c>
+      <c r="P222" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q222">
+        <v>5</v>
+      </c>
+      <c r="R222">
+        <v>2.38</v>
+      </c>
+      <c r="S222">
+        <v>2.2</v>
+      </c>
+      <c r="T222">
+        <v>1.3</v>
+      </c>
+      <c r="U222">
+        <v>3.4</v>
+      </c>
+      <c r="V222">
+        <v>2.5</v>
+      </c>
+      <c r="W222">
+        <v>1.5</v>
+      </c>
+      <c r="X222">
+        <v>6</v>
+      </c>
+      <c r="Y222">
+        <v>1.13</v>
+      </c>
+      <c r="Z222">
+        <v>5.1</v>
+      </c>
+      <c r="AA222">
+        <v>4.2</v>
+      </c>
+      <c r="AB222">
+        <v>1.67</v>
+      </c>
+      <c r="AC222">
+        <v>1.02</v>
+      </c>
+      <c r="AD222">
+        <v>17</v>
+      </c>
+      <c r="AE222">
+        <v>1.18</v>
+      </c>
+      <c r="AF222">
+        <v>4.65</v>
+      </c>
+      <c r="AG222">
+        <v>1.57</v>
+      </c>
+      <c r="AH222">
+        <v>2.25</v>
+      </c>
+      <c r="AI222">
+        <v>1.7</v>
+      </c>
+      <c r="AJ222">
+        <v>2.05</v>
+      </c>
+      <c r="AK222">
+        <v>2.2</v>
+      </c>
+      <c r="AL222">
+        <v>1.23</v>
+      </c>
+      <c r="AM222">
+        <v>1.18</v>
+      </c>
+      <c r="AN222">
+        <v>1.42</v>
+      </c>
+      <c r="AO222">
+        <v>2.17</v>
+      </c>
+      <c r="AP222">
+        <v>1.31</v>
+      </c>
+      <c r="AQ222">
+        <v>2.23</v>
+      </c>
+      <c r="AR222">
+        <v>1.26</v>
+      </c>
+      <c r="AS222">
+        <v>1.35</v>
+      </c>
+      <c r="AT222">
+        <v>2.61</v>
+      </c>
+      <c r="AU222">
+        <v>3</v>
+      </c>
+      <c r="AV222">
+        <v>6</v>
+      </c>
+      <c r="AW222">
+        <v>8</v>
+      </c>
+      <c r="AX222">
+        <v>6</v>
+      </c>
+      <c r="AY222">
+        <v>12</v>
+      </c>
+      <c r="AZ222">
+        <v>15</v>
+      </c>
+      <c r="BA222">
+        <v>3</v>
+      </c>
+      <c r="BB222">
+        <v>3</v>
+      </c>
+      <c r="BC222">
+        <v>6</v>
+      </c>
+      <c r="BD222">
+        <v>3.55</v>
+      </c>
+      <c r="BE222">
+        <v>7.5</v>
+      </c>
+      <c r="BF222">
+        <v>1.34</v>
+      </c>
+      <c r="BG222">
+        <v>1.3</v>
+      </c>
+      <c r="BH222">
+        <v>3.1</v>
+      </c>
+      <c r="BI222">
+        <v>1.52</v>
+      </c>
+      <c r="BJ222">
+        <v>2.32</v>
+      </c>
+      <c r="BK222">
+        <v>1.86</v>
+      </c>
+      <c r="BL222">
+        <v>1.82</v>
+      </c>
+      <c r="BM222">
+        <v>2.33</v>
+      </c>
+      <c r="BN222">
+        <v>1.52</v>
+      </c>
+      <c r="BO222">
+        <v>3</v>
+      </c>
+      <c r="BP222">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7466273</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45725.4375</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>72</v>
+      </c>
+      <c r="H223" t="s">
+        <v>77</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>1</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+      <c r="L223">
+        <v>2</v>
+      </c>
+      <c r="M223">
+        <v>3</v>
+      </c>
+      <c r="N223">
+        <v>5</v>
+      </c>
+      <c r="O223" t="s">
+        <v>243</v>
+      </c>
+      <c r="P223" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q223">
+        <v>2.75</v>
+      </c>
+      <c r="R223">
+        <v>2.25</v>
+      </c>
+      <c r="S223">
+        <v>3.6</v>
+      </c>
+      <c r="T223">
+        <v>1.33</v>
+      </c>
+      <c r="U223">
+        <v>3.25</v>
+      </c>
+      <c r="V223">
+        <v>2.63</v>
+      </c>
+      <c r="W223">
+        <v>1.44</v>
+      </c>
+      <c r="X223">
+        <v>7</v>
+      </c>
+      <c r="Y223">
+        <v>1.1</v>
+      </c>
+      <c r="Z223">
+        <v>2.18</v>
+      </c>
+      <c r="AA223">
+        <v>3.64</v>
+      </c>
+      <c r="AB223">
+        <v>3.33</v>
+      </c>
+      <c r="AC223">
+        <v>1.02</v>
+      </c>
+      <c r="AD223">
+        <v>17</v>
+      </c>
+      <c r="AE223">
+        <v>1.16</v>
+      </c>
+      <c r="AF223">
+        <v>4.87</v>
+      </c>
+      <c r="AG223">
+        <v>1.65</v>
+      </c>
+      <c r="AH223">
+        <v>2.1</v>
+      </c>
+      <c r="AI223">
+        <v>1.62</v>
+      </c>
+      <c r="AJ223">
+        <v>2.2</v>
+      </c>
+      <c r="AK223">
+        <v>1.35</v>
+      </c>
+      <c r="AL223">
+        <v>1.28</v>
+      </c>
+      <c r="AM223">
+        <v>1.66</v>
+      </c>
+      <c r="AN223">
+        <v>1.33</v>
+      </c>
+      <c r="AO223">
+        <v>1</v>
+      </c>
+      <c r="AP223">
+        <v>1.23</v>
+      </c>
+      <c r="AQ223">
+        <v>1.17</v>
+      </c>
+      <c r="AR223">
+        <v>1.55</v>
+      </c>
+      <c r="AS223">
+        <v>1.18</v>
+      </c>
+      <c r="AT223">
+        <v>2.73</v>
+      </c>
+      <c r="AU223">
+        <v>6</v>
+      </c>
+      <c r="AV223">
+        <v>15</v>
+      </c>
+      <c r="AW223">
+        <v>6</v>
+      </c>
+      <c r="AX223">
+        <v>13</v>
+      </c>
+      <c r="AY223">
+        <v>14</v>
+      </c>
+      <c r="AZ223">
+        <v>30</v>
+      </c>
+      <c r="BA223">
+        <v>3</v>
+      </c>
+      <c r="BB223">
+        <v>15</v>
+      </c>
+      <c r="BC223">
+        <v>18</v>
+      </c>
+      <c r="BD223">
+        <v>1.61</v>
+      </c>
+      <c r="BE223">
+        <v>6.75</v>
+      </c>
+      <c r="BF223">
+        <v>2.55</v>
+      </c>
+      <c r="BG223">
+        <v>1.2</v>
+      </c>
+      <c r="BH223">
+        <v>3.95</v>
+      </c>
+      <c r="BI223">
+        <v>1.35</v>
+      </c>
+      <c r="BJ223">
+        <v>2.9</v>
+      </c>
+      <c r="BK223">
+        <v>1.58</v>
+      </c>
+      <c r="BL223">
+        <v>2.2</v>
+      </c>
+      <c r="BM223">
+        <v>1.92</v>
+      </c>
+      <c r="BN223">
+        <v>1.77</v>
+      </c>
+      <c r="BO223">
+        <v>2.4</v>
+      </c>
+      <c r="BP223">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7466270</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45725.53125</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>81</v>
+      </c>
+      <c r="H224" t="s">
+        <v>73</v>
+      </c>
+      <c r="I224">
+        <v>1</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>1</v>
+      </c>
+      <c r="O224" t="s">
+        <v>244</v>
+      </c>
+      <c r="P224" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q224">
+        <v>1.73</v>
+      </c>
+      <c r="R224">
+        <v>2.63</v>
+      </c>
+      <c r="S224">
+        <v>8</v>
+      </c>
+      <c r="T224">
+        <v>1.29</v>
+      </c>
+      <c r="U224">
+        <v>3.5</v>
+      </c>
+      <c r="V224">
+        <v>2.25</v>
+      </c>
+      <c r="W224">
+        <v>1.57</v>
+      </c>
+      <c r="X224">
+        <v>5.5</v>
+      </c>
+      <c r="Y224">
+        <v>1.14</v>
+      </c>
+      <c r="Z224">
+        <v>1.3</v>
+      </c>
+      <c r="AA224">
+        <v>6</v>
+      </c>
+      <c r="AB224">
+        <v>9.6</v>
+      </c>
+      <c r="AC224">
+        <v>1.01</v>
+      </c>
+      <c r="AD224">
+        <v>17</v>
+      </c>
+      <c r="AE224">
+        <v>1.08</v>
+      </c>
+      <c r="AF224">
+        <v>7.29</v>
+      </c>
+      <c r="AG224">
+        <v>1.55</v>
+      </c>
+      <c r="AH224">
+        <v>2.35</v>
+      </c>
+      <c r="AI224">
+        <v>1.95</v>
+      </c>
+      <c r="AJ224">
+        <v>1.8</v>
+      </c>
+      <c r="AK224">
+        <v>1.07</v>
+      </c>
+      <c r="AL224">
+        <v>1.14</v>
+      </c>
+      <c r="AM224">
+        <v>3.4</v>
+      </c>
+      <c r="AN224">
+        <v>2.45</v>
+      </c>
+      <c r="AO224">
+        <v>0.58</v>
+      </c>
+      <c r="AP224">
+        <v>2.5</v>
+      </c>
+      <c r="AQ224">
+        <v>0.54</v>
+      </c>
+      <c r="AR224">
+        <v>2.02</v>
+      </c>
+      <c r="AS224">
+        <v>1.21</v>
+      </c>
+      <c r="AT224">
+        <v>3.23</v>
+      </c>
+      <c r="AU224">
+        <v>5</v>
+      </c>
+      <c r="AV224">
+        <v>2</v>
+      </c>
+      <c r="AW224">
+        <v>11</v>
+      </c>
+      <c r="AX224">
+        <v>6</v>
+      </c>
+      <c r="AY224">
+        <v>17</v>
+      </c>
+      <c r="AZ224">
+        <v>10</v>
+      </c>
+      <c r="BA224">
+        <v>4</v>
+      </c>
+      <c r="BB224">
+        <v>3</v>
+      </c>
+      <c r="BC224">
+        <v>7</v>
+      </c>
+      <c r="BD224">
+        <v>0</v>
+      </c>
+      <c r="BE224">
+        <v>0</v>
+      </c>
+      <c r="BF224">
+        <v>0</v>
+      </c>
+      <c r="BG224">
+        <v>0</v>
+      </c>
+      <c r="BH224">
+        <v>0</v>
+      </c>
+      <c r="BI224">
+        <v>0</v>
+      </c>
+      <c r="BJ224">
+        <v>0</v>
+      </c>
+      <c r="BK224">
+        <v>0</v>
+      </c>
+      <c r="BL224">
+        <v>0</v>
+      </c>
+      <c r="BM224">
+        <v>0</v>
+      </c>
+      <c r="BN224">
+        <v>0</v>
+      </c>
+      <c r="BO224">
+        <v>0</v>
+      </c>
+      <c r="BP224">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="344">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1407,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP224"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1744,7 +1744,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ2">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ5">
         <v>1.75</v>
@@ -5655,7 +5655,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ21">
         <v>1.83</v>
@@ -7097,7 +7097,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ28">
         <v>0.67</v>
@@ -7512,7 +7512,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ30">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR30">
         <v>2.4</v>
@@ -11835,7 +11835,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ51">
         <v>1.23</v>
@@ -12044,7 +12044,7 @@
         <v>2</v>
       </c>
       <c r="AQ52">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR52">
         <v>2.23</v>
@@ -13486,7 +13486,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ59">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR59">
         <v>2.11</v>
@@ -14307,7 +14307,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ63">
         <v>1</v>
@@ -17812,7 +17812,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ80">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR80">
         <v>1.12</v>
@@ -18015,7 +18015,7 @@
         <v>0.75</v>
       </c>
       <c r="AP81">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ81">
         <v>0.83</v>
@@ -20284,7 +20284,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ92">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR92">
         <v>1.39</v>
@@ -22959,7 +22959,7 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ105">
         <v>1.67</v>
@@ -25228,7 +25228,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ116">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR116">
         <v>1.02</v>
@@ -28112,7 +28112,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ130">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR130">
         <v>1.55</v>
@@ -29345,7 +29345,7 @@
         <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ136">
         <v>2.23</v>
@@ -31614,7 +31614,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ147">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR147">
         <v>1.7</v>
@@ -31817,7 +31817,7 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ148">
         <v>0.54</v>
@@ -35937,7 +35937,7 @@
         <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ168">
         <v>0.67</v>
@@ -36970,7 +36970,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ173">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR173">
         <v>2.35</v>
@@ -39027,7 +39027,7 @@
         <v>0.3</v>
       </c>
       <c r="AP183">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ183">
         <v>0.5</v>
@@ -41090,7 +41090,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ193">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR193">
         <v>1.22</v>
@@ -44592,7 +44592,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ210">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR210">
         <v>1.55</v>
@@ -45825,7 +45825,7 @@
         <v>2.09</v>
       </c>
       <c r="AP216">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ216">
         <v>2.23</v>
@@ -47552,6 +47552,212 @@
       </c>
       <c r="BP224">
         <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7466279</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F225">
+        <v>26</v>
+      </c>
+      <c r="G225" t="s">
+        <v>73</v>
+      </c>
+      <c r="H225" t="s">
+        <v>87</v>
+      </c>
+      <c r="I225">
+        <v>1</v>
+      </c>
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="K225">
+        <v>2</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
+      </c>
+      <c r="N225">
+        <v>2</v>
+      </c>
+      <c r="O225" t="s">
+        <v>244</v>
+      </c>
+      <c r="P225" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q225">
+        <v>3</v>
+      </c>
+      <c r="R225">
+        <v>2.2</v>
+      </c>
+      <c r="S225">
+        <v>3.5</v>
+      </c>
+      <c r="T225">
+        <v>1.4</v>
+      </c>
+      <c r="U225">
+        <v>2.75</v>
+      </c>
+      <c r="V225">
+        <v>2.75</v>
+      </c>
+      <c r="W225">
+        <v>1.4</v>
+      </c>
+      <c r="X225">
+        <v>8</v>
+      </c>
+      <c r="Y225">
+        <v>1.08</v>
+      </c>
+      <c r="Z225">
+        <v>2.76</v>
+      </c>
+      <c r="AA225">
+        <v>3.7</v>
+      </c>
+      <c r="AB225">
+        <v>2.49</v>
+      </c>
+      <c r="AC225">
+        <v>1.05</v>
+      </c>
+      <c r="AD225">
+        <v>9</v>
+      </c>
+      <c r="AE225">
+        <v>1.3</v>
+      </c>
+      <c r="AF225">
+        <v>3.45</v>
+      </c>
+      <c r="AG225">
+        <v>1.88</v>
+      </c>
+      <c r="AH225">
+        <v>1.93</v>
+      </c>
+      <c r="AI225">
+        <v>1.75</v>
+      </c>
+      <c r="AJ225">
+        <v>2</v>
+      </c>
+      <c r="AK225">
+        <v>1.5</v>
+      </c>
+      <c r="AL225">
+        <v>1.28</v>
+      </c>
+      <c r="AM225">
+        <v>1.49</v>
+      </c>
+      <c r="AN225">
+        <v>0.58</v>
+      </c>
+      <c r="AO225">
+        <v>0.58</v>
+      </c>
+      <c r="AP225">
+        <v>0.62</v>
+      </c>
+      <c r="AQ225">
+        <v>0.62</v>
+      </c>
+      <c r="AR225">
+        <v>1.36</v>
+      </c>
+      <c r="AS225">
+        <v>1.16</v>
+      </c>
+      <c r="AT225">
+        <v>2.52</v>
+      </c>
+      <c r="AU225">
+        <v>8</v>
+      </c>
+      <c r="AV225">
+        <v>4</v>
+      </c>
+      <c r="AW225">
+        <v>8</v>
+      </c>
+      <c r="AX225">
+        <v>9</v>
+      </c>
+      <c r="AY225">
+        <v>17</v>
+      </c>
+      <c r="AZ225">
+        <v>13</v>
+      </c>
+      <c r="BA225">
+        <v>3</v>
+      </c>
+      <c r="BB225">
+        <v>6</v>
+      </c>
+      <c r="BC225">
+        <v>9</v>
+      </c>
+      <c r="BD225">
+        <v>1.74</v>
+      </c>
+      <c r="BE225">
+        <v>6.4</v>
+      </c>
+      <c r="BF225">
+        <v>2.32</v>
+      </c>
+      <c r="BG225">
+        <v>1.25</v>
+      </c>
+      <c r="BH225">
+        <v>3.4</v>
+      </c>
+      <c r="BI225">
+        <v>1.44</v>
+      </c>
+      <c r="BJ225">
+        <v>2.55</v>
+      </c>
+      <c r="BK225">
+        <v>1.72</v>
+      </c>
+      <c r="BL225">
+        <v>1.98</v>
+      </c>
+      <c r="BM225">
+        <v>2.15</v>
+      </c>
+      <c r="BN225">
+        <v>1.61</v>
+      </c>
+      <c r="BO225">
+        <v>2.75</v>
+      </c>
+      <c r="BP225">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="347">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,12 @@
     <t>['19']</t>
   </si>
   <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1046,6 +1052,9 @@
   </si>
   <si>
     <t>['41', '66', '75']</t>
+  </si>
+  <si>
+    <t>['4', '39', '53']</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2075,7 +2084,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2487,7 +2496,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2774,7 +2783,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ7">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2977,10 +2986,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ8">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3105,7 +3114,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3801,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ12">
         <v>2.23</v>
@@ -4216,7 +4225,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ14">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4341,7 +4350,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4419,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -4547,7 +4556,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4628,7 +4637,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ16">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4753,7 +4762,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5452,7 +5461,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ20">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR20">
         <v>1.11</v>
@@ -5577,7 +5586,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5658,7 +5667,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ21">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR21">
         <v>0.96</v>
@@ -5783,7 +5792,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6813,7 +6822,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6891,7 +6900,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ27">
         <v>1.75</v>
@@ -7225,7 +7234,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7306,7 +7315,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>2.19</v>
@@ -7509,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ30">
         <v>0.62</v>
@@ -7637,7 +7646,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7921,7 +7930,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ32">
         <v>1.23</v>
@@ -8130,7 +8139,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ33">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR33">
         <v>0.7</v>
@@ -8542,7 +8551,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ35">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>2.65</v>
@@ -8748,7 +8757,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ36">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR36">
         <v>1.72</v>
@@ -8873,7 +8882,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9491,7 +9500,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -10521,7 +10530,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10727,7 +10736,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10805,7 +10814,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -10933,7 +10942,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11011,7 +11020,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -11139,7 +11148,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11345,7 +11354,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11426,7 +11435,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ49">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR49">
         <v>1.18</v>
@@ -11551,7 +11560,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11629,7 +11638,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ50">
         <v>0.67</v>
@@ -11757,7 +11766,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12169,7 +12178,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12250,7 +12259,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ53">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12581,7 +12590,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12662,7 +12671,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ55">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR55">
         <v>1.25</v>
@@ -12787,7 +12796,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13817,7 +13826,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13895,7 +13904,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ61">
         <v>2.23</v>
@@ -14023,7 +14032,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14516,7 +14525,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ64">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -14847,7 +14856,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14925,7 +14934,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ66">
         <v>0.5</v>
@@ -15053,7 +15062,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15134,7 +15143,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ67">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15543,10 +15552,10 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ69">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR69">
         <v>2.09</v>
@@ -15671,7 +15680,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -16083,7 +16092,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16289,7 +16298,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16370,7 +16379,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ73">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR73">
         <v>2.44</v>
@@ -16779,7 +16788,7 @@
         <v>1.5</v>
       </c>
       <c r="AP75">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ75">
         <v>1.23</v>
@@ -16907,7 +16916,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17525,7 +17534,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17731,7 +17740,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18018,7 +18027,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ81">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.25</v>
@@ -18430,7 +18439,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ83">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR83">
         <v>2.49</v>
@@ -18555,7 +18564,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18839,7 +18848,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -18967,7 +18976,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19045,7 +19054,7 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ86">
         <v>1.67</v>
@@ -19254,7 +19263,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ87">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -19585,7 +19594,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19791,7 +19800,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -20409,7 +20418,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20490,7 +20499,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ93">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR93">
         <v>2.04</v>
@@ -20615,7 +20624,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -21027,7 +21036,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21108,7 +21117,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ96">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21439,7 +21448,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21723,7 +21732,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ99">
         <v>0.54</v>
@@ -21929,10 +21938,10 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ100">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR100">
         <v>1.37</v>
@@ -22469,7 +22478,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22550,7 +22559,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ103">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR103">
         <v>1.38</v>
@@ -22675,7 +22684,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22753,10 +22762,10 @@
         <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ104">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.2</v>
@@ -22881,7 +22890,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23087,7 +23096,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23371,7 +23380,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ107">
         <v>1.17</v>
@@ -23499,7 +23508,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -24117,7 +24126,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24529,7 +24538,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24735,7 +24744,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24941,7 +24950,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25147,7 +25156,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25434,7 +25443,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ117">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR117">
         <v>2.01</v>
@@ -25637,7 +25646,7 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ118">
         <v>0.5</v>
@@ -26589,7 +26598,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26667,10 +26676,10 @@
         <v>2.57</v>
       </c>
       <c r="AP123">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ123">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR123">
         <v>1.43</v>
@@ -26795,7 +26804,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27082,7 +27091,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ125">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR125">
         <v>1.92</v>
@@ -27207,7 +27216,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27413,7 +27422,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27906,7 +27915,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ129">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -28031,7 +28040,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28237,7 +28246,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28315,7 +28324,7 @@
         <v>2.14</v>
       </c>
       <c r="AP131">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ131">
         <v>1.67</v>
@@ -28443,7 +28452,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28730,7 +28739,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ133">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR133">
         <v>1.23</v>
@@ -28855,7 +28864,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29267,7 +29276,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29757,10 +29766,10 @@
         <v>2.63</v>
       </c>
       <c r="AP138">
+        <v>1.85</v>
+      </c>
+      <c r="AQ138">
         <v>1.92</v>
-      </c>
-      <c r="AQ138">
-        <v>1.83</v>
       </c>
       <c r="AR138">
         <v>1.59</v>
@@ -29885,7 +29894,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30091,7 +30100,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30172,7 +30181,7 @@
         <v>2</v>
       </c>
       <c r="AQ140">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR140">
         <v>1.81</v>
@@ -30297,7 +30306,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30375,7 +30384,7 @@
         <v>1</v>
       </c>
       <c r="AP141">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ141">
         <v>1.17</v>
@@ -31121,7 +31130,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31327,7 +31336,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31405,10 +31414,10 @@
         <v>0.5</v>
       </c>
       <c r="AP146">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ146">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR146">
         <v>1.16</v>
@@ -32151,7 +32160,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32563,7 +32572,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32641,7 +32650,7 @@
         <v>0.88</v>
       </c>
       <c r="AP152">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ152">
         <v>1.08</v>
@@ -32850,7 +32859,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ153">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR153">
         <v>1.13</v>
@@ -32975,7 +32984,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33593,7 +33602,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33674,7 +33683,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ157">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR157">
         <v>1.23</v>
@@ -33799,7 +33808,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -34005,7 +34014,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34417,7 +34426,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34623,7 +34632,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34829,7 +34838,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -34910,7 +34919,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ163">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR163">
         <v>1.24</v>
@@ -35113,7 +35122,7 @@
         <v>1.89</v>
       </c>
       <c r="AP164">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ164">
         <v>1.75</v>
@@ -35241,7 +35250,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35653,7 +35662,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35859,7 +35868,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -35940,7 +35949,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ168">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR168">
         <v>1.26</v>
@@ -36065,7 +36074,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36143,7 +36152,7 @@
         <v>1.89</v>
       </c>
       <c r="AP169">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ169">
         <v>2.23</v>
@@ -36271,7 +36280,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36889,7 +36898,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37301,7 +37310,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37382,7 +37391,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ175">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR175">
         <v>1.34</v>
@@ -37585,7 +37594,7 @@
         <v>1.22</v>
       </c>
       <c r="AP176">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ176">
         <v>1</v>
@@ -37713,7 +37722,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37919,7 +37928,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38206,7 +38215,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ179">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR179">
         <v>1.35</v>
@@ -38331,7 +38340,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38537,7 +38546,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38615,7 +38624,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ181">
         <v>1.08</v>
@@ -38743,7 +38752,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38824,7 +38833,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ182">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR182">
         <v>1.6</v>
@@ -38949,7 +38958,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39361,7 +39370,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39773,7 +39782,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39979,7 +39988,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40185,7 +40194,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40472,7 +40481,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ190">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR190">
         <v>1.38</v>
@@ -40881,7 +40890,7 @@
         <v>0.33</v>
       </c>
       <c r="AP192">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ192">
         <v>0.54</v>
@@ -41087,7 +41096,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ193">
         <v>0.62</v>
@@ -41215,7 +41224,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41502,7 +41511,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ195">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR195">
         <v>1.82</v>
@@ -41627,7 +41636,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41705,7 +41714,7 @@
         <v>1.27</v>
       </c>
       <c r="AP196">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ196">
         <v>1.23</v>
@@ -42039,7 +42048,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42451,7 +42460,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42657,7 +42666,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43356,7 +43365,7 @@
         <v>2.83</v>
       </c>
       <c r="AQ204">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR204">
         <v>1.82</v>
@@ -43974,7 +43983,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ207">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR207">
         <v>2.08</v>
@@ -44305,7 +44314,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44383,7 +44392,7 @@
         <v>0.92</v>
       </c>
       <c r="AP209">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ209">
         <v>1.08</v>
@@ -44589,7 +44598,7 @@
         <v>0.64</v>
       </c>
       <c r="AP210">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ210">
         <v>0.62</v>
@@ -44717,7 +44726,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44798,7 +44807,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ211">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR211">
         <v>1.68</v>
@@ -44923,7 +44932,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45210,7 +45219,7 @@
         <v>2</v>
       </c>
       <c r="AQ213">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR213">
         <v>1.91</v>
@@ -45413,7 +45422,7 @@
         <v>1.91</v>
       </c>
       <c r="AP214">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ214">
         <v>1.75</v>
@@ -45541,7 +45550,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45622,7 +45631,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ215">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR215">
         <v>1.42</v>
@@ -46446,7 +46455,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ219">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR219">
         <v>1.35</v>
@@ -46571,7 +46580,7 @@
         <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q220">
         <v>1.62</v>
@@ -46777,7 +46786,7 @@
         <v>242</v>
       </c>
       <c r="P221" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q221">
         <v>4.33</v>
@@ -46983,7 +46992,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q222">
         <v>5</v>
@@ -47189,7 +47198,7 @@
         <v>243</v>
       </c>
       <c r="P223" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q223">
         <v>2.75</v>
@@ -47758,6 +47767,830 @@
       </c>
       <c r="BP225">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7466282</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45731.52083333334</v>
+      </c>
+      <c r="F226">
+        <v>26</v>
+      </c>
+      <c r="G226" t="s">
+        <v>76</v>
+      </c>
+      <c r="H226" t="s">
+        <v>72</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>1</v>
+      </c>
+      <c r="O226" t="s">
+        <v>91</v>
+      </c>
+      <c r="P226" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q226">
+        <v>2.38</v>
+      </c>
+      <c r="R226">
+        <v>2.3</v>
+      </c>
+      <c r="S226">
+        <v>4.33</v>
+      </c>
+      <c r="T226">
+        <v>1.33</v>
+      </c>
+      <c r="U226">
+        <v>3.25</v>
+      </c>
+      <c r="V226">
+        <v>2.5</v>
+      </c>
+      <c r="W226">
+        <v>1.5</v>
+      </c>
+      <c r="X226">
+        <v>6.5</v>
+      </c>
+      <c r="Y226">
+        <v>1.11</v>
+      </c>
+      <c r="Z226">
+        <v>1.72</v>
+      </c>
+      <c r="AA226">
+        <v>4.3</v>
+      </c>
+      <c r="AB226">
+        <v>4.5</v>
+      </c>
+      <c r="AC226">
+        <v>1.04</v>
+      </c>
+      <c r="AD226">
+        <v>10</v>
+      </c>
+      <c r="AE226">
+        <v>1.22</v>
+      </c>
+      <c r="AF226">
+        <v>4.2</v>
+      </c>
+      <c r="AG226">
+        <v>1.54</v>
+      </c>
+      <c r="AH226">
+        <v>2.26</v>
+      </c>
+      <c r="AI226">
+        <v>1.67</v>
+      </c>
+      <c r="AJ226">
+        <v>2.1</v>
+      </c>
+      <c r="AK226">
+        <v>1.24</v>
+      </c>
+      <c r="AL226">
+        <v>1.25</v>
+      </c>
+      <c r="AM226">
+        <v>1.95</v>
+      </c>
+      <c r="AN226">
+        <v>1.67</v>
+      </c>
+      <c r="AO226">
+        <v>0.83</v>
+      </c>
+      <c r="AP226">
+        <v>1.54</v>
+      </c>
+      <c r="AQ226">
+        <v>1</v>
+      </c>
+      <c r="AR226">
+        <v>1.62</v>
+      </c>
+      <c r="AS226">
+        <v>1.28</v>
+      </c>
+      <c r="AT226">
+        <v>2.9</v>
+      </c>
+      <c r="AU226">
+        <v>4</v>
+      </c>
+      <c r="AV226">
+        <v>4</v>
+      </c>
+      <c r="AW226">
+        <v>8</v>
+      </c>
+      <c r="AX226">
+        <v>11</v>
+      </c>
+      <c r="AY226">
+        <v>14</v>
+      </c>
+      <c r="AZ226">
+        <v>18</v>
+      </c>
+      <c r="BA226">
+        <v>6</v>
+      </c>
+      <c r="BB226">
+        <v>5</v>
+      </c>
+      <c r="BC226">
+        <v>11</v>
+      </c>
+      <c r="BD226">
+        <v>1.43</v>
+      </c>
+      <c r="BE226">
+        <v>7</v>
+      </c>
+      <c r="BF226">
+        <v>3.15</v>
+      </c>
+      <c r="BG226">
+        <v>1.16</v>
+      </c>
+      <c r="BH226">
+        <v>4.3</v>
+      </c>
+      <c r="BI226">
+        <v>1.3</v>
+      </c>
+      <c r="BJ226">
+        <v>3.05</v>
+      </c>
+      <c r="BK226">
+        <v>1.52</v>
+      </c>
+      <c r="BL226">
+        <v>2.33</v>
+      </c>
+      <c r="BM226">
+        <v>1.82</v>
+      </c>
+      <c r="BN226">
+        <v>1.86</v>
+      </c>
+      <c r="BO226">
+        <v>2.28</v>
+      </c>
+      <c r="BP226">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7466286</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45731.61458333334</v>
+      </c>
+      <c r="F227">
+        <v>26</v>
+      </c>
+      <c r="G227" t="s">
+        <v>75</v>
+      </c>
+      <c r="H227" t="s">
+        <v>85</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>0</v>
+      </c>
+      <c r="L227">
+        <v>1</v>
+      </c>
+      <c r="M227">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>2</v>
+      </c>
+      <c r="O227" t="s">
+        <v>245</v>
+      </c>
+      <c r="P227" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q227">
+        <v>2.2</v>
+      </c>
+      <c r="R227">
+        <v>2.3</v>
+      </c>
+      <c r="S227">
+        <v>5.5</v>
+      </c>
+      <c r="T227">
+        <v>1.36</v>
+      </c>
+      <c r="U227">
+        <v>3</v>
+      </c>
+      <c r="V227">
+        <v>2.63</v>
+      </c>
+      <c r="W227">
+        <v>1.44</v>
+      </c>
+      <c r="X227">
+        <v>7</v>
+      </c>
+      <c r="Y227">
+        <v>1.1</v>
+      </c>
+      <c r="Z227">
+        <v>1.64</v>
+      </c>
+      <c r="AA227">
+        <v>4.2</v>
+      </c>
+      <c r="AB227">
+        <v>5.2</v>
+      </c>
+      <c r="AC227">
+        <v>1.05</v>
+      </c>
+      <c r="AD227">
+        <v>9.5</v>
+      </c>
+      <c r="AE227">
+        <v>1.25</v>
+      </c>
+      <c r="AF227">
+        <v>3.85</v>
+      </c>
+      <c r="AG227">
+        <v>1.83</v>
+      </c>
+      <c r="AH227">
+        <v>1.98</v>
+      </c>
+      <c r="AI227">
+        <v>1.8</v>
+      </c>
+      <c r="AJ227">
+        <v>1.95</v>
+      </c>
+      <c r="AK227">
+        <v>1.17</v>
+      </c>
+      <c r="AL227">
+        <v>1.23</v>
+      </c>
+      <c r="AM227">
+        <v>2.2</v>
+      </c>
+      <c r="AN227">
+        <v>0.92</v>
+      </c>
+      <c r="AO227">
+        <v>0.67</v>
+      </c>
+      <c r="AP227">
+        <v>0.92</v>
+      </c>
+      <c r="AQ227">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR227">
+        <v>1.66</v>
+      </c>
+      <c r="AS227">
+        <v>1.02</v>
+      </c>
+      <c r="AT227">
+        <v>2.68</v>
+      </c>
+      <c r="AU227">
+        <v>4</v>
+      </c>
+      <c r="AV227">
+        <v>5</v>
+      </c>
+      <c r="AW227">
+        <v>6</v>
+      </c>
+      <c r="AX227">
+        <v>3</v>
+      </c>
+      <c r="AY227">
+        <v>11</v>
+      </c>
+      <c r="AZ227">
+        <v>9</v>
+      </c>
+      <c r="BA227">
+        <v>1</v>
+      </c>
+      <c r="BB227">
+        <v>4</v>
+      </c>
+      <c r="BC227">
+        <v>5</v>
+      </c>
+      <c r="BD227">
+        <v>1.27</v>
+      </c>
+      <c r="BE227">
+        <v>8</v>
+      </c>
+      <c r="BF227">
+        <v>4</v>
+      </c>
+      <c r="BG227">
+        <v>1.16</v>
+      </c>
+      <c r="BH227">
+        <v>4.4</v>
+      </c>
+      <c r="BI227">
+        <v>1.29</v>
+      </c>
+      <c r="BJ227">
+        <v>3.15</v>
+      </c>
+      <c r="BK227">
+        <v>1.49</v>
+      </c>
+      <c r="BL227">
+        <v>2.4</v>
+      </c>
+      <c r="BM227">
+        <v>1.85</v>
+      </c>
+      <c r="BN227">
+        <v>1.85</v>
+      </c>
+      <c r="BO227">
+        <v>2.18</v>
+      </c>
+      <c r="BP227">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7466284</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45731.66666666666</v>
+      </c>
+      <c r="F228">
+        <v>26</v>
+      </c>
+      <c r="G228" t="s">
+        <v>83</v>
+      </c>
+      <c r="H228" t="s">
+        <v>74</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>2</v>
+      </c>
+      <c r="K228">
+        <v>2</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228">
+        <v>3</v>
+      </c>
+      <c r="N228">
+        <v>3</v>
+      </c>
+      <c r="O228" t="s">
+        <v>91</v>
+      </c>
+      <c r="P228" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q228">
+        <v>8</v>
+      </c>
+      <c r="R228">
+        <v>3</v>
+      </c>
+      <c r="S228">
+        <v>1.62</v>
+      </c>
+      <c r="T228">
+        <v>1.18</v>
+      </c>
+      <c r="U228">
+        <v>4.5</v>
+      </c>
+      <c r="V228">
+        <v>1.83</v>
+      </c>
+      <c r="W228">
+        <v>1.83</v>
+      </c>
+      <c r="X228">
+        <v>3.75</v>
+      </c>
+      <c r="Y228">
+        <v>1.25</v>
+      </c>
+      <c r="Z228">
+        <v>12</v>
+      </c>
+      <c r="AA228">
+        <v>7.6</v>
+      </c>
+      <c r="AB228">
+        <v>1.22</v>
+      </c>
+      <c r="AC228">
+        <v>1.01</v>
+      </c>
+      <c r="AD228">
+        <v>29</v>
+      </c>
+      <c r="AE228">
+        <v>1.09</v>
+      </c>
+      <c r="AF228">
+        <v>7</v>
+      </c>
+      <c r="AG228">
+        <v>1.31</v>
+      </c>
+      <c r="AH228">
+        <v>3.15</v>
+      </c>
+      <c r="AI228">
+        <v>1.7</v>
+      </c>
+      <c r="AJ228">
+        <v>2.05</v>
+      </c>
+      <c r="AK228">
+        <v>4</v>
+      </c>
+      <c r="AL228">
+        <v>1.1</v>
+      </c>
+      <c r="AM228">
+        <v>1.06</v>
+      </c>
+      <c r="AN228">
+        <v>0.92</v>
+      </c>
+      <c r="AO228">
+        <v>1.83</v>
+      </c>
+      <c r="AP228">
+        <v>0.85</v>
+      </c>
+      <c r="AQ228">
+        <v>1.92</v>
+      </c>
+      <c r="AR228">
+        <v>1.35</v>
+      </c>
+      <c r="AS228">
+        <v>1.89</v>
+      </c>
+      <c r="AT228">
+        <v>3.24</v>
+      </c>
+      <c r="AU228">
+        <v>2</v>
+      </c>
+      <c r="AV228">
+        <v>7</v>
+      </c>
+      <c r="AW228">
+        <v>2</v>
+      </c>
+      <c r="AX228">
+        <v>11</v>
+      </c>
+      <c r="AY228">
+        <v>4</v>
+      </c>
+      <c r="AZ228">
+        <v>18</v>
+      </c>
+      <c r="BA228">
+        <v>1</v>
+      </c>
+      <c r="BB228">
+        <v>5</v>
+      </c>
+      <c r="BC228">
+        <v>6</v>
+      </c>
+      <c r="BD228">
+        <v>6.1</v>
+      </c>
+      <c r="BE228">
+        <v>10.5</v>
+      </c>
+      <c r="BF228">
+        <v>1.13</v>
+      </c>
+      <c r="BG228">
+        <v>1.17</v>
+      </c>
+      <c r="BH228">
+        <v>4.35</v>
+      </c>
+      <c r="BI228">
+        <v>1.3</v>
+      </c>
+      <c r="BJ228">
+        <v>3.15</v>
+      </c>
+      <c r="BK228">
+        <v>1.5</v>
+      </c>
+      <c r="BL228">
+        <v>2.38</v>
+      </c>
+      <c r="BM228">
+        <v>1.91</v>
+      </c>
+      <c r="BN228">
+        <v>1.8</v>
+      </c>
+      <c r="BO228">
+        <v>2.2</v>
+      </c>
+      <c r="BP228">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7466285</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45731.70833333334</v>
+      </c>
+      <c r="F229">
+        <v>26</v>
+      </c>
+      <c r="G229" t="s">
+        <v>80</v>
+      </c>
+      <c r="H229" t="s">
+        <v>84</v>
+      </c>
+      <c r="I229">
+        <v>1</v>
+      </c>
+      <c r="J229">
+        <v>1</v>
+      </c>
+      <c r="K229">
+        <v>2</v>
+      </c>
+      <c r="L229">
+        <v>1</v>
+      </c>
+      <c r="M229">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>2</v>
+      </c>
+      <c r="O229" t="s">
+        <v>246</v>
+      </c>
+      <c r="P229" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q229">
+        <v>2.4</v>
+      </c>
+      <c r="R229">
+        <v>2.3</v>
+      </c>
+      <c r="S229">
+        <v>4.5</v>
+      </c>
+      <c r="T229">
+        <v>1.33</v>
+      </c>
+      <c r="U229">
+        <v>3.25</v>
+      </c>
+      <c r="V229">
+        <v>2.63</v>
+      </c>
+      <c r="W229">
+        <v>1.44</v>
+      </c>
+      <c r="X229">
+        <v>6.5</v>
+      </c>
+      <c r="Y229">
+        <v>1.11</v>
+      </c>
+      <c r="Z229">
+        <v>1.84</v>
+      </c>
+      <c r="AA229">
+        <v>3.59</v>
+      </c>
+      <c r="AB229">
+        <v>4.7</v>
+      </c>
+      <c r="AC229">
+        <v>1.05</v>
+      </c>
+      <c r="AD229">
+        <v>9.5</v>
+      </c>
+      <c r="AE229">
+        <v>1.25</v>
+      </c>
+      <c r="AF229">
+        <v>3.9</v>
+      </c>
+      <c r="AG229">
+        <v>1.81</v>
+      </c>
+      <c r="AH229">
+        <v>2.01</v>
+      </c>
+      <c r="AI229">
+        <v>1.7</v>
+      </c>
+      <c r="AJ229">
+        <v>2.05</v>
+      </c>
+      <c r="AK229">
+        <v>1.23</v>
+      </c>
+      <c r="AL229">
+        <v>1.27</v>
+      </c>
+      <c r="AM229">
+        <v>1.93</v>
+      </c>
+      <c r="AN229">
+        <v>1.92</v>
+      </c>
+      <c r="AO229">
+        <v>0.67</v>
+      </c>
+      <c r="AP229">
+        <v>1.85</v>
+      </c>
+      <c r="AQ229">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR229">
+        <v>1.69</v>
+      </c>
+      <c r="AS229">
+        <v>1.01</v>
+      </c>
+      <c r="AT229">
+        <v>2.7</v>
+      </c>
+      <c r="AU229">
+        <v>2</v>
+      </c>
+      <c r="AV229">
+        <v>2</v>
+      </c>
+      <c r="AW229">
+        <v>6</v>
+      </c>
+      <c r="AX229">
+        <v>2</v>
+      </c>
+      <c r="AY229">
+        <v>8</v>
+      </c>
+      <c r="AZ229">
+        <v>4</v>
+      </c>
+      <c r="BA229">
+        <v>10</v>
+      </c>
+      <c r="BB229">
+        <v>1</v>
+      </c>
+      <c r="BC229">
+        <v>11</v>
+      </c>
+      <c r="BD229">
+        <v>1.45</v>
+      </c>
+      <c r="BE229">
+        <v>6.75</v>
+      </c>
+      <c r="BF229">
+        <v>3.05</v>
+      </c>
+      <c r="BG229">
+        <v>1.2</v>
+      </c>
+      <c r="BH229">
+        <v>3.9</v>
+      </c>
+      <c r="BI229">
+        <v>1.38</v>
+      </c>
+      <c r="BJ229">
+        <v>2.7</v>
+      </c>
+      <c r="BK229">
+        <v>1.62</v>
+      </c>
+      <c r="BL229">
+        <v>2.12</v>
+      </c>
+      <c r="BM229">
+        <v>1.95</v>
+      </c>
+      <c r="BN229">
+        <v>1.77</v>
+      </c>
+      <c r="BO229">
+        <v>2.48</v>
+      </c>
+      <c r="BP229">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="351">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -757,6 +757,15 @@
     <t>['44']</t>
   </si>
   <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['41', '71']</t>
+  </si>
+  <si>
+    <t>['58', '85']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1012,9 +1021,6 @@
     <t>['31', '82']</t>
   </si>
   <si>
-    <t>['83']</t>
-  </si>
-  <si>
     <t>['68', '90+4']</t>
   </si>
   <si>
@@ -1055,6 +1061,12 @@
   </si>
   <si>
     <t>['4', '39', '53']</t>
+  </si>
+  <si>
+    <t>['10', '14', '23', '53', '62', '90']</t>
+  </si>
+  <si>
+    <t>['52', '83']</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1750,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ2">
         <v>0.62</v>
@@ -1959,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2084,7 +2096,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2371,7 +2383,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ5">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2496,7 +2508,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -3114,7 +3126,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3192,10 +3204,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ9">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3398,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ10">
         <v>0.54</v>
@@ -4016,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -4350,7 +4362,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4556,7 +4568,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4762,7 +4774,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4843,7 +4855,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5586,7 +5598,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5792,7 +5804,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6076,10 +6088,10 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ23">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR23">
         <v>1.65</v>
@@ -6285,7 +6297,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -6491,7 +6503,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ25">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR25">
         <v>1.08</v>
@@ -6694,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6822,7 +6834,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6903,7 +6915,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ27">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR27">
         <v>1.81</v>
@@ -7234,7 +7246,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7646,7 +7658,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8754,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ36">
         <v>0.6899999999999999</v>
@@ -8882,7 +8894,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -8960,10 +8972,10 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ37">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR37">
         <v>1.07</v>
@@ -9169,7 +9181,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ38">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>0.83</v>
@@ -9500,7 +9512,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -10196,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ43">
         <v>0.54</v>
@@ -10402,10 +10414,10 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ44">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.45</v>
@@ -10530,7 +10542,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10611,7 +10623,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ45">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -10736,7 +10748,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10817,7 +10829,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR46">
         <v>1.08</v>
@@ -10942,7 +10954,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11148,7 +11160,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11226,7 +11238,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ48">
         <v>2.23</v>
@@ -11354,7 +11366,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11560,7 +11572,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11766,7 +11778,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12178,7 +12190,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12590,7 +12602,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12796,7 +12808,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -12877,7 +12889,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ56">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR56">
         <v>1.55</v>
@@ -13083,7 +13095,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ57">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13492,7 +13504,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ59">
         <v>0.62</v>
@@ -13698,7 +13710,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ60">
         <v>1.17</v>
@@ -13826,7 +13838,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -14032,7 +14044,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14319,7 +14331,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR63">
         <v>1.02</v>
@@ -14856,7 +14868,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15062,7 +15074,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15140,7 +15152,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ67">
         <v>0.6899999999999999</v>
@@ -15680,7 +15692,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15758,7 +15770,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ70">
         <v>0.67</v>
@@ -15967,7 +15979,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ71">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR71">
         <v>1.43</v>
@@ -16092,7 +16104,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16298,7 +16310,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16916,7 +16928,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -16994,10 +17006,10 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ76">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR76">
         <v>1.77</v>
@@ -17203,7 +17215,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ77">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.05</v>
@@ -17406,7 +17418,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ78">
         <v>2.23</v>
@@ -17534,7 +17546,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17740,7 +17752,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18564,7 +18576,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18976,7 +18988,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19057,7 +19069,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ86">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19260,7 +19272,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ87">
         <v>0.6899999999999999</v>
@@ -19466,10 +19478,10 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR88">
         <v>2.16</v>
@@ -19594,7 +19606,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19800,7 +19812,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -20418,7 +20430,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20496,7 +20508,7 @@
         <v>3</v>
       </c>
       <c r="AP93">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ93">
         <v>1.92</v>
@@ -20624,7 +20636,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20705,7 +20717,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR94">
         <v>1.67</v>
@@ -21036,7 +21048,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21114,7 +21126,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ96">
         <v>0.6899999999999999</v>
@@ -21448,7 +21460,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22144,7 +22156,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22353,7 +22365,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ102">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>1.15</v>
@@ -22478,7 +22490,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22684,7 +22696,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22890,7 +22902,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22971,7 +22983,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ105">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR105">
         <v>1.24</v>
@@ -23096,7 +23108,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23174,7 +23186,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ106">
         <v>2.23</v>
@@ -23508,7 +23520,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23589,7 +23601,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR108">
         <v>1.94</v>
@@ -23792,7 +23804,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ109">
         <v>0.54</v>
@@ -24126,7 +24138,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24538,7 +24550,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24744,7 +24756,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24950,7 +24962,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25031,7 +25043,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ115">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR115">
         <v>1.6</v>
@@ -25156,7 +25168,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25440,7 +25452,7 @@
         <v>0.5</v>
       </c>
       <c r="AP117">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ117">
         <v>0.6899999999999999</v>
@@ -26058,10 +26070,10 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR120">
         <v>1.14</v>
@@ -26267,7 +26279,7 @@
         <v>2</v>
       </c>
       <c r="AQ121">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR121">
         <v>1.62</v>
@@ -26598,7 +26610,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26804,7 +26816,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26882,7 +26894,7 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ124">
         <v>1.17</v>
@@ -27216,7 +27228,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27422,7 +27434,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27500,7 +27512,7 @@
         <v>2.67</v>
       </c>
       <c r="AP127">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ127">
         <v>2.23</v>
@@ -27912,7 +27924,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ129">
         <v>1</v>
@@ -28040,7 +28052,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28246,7 +28258,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28327,7 +28339,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ131">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28452,7 +28464,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28533,7 +28545,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ132">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28736,7 +28748,7 @@
         <v>0.43</v>
       </c>
       <c r="AP133">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ133">
         <v>0.6899999999999999</v>
@@ -28864,7 +28876,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29276,7 +29288,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29563,7 +29575,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ137">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR137">
         <v>1.19</v>
@@ -29894,7 +29906,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30100,7 +30112,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30306,7 +30318,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30796,7 +30808,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ143">
         <v>0.67</v>
@@ -31002,7 +31014,7 @@
         <v>0.29</v>
       </c>
       <c r="AP144">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ144">
         <v>0.54</v>
@@ -31130,7 +31142,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31211,7 +31223,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ145">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -31336,7 +31348,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31620,7 +31632,7 @@
         <v>0.88</v>
       </c>
       <c r="AP147">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ147">
         <v>0.62</v>
@@ -32160,7 +32172,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32447,7 +32459,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ151">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR151">
         <v>2.48</v>
@@ -32572,7 +32584,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32653,7 +32665,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ152">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.54</v>
@@ -32984,7 +32996,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33474,7 +33486,7 @@
         <v>0.25</v>
       </c>
       <c r="AP156">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ156">
         <v>0.5</v>
@@ -33602,7 +33614,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33808,7 +33820,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33889,7 +33901,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ158">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR158">
         <v>2.37</v>
@@ -34014,7 +34026,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34092,10 +34104,10 @@
         <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ159">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR159">
         <v>1.99</v>
@@ -34298,7 +34310,7 @@
         <v>0.25</v>
       </c>
       <c r="AP160">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ160">
         <v>0.54</v>
@@ -34426,7 +34438,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34632,7 +34644,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34838,7 +34850,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35125,7 +35137,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ164">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR164">
         <v>1.55</v>
@@ -35250,7 +35262,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35331,7 +35343,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ165">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR165">
         <v>1.19</v>
@@ -35534,7 +35546,7 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ166">
         <v>0.67</v>
@@ -35662,7 +35674,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35868,7 +35880,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36074,7 +36086,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36280,7 +36292,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36361,7 +36373,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ170">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR170">
         <v>1.58</v>
@@ -36898,7 +36910,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37182,7 +37194,7 @@
         <v>0.6</v>
       </c>
       <c r="AP174">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ174">
         <v>0.54</v>
@@ -37310,7 +37322,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37597,7 +37609,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ176">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR176">
         <v>1.2</v>
@@ -37722,7 +37734,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37928,7 +37940,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38340,7 +38352,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38546,7 +38558,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38627,7 +38639,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ181">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR181">
         <v>1.53</v>
@@ -38752,7 +38764,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38958,7 +38970,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39242,10 +39254,10 @@
         <v>1.9</v>
       </c>
       <c r="AP184">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ184">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR184">
         <v>1.78</v>
@@ -39370,7 +39382,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39448,7 +39460,7 @@
         <v>1.3</v>
       </c>
       <c r="AP185">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ185">
         <v>1.23</v>
@@ -39782,7 +39794,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39863,7 +39875,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ187">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR187">
         <v>1.16</v>
@@ -39988,7 +40000,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40194,7 +40206,7 @@
         <v>171</v>
       </c>
       <c r="P189" t="s">
-        <v>332</v>
+        <v>247</v>
       </c>
       <c r="Q189">
         <v>1.44</v>
@@ -40275,7 +40287,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ189">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR189">
         <v>2.4</v>
@@ -40478,7 +40490,7 @@
         <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ190">
         <v>1</v>
@@ -41224,7 +41236,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41636,7 +41648,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41920,7 +41932,7 @@
         <v>1.09</v>
       </c>
       <c r="AP197">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ197">
         <v>1</v>
@@ -42048,7 +42060,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42335,7 +42347,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ199">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR199">
         <v>1.41</v>
@@ -42460,7 +42472,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42666,7 +42678,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43156,7 +43168,7 @@
         <v>0.55</v>
       </c>
       <c r="AP203">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ203">
         <v>0.5</v>
@@ -43362,7 +43374,7 @@
         <v>0.8</v>
       </c>
       <c r="AP204">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ204">
         <v>0.6899999999999999</v>
@@ -43774,7 +43786,7 @@
         <v>1.1</v>
       </c>
       <c r="AP206">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AQ206">
         <v>1.17</v>
@@ -43980,7 +43992,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44189,7 +44201,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ208">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR208">
         <v>1.81</v>
@@ -44314,7 +44326,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44395,7 +44407,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ209">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR209">
         <v>1.29</v>
@@ -44726,7 +44738,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44804,7 +44816,7 @@
         <v>2</v>
       </c>
       <c r="AP211">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ211">
         <v>1.92</v>
@@ -44932,7 +44944,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45010,7 +45022,7 @@
         <v>1.25</v>
       </c>
       <c r="AP212">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ212">
         <v>1.23</v>
@@ -45425,7 +45437,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ214">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR214">
         <v>1.72</v>
@@ -45550,7 +45562,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46043,7 +46055,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ217">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR217">
         <v>1.56</v>
@@ -46580,7 +46592,7 @@
         <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q220">
         <v>1.62</v>
@@ -46786,7 +46798,7 @@
         <v>242</v>
       </c>
       <c r="P221" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q221">
         <v>4.33</v>
@@ -46992,7 +47004,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q222">
         <v>5</v>
@@ -47198,7 +47210,7 @@
         <v>243</v>
       </c>
       <c r="P223" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q223">
         <v>2.75</v>
@@ -47482,7 +47494,7 @@
         <v>0.58</v>
       </c>
       <c r="AP224">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ224">
         <v>0.54</v>
@@ -48228,7 +48240,7 @@
         <v>91</v>
       </c>
       <c r="P228" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q228">
         <v>8</v>
@@ -48591,6 +48603,830 @@
       </c>
       <c r="BP229">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7466283</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45732.34375</v>
+      </c>
+      <c r="F230">
+        <v>26</v>
+      </c>
+      <c r="G230" t="s">
+        <v>77</v>
+      </c>
+      <c r="H230" t="s">
+        <v>86</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>1</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>1</v>
+      </c>
+      <c r="O230" t="s">
+        <v>247</v>
+      </c>
+      <c r="P230" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q230">
+        <v>2.2</v>
+      </c>
+      <c r="R230">
+        <v>2.3</v>
+      </c>
+      <c r="S230">
+        <v>5.5</v>
+      </c>
+      <c r="T230">
+        <v>1.36</v>
+      </c>
+      <c r="U230">
+        <v>3</v>
+      </c>
+      <c r="V230">
+        <v>2.75</v>
+      </c>
+      <c r="W230">
+        <v>1.4</v>
+      </c>
+      <c r="X230">
+        <v>7</v>
+      </c>
+      <c r="Y230">
+        <v>1.1</v>
+      </c>
+      <c r="Z230">
+        <v>1.62</v>
+      </c>
+      <c r="AA230">
+        <v>3.93</v>
+      </c>
+      <c r="AB230">
+        <v>6.2</v>
+      </c>
+      <c r="AC230">
+        <v>1.05</v>
+      </c>
+      <c r="AD230">
+        <v>9.5</v>
+      </c>
+      <c r="AE230">
+        <v>1.25</v>
+      </c>
+      <c r="AF230">
+        <v>3.75</v>
+      </c>
+      <c r="AG230">
+        <v>1.8</v>
+      </c>
+      <c r="AH230">
+        <v>1.9</v>
+      </c>
+      <c r="AI230">
+        <v>1.91</v>
+      </c>
+      <c r="AJ230">
+        <v>1.91</v>
+      </c>
+      <c r="AK230">
+        <v>1.16</v>
+      </c>
+      <c r="AL230">
+        <v>1.23</v>
+      </c>
+      <c r="AM230">
+        <v>2.25</v>
+      </c>
+      <c r="AN230">
+        <v>2.08</v>
+      </c>
+      <c r="AO230">
+        <v>1</v>
+      </c>
+      <c r="AP230">
+        <v>2.14</v>
+      </c>
+      <c r="AQ230">
+        <v>0.92</v>
+      </c>
+      <c r="AR230">
+        <v>1.64</v>
+      </c>
+      <c r="AS230">
+        <v>0.93</v>
+      </c>
+      <c r="AT230">
+        <v>2.57</v>
+      </c>
+      <c r="AU230">
+        <v>10</v>
+      </c>
+      <c r="AV230">
+        <v>4</v>
+      </c>
+      <c r="AW230">
+        <v>14</v>
+      </c>
+      <c r="AX230">
+        <v>2</v>
+      </c>
+      <c r="AY230">
+        <v>30</v>
+      </c>
+      <c r="AZ230">
+        <v>6</v>
+      </c>
+      <c r="BA230">
+        <v>11</v>
+      </c>
+      <c r="BB230">
+        <v>1</v>
+      </c>
+      <c r="BC230">
+        <v>12</v>
+      </c>
+      <c r="BD230">
+        <v>1.25</v>
+      </c>
+      <c r="BE230">
+        <v>8</v>
+      </c>
+      <c r="BF230">
+        <v>4.3</v>
+      </c>
+      <c r="BG230">
+        <v>1.19</v>
+      </c>
+      <c r="BH230">
+        <v>4</v>
+      </c>
+      <c r="BI230">
+        <v>1.34</v>
+      </c>
+      <c r="BJ230">
+        <v>2.9</v>
+      </c>
+      <c r="BK230">
+        <v>1.56</v>
+      </c>
+      <c r="BL230">
+        <v>2.23</v>
+      </c>
+      <c r="BM230">
+        <v>1.91</v>
+      </c>
+      <c r="BN230">
+        <v>1.8</v>
+      </c>
+      <c r="BO230">
+        <v>2.35</v>
+      </c>
+      <c r="BP230">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7466280</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45732.4375</v>
+      </c>
+      <c r="F231">
+        <v>26</v>
+      </c>
+      <c r="G231" t="s">
+        <v>70</v>
+      </c>
+      <c r="H231" t="s">
+        <v>79</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>1</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>1</v>
+      </c>
+      <c r="O231" t="s">
+        <v>100</v>
+      </c>
+      <c r="P231" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q231">
+        <v>2.6</v>
+      </c>
+      <c r="R231">
+        <v>2.1</v>
+      </c>
+      <c r="S231">
+        <v>4.5</v>
+      </c>
+      <c r="T231">
+        <v>1.44</v>
+      </c>
+      <c r="U231">
+        <v>2.63</v>
+      </c>
+      <c r="V231">
+        <v>3</v>
+      </c>
+      <c r="W231">
+        <v>1.36</v>
+      </c>
+      <c r="X231">
+        <v>9</v>
+      </c>
+      <c r="Y231">
+        <v>1.07</v>
+      </c>
+      <c r="Z231">
+        <v>2.1</v>
+      </c>
+      <c r="AA231">
+        <v>3.45</v>
+      </c>
+      <c r="AB231">
+        <v>3.75</v>
+      </c>
+      <c r="AC231">
+        <v>1.07</v>
+      </c>
+      <c r="AD231">
+        <v>8</v>
+      </c>
+      <c r="AE231">
+        <v>1.35</v>
+      </c>
+      <c r="AF231">
+        <v>3.1</v>
+      </c>
+      <c r="AG231">
+        <v>2.03</v>
+      </c>
+      <c r="AH231">
+        <v>1.79</v>
+      </c>
+      <c r="AI231">
+        <v>1.91</v>
+      </c>
+      <c r="AJ231">
+        <v>1.91</v>
+      </c>
+      <c r="AK231">
+        <v>1.24</v>
+      </c>
+      <c r="AL231">
+        <v>1.3</v>
+      </c>
+      <c r="AM231">
+        <v>1.83</v>
+      </c>
+      <c r="AN231">
+        <v>1.67</v>
+      </c>
+      <c r="AO231">
+        <v>1.08</v>
+      </c>
+      <c r="AP231">
+        <v>1.77</v>
+      </c>
+      <c r="AQ231">
+        <v>1</v>
+      </c>
+      <c r="AR231">
+        <v>1.41</v>
+      </c>
+      <c r="AS231">
+        <v>1.1</v>
+      </c>
+      <c r="AT231">
+        <v>2.51</v>
+      </c>
+      <c r="AU231">
+        <v>6</v>
+      </c>
+      <c r="AV231">
+        <v>2</v>
+      </c>
+      <c r="AW231">
+        <v>3</v>
+      </c>
+      <c r="AX231">
+        <v>3</v>
+      </c>
+      <c r="AY231">
+        <v>10</v>
+      </c>
+      <c r="AZ231">
+        <v>7</v>
+      </c>
+      <c r="BA231">
+        <v>9</v>
+      </c>
+      <c r="BB231">
+        <v>1</v>
+      </c>
+      <c r="BC231">
+        <v>10</v>
+      </c>
+      <c r="BD231">
+        <v>1.55</v>
+      </c>
+      <c r="BE231">
+        <v>6.5</v>
+      </c>
+      <c r="BF231">
+        <v>2.75</v>
+      </c>
+      <c r="BG231">
+        <v>1.3</v>
+      </c>
+      <c r="BH231">
+        <v>3.15</v>
+      </c>
+      <c r="BI231">
+        <v>1.52</v>
+      </c>
+      <c r="BJ231">
+        <v>2.32</v>
+      </c>
+      <c r="BK231">
+        <v>1.77</v>
+      </c>
+      <c r="BL231">
+        <v>1.95</v>
+      </c>
+      <c r="BM231">
+        <v>2.33</v>
+      </c>
+      <c r="BN231">
+        <v>1.52</v>
+      </c>
+      <c r="BO231">
+        <v>3.05</v>
+      </c>
+      <c r="BP231">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7466281</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45732.4375</v>
+      </c>
+      <c r="F232">
+        <v>26</v>
+      </c>
+      <c r="G232" t="s">
+        <v>81</v>
+      </c>
+      <c r="H232" t="s">
+        <v>71</v>
+      </c>
+      <c r="I232">
+        <v>1</v>
+      </c>
+      <c r="J232">
+        <v>3</v>
+      </c>
+      <c r="K232">
+        <v>4</v>
+      </c>
+      <c r="L232">
+        <v>2</v>
+      </c>
+      <c r="M232">
+        <v>6</v>
+      </c>
+      <c r="N232">
+        <v>8</v>
+      </c>
+      <c r="O232" t="s">
+        <v>248</v>
+      </c>
+      <c r="P232" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q232">
+        <v>2.88</v>
+      </c>
+      <c r="R232">
+        <v>2.2</v>
+      </c>
+      <c r="S232">
+        <v>3.5</v>
+      </c>
+      <c r="T232">
+        <v>1.36</v>
+      </c>
+      <c r="U232">
+        <v>3</v>
+      </c>
+      <c r="V232">
+        <v>2.63</v>
+      </c>
+      <c r="W232">
+        <v>1.44</v>
+      </c>
+      <c r="X232">
+        <v>7</v>
+      </c>
+      <c r="Y232">
+        <v>1.1</v>
+      </c>
+      <c r="Z232">
+        <v>2.41</v>
+      </c>
+      <c r="AA232">
+        <v>3.6</v>
+      </c>
+      <c r="AB232">
+        <v>2.92</v>
+      </c>
+      <c r="AC232">
+        <v>1.05</v>
+      </c>
+      <c r="AD232">
+        <v>9.5</v>
+      </c>
+      <c r="AE232">
+        <v>1.25</v>
+      </c>
+      <c r="AF232">
+        <v>3.8</v>
+      </c>
+      <c r="AG232">
+        <v>1.82</v>
+      </c>
+      <c r="AH232">
+        <v>2</v>
+      </c>
+      <c r="AI232">
+        <v>1.67</v>
+      </c>
+      <c r="AJ232">
+        <v>2.1</v>
+      </c>
+      <c r="AK232">
+        <v>1.38</v>
+      </c>
+      <c r="AL232">
+        <v>1.28</v>
+      </c>
+      <c r="AM232">
+        <v>1.61</v>
+      </c>
+      <c r="AN232">
+        <v>2.5</v>
+      </c>
+      <c r="AO232">
+        <v>1.67</v>
+      </c>
+      <c r="AP232">
+        <v>2.31</v>
+      </c>
+      <c r="AQ232">
+        <v>1.77</v>
+      </c>
+      <c r="AR232">
+        <v>2</v>
+      </c>
+      <c r="AS232">
+        <v>1.97</v>
+      </c>
+      <c r="AT232">
+        <v>3.97</v>
+      </c>
+      <c r="AU232">
+        <v>3</v>
+      </c>
+      <c r="AV232">
+        <v>7</v>
+      </c>
+      <c r="AW232">
+        <v>3</v>
+      </c>
+      <c r="AX232">
+        <v>3</v>
+      </c>
+      <c r="AY232">
+        <v>7</v>
+      </c>
+      <c r="AZ232">
+        <v>10</v>
+      </c>
+      <c r="BA232">
+        <v>2</v>
+      </c>
+      <c r="BB232">
+        <v>5</v>
+      </c>
+      <c r="BC232">
+        <v>7</v>
+      </c>
+      <c r="BD232">
+        <v>1.94</v>
+      </c>
+      <c r="BE232">
+        <v>6.25</v>
+      </c>
+      <c r="BF232">
+        <v>2.07</v>
+      </c>
+      <c r="BG232">
+        <v>1.29</v>
+      </c>
+      <c r="BH232">
+        <v>3.15</v>
+      </c>
+      <c r="BI232">
+        <v>1.52</v>
+      </c>
+      <c r="BJ232">
+        <v>2.33</v>
+      </c>
+      <c r="BK232">
+        <v>1.84</v>
+      </c>
+      <c r="BL232">
+        <v>1.84</v>
+      </c>
+      <c r="BM232">
+        <v>2.33</v>
+      </c>
+      <c r="BN232">
+        <v>1.52</v>
+      </c>
+      <c r="BO232">
+        <v>2.95</v>
+      </c>
+      <c r="BP232">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7466278</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45732.53125</v>
+      </c>
+      <c r="F233">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>78</v>
+      </c>
+      <c r="H233" t="s">
+        <v>82</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>2</v>
+      </c>
+      <c r="M233">
+        <v>2</v>
+      </c>
+      <c r="N233">
+        <v>4</v>
+      </c>
+      <c r="O233" t="s">
+        <v>249</v>
+      </c>
+      <c r="P233" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q233">
+        <v>2.5</v>
+      </c>
+      <c r="R233">
+        <v>2.2</v>
+      </c>
+      <c r="S233">
+        <v>4.5</v>
+      </c>
+      <c r="T233">
+        <v>1.4</v>
+      </c>
+      <c r="U233">
+        <v>2.75</v>
+      </c>
+      <c r="V233">
+        <v>2.75</v>
+      </c>
+      <c r="W233">
+        <v>1.4</v>
+      </c>
+      <c r="X233">
+        <v>8</v>
+      </c>
+      <c r="Y233">
+        <v>1.08</v>
+      </c>
+      <c r="Z233">
+        <v>1.8</v>
+      </c>
+      <c r="AA233">
+        <v>3.9</v>
+      </c>
+      <c r="AB233">
+        <v>4.5</v>
+      </c>
+      <c r="AC233">
+        <v>1.05</v>
+      </c>
+      <c r="AD233">
+        <v>9.5</v>
+      </c>
+      <c r="AE233">
+        <v>1.28</v>
+      </c>
+      <c r="AF233">
+        <v>3.6</v>
+      </c>
+      <c r="AG233">
+        <v>1.89</v>
+      </c>
+      <c r="AH233">
+        <v>1.92</v>
+      </c>
+      <c r="AI233">
+        <v>1.8</v>
+      </c>
+      <c r="AJ233">
+        <v>1.95</v>
+      </c>
+      <c r="AK233">
+        <v>1.23</v>
+      </c>
+      <c r="AL233">
+        <v>1.27</v>
+      </c>
+      <c r="AM233">
+        <v>1.93</v>
+      </c>
+      <c r="AN233">
+        <v>2.83</v>
+      </c>
+      <c r="AO233">
+        <v>1.75</v>
+      </c>
+      <c r="AP233">
+        <v>2.69</v>
+      </c>
+      <c r="AQ233">
+        <v>1.69</v>
+      </c>
+      <c r="AR233">
+        <v>1.84</v>
+      </c>
+      <c r="AS233">
+        <v>1.47</v>
+      </c>
+      <c r="AT233">
+        <v>3.31</v>
+      </c>
+      <c r="AU233">
+        <v>6</v>
+      </c>
+      <c r="AV233">
+        <v>3</v>
+      </c>
+      <c r="AW233">
+        <v>7</v>
+      </c>
+      <c r="AX233">
+        <v>4</v>
+      </c>
+      <c r="AY233">
+        <v>16</v>
+      </c>
+      <c r="AZ233">
+        <v>7</v>
+      </c>
+      <c r="BA233">
+        <v>3</v>
+      </c>
+      <c r="BB233">
+        <v>3</v>
+      </c>
+      <c r="BC233">
+        <v>6</v>
+      </c>
+      <c r="BD233">
+        <v>1.48</v>
+      </c>
+      <c r="BE233">
+        <v>6.75</v>
+      </c>
+      <c r="BF233">
+        <v>2.95</v>
+      </c>
+      <c r="BG233">
+        <v>1.4</v>
+      </c>
+      <c r="BH233">
+        <v>2.7</v>
+      </c>
+      <c r="BI233">
+        <v>1.73</v>
+      </c>
+      <c r="BJ233">
+        <v>1.95</v>
+      </c>
+      <c r="BK233">
+        <v>2.07</v>
+      </c>
+      <c r="BL233">
+        <v>1.66</v>
+      </c>
+      <c r="BM233">
+        <v>2.65</v>
+      </c>
+      <c r="BN233">
+        <v>1.41</v>
+      </c>
+      <c r="BO233">
+        <v>3.45</v>
+      </c>
+      <c r="BP233">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="360">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -766,6 +766,21 @@
     <t>['58', '85']</t>
   </si>
   <si>
+    <t>['90+8']</t>
+  </si>
+  <si>
+    <t>['74', '83']</t>
+  </si>
+  <si>
+    <t>['10', '63', '71']</t>
+  </si>
+  <si>
+    <t>['22', '58']</t>
+  </si>
+  <si>
+    <t>['9', '76']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1067,6 +1082,18 @@
   </si>
   <si>
     <t>['52', '83']</t>
+  </si>
+  <si>
+    <t>['12', '49']</t>
+  </si>
+  <si>
+    <t>['4', '45+3', '63']</t>
+  </si>
+  <si>
+    <t>['4', '32', '46']</t>
+  </si>
+  <si>
+    <t>['35', '67']</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2096,7 +2123,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2174,10 +2201,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2383,7 +2410,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ5">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2508,7 +2535,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2586,10 +2613,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2998,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ8">
         <v>0.6899999999999999</v>
@@ -3126,7 +3153,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3413,7 +3440,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ10">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3616,10 +3643,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ11">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4031,7 +4058,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4362,7 +4389,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4443,7 +4470,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4568,7 +4595,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4646,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ16">
         <v>1.92</v>
@@ -4774,7 +4801,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4852,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ17">
         <v>1.77</v>
@@ -5058,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ18">
         <v>1.17</v>
@@ -5264,10 +5291,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ19">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5470,7 +5497,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ20">
         <v>0.6899999999999999</v>
@@ -5598,7 +5625,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5804,7 +5831,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5882,7 +5909,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ22">
         <v>2.23</v>
@@ -6091,7 +6118,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ23">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR23">
         <v>1.65</v>
@@ -6294,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ24">
         <v>0.92</v>
@@ -6709,7 +6736,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ26">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6834,7 +6861,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6915,7 +6942,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ27">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR27">
         <v>1.81</v>
@@ -7121,7 +7148,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ28">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR28">
         <v>0.73</v>
@@ -7246,7 +7273,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7324,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7658,7 +7685,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7736,10 +7763,10 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR31">
         <v>0.77</v>
@@ -7942,10 +7969,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ32">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR32">
         <v>1.07</v>
@@ -8148,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ33">
         <v>0.6899999999999999</v>
@@ -8354,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ34">
         <v>1.17</v>
@@ -8560,7 +8587,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8894,7 +8921,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9178,7 +9205,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9387,7 +9414,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ39">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR39">
         <v>1.82</v>
@@ -9512,7 +9539,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9796,10 +9823,10 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ41">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -10002,10 +10029,10 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ42">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR42">
         <v>1.23</v>
@@ -10211,7 +10238,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ43">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR43">
         <v>2.19</v>
@@ -10542,7 +10569,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10620,10 +10647,10 @@
         <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ45">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -10748,7 +10775,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10826,7 +10853,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ46">
         <v>0.92</v>
@@ -10954,7 +10981,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11035,7 +11062,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR47">
         <v>1.15</v>
@@ -11160,7 +11187,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11241,7 +11268,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ48">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR48">
         <v>1.91</v>
@@ -11366,7 +11393,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11444,7 +11471,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ49">
         <v>0.6899999999999999</v>
@@ -11572,7 +11599,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11653,7 +11680,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ50">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -11778,7 +11805,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11859,7 +11886,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ51">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR51">
         <v>0.82</v>
@@ -12190,7 +12217,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12268,7 +12295,7 @@
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ53">
         <v>1.92</v>
@@ -12474,10 +12501,10 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ54">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR54">
         <v>1.37</v>
@@ -12602,7 +12629,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12680,7 +12707,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ55">
         <v>1.92</v>
@@ -12808,7 +12835,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -12886,7 +12913,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ56">
         <v>1.77</v>
@@ -13298,10 +13325,10 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ58">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR58">
         <v>1.08</v>
@@ -13838,7 +13865,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13919,7 +13946,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ61">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR61">
         <v>1.5</v>
@@ -14044,7 +14071,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14534,7 +14561,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14740,10 +14767,10 @@
         <v>2.33</v>
       </c>
       <c r="AP65">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR65">
         <v>2.79</v>
@@ -14868,7 +14895,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14946,10 +14973,10 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ66">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR66">
         <v>1.08</v>
@@ -15074,7 +15101,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15361,7 +15388,7 @@
         <v>2</v>
       </c>
       <c r="AQ68">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR68">
         <v>2.17</v>
@@ -15692,7 +15719,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15773,7 +15800,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ70">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR70">
         <v>2.32</v>
@@ -15976,10 +16003,10 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ71">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR71">
         <v>1.43</v>
@@ -16104,7 +16131,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16185,7 +16212,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ72">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -16310,7 +16337,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16594,10 +16621,10 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ74">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR74">
         <v>1.44</v>
@@ -16803,7 +16830,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ75">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR75">
         <v>1.24</v>
@@ -16928,7 +16955,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17212,7 +17239,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17546,7 +17573,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17624,10 +17651,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ79">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR79">
         <v>1.54</v>
@@ -17752,7 +17779,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17830,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ80">
         <v>0.62</v>
@@ -18242,10 +18269,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ82">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR82">
         <v>1.34</v>
@@ -18448,7 +18475,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ83">
         <v>0.6899999999999999</v>
@@ -18576,7 +18603,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18654,10 +18681,10 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ84">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR84">
         <v>1.12</v>
@@ -18863,7 +18890,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR85">
         <v>1.93</v>
@@ -18988,7 +19015,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19066,7 +19093,7 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ86">
         <v>1.77</v>
@@ -19606,7 +19633,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19812,7 +19839,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19893,7 +19920,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR90">
         <v>1.77</v>
@@ -20096,10 +20123,10 @@
         <v>1.4</v>
       </c>
       <c r="AP91">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ91">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR91">
         <v>1.05</v>
@@ -20302,7 +20329,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ92">
         <v>0.62</v>
@@ -20430,7 +20457,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20636,7 +20663,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20717,7 +20744,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR94">
         <v>1.67</v>
@@ -20920,10 +20947,10 @@
         <v>0</v>
       </c>
       <c r="AP95">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ95">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR95">
         <v>1.29</v>
@@ -21048,7 +21075,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21332,10 +21359,10 @@
         <v>0.8</v>
       </c>
       <c r="AP97">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ97">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR97">
         <v>1.38</v>
@@ -21460,7 +21487,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21747,7 +21774,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ99">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21950,7 +21977,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ100">
         <v>0.6899999999999999</v>
@@ -22159,7 +22186,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR101">
         <v>1.12</v>
@@ -22362,7 +22389,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22490,7 +22517,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22568,7 +22595,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ103">
         <v>1.92</v>
@@ -22696,7 +22723,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22902,7 +22929,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23108,7 +23135,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23189,7 +23216,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ106">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR106">
         <v>2.03</v>
@@ -23520,7 +23547,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23807,7 +23834,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ109">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -24013,7 +24040,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR110">
         <v>1.62</v>
@@ -24138,7 +24165,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24216,10 +24243,10 @@
         <v>0</v>
       </c>
       <c r="AP111">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ111">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR111">
         <v>1.37</v>
@@ -24422,10 +24449,10 @@
         <v>0.67</v>
       </c>
       <c r="AP112">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ112">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR112">
         <v>2.46</v>
@@ -24550,7 +24577,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24628,10 +24655,10 @@
         <v>1.67</v>
       </c>
       <c r="AP113">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ113">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR113">
         <v>1.21</v>
@@ -24756,7 +24783,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24834,7 +24861,7 @@
         <v>2.6</v>
       </c>
       <c r="AP114">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ114">
         <v>2.23</v>
@@ -24962,7 +24989,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25043,7 +25070,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ115">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR115">
         <v>1.6</v>
@@ -25168,7 +25195,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25246,7 +25273,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ116">
         <v>0.62</v>
@@ -25661,7 +25688,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ118">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR118">
         <v>1.65</v>
@@ -25864,10 +25891,10 @@
         <v>0.33</v>
       </c>
       <c r="AP119">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ119">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR119">
         <v>1.34</v>
@@ -26482,10 +26509,10 @@
         <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR122">
         <v>1.18</v>
@@ -26610,7 +26637,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26688,7 +26715,7 @@
         <v>2.57</v>
       </c>
       <c r="AP123">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ123">
         <v>1.92</v>
@@ -26816,7 +26843,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27228,7 +27255,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27306,10 +27333,10 @@
         <v>1.83</v>
       </c>
       <c r="AP126">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ126">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR126">
         <v>1.45</v>
@@ -27434,7 +27461,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27718,10 +27745,10 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ128">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR128">
         <v>2.46</v>
@@ -28052,7 +28079,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28258,7 +28285,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28464,7 +28491,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28542,7 +28569,7 @@
         <v>0.86</v>
       </c>
       <c r="AP132">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -28876,7 +28903,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28954,10 +28981,10 @@
         <v>0</v>
       </c>
       <c r="AP134">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ134">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR134">
         <v>1.12</v>
@@ -29163,7 +29190,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ135">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR135">
         <v>1.92</v>
@@ -29288,7 +29315,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29572,7 +29599,7 @@
         <v>1.14</v>
       </c>
       <c r="AP137">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ137">
         <v>0.92</v>
@@ -29906,7 +29933,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29984,10 +30011,10 @@
         <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ139">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR139">
         <v>1.21</v>
@@ -30112,7 +30139,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30318,7 +30345,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30396,7 +30423,7 @@
         <v>1</v>
       </c>
       <c r="AP141">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ141">
         <v>1.17</v>
@@ -30602,10 +30629,10 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ142">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR142">
         <v>1.53</v>
@@ -30811,7 +30838,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ143">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR143">
         <v>2.08</v>
@@ -31017,7 +31044,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ144">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR144">
         <v>1.74</v>
@@ -31142,7 +31169,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31220,10 +31247,10 @@
         <v>1.86</v>
       </c>
       <c r="AP145">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ145">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -31348,7 +31375,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31841,7 +31868,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ148">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR148">
         <v>1.21</v>
@@ -32047,7 +32074,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ149">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR149">
         <v>1.83</v>
@@ -32172,7 +32199,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32253,7 +32280,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ150">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR150">
         <v>1.58</v>
@@ -32456,7 +32483,7 @@
         <v>2.25</v>
       </c>
       <c r="AP151">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ151">
         <v>1.77</v>
@@ -32584,7 +32611,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32662,7 +32689,7 @@
         <v>0.88</v>
       </c>
       <c r="AP152">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -32868,7 +32895,7 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -32996,7 +33023,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33074,7 +33101,7 @@
         <v>1</v>
       </c>
       <c r="AP154">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ154">
         <v>1.17</v>
@@ -33280,10 +33307,10 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR155">
         <v>1.47</v>
@@ -33489,7 +33516,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ156">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR156">
         <v>1.73</v>
@@ -33614,7 +33641,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33692,7 +33719,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ157">
         <v>1</v>
@@ -33820,7 +33847,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33898,10 +33925,10 @@
         <v>2</v>
       </c>
       <c r="AP158">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ158">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR158">
         <v>2.37</v>
@@ -34026,7 +34053,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34313,7 +34340,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ160">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR160">
         <v>1.27</v>
@@ -34438,7 +34465,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34644,7 +34671,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34722,10 +34749,10 @@
         <v>0.33</v>
       </c>
       <c r="AP162">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ162">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR162">
         <v>1.26</v>
@@ -34850,7 +34877,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -34928,7 +34955,7 @@
         <v>2.33</v>
       </c>
       <c r="AP163">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ163">
         <v>1.92</v>
@@ -35134,10 +35161,10 @@
         <v>1.89</v>
       </c>
       <c r="AP164">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ164">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR164">
         <v>1.55</v>
@@ -35262,7 +35289,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35340,7 +35367,7 @@
         <v>2</v>
       </c>
       <c r="AP165">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ165">
         <v>1.77</v>
@@ -35549,7 +35576,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ166">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR166">
         <v>1.78</v>
@@ -35674,7 +35701,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35752,10 +35779,10 @@
         <v>1.44</v>
       </c>
       <c r="AP167">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ167">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR167">
         <v>1.33</v>
@@ -35880,7 +35907,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36086,7 +36113,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36167,7 +36194,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ169">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR169">
         <v>1.56</v>
@@ -36292,7 +36319,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36370,7 +36397,7 @@
         <v>1.11</v>
       </c>
       <c r="AP170">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36579,7 +36606,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ171">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR171">
         <v>1.53</v>
@@ -36782,7 +36809,7 @@
         <v>2.56</v>
       </c>
       <c r="AP172">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ172">
         <v>2.23</v>
@@ -36910,7 +36937,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -36988,7 +37015,7 @@
         <v>0.78</v>
       </c>
       <c r="AP173">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ173">
         <v>0.62</v>
@@ -37197,7 +37224,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ174">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR174">
         <v>1.36</v>
@@ -37322,7 +37349,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37400,7 +37427,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP175">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ175">
         <v>0.6899999999999999</v>
@@ -37734,7 +37761,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37815,7 +37842,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ177">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR177">
         <v>1.77</v>
@@ -37940,7 +37967,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38018,10 +38045,10 @@
         <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ178">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR178">
         <v>1.43</v>
@@ -38224,7 +38251,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ179">
         <v>0.6899999999999999</v>
@@ -38352,7 +38379,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38430,7 +38457,7 @@
         <v>2.4</v>
       </c>
       <c r="AP180">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ180">
         <v>2.23</v>
@@ -38558,7 +38585,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38764,7 +38791,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38842,7 +38869,7 @@
         <v>2.1</v>
       </c>
       <c r="AP182">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ182">
         <v>1.92</v>
@@ -38970,7 +38997,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39051,7 +39078,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ183">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR183">
         <v>1.31</v>
@@ -39382,7 +39409,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39463,7 +39490,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ185">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR185">
         <v>1.74</v>
@@ -39669,7 +39696,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ186">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR186">
         <v>1.58</v>
@@ -39794,7 +39821,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39872,10 +39899,10 @@
         <v>1.8</v>
       </c>
       <c r="AP187">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ187">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR187">
         <v>1.16</v>
@@ -40000,7 +40027,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40078,7 +40105,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ188">
         <v>1.17</v>
@@ -40284,7 +40311,7 @@
         <v>1.1</v>
       </c>
       <c r="AP189">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ189">
         <v>0.92</v>
@@ -40699,7 +40726,7 @@
         <v>2</v>
       </c>
       <c r="AQ191">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR191">
         <v>1.85</v>
@@ -40902,10 +40929,10 @@
         <v>0.33</v>
       </c>
       <c r="AP192">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ192">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR192">
         <v>1.52</v>
@@ -41236,7 +41263,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41314,10 +41341,10 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ194">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR194">
         <v>1.36</v>
@@ -41648,7 +41675,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41729,7 +41756,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ196">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR196">
         <v>1.64</v>
@@ -41935,7 +41962,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ197">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR197">
         <v>1.68</v>
@@ -42060,7 +42087,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42138,7 +42165,7 @@
         <v>2.27</v>
       </c>
       <c r="AP198">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ198">
         <v>2.23</v>
@@ -42344,7 +42371,7 @@
         <v>1.73</v>
       </c>
       <c r="AP199">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ199">
         <v>1.77</v>
@@ -42472,7 +42499,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42550,10 +42577,10 @@
         <v>0.45</v>
       </c>
       <c r="AP200">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ200">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR200">
         <v>1.12</v>
@@ -42678,7 +42705,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42756,10 +42783,10 @@
         <v>0.6</v>
       </c>
       <c r="AP201">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ201">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR201">
         <v>1.59</v>
@@ -42962,10 +42989,10 @@
         <v>0.55</v>
       </c>
       <c r="AP202">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ202">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR202">
         <v>1.27</v>
@@ -43171,7 +43198,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ203">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR203">
         <v>2.08</v>
@@ -43583,7 +43610,7 @@
         <v>2</v>
       </c>
       <c r="AQ205">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR205">
         <v>1.87</v>
@@ -44326,7 +44353,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44610,7 +44637,7 @@
         <v>0.64</v>
       </c>
       <c r="AP210">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ210">
         <v>0.62</v>
@@ -44738,7 +44765,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44944,7 +44971,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45025,7 +45052,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ212">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR212">
         <v>1.44</v>
@@ -45437,7 +45464,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ214">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR214">
         <v>1.72</v>
@@ -45562,7 +45589,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45640,7 +45667,7 @@
         <v>0.73</v>
       </c>
       <c r="AP215">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ215">
         <v>0.6899999999999999</v>
@@ -45849,7 +45876,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ216">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR216">
         <v>1.35</v>
@@ -46258,10 +46285,10 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ218">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR218">
         <v>1.39</v>
@@ -46464,7 +46491,7 @@
         <v>0.73</v>
       </c>
       <c r="AP219">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ219">
         <v>0.6899999999999999</v>
@@ -46592,7 +46619,7 @@
         <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q220">
         <v>1.62</v>
@@ -46670,10 +46697,10 @@
         <v>0.58</v>
       </c>
       <c r="AP220">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AQ220">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR220">
         <v>2.5</v>
@@ -46798,7 +46825,7 @@
         <v>242</v>
       </c>
       <c r="P221" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q221">
         <v>4.33</v>
@@ -46876,7 +46903,7 @@
         <v>2.17</v>
       </c>
       <c r="AP221">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ221">
         <v>2.23</v>
@@ -47004,7 +47031,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Q222">
         <v>5</v>
@@ -47082,10 +47109,10 @@
         <v>2.17</v>
       </c>
       <c r="AP222">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ222">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR222">
         <v>1.26</v>
@@ -47210,7 +47237,7 @@
         <v>243</v>
       </c>
       <c r="P223" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="Q223">
         <v>2.75</v>
@@ -47288,7 +47315,7 @@
         <v>1</v>
       </c>
       <c r="AP223">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ223">
         <v>1.17</v>
@@ -47497,7 +47524,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ224">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR224">
         <v>2.02</v>
@@ -47906,7 +47933,7 @@
         <v>0.83</v>
       </c>
       <c r="AP226">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ226">
         <v>1</v>
@@ -48240,7 +48267,7 @@
         <v>91</v>
       </c>
       <c r="P228" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Q228">
         <v>8</v>
@@ -49064,7 +49091,7 @@
         <v>248</v>
       </c>
       <c r="P232" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49270,7 +49297,7 @@
         <v>249</v>
       </c>
       <c r="P233" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Q233">
         <v>2.5</v>
@@ -49351,7 +49378,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ233">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR233">
         <v>1.84</v>
@@ -49427,6 +49454,1654 @@
       </c>
       <c r="BP233">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7466292</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45745.52083333334</v>
+      </c>
+      <c r="F234">
+        <v>27</v>
+      </c>
+      <c r="G234" t="s">
+        <v>87</v>
+      </c>
+      <c r="H234" t="s">
+        <v>70</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>1</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>2</v>
+      </c>
+      <c r="O234" t="s">
+        <v>250</v>
+      </c>
+      <c r="P234" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q234">
+        <v>3.2</v>
+      </c>
+      <c r="R234">
+        <v>2.05</v>
+      </c>
+      <c r="S234">
+        <v>3.6</v>
+      </c>
+      <c r="T234">
+        <v>1.44</v>
+      </c>
+      <c r="U234">
+        <v>2.63</v>
+      </c>
+      <c r="V234">
+        <v>3.25</v>
+      </c>
+      <c r="W234">
+        <v>1.33</v>
+      </c>
+      <c r="X234">
+        <v>10</v>
+      </c>
+      <c r="Y234">
+        <v>1.06</v>
+      </c>
+      <c r="Z234">
+        <v>2.47</v>
+      </c>
+      <c r="AA234">
+        <v>3.23</v>
+      </c>
+      <c r="AB234">
+        <v>3.12</v>
+      </c>
+      <c r="AC234">
+        <v>0</v>
+      </c>
+      <c r="AD234">
+        <v>0</v>
+      </c>
+      <c r="AE234">
+        <v>2.25</v>
+      </c>
+      <c r="AF234">
+        <v>1.68</v>
+      </c>
+      <c r="AG234">
+        <v>1.91</v>
+      </c>
+      <c r="AH234">
+        <v>1.8</v>
+      </c>
+      <c r="AI234">
+        <v>1.91</v>
+      </c>
+      <c r="AJ234">
+        <v>1.91</v>
+      </c>
+      <c r="AK234">
+        <v>0</v>
+      </c>
+      <c r="AL234">
+        <v>0</v>
+      </c>
+      <c r="AM234">
+        <v>0</v>
+      </c>
+      <c r="AN234">
+        <v>1.62</v>
+      </c>
+      <c r="AO234">
+        <v>0.67</v>
+      </c>
+      <c r="AP234">
+        <v>1.57</v>
+      </c>
+      <c r="AQ234">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR234">
+        <v>1.42</v>
+      </c>
+      <c r="AS234">
+        <v>1.16</v>
+      </c>
+      <c r="AT234">
+        <v>2.58</v>
+      </c>
+      <c r="AU234">
+        <v>5</v>
+      </c>
+      <c r="AV234">
+        <v>6</v>
+      </c>
+      <c r="AW234">
+        <v>9</v>
+      </c>
+      <c r="AX234">
+        <v>1</v>
+      </c>
+      <c r="AY234">
+        <v>18</v>
+      </c>
+      <c r="AZ234">
+        <v>9</v>
+      </c>
+      <c r="BA234">
+        <v>3</v>
+      </c>
+      <c r="BB234">
+        <v>2</v>
+      </c>
+      <c r="BC234">
+        <v>5</v>
+      </c>
+      <c r="BD234">
+        <v>0</v>
+      </c>
+      <c r="BE234">
+        <v>0</v>
+      </c>
+      <c r="BF234">
+        <v>0</v>
+      </c>
+      <c r="BG234">
+        <v>0</v>
+      </c>
+      <c r="BH234">
+        <v>0</v>
+      </c>
+      <c r="BI234">
+        <v>0</v>
+      </c>
+      <c r="BJ234">
+        <v>0</v>
+      </c>
+      <c r="BK234">
+        <v>0</v>
+      </c>
+      <c r="BL234">
+        <v>0</v>
+      </c>
+      <c r="BM234">
+        <v>0</v>
+      </c>
+      <c r="BN234">
+        <v>0</v>
+      </c>
+      <c r="BO234">
+        <v>0</v>
+      </c>
+      <c r="BP234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7466295</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45745.61458333334</v>
+      </c>
+      <c r="F235">
+        <v>27</v>
+      </c>
+      <c r="G235" t="s">
+        <v>86</v>
+      </c>
+      <c r="H235" t="s">
+        <v>73</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>1</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>2</v>
+      </c>
+      <c r="N235">
+        <v>2</v>
+      </c>
+      <c r="O235" t="s">
+        <v>91</v>
+      </c>
+      <c r="P235" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q235">
+        <v>2.88</v>
+      </c>
+      <c r="R235">
+        <v>2.05</v>
+      </c>
+      <c r="S235">
+        <v>4</v>
+      </c>
+      <c r="T235">
+        <v>1.5</v>
+      </c>
+      <c r="U235">
+        <v>2.5</v>
+      </c>
+      <c r="V235">
+        <v>3.4</v>
+      </c>
+      <c r="W235">
+        <v>1.3</v>
+      </c>
+      <c r="X235">
+        <v>10</v>
+      </c>
+      <c r="Y235">
+        <v>1.06</v>
+      </c>
+      <c r="Z235">
+        <v>2.19</v>
+      </c>
+      <c r="AA235">
+        <v>3.45</v>
+      </c>
+      <c r="AB235">
+        <v>3.45</v>
+      </c>
+      <c r="AC235">
+        <v>0</v>
+      </c>
+      <c r="AD235">
+        <v>0</v>
+      </c>
+      <c r="AE235">
+        <v>0</v>
+      </c>
+      <c r="AF235">
+        <v>0</v>
+      </c>
+      <c r="AG235">
+        <v>1.75</v>
+      </c>
+      <c r="AH235">
+        <v>2</v>
+      </c>
+      <c r="AI235">
+        <v>1.95</v>
+      </c>
+      <c r="AJ235">
+        <v>1.8</v>
+      </c>
+      <c r="AK235">
+        <v>0</v>
+      </c>
+      <c r="AL235">
+        <v>0</v>
+      </c>
+      <c r="AM235">
+        <v>0</v>
+      </c>
+      <c r="AN235">
+        <v>0.92</v>
+      </c>
+      <c r="AO235">
+        <v>0.54</v>
+      </c>
+      <c r="AP235">
+        <v>0.86</v>
+      </c>
+      <c r="AQ235">
+        <v>0.71</v>
+      </c>
+      <c r="AR235">
+        <v>1.23</v>
+      </c>
+      <c r="AS235">
+        <v>1.19</v>
+      </c>
+      <c r="AT235">
+        <v>2.42</v>
+      </c>
+      <c r="AU235">
+        <v>7</v>
+      </c>
+      <c r="AV235">
+        <v>5</v>
+      </c>
+      <c r="AW235">
+        <v>8</v>
+      </c>
+      <c r="AX235">
+        <v>15</v>
+      </c>
+      <c r="AY235">
+        <v>16</v>
+      </c>
+      <c r="AZ235">
+        <v>23</v>
+      </c>
+      <c r="BA235">
+        <v>8</v>
+      </c>
+      <c r="BB235">
+        <v>5</v>
+      </c>
+      <c r="BC235">
+        <v>13</v>
+      </c>
+      <c r="BD235">
+        <v>0</v>
+      </c>
+      <c r="BE235">
+        <v>0</v>
+      </c>
+      <c r="BF235">
+        <v>0</v>
+      </c>
+      <c r="BG235">
+        <v>0</v>
+      </c>
+      <c r="BH235">
+        <v>0</v>
+      </c>
+      <c r="BI235">
+        <v>0</v>
+      </c>
+      <c r="BJ235">
+        <v>0</v>
+      </c>
+      <c r="BK235">
+        <v>0</v>
+      </c>
+      <c r="BL235">
+        <v>0</v>
+      </c>
+      <c r="BM235">
+        <v>0</v>
+      </c>
+      <c r="BN235">
+        <v>0</v>
+      </c>
+      <c r="BO235">
+        <v>0</v>
+      </c>
+      <c r="BP235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7466289</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45745.61458333334</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>79</v>
+      </c>
+      <c r="H236" t="s">
+        <v>75</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>2</v>
+      </c>
+      <c r="K236">
+        <v>2</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+      <c r="M236">
+        <v>3</v>
+      </c>
+      <c r="N236">
+        <v>3</v>
+      </c>
+      <c r="O236" t="s">
+        <v>91</v>
+      </c>
+      <c r="P236" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q236">
+        <v>3.75</v>
+      </c>
+      <c r="R236">
+        <v>2.1</v>
+      </c>
+      <c r="S236">
+        <v>2.88</v>
+      </c>
+      <c r="T236">
+        <v>1.4</v>
+      </c>
+      <c r="U236">
+        <v>2.75</v>
+      </c>
+      <c r="V236">
+        <v>3</v>
+      </c>
+      <c r="W236">
+        <v>1.36</v>
+      </c>
+      <c r="X236">
+        <v>8</v>
+      </c>
+      <c r="Y236">
+        <v>1.08</v>
+      </c>
+      <c r="Z236">
+        <v>3.25</v>
+      </c>
+      <c r="AA236">
+        <v>3.63</v>
+      </c>
+      <c r="AB236">
+        <v>2.22</v>
+      </c>
+      <c r="AC236">
+        <v>0</v>
+      </c>
+      <c r="AD236">
+        <v>0</v>
+      </c>
+      <c r="AE236">
+        <v>0</v>
+      </c>
+      <c r="AF236">
+        <v>0</v>
+      </c>
+      <c r="AG236">
+        <v>1.97</v>
+      </c>
+      <c r="AH236">
+        <v>1.84</v>
+      </c>
+      <c r="AI236">
+        <v>1.75</v>
+      </c>
+      <c r="AJ236">
+        <v>2</v>
+      </c>
+      <c r="AK236">
+        <v>0</v>
+      </c>
+      <c r="AL236">
+        <v>0</v>
+      </c>
+      <c r="AM236">
+        <v>0</v>
+      </c>
+      <c r="AN236">
+        <v>1.5</v>
+      </c>
+      <c r="AO236">
+        <v>1</v>
+      </c>
+      <c r="AP236">
+        <v>1.38</v>
+      </c>
+      <c r="AQ236">
+        <v>1.14</v>
+      </c>
+      <c r="AR236">
+        <v>1.35</v>
+      </c>
+      <c r="AS236">
+        <v>1.46</v>
+      </c>
+      <c r="AT236">
+        <v>2.81</v>
+      </c>
+      <c r="AU236">
+        <v>5</v>
+      </c>
+      <c r="AV236">
+        <v>8</v>
+      </c>
+      <c r="AW236">
+        <v>13</v>
+      </c>
+      <c r="AX236">
+        <v>8</v>
+      </c>
+      <c r="AY236">
+        <v>22</v>
+      </c>
+      <c r="AZ236">
+        <v>20</v>
+      </c>
+      <c r="BA236">
+        <v>1</v>
+      </c>
+      <c r="BB236">
+        <v>4</v>
+      </c>
+      <c r="BC236">
+        <v>5</v>
+      </c>
+      <c r="BD236">
+        <v>0</v>
+      </c>
+      <c r="BE236">
+        <v>0</v>
+      </c>
+      <c r="BF236">
+        <v>0</v>
+      </c>
+      <c r="BG236">
+        <v>0</v>
+      </c>
+      <c r="BH236">
+        <v>0</v>
+      </c>
+      <c r="BI236">
+        <v>0</v>
+      </c>
+      <c r="BJ236">
+        <v>0</v>
+      </c>
+      <c r="BK236">
+        <v>0</v>
+      </c>
+      <c r="BL236">
+        <v>0</v>
+      </c>
+      <c r="BM236">
+        <v>0</v>
+      </c>
+      <c r="BN236">
+        <v>0</v>
+      </c>
+      <c r="BO236">
+        <v>0</v>
+      </c>
+      <c r="BP236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7466293</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45745.70833333334</v>
+      </c>
+      <c r="F237">
+        <v>27</v>
+      </c>
+      <c r="G237" t="s">
+        <v>85</v>
+      </c>
+      <c r="H237" t="s">
+        <v>83</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>2</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>2</v>
+      </c>
+      <c r="O237" t="s">
+        <v>251</v>
+      </c>
+      <c r="P237" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q237">
+        <v>2.5</v>
+      </c>
+      <c r="R237">
+        <v>2.3</v>
+      </c>
+      <c r="S237">
+        <v>4</v>
+      </c>
+      <c r="T237">
+        <v>1.33</v>
+      </c>
+      <c r="U237">
+        <v>3.25</v>
+      </c>
+      <c r="V237">
+        <v>2.5</v>
+      </c>
+      <c r="W237">
+        <v>1.5</v>
+      </c>
+      <c r="X237">
+        <v>6.5</v>
+      </c>
+      <c r="Y237">
+        <v>1.11</v>
+      </c>
+      <c r="Z237">
+        <v>2.04</v>
+      </c>
+      <c r="AA237">
+        <v>3.95</v>
+      </c>
+      <c r="AB237">
+        <v>3.45</v>
+      </c>
+      <c r="AC237">
+        <v>0</v>
+      </c>
+      <c r="AD237">
+        <v>0</v>
+      </c>
+      <c r="AE237">
+        <v>0</v>
+      </c>
+      <c r="AF237">
+        <v>0</v>
+      </c>
+      <c r="AG237">
+        <v>1.6</v>
+      </c>
+      <c r="AH237">
+        <v>2.25</v>
+      </c>
+      <c r="AI237">
+        <v>1.62</v>
+      </c>
+      <c r="AJ237">
+        <v>2.2</v>
+      </c>
+      <c r="AK237">
+        <v>0</v>
+      </c>
+      <c r="AL237">
+        <v>0</v>
+      </c>
+      <c r="AM237">
+        <v>0</v>
+      </c>
+      <c r="AN237">
+        <v>1.31</v>
+      </c>
+      <c r="AO237">
+        <v>0.5</v>
+      </c>
+      <c r="AP237">
+        <v>1.43</v>
+      </c>
+      <c r="AQ237">
+        <v>0.46</v>
+      </c>
+      <c r="AR237">
+        <v>1.26</v>
+      </c>
+      <c r="AS237">
+        <v>1.31</v>
+      </c>
+      <c r="AT237">
+        <v>2.57</v>
+      </c>
+      <c r="AU237">
+        <v>12</v>
+      </c>
+      <c r="AV237">
+        <v>3</v>
+      </c>
+      <c r="AW237">
+        <v>14</v>
+      </c>
+      <c r="AX237">
+        <v>8</v>
+      </c>
+      <c r="AY237">
+        <v>30</v>
+      </c>
+      <c r="AZ237">
+        <v>13</v>
+      </c>
+      <c r="BA237">
+        <v>11</v>
+      </c>
+      <c r="BB237">
+        <v>3</v>
+      </c>
+      <c r="BC237">
+        <v>14</v>
+      </c>
+      <c r="BD237">
+        <v>0</v>
+      </c>
+      <c r="BE237">
+        <v>0</v>
+      </c>
+      <c r="BF237">
+        <v>0</v>
+      </c>
+      <c r="BG237">
+        <v>0</v>
+      </c>
+      <c r="BH237">
+        <v>0</v>
+      </c>
+      <c r="BI237">
+        <v>0</v>
+      </c>
+      <c r="BJ237">
+        <v>0</v>
+      </c>
+      <c r="BK237">
+        <v>0</v>
+      </c>
+      <c r="BL237">
+        <v>0</v>
+      </c>
+      <c r="BM237">
+        <v>0</v>
+      </c>
+      <c r="BN237">
+        <v>0</v>
+      </c>
+      <c r="BO237">
+        <v>0</v>
+      </c>
+      <c r="BP237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7466291</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45745.70833333334</v>
+      </c>
+      <c r="F238">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>72</v>
+      </c>
+      <c r="H238" t="s">
+        <v>82</v>
+      </c>
+      <c r="I238">
+        <v>1</v>
+      </c>
+      <c r="J238">
+        <v>2</v>
+      </c>
+      <c r="K238">
+        <v>3</v>
+      </c>
+      <c r="L238">
+        <v>3</v>
+      </c>
+      <c r="M238">
+        <v>3</v>
+      </c>
+      <c r="N238">
+        <v>6</v>
+      </c>
+      <c r="O238" t="s">
+        <v>252</v>
+      </c>
+      <c r="P238" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q238">
+        <v>3.75</v>
+      </c>
+      <c r="R238">
+        <v>2.2</v>
+      </c>
+      <c r="S238">
+        <v>2.88</v>
+      </c>
+      <c r="T238">
+        <v>1.4</v>
+      </c>
+      <c r="U238">
+        <v>2.75</v>
+      </c>
+      <c r="V238">
+        <v>2.75</v>
+      </c>
+      <c r="W238">
+        <v>1.4</v>
+      </c>
+      <c r="X238">
+        <v>8</v>
+      </c>
+      <c r="Y238">
+        <v>1.08</v>
+      </c>
+      <c r="Z238">
+        <v>3.35</v>
+      </c>
+      <c r="AA238">
+        <v>3.45</v>
+      </c>
+      <c r="AB238">
+        <v>2.24</v>
+      </c>
+      <c r="AC238">
+        <v>0</v>
+      </c>
+      <c r="AD238">
+        <v>0</v>
+      </c>
+      <c r="AE238">
+        <v>0</v>
+      </c>
+      <c r="AF238">
+        <v>0</v>
+      </c>
+      <c r="AG238">
+        <v>1.92</v>
+      </c>
+      <c r="AH238">
+        <v>1.89</v>
+      </c>
+      <c r="AI238">
+        <v>1.75</v>
+      </c>
+      <c r="AJ238">
+        <v>2</v>
+      </c>
+      <c r="AK238">
+        <v>0</v>
+      </c>
+      <c r="AL238">
+        <v>0</v>
+      </c>
+      <c r="AM238">
+        <v>0</v>
+      </c>
+      <c r="AN238">
+        <v>1.23</v>
+      </c>
+      <c r="AO238">
+        <v>1.69</v>
+      </c>
+      <c r="AP238">
+        <v>1.21</v>
+      </c>
+      <c r="AQ238">
+        <v>1.64</v>
+      </c>
+      <c r="AR238">
+        <v>1.54</v>
+      </c>
+      <c r="AS238">
+        <v>1.44</v>
+      </c>
+      <c r="AT238">
+        <v>2.98</v>
+      </c>
+      <c r="AU238">
+        <v>5</v>
+      </c>
+      <c r="AV238">
+        <v>5</v>
+      </c>
+      <c r="AW238">
+        <v>10</v>
+      </c>
+      <c r="AX238">
+        <v>4</v>
+      </c>
+      <c r="AY238">
+        <v>16</v>
+      </c>
+      <c r="AZ238">
+        <v>10</v>
+      </c>
+      <c r="BA238">
+        <v>5</v>
+      </c>
+      <c r="BB238">
+        <v>7</v>
+      </c>
+      <c r="BC238">
+        <v>12</v>
+      </c>
+      <c r="BD238">
+        <v>0</v>
+      </c>
+      <c r="BE238">
+        <v>0</v>
+      </c>
+      <c r="BF238">
+        <v>0</v>
+      </c>
+      <c r="BG238">
+        <v>0</v>
+      </c>
+      <c r="BH238">
+        <v>0</v>
+      </c>
+      <c r="BI238">
+        <v>0</v>
+      </c>
+      <c r="BJ238">
+        <v>0</v>
+      </c>
+      <c r="BK238">
+        <v>0</v>
+      </c>
+      <c r="BL238">
+        <v>0</v>
+      </c>
+      <c r="BM238">
+        <v>0</v>
+      </c>
+      <c r="BN238">
+        <v>0</v>
+      </c>
+      <c r="BO238">
+        <v>0</v>
+      </c>
+      <c r="BP238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7466287</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45746.30208333334</v>
+      </c>
+      <c r="F239">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>76</v>
+      </c>
+      <c r="H239" t="s">
+        <v>80</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>2</v>
+      </c>
+      <c r="M239">
+        <v>0</v>
+      </c>
+      <c r="N239">
+        <v>2</v>
+      </c>
+      <c r="O239" t="s">
+        <v>253</v>
+      </c>
+      <c r="P239" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q239">
+        <v>2.38</v>
+      </c>
+      <c r="R239">
+        <v>2.3</v>
+      </c>
+      <c r="S239">
+        <v>4.5</v>
+      </c>
+      <c r="T239">
+        <v>1.33</v>
+      </c>
+      <c r="U239">
+        <v>3.25</v>
+      </c>
+      <c r="V239">
+        <v>2.63</v>
+      </c>
+      <c r="W239">
+        <v>1.44</v>
+      </c>
+      <c r="X239">
+        <v>6.5</v>
+      </c>
+      <c r="Y239">
+        <v>1.11</v>
+      </c>
+      <c r="Z239">
+        <v>1.77</v>
+      </c>
+      <c r="AA239">
+        <v>3.97</v>
+      </c>
+      <c r="AB239">
+        <v>4.6</v>
+      </c>
+      <c r="AC239">
+        <v>0</v>
+      </c>
+      <c r="AD239">
+        <v>0</v>
+      </c>
+      <c r="AE239">
+        <v>0</v>
+      </c>
+      <c r="AF239">
+        <v>0</v>
+      </c>
+      <c r="AG239">
+        <v>1.55</v>
+      </c>
+      <c r="AH239">
+        <v>2.3</v>
+      </c>
+      <c r="AI239">
+        <v>1.7</v>
+      </c>
+      <c r="AJ239">
+        <v>2.05</v>
+      </c>
+      <c r="AK239">
+        <v>0</v>
+      </c>
+      <c r="AL239">
+        <v>0</v>
+      </c>
+      <c r="AM239">
+        <v>0</v>
+      </c>
+      <c r="AN239">
+        <v>1.54</v>
+      </c>
+      <c r="AO239">
+        <v>0.54</v>
+      </c>
+      <c r="AP239">
+        <v>1.64</v>
+      </c>
+      <c r="AQ239">
+        <v>0.5</v>
+      </c>
+      <c r="AR239">
+        <v>1.62</v>
+      </c>
+      <c r="AS239">
+        <v>1.3</v>
+      </c>
+      <c r="AT239">
+        <v>2.92</v>
+      </c>
+      <c r="AU239">
+        <v>5</v>
+      </c>
+      <c r="AV239">
+        <v>0</v>
+      </c>
+      <c r="AW239">
+        <v>8</v>
+      </c>
+      <c r="AX239">
+        <v>12</v>
+      </c>
+      <c r="AY239">
+        <v>13</v>
+      </c>
+      <c r="AZ239">
+        <v>13</v>
+      </c>
+      <c r="BA239">
+        <v>4</v>
+      </c>
+      <c r="BB239">
+        <v>5</v>
+      </c>
+      <c r="BC239">
+        <v>9</v>
+      </c>
+      <c r="BD239">
+        <v>0</v>
+      </c>
+      <c r="BE239">
+        <v>0</v>
+      </c>
+      <c r="BF239">
+        <v>0</v>
+      </c>
+      <c r="BG239">
+        <v>0</v>
+      </c>
+      <c r="BH239">
+        <v>0</v>
+      </c>
+      <c r="BI239">
+        <v>0</v>
+      </c>
+      <c r="BJ239">
+        <v>0</v>
+      </c>
+      <c r="BK239">
+        <v>0</v>
+      </c>
+      <c r="BL239">
+        <v>0</v>
+      </c>
+      <c r="BM239">
+        <v>0</v>
+      </c>
+      <c r="BN239">
+        <v>0</v>
+      </c>
+      <c r="BO239">
+        <v>0</v>
+      </c>
+      <c r="BP239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7466294</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45746.39583333334</v>
+      </c>
+      <c r="F240">
+        <v>27</v>
+      </c>
+      <c r="G240" t="s">
+        <v>74</v>
+      </c>
+      <c r="H240" t="s">
+        <v>78</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>1</v>
+      </c>
+      <c r="K240">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+      <c r="M240">
+        <v>2</v>
+      </c>
+      <c r="N240">
+        <v>2</v>
+      </c>
+      <c r="O240" t="s">
+        <v>91</v>
+      </c>
+      <c r="P240" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q240">
+        <v>2.2</v>
+      </c>
+      <c r="R240">
+        <v>2.5</v>
+      </c>
+      <c r="S240">
+        <v>4.5</v>
+      </c>
+      <c r="T240">
+        <v>1.25</v>
+      </c>
+      <c r="U240">
+        <v>3.75</v>
+      </c>
+      <c r="V240">
+        <v>2.2</v>
+      </c>
+      <c r="W240">
+        <v>1.62</v>
+      </c>
+      <c r="X240">
+        <v>5</v>
+      </c>
+      <c r="Y240">
+        <v>1.17</v>
+      </c>
+      <c r="Z240">
+        <v>1.69</v>
+      </c>
+      <c r="AA240">
+        <v>4.4</v>
+      </c>
+      <c r="AB240">
+        <v>4.6</v>
+      </c>
+      <c r="AC240">
+        <v>0</v>
+      </c>
+      <c r="AD240">
+        <v>0</v>
+      </c>
+      <c r="AE240">
+        <v>0</v>
+      </c>
+      <c r="AF240">
+        <v>0</v>
+      </c>
+      <c r="AG240">
+        <v>1.46</v>
+      </c>
+      <c r="AH240">
+        <v>2.6</v>
+      </c>
+      <c r="AI240">
+        <v>1.53</v>
+      </c>
+      <c r="AJ240">
+        <v>2.38</v>
+      </c>
+      <c r="AK240">
+        <v>0</v>
+      </c>
+      <c r="AL240">
+        <v>0</v>
+      </c>
+      <c r="AM240">
+        <v>0</v>
+      </c>
+      <c r="AN240">
+        <v>2.54</v>
+      </c>
+      <c r="AO240">
+        <v>2.23</v>
+      </c>
+      <c r="AP240">
+        <v>2.36</v>
+      </c>
+      <c r="AQ240">
+        <v>2.29</v>
+      </c>
+      <c r="AR240">
+        <v>2.54</v>
+      </c>
+      <c r="AS240">
+        <v>1.36</v>
+      </c>
+      <c r="AT240">
+        <v>3.9</v>
+      </c>
+      <c r="AU240">
+        <v>5</v>
+      </c>
+      <c r="AV240">
+        <v>3</v>
+      </c>
+      <c r="AW240">
+        <v>12</v>
+      </c>
+      <c r="AX240">
+        <v>7</v>
+      </c>
+      <c r="AY240">
+        <v>20</v>
+      </c>
+      <c r="AZ240">
+        <v>10</v>
+      </c>
+      <c r="BA240">
+        <v>5</v>
+      </c>
+      <c r="BB240">
+        <v>2</v>
+      </c>
+      <c r="BC240">
+        <v>7</v>
+      </c>
+      <c r="BD240">
+        <v>0</v>
+      </c>
+      <c r="BE240">
+        <v>0</v>
+      </c>
+      <c r="BF240">
+        <v>0</v>
+      </c>
+      <c r="BG240">
+        <v>0</v>
+      </c>
+      <c r="BH240">
+        <v>0</v>
+      </c>
+      <c r="BI240">
+        <v>0</v>
+      </c>
+      <c r="BJ240">
+        <v>0</v>
+      </c>
+      <c r="BK240">
+        <v>0</v>
+      </c>
+      <c r="BL240">
+        <v>0</v>
+      </c>
+      <c r="BM240">
+        <v>0</v>
+      </c>
+      <c r="BN240">
+        <v>0</v>
+      </c>
+      <c r="BO240">
+        <v>0</v>
+      </c>
+      <c r="BP240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7466290</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45746.39583333334</v>
+      </c>
+      <c r="F241">
+        <v>27</v>
+      </c>
+      <c r="G241" t="s">
+        <v>84</v>
+      </c>
+      <c r="H241" t="s">
+        <v>81</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>2</v>
+      </c>
+      <c r="M241">
+        <v>1</v>
+      </c>
+      <c r="N241">
+        <v>3</v>
+      </c>
+      <c r="O241" t="s">
+        <v>254</v>
+      </c>
+      <c r="P241" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q241">
+        <v>4.33</v>
+      </c>
+      <c r="R241">
+        <v>2.25</v>
+      </c>
+      <c r="S241">
+        <v>2.4</v>
+      </c>
+      <c r="T241">
+        <v>1.36</v>
+      </c>
+      <c r="U241">
+        <v>3</v>
+      </c>
+      <c r="V241">
+        <v>2.63</v>
+      </c>
+      <c r="W241">
+        <v>1.44</v>
+      </c>
+      <c r="X241">
+        <v>7</v>
+      </c>
+      <c r="Y241">
+        <v>1.1</v>
+      </c>
+      <c r="Z241">
+        <v>4.1</v>
+      </c>
+      <c r="AA241">
+        <v>3.93</v>
+      </c>
+      <c r="AB241">
+        <v>1.86</v>
+      </c>
+      <c r="AC241">
+        <v>0</v>
+      </c>
+      <c r="AD241">
+        <v>0</v>
+      </c>
+      <c r="AE241">
+        <v>1.83</v>
+      </c>
+      <c r="AF241">
+        <v>2.05</v>
+      </c>
+      <c r="AG241">
+        <v>1.81</v>
+      </c>
+      <c r="AH241">
+        <v>2.01</v>
+      </c>
+      <c r="AI241">
+        <v>1.75</v>
+      </c>
+      <c r="AJ241">
+        <v>2</v>
+      </c>
+      <c r="AK241">
+        <v>0</v>
+      </c>
+      <c r="AL241">
+        <v>0</v>
+      </c>
+      <c r="AM241">
+        <v>0</v>
+      </c>
+      <c r="AN241">
+        <v>1.46</v>
+      </c>
+      <c r="AO241">
+        <v>1.23</v>
+      </c>
+      <c r="AP241">
+        <v>1.57</v>
+      </c>
+      <c r="AQ241">
+        <v>1.14</v>
+      </c>
+      <c r="AR241">
+        <v>1.45</v>
+      </c>
+      <c r="AS241">
+        <v>1.61</v>
+      </c>
+      <c r="AT241">
+        <v>3.06</v>
+      </c>
+      <c r="AU241">
+        <v>3</v>
+      </c>
+      <c r="AV241">
+        <v>7</v>
+      </c>
+      <c r="AW241">
+        <v>3</v>
+      </c>
+      <c r="AX241">
+        <v>6</v>
+      </c>
+      <c r="AY241">
+        <v>7</v>
+      </c>
+      <c r="AZ241">
+        <v>15</v>
+      </c>
+      <c r="BA241">
+        <v>1</v>
+      </c>
+      <c r="BB241">
+        <v>6</v>
+      </c>
+      <c r="BC241">
+        <v>7</v>
+      </c>
+      <c r="BD241">
+        <v>0</v>
+      </c>
+      <c r="BE241">
+        <v>0</v>
+      </c>
+      <c r="BF241">
+        <v>0</v>
+      </c>
+      <c r="BG241">
+        <v>0</v>
+      </c>
+      <c r="BH241">
+        <v>0</v>
+      </c>
+      <c r="BI241">
+        <v>0</v>
+      </c>
+      <c r="BJ241">
+        <v>0</v>
+      </c>
+      <c r="BK241">
+        <v>0</v>
+      </c>
+      <c r="BL241">
+        <v>0</v>
+      </c>
+      <c r="BM241">
+        <v>0</v>
+      </c>
+      <c r="BN241">
+        <v>0</v>
+      </c>
+      <c r="BO241">
+        <v>0</v>
+      </c>
+      <c r="BP241">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="362">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -781,6 +781,9 @@
     <t>['9', '76']</t>
   </si>
   <si>
+    <t>['33', '57', '74']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1094,6 +1097,9 @@
   </si>
   <si>
     <t>['35', '67']</t>
+  </si>
+  <si>
+    <t>['45+2', '61']</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1995,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ3">
         <v>0.92</v>
@@ -2123,7 +2129,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2535,7 +2541,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -3153,7 +3159,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -4389,7 +4395,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4595,7 +4601,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4801,7 +4807,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5088,7 +5094,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ18">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5625,7 +5631,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5831,7 +5837,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6861,7 +6867,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7273,7 +7279,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7685,7 +7691,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8384,7 +8390,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ34">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR34">
         <v>2.85</v>
@@ -8921,7 +8927,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9539,7 +9545,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9620,7 +9626,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ40">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR40">
         <v>1.21</v>
@@ -10569,7 +10575,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10775,7 +10781,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10981,7 +10987,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11187,7 +11193,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11393,7 +11399,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11599,7 +11605,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11805,7 +11811,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12089,7 +12095,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ52">
         <v>0.62</v>
@@ -12217,7 +12223,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12629,7 +12635,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12835,7 +12841,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13740,7 +13746,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ60">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR60">
         <v>1.17</v>
@@ -13865,7 +13871,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -14071,7 +14077,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14895,7 +14901,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15101,7 +15107,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15385,7 +15391,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ68">
         <v>1.14</v>
@@ -15719,7 +15725,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -16131,7 +16137,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16337,7 +16343,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16955,7 +16961,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17573,7 +17579,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17779,7 +17785,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18603,7 +18609,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -19015,7 +19021,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19633,7 +19639,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19714,7 +19720,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ89">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR89">
         <v>2.01</v>
@@ -19839,7 +19845,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19917,7 +19923,7 @@
         <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ90">
         <v>2.29</v>
@@ -20457,7 +20463,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20663,7 +20669,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20741,7 +20747,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ94">
         <v>1.64</v>
@@ -21075,7 +21081,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21487,7 +21493,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22517,7 +22523,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22723,7 +22729,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22929,7 +22935,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23135,7 +23141,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23422,7 +23428,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ107">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR107">
         <v>1.85</v>
@@ -23547,7 +23553,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -24037,7 +24043,7 @@
         <v>0</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ110">
         <v>0.5</v>
@@ -24165,7 +24171,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24577,7 +24583,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24783,7 +24789,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24989,7 +24995,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25195,7 +25201,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -26303,7 +26309,7 @@
         <v>0.83</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26637,7 +26643,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26843,7 +26849,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26924,7 +26930,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ124">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR124">
         <v>1.98</v>
@@ -27255,7 +27261,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27461,7 +27467,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -28079,7 +28085,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28285,7 +28291,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28491,7 +28497,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28903,7 +28909,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29315,7 +29321,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29933,7 +29939,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30139,7 +30145,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30217,7 +30223,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ140">
         <v>0.6899999999999999</v>
@@ -30345,7 +30351,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30426,7 +30432,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ141">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -31169,7 +31175,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31375,7 +31381,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -32199,7 +32205,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32611,7 +32617,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -33023,7 +33029,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33104,7 +33110,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ154">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR154">
         <v>1.32</v>
@@ -33641,7 +33647,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33847,7 +33853,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -34053,7 +34059,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34465,7 +34471,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34543,7 +34549,7 @@
         <v>2.5</v>
       </c>
       <c r="AP161">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ161">
         <v>2.23</v>
@@ -34671,7 +34677,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34877,7 +34883,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35289,7 +35295,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35701,7 +35707,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35907,7 +35913,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36113,7 +36119,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36319,7 +36325,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36937,7 +36943,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37349,7 +37355,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37761,7 +37767,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37967,7 +37973,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38379,7 +38385,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38585,7 +38591,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38791,7 +38797,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38997,7 +39003,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39409,7 +39415,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39821,7 +39827,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -40027,7 +40033,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40108,7 +40114,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ188">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR188">
         <v>1.33</v>
@@ -40723,7 +40729,7 @@
         <v>1.2</v>
       </c>
       <c r="AP191">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ191">
         <v>1.14</v>
@@ -41263,7 +41269,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41675,7 +41681,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -42087,7 +42093,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42499,7 +42505,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42705,7 +42711,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43607,7 +43613,7 @@
         <v>0.64</v>
       </c>
       <c r="AP205">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ205">
         <v>0.71</v>
@@ -43816,7 +43822,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ206">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR206">
         <v>1.8</v>
@@ -44353,7 +44359,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44765,7 +44771,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44971,7 +44977,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45255,7 +45261,7 @@
         <v>0.82</v>
       </c>
       <c r="AP213">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ213">
         <v>1</v>
@@ -45589,7 +45595,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46619,7 +46625,7 @@
         <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q220">
         <v>1.62</v>
@@ -46825,7 +46831,7 @@
         <v>242</v>
       </c>
       <c r="P221" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q221">
         <v>4.33</v>
@@ -47031,7 +47037,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q222">
         <v>5</v>
@@ -47237,7 +47243,7 @@
         <v>243</v>
       </c>
       <c r="P223" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q223">
         <v>2.75</v>
@@ -47318,7 +47324,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ223">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR223">
         <v>1.55</v>
@@ -48267,7 +48273,7 @@
         <v>91</v>
       </c>
       <c r="P228" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q228">
         <v>8</v>
@@ -49091,7 +49097,7 @@
         <v>248</v>
       </c>
       <c r="P232" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49297,7 +49303,7 @@
         <v>249</v>
       </c>
       <c r="P233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q233">
         <v>2.5</v>
@@ -49709,7 +49715,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q235">
         <v>2.88</v>
@@ -49915,7 +49921,7 @@
         <v>91</v>
       </c>
       <c r="P236" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q236">
         <v>3.75</v>
@@ -50026,13 +50032,13 @@
         <v>20</v>
       </c>
       <c r="BA236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB236">
         <v>4</v>
       </c>
       <c r="BC236">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD236">
         <v>0</v>
@@ -50327,7 +50333,7 @@
         <v>252</v>
       </c>
       <c r="P238" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q238">
         <v>3.75</v>
@@ -50739,7 +50745,7 @@
         <v>91</v>
       </c>
       <c r="P240" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51101,6 +51107,212 @@
         <v>0</v>
       </c>
       <c r="BP241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7466288</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45746.48958333334</v>
+      </c>
+      <c r="F242">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>71</v>
+      </c>
+      <c r="H242" t="s">
+        <v>77</v>
+      </c>
+      <c r="I242">
+        <v>1</v>
+      </c>
+      <c r="J242">
+        <v>1</v>
+      </c>
+      <c r="K242">
+        <v>2</v>
+      </c>
+      <c r="L242">
+        <v>3</v>
+      </c>
+      <c r="M242">
+        <v>2</v>
+      </c>
+      <c r="N242">
+        <v>5</v>
+      </c>
+      <c r="O242" t="s">
+        <v>255</v>
+      </c>
+      <c r="P242" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q242">
+        <v>1.91</v>
+      </c>
+      <c r="R242">
+        <v>2.6</v>
+      </c>
+      <c r="S242">
+        <v>6</v>
+      </c>
+      <c r="T242">
+        <v>1.25</v>
+      </c>
+      <c r="U242">
+        <v>3.75</v>
+      </c>
+      <c r="V242">
+        <v>2.2</v>
+      </c>
+      <c r="W242">
+        <v>1.62</v>
+      </c>
+      <c r="X242">
+        <v>5</v>
+      </c>
+      <c r="Y242">
+        <v>1.17</v>
+      </c>
+      <c r="Z242">
+        <v>1.44</v>
+      </c>
+      <c r="AA242">
+        <v>5.2</v>
+      </c>
+      <c r="AB242">
+        <v>6.8</v>
+      </c>
+      <c r="AC242">
+        <v>0</v>
+      </c>
+      <c r="AD242">
+        <v>0</v>
+      </c>
+      <c r="AE242">
+        <v>0</v>
+      </c>
+      <c r="AF242">
+        <v>0</v>
+      </c>
+      <c r="AG242">
+        <v>1.55</v>
+      </c>
+      <c r="AH242">
+        <v>2.3</v>
+      </c>
+      <c r="AI242">
+        <v>1.67</v>
+      </c>
+      <c r="AJ242">
+        <v>2.1</v>
+      </c>
+      <c r="AK242">
+        <v>0</v>
+      </c>
+      <c r="AL242">
+        <v>0</v>
+      </c>
+      <c r="AM242">
+        <v>0</v>
+      </c>
+      <c r="AN242">
+        <v>2</v>
+      </c>
+      <c r="AO242">
+        <v>1.17</v>
+      </c>
+      <c r="AP242">
+        <v>2.08</v>
+      </c>
+      <c r="AQ242">
+        <v>1.08</v>
+      </c>
+      <c r="AR242">
+        <v>1.95</v>
+      </c>
+      <c r="AS242">
+        <v>1.34</v>
+      </c>
+      <c r="AT242">
+        <v>3.29</v>
+      </c>
+      <c r="AU242">
+        <v>10</v>
+      </c>
+      <c r="AV242">
+        <v>5</v>
+      </c>
+      <c r="AW242">
+        <v>9</v>
+      </c>
+      <c r="AX242">
+        <v>10</v>
+      </c>
+      <c r="AY242">
+        <v>24</v>
+      </c>
+      <c r="AZ242">
+        <v>17</v>
+      </c>
+      <c r="BA242">
+        <v>2</v>
+      </c>
+      <c r="BB242">
+        <v>4</v>
+      </c>
+      <c r="BC242">
+        <v>6</v>
+      </c>
+      <c r="BD242">
+        <v>0</v>
+      </c>
+      <c r="BE242">
+        <v>0</v>
+      </c>
+      <c r="BF242">
+        <v>0</v>
+      </c>
+      <c r="BG242">
+        <v>0</v>
+      </c>
+      <c r="BH242">
+        <v>0</v>
+      </c>
+      <c r="BI242">
+        <v>0</v>
+      </c>
+      <c r="BJ242">
+        <v>0</v>
+      </c>
+      <c r="BK242">
+        <v>0</v>
+      </c>
+      <c r="BL242">
+        <v>0</v>
+      </c>
+      <c r="BM242">
+        <v>0</v>
+      </c>
+      <c r="BN242">
+        <v>0</v>
+      </c>
+      <c r="BO242">
+        <v>0</v>
+      </c>
+      <c r="BP242">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="364">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -784,6 +784,9 @@
     <t>['33', '57', '74']</t>
   </si>
   <si>
+    <t>['13', '84']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1100,6 +1103,9 @@
   </si>
   <si>
     <t>['45+2', '61']</t>
+  </si>
+  <si>
+    <t>['62', '82']</t>
   </si>
 </sst>
 </file>
@@ -1461,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP242"/>
+  <dimension ref="A1:BP243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2129,7 +2135,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2541,7 +2547,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2622,7 +2628,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ6">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3159,7 +3165,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -4267,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4395,7 +4401,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4601,7 +4607,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4807,7 +4813,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5631,7 +5637,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5837,7 +5843,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6742,7 +6748,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ26">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6867,7 +6873,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7279,7 +7285,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7691,7 +7697,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8927,7 +8933,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9417,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ39">
         <v>0.5</v>
@@ -9545,7 +9551,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9832,7 +9838,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ41">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -10575,7 +10581,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10781,7 +10787,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10987,7 +10993,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11193,7 +11199,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11399,7 +11405,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11605,7 +11611,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11811,7 +11817,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12223,7 +12229,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12635,7 +12641,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12841,7 +12847,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13871,7 +13877,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -14077,7 +14083,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14155,7 +14161,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ62">
         <v>2.23</v>
@@ -14901,7 +14907,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14982,7 +14988,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ66">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR66">
         <v>1.08</v>
@@ -15107,7 +15113,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15725,7 +15731,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -16137,7 +16143,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16343,7 +16349,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16421,7 +16427,7 @@
         <v>3</v>
       </c>
       <c r="AP73">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ73">
         <v>1.92</v>
@@ -16961,7 +16967,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17579,7 +17585,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17785,7 +17791,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18609,7 +18615,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18690,7 +18696,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ84">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR84">
         <v>1.12</v>
@@ -19021,7 +19027,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19639,7 +19645,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19717,7 +19723,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ89">
         <v>1.08</v>
@@ -19845,7 +19851,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -20463,7 +20469,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20669,7 +20675,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -21081,7 +21087,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21493,7 +21499,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22523,7 +22529,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22729,7 +22735,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22935,7 +22941,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23141,7 +23147,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23553,7 +23559,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23631,7 +23637,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ108">
         <v>0.92</v>
@@ -24171,7 +24177,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24252,7 +24258,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ111">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR111">
         <v>1.37</v>
@@ -24583,7 +24589,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24789,7 +24795,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24995,7 +25001,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25201,7 +25207,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25694,7 +25700,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ118">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR118">
         <v>1.65</v>
@@ -26643,7 +26649,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26849,7 +26855,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27133,7 +27139,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ125">
         <v>0.6899999999999999</v>
@@ -27261,7 +27267,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27467,7 +27473,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -28085,7 +28091,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28291,7 +28297,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28497,7 +28503,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28909,7 +28915,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29193,7 +29199,7 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ135">
         <v>2.29</v>
@@ -29321,7 +29327,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29939,7 +29945,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30020,7 +30026,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ139">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR139">
         <v>1.21</v>
@@ -30145,7 +30151,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30351,7 +30357,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -31175,7 +31181,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31381,7 +31387,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -32077,7 +32083,7 @@
         <v>1.63</v>
       </c>
       <c r="AP149">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ149">
         <v>1.14</v>
@@ -32205,7 +32211,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32617,7 +32623,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -33029,7 +33035,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33522,7 +33528,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ156">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR156">
         <v>1.73</v>
@@ -33647,7 +33653,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33853,7 +33859,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -34059,7 +34065,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34471,7 +34477,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34677,7 +34683,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34883,7 +34889,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35295,7 +35301,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35707,7 +35713,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35913,7 +35919,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36119,7 +36125,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36325,7 +36331,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36612,7 +36618,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ171">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR171">
         <v>1.53</v>
@@ -36943,7 +36949,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37355,7 +37361,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37767,7 +37773,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37845,7 +37851,7 @@
         <v>1</v>
       </c>
       <c r="AP177">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ177">
         <v>1.14</v>
@@ -37973,7 +37979,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38385,7 +38391,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38591,7 +38597,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38797,7 +38803,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -39003,7 +39009,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39084,7 +39090,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ183">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR183">
         <v>1.31</v>
@@ -39415,7 +39421,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39827,7 +39833,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -40033,7 +40039,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -41269,7 +41275,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41553,7 +41559,7 @@
         <v>0.8</v>
       </c>
       <c r="AP195">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ195">
         <v>0.6899999999999999</v>
@@ -41681,7 +41687,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -42093,7 +42099,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42505,7 +42511,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42711,7 +42717,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43204,7 +43210,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ203">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR203">
         <v>2.08</v>
@@ -44231,7 +44237,7 @@
         <v>1</v>
       </c>
       <c r="AP208">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ208">
         <v>1</v>
@@ -44359,7 +44365,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44771,7 +44777,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44977,7 +44983,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45595,7 +45601,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46625,7 +46631,7 @@
         <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q220">
         <v>1.62</v>
@@ -46831,7 +46837,7 @@
         <v>242</v>
       </c>
       <c r="P221" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q221">
         <v>4.33</v>
@@ -47037,7 +47043,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q222">
         <v>5</v>
@@ -47243,7 +47249,7 @@
         <v>243</v>
       </c>
       <c r="P223" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q223">
         <v>2.75</v>
@@ -48273,7 +48279,7 @@
         <v>91</v>
       </c>
       <c r="P228" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q228">
         <v>8</v>
@@ -49097,7 +49103,7 @@
         <v>248</v>
       </c>
       <c r="P232" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49303,7 +49309,7 @@
         <v>249</v>
       </c>
       <c r="P233" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q233">
         <v>2.5</v>
@@ -49715,7 +49721,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q235">
         <v>2.88</v>
@@ -49921,7 +49927,7 @@
         <v>91</v>
       </c>
       <c r="P236" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q236">
         <v>3.75</v>
@@ -50208,7 +50214,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ237">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR237">
         <v>1.26</v>
@@ -50333,7 +50339,7 @@
         <v>252</v>
       </c>
       <c r="P238" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q238">
         <v>3.75</v>
@@ -50745,7 +50751,7 @@
         <v>91</v>
       </c>
       <c r="P240" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51157,7 +51163,7 @@
         <v>255</v>
       </c>
       <c r="P242" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q242">
         <v>1.91</v>
@@ -51314,6 +51320,212 @@
       </c>
       <c r="BP242">
         <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7466269</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45748.625</v>
+      </c>
+      <c r="F243">
+        <v>25</v>
+      </c>
+      <c r="G243" t="s">
+        <v>82</v>
+      </c>
+      <c r="H243" t="s">
+        <v>83</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>1</v>
+      </c>
+      <c r="L243">
+        <v>2</v>
+      </c>
+      <c r="M243">
+        <v>2</v>
+      </c>
+      <c r="N243">
+        <v>4</v>
+      </c>
+      <c r="O243" t="s">
+        <v>256</v>
+      </c>
+      <c r="P243" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q243">
+        <v>1.8</v>
+      </c>
+      <c r="R243">
+        <v>2.6</v>
+      </c>
+      <c r="S243">
+        <v>8</v>
+      </c>
+      <c r="T243">
+        <v>1.29</v>
+      </c>
+      <c r="U243">
+        <v>3.5</v>
+      </c>
+      <c r="V243">
+        <v>2.38</v>
+      </c>
+      <c r="W243">
+        <v>1.53</v>
+      </c>
+      <c r="X243">
+        <v>5.5</v>
+      </c>
+      <c r="Y243">
+        <v>1.14</v>
+      </c>
+      <c r="Z243">
+        <v>1.35</v>
+      </c>
+      <c r="AA243">
+        <v>5.4</v>
+      </c>
+      <c r="AB243">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AC243">
+        <v>1.03</v>
+      </c>
+      <c r="AD243">
+        <v>11</v>
+      </c>
+      <c r="AE243">
+        <v>1.14</v>
+      </c>
+      <c r="AF243">
+        <v>5.5</v>
+      </c>
+      <c r="AG243">
+        <v>1.54</v>
+      </c>
+      <c r="AH243">
+        <v>2.26</v>
+      </c>
+      <c r="AI243">
+        <v>1.95</v>
+      </c>
+      <c r="AJ243">
+        <v>1.8</v>
+      </c>
+      <c r="AK243">
+        <v>1.06</v>
+      </c>
+      <c r="AL243">
+        <v>1.14</v>
+      </c>
+      <c r="AM243">
+        <v>3.5</v>
+      </c>
+      <c r="AN243">
+        <v>1.83</v>
+      </c>
+      <c r="AO243">
+        <v>0.46</v>
+      </c>
+      <c r="AP243">
+        <v>1.77</v>
+      </c>
+      <c r="AQ243">
+        <v>0.5</v>
+      </c>
+      <c r="AR243">
+        <v>1.8</v>
+      </c>
+      <c r="AS243">
+        <v>1.29</v>
+      </c>
+      <c r="AT243">
+        <v>3.09</v>
+      </c>
+      <c r="AU243">
+        <v>3</v>
+      </c>
+      <c r="AV243">
+        <v>3</v>
+      </c>
+      <c r="AW243">
+        <v>22</v>
+      </c>
+      <c r="AX243">
+        <v>4</v>
+      </c>
+      <c r="AY243">
+        <v>31</v>
+      </c>
+      <c r="AZ243">
+        <v>8</v>
+      </c>
+      <c r="BA243">
+        <v>12</v>
+      </c>
+      <c r="BB243">
+        <v>5</v>
+      </c>
+      <c r="BC243">
+        <v>17</v>
+      </c>
+      <c r="BD243">
+        <v>1.06</v>
+      </c>
+      <c r="BE243">
+        <v>13.5</v>
+      </c>
+      <c r="BF243">
+        <v>12.5</v>
+      </c>
+      <c r="BG243">
+        <v>1.12</v>
+      </c>
+      <c r="BH243">
+        <v>4.7</v>
+      </c>
+      <c r="BI243">
+        <v>1.33</v>
+      </c>
+      <c r="BJ243">
+        <v>2.95</v>
+      </c>
+      <c r="BK243">
+        <v>1.6</v>
+      </c>
+      <c r="BL243">
+        <v>2.15</v>
+      </c>
+      <c r="BM243">
+        <v>2</v>
+      </c>
+      <c r="BN243">
+        <v>1.66</v>
+      </c>
+      <c r="BO243">
+        <v>2.65</v>
+      </c>
+      <c r="BP243">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="365">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -787,6 +787,9 @@
     <t>['13', '84']</t>
   </si>
   <si>
+    <t>['10', '33', '82', '90']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1467,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP243"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2007,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ3">
         <v>0.92</v>
@@ -2135,7 +2138,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2547,7 +2550,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -3165,7 +3168,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -4401,7 +4404,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4482,7 +4485,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ15">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4607,7 +4610,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4813,7 +4816,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5637,7 +5640,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5843,7 +5846,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6873,7 +6876,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7160,7 +7163,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ28">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR28">
         <v>0.73</v>
@@ -7285,7 +7288,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7697,7 +7700,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8933,7 +8936,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9551,7 +9554,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -10581,7 +10584,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10787,7 +10790,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10993,7 +10996,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11199,7 +11202,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11405,7 +11408,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11611,7 +11614,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11692,7 +11695,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ50">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -11817,7 +11820,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12101,7 +12104,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ52">
         <v>0.62</v>
@@ -12229,7 +12232,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12641,7 +12644,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12847,7 +12850,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13877,7 +13880,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -14083,7 +14086,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14907,7 +14910,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15113,7 +15116,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15397,7 +15400,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ68">
         <v>1.14</v>
@@ -15731,7 +15734,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15812,7 +15815,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ70">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR70">
         <v>2.32</v>
@@ -16143,7 +16146,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16349,7 +16352,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16967,7 +16970,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17585,7 +17588,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17791,7 +17794,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18284,7 +18287,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ82">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR82">
         <v>1.34</v>
@@ -18615,7 +18618,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -19027,7 +19030,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19645,7 +19648,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19851,7 +19854,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19929,7 +19932,7 @@
         <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ90">
         <v>2.29</v>
@@ -20469,7 +20472,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20675,7 +20678,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20753,7 +20756,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ94">
         <v>1.64</v>
@@ -21087,7 +21090,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21374,7 +21377,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ97">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR97">
         <v>1.38</v>
@@ -21499,7 +21502,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22529,7 +22532,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22735,7 +22738,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22941,7 +22944,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23147,7 +23150,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23559,7 +23562,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -24049,7 +24052,7 @@
         <v>0</v>
       </c>
       <c r="AP110">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ110">
         <v>0.5</v>
@@ -24177,7 +24180,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24464,7 +24467,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ112">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR112">
         <v>2.46</v>
@@ -24589,7 +24592,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24795,7 +24798,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -25001,7 +25004,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25207,7 +25210,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -26315,7 +26318,7 @@
         <v>0.83</v>
       </c>
       <c r="AP121">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26649,7 +26652,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26855,7 +26858,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27267,7 +27270,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27473,7 +27476,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -28091,7 +28094,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28297,7 +28300,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28503,7 +28506,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28915,7 +28918,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29327,7 +29330,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29945,7 +29948,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30151,7 +30154,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30229,7 +30232,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ140">
         <v>0.6899999999999999</v>
@@ -30357,7 +30360,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30850,7 +30853,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ143">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR143">
         <v>2.08</v>
@@ -31181,7 +31184,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31387,7 +31390,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -32211,7 +32214,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32623,7 +32626,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -33035,7 +33038,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33653,7 +33656,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33859,7 +33862,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -34065,7 +34068,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34477,7 +34480,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34555,7 +34558,7 @@
         <v>2.5</v>
       </c>
       <c r="AP161">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ161">
         <v>2.23</v>
@@ -34683,7 +34686,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34889,7 +34892,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35301,7 +35304,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35588,7 +35591,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ166">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR166">
         <v>1.78</v>
@@ -35713,7 +35716,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35919,7 +35922,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36125,7 +36128,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36331,7 +36334,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36949,7 +36952,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37361,7 +37364,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37773,7 +37776,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37979,7 +37982,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38060,7 +38063,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ178">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR178">
         <v>1.43</v>
@@ -38391,7 +38394,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38597,7 +38600,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38803,7 +38806,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -39009,7 +39012,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39421,7 +39424,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39708,7 +39711,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ186">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR186">
         <v>1.58</v>
@@ -39833,7 +39836,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -40039,7 +40042,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40735,7 +40738,7 @@
         <v>1.2</v>
       </c>
       <c r="AP191">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ191">
         <v>1.14</v>
@@ -41275,7 +41278,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41687,7 +41690,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -42099,7 +42102,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42511,7 +42514,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42592,7 +42595,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ200">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR200">
         <v>1.12</v>
@@ -42717,7 +42720,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43619,7 +43622,7 @@
         <v>0.64</v>
       </c>
       <c r="AP205">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ205">
         <v>0.71</v>
@@ -44365,7 +44368,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44777,7 +44780,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44983,7 +44986,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45267,7 +45270,7 @@
         <v>0.82</v>
       </c>
       <c r="AP213">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ213">
         <v>1</v>
@@ -45601,7 +45604,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46631,7 +46634,7 @@
         <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q220">
         <v>1.62</v>
@@ -46837,7 +46840,7 @@
         <v>242</v>
       </c>
       <c r="P221" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q221">
         <v>4.33</v>
@@ -47043,7 +47046,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q222">
         <v>5</v>
@@ -47249,7 +47252,7 @@
         <v>243</v>
       </c>
       <c r="P223" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q223">
         <v>2.75</v>
@@ -48279,7 +48282,7 @@
         <v>91</v>
       </c>
       <c r="P228" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q228">
         <v>8</v>
@@ -49103,7 +49106,7 @@
         <v>248</v>
       </c>
       <c r="P232" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49309,7 +49312,7 @@
         <v>249</v>
       </c>
       <c r="P233" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q233">
         <v>2.5</v>
@@ -49596,7 +49599,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ234">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR234">
         <v>1.42</v>
@@ -49721,7 +49724,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q235">
         <v>2.88</v>
@@ -49927,7 +49930,7 @@
         <v>91</v>
       </c>
       <c r="P236" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q236">
         <v>3.75</v>
@@ -50339,7 +50342,7 @@
         <v>252</v>
       </c>
       <c r="P238" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q238">
         <v>3.75</v>
@@ -50751,7 +50754,7 @@
         <v>91</v>
       </c>
       <c r="P240" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51163,7 +51166,7 @@
         <v>255</v>
       </c>
       <c r="P242" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q242">
         <v>1.91</v>
@@ -51241,7 +51244,7 @@
         <v>1.17</v>
       </c>
       <c r="AP242">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ242">
         <v>1.08</v>
@@ -51369,7 +51372,7 @@
         <v>256</v>
       </c>
       <c r="P243" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q243">
         <v>1.8</v>
@@ -51526,6 +51529,212 @@
       </c>
       <c r="BP243">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7466271</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45749.625</v>
+      </c>
+      <c r="F244">
+        <v>25</v>
+      </c>
+      <c r="G244" t="s">
+        <v>71</v>
+      </c>
+      <c r="H244" t="s">
+        <v>70</v>
+      </c>
+      <c r="I244">
+        <v>2</v>
+      </c>
+      <c r="J244">
+        <v>1</v>
+      </c>
+      <c r="K244">
+        <v>3</v>
+      </c>
+      <c r="L244">
+        <v>4</v>
+      </c>
+      <c r="M244">
+        <v>1</v>
+      </c>
+      <c r="N244">
+        <v>5</v>
+      </c>
+      <c r="O244" t="s">
+        <v>257</v>
+      </c>
+      <c r="P244" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q244">
+        <v>1.73</v>
+      </c>
+      <c r="R244">
+        <v>2.63</v>
+      </c>
+      <c r="S244">
+        <v>8</v>
+      </c>
+      <c r="T244">
+        <v>1.25</v>
+      </c>
+      <c r="U244">
+        <v>3.75</v>
+      </c>
+      <c r="V244">
+        <v>2.25</v>
+      </c>
+      <c r="W244">
+        <v>1.57</v>
+      </c>
+      <c r="X244">
+        <v>5.5</v>
+      </c>
+      <c r="Y244">
+        <v>1.14</v>
+      </c>
+      <c r="Z244">
+        <v>1.32</v>
+      </c>
+      <c r="AA244">
+        <v>6.2</v>
+      </c>
+      <c r="AB244">
+        <v>8.6</v>
+      </c>
+      <c r="AC244">
+        <v>1.03</v>
+      </c>
+      <c r="AD244">
+        <v>11</v>
+      </c>
+      <c r="AE244">
+        <v>1.2</v>
+      </c>
+      <c r="AF244">
+        <v>4.33</v>
+      </c>
+      <c r="AG244">
+        <v>1.72</v>
+      </c>
+      <c r="AH244">
+        <v>2.05</v>
+      </c>
+      <c r="AI244">
+        <v>1.95</v>
+      </c>
+      <c r="AJ244">
+        <v>1.8</v>
+      </c>
+      <c r="AK244">
+        <v>1.08</v>
+      </c>
+      <c r="AL244">
+        <v>1.16</v>
+      </c>
+      <c r="AM244">
+        <v>3.1</v>
+      </c>
+      <c r="AN244">
+        <v>2.08</v>
+      </c>
+      <c r="AO244">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP244">
+        <v>2.14</v>
+      </c>
+      <c r="AQ244">
+        <v>0.64</v>
+      </c>
+      <c r="AR244">
+        <v>1.96</v>
+      </c>
+      <c r="AS244">
+        <v>1.15</v>
+      </c>
+      <c r="AT244">
+        <v>3.11</v>
+      </c>
+      <c r="AU244">
+        <v>6</v>
+      </c>
+      <c r="AV244">
+        <v>2</v>
+      </c>
+      <c r="AW244">
+        <v>9</v>
+      </c>
+      <c r="AX244">
+        <v>5</v>
+      </c>
+      <c r="AY244">
+        <v>16</v>
+      </c>
+      <c r="AZ244">
+        <v>7</v>
+      </c>
+      <c r="BA244">
+        <v>1</v>
+      </c>
+      <c r="BB244">
+        <v>1</v>
+      </c>
+      <c r="BC244">
+        <v>2</v>
+      </c>
+      <c r="BD244">
+        <v>1.19</v>
+      </c>
+      <c r="BE244">
+        <v>9</v>
+      </c>
+      <c r="BF244">
+        <v>6.25</v>
+      </c>
+      <c r="BG244">
+        <v>1.19</v>
+      </c>
+      <c r="BH244">
+        <v>4</v>
+      </c>
+      <c r="BI244">
+        <v>1.37</v>
+      </c>
+      <c r="BJ244">
+        <v>2.75</v>
+      </c>
+      <c r="BK244">
+        <v>1.66</v>
+      </c>
+      <c r="BL244">
+        <v>2</v>
+      </c>
+      <c r="BM244">
+        <v>2.1</v>
+      </c>
+      <c r="BN244">
+        <v>1.6</v>
+      </c>
+      <c r="BO244">
+        <v>2.85</v>
+      </c>
+      <c r="BP244">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="366">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -790,6 +790,9 @@
     <t>['10', '33', '82', '90']</t>
   </si>
   <si>
+    <t>['11', '32', '66']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1470,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2013,7 +2016,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ3">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2138,7 +2141,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2550,7 +2553,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -3168,7 +3171,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3864,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ12">
         <v>2.23</v>
@@ -4404,7 +4407,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4610,7 +4613,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4816,7 +4819,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5640,7 +5643,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5846,7 +5849,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6339,7 +6342,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ24">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -6876,7 +6879,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7288,7 +7291,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7572,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ30">
         <v>0.62</v>
@@ -7700,7 +7703,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8936,7 +8939,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9554,7 +9557,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -10584,7 +10587,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10790,7 +10793,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10871,7 +10874,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ46">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR46">
         <v>1.08</v>
@@ -10996,7 +10999,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11202,7 +11205,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11408,7 +11411,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11614,7 +11617,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11692,7 +11695,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ50">
         <v>0.64</v>
@@ -11820,7 +11823,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12232,7 +12235,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12644,7 +12647,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12850,7 +12853,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13880,7 +13883,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -14086,7 +14089,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14373,7 +14376,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ63">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR63">
         <v>1.02</v>
@@ -14910,7 +14913,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15116,7 +15119,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15606,7 +15609,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ69">
         <v>0.6899999999999999</v>
@@ -15734,7 +15737,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -16146,7 +16149,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16352,7 +16355,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16970,7 +16973,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17588,7 +17591,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17794,7 +17797,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18618,7 +18621,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18902,7 +18905,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ85">
         <v>1.14</v>
@@ -19030,7 +19033,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19523,7 +19526,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ88">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR88">
         <v>2.16</v>
@@ -19648,7 +19651,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19854,7 +19857,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -20472,7 +20475,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20678,7 +20681,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -21090,7 +21093,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21502,7 +21505,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22532,7 +22535,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22738,7 +22741,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22944,7 +22947,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23150,7 +23153,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23434,7 +23437,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ107">
         <v>1.08</v>
@@ -23562,7 +23565,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23643,7 +23646,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ108">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR108">
         <v>1.94</v>
@@ -24180,7 +24183,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24592,7 +24595,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24798,7 +24801,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -25004,7 +25007,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25210,7 +25213,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25700,7 +25703,7 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ118">
         <v>0.5</v>
@@ -26115,7 +26118,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ120">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR120">
         <v>1.14</v>
@@ -26652,7 +26655,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26858,7 +26861,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27270,7 +27273,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27476,7 +27479,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -28094,7 +28097,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28300,7 +28303,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28506,7 +28509,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28918,7 +28921,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29330,7 +29333,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29617,7 +29620,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ137">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR137">
         <v>1.19</v>
@@ -29820,7 +29823,7 @@
         <v>2.63</v>
       </c>
       <c r="AP138">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ138">
         <v>1.92</v>
@@ -29948,7 +29951,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30154,7 +30157,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30360,7 +30363,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -31184,7 +31187,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31390,7 +31393,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -32214,7 +32217,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32626,7 +32629,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -33038,7 +33041,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33656,7 +33659,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33862,7 +33865,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -34068,7 +34071,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34149,7 +34152,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ159">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR159">
         <v>1.99</v>
@@ -34480,7 +34483,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34686,7 +34689,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34892,7 +34895,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35304,7 +35307,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35716,7 +35719,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35922,7 +35925,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36128,7 +36131,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36206,7 +36209,7 @@
         <v>1.89</v>
       </c>
       <c r="AP169">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ169">
         <v>2.29</v>
@@ -36334,7 +36337,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36952,7 +36955,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37364,7 +37367,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37651,7 +37654,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ176">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR176">
         <v>1.2</v>
@@ -37776,7 +37779,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37982,7 +37985,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38394,7 +38397,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38600,7 +38603,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38678,7 +38681,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ181">
         <v>1</v>
@@ -38806,7 +38809,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -39012,7 +39015,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39424,7 +39427,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39836,7 +39839,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -40042,7 +40045,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40329,7 +40332,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ189">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR189">
         <v>2.4</v>
@@ -41278,7 +41281,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41690,7 +41693,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41768,7 +41771,7 @@
         <v>1.27</v>
       </c>
       <c r="AP196">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ196">
         <v>1.14</v>
@@ -42102,7 +42105,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42514,7 +42517,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42720,7 +42723,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -44368,7 +44371,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44780,7 +44783,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44986,7 +44989,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45476,7 +45479,7 @@
         <v>1.91</v>
       </c>
       <c r="AP214">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ214">
         <v>1.64</v>
@@ -45604,7 +45607,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46097,7 +46100,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ217">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR217">
         <v>1.56</v>
@@ -46634,7 +46637,7 @@
         <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q220">
         <v>1.62</v>
@@ -46840,7 +46843,7 @@
         <v>242</v>
       </c>
       <c r="P221" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q221">
         <v>4.33</v>
@@ -47046,7 +47049,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q222">
         <v>5</v>
@@ -47252,7 +47255,7 @@
         <v>243</v>
       </c>
       <c r="P223" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q223">
         <v>2.75</v>
@@ -48282,7 +48285,7 @@
         <v>91</v>
       </c>
       <c r="P228" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q228">
         <v>8</v>
@@ -48566,7 +48569,7 @@
         <v>0.67</v>
       </c>
       <c r="AP229">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ229">
         <v>0.6899999999999999</v>
@@ -48775,7 +48778,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ230">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR230">
         <v>1.64</v>
@@ -49106,7 +49109,7 @@
         <v>248</v>
       </c>
       <c r="P232" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49312,7 +49315,7 @@
         <v>249</v>
       </c>
       <c r="P233" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q233">
         <v>2.5</v>
@@ -49724,7 +49727,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q235">
         <v>2.88</v>
@@ -49930,7 +49933,7 @@
         <v>91</v>
       </c>
       <c r="P236" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q236">
         <v>3.75</v>
@@ -50342,7 +50345,7 @@
         <v>252</v>
       </c>
       <c r="P238" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q238">
         <v>3.75</v>
@@ -50754,7 +50757,7 @@
         <v>91</v>
       </c>
       <c r="P240" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51166,7 +51169,7 @@
         <v>255</v>
       </c>
       <c r="P242" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q242">
         <v>1.91</v>
@@ -51372,7 +51375,7 @@
         <v>256</v>
       </c>
       <c r="P243" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q243">
         <v>1.8</v>
@@ -51735,6 +51738,212 @@
       </c>
       <c r="BP244">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7466303</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F245">
+        <v>28</v>
+      </c>
+      <c r="G245" t="s">
+        <v>80</v>
+      </c>
+      <c r="H245" t="s">
+        <v>86</v>
+      </c>
+      <c r="I245">
+        <v>2</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>2</v>
+      </c>
+      <c r="L245">
+        <v>3</v>
+      </c>
+      <c r="M245">
+        <v>1</v>
+      </c>
+      <c r="N245">
+        <v>4</v>
+      </c>
+      <c r="O245" t="s">
+        <v>258</v>
+      </c>
+      <c r="P245" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q245">
+        <v>2.1</v>
+      </c>
+      <c r="R245">
+        <v>2.2</v>
+      </c>
+      <c r="S245">
+        <v>6.5</v>
+      </c>
+      <c r="T245">
+        <v>1.4</v>
+      </c>
+      <c r="U245">
+        <v>2.75</v>
+      </c>
+      <c r="V245">
+        <v>3</v>
+      </c>
+      <c r="W245">
+        <v>1.36</v>
+      </c>
+      <c r="X245">
+        <v>8</v>
+      </c>
+      <c r="Y245">
+        <v>1.08</v>
+      </c>
+      <c r="Z245">
+        <v>1.81</v>
+      </c>
+      <c r="AA245">
+        <v>4.1</v>
+      </c>
+      <c r="AB245">
+        <v>4.1</v>
+      </c>
+      <c r="AC245">
+        <v>1.05</v>
+      </c>
+      <c r="AD245">
+        <v>9.5</v>
+      </c>
+      <c r="AE245">
+        <v>1.28</v>
+      </c>
+      <c r="AF245">
+        <v>3.5</v>
+      </c>
+      <c r="AG245">
+        <v>1.85</v>
+      </c>
+      <c r="AH245">
+        <v>1.96</v>
+      </c>
+      <c r="AI245">
+        <v>2.05</v>
+      </c>
+      <c r="AJ245">
+        <v>1.7</v>
+      </c>
+      <c r="AK245">
+        <v>1.14</v>
+      </c>
+      <c r="AL245">
+        <v>1.24</v>
+      </c>
+      <c r="AM245">
+        <v>2.3</v>
+      </c>
+      <c r="AN245">
+        <v>1.85</v>
+      </c>
+      <c r="AO245">
+        <v>0.92</v>
+      </c>
+      <c r="AP245">
+        <v>1.93</v>
+      </c>
+      <c r="AQ245">
+        <v>0.86</v>
+      </c>
+      <c r="AR245">
+        <v>1.65</v>
+      </c>
+      <c r="AS245">
+        <v>0.93</v>
+      </c>
+      <c r="AT245">
+        <v>2.58</v>
+      </c>
+      <c r="AU245">
+        <v>11</v>
+      </c>
+      <c r="AV245">
+        <v>4</v>
+      </c>
+      <c r="AW245">
+        <v>11</v>
+      </c>
+      <c r="AX245">
+        <v>8</v>
+      </c>
+      <c r="AY245">
+        <v>28</v>
+      </c>
+      <c r="AZ245">
+        <v>14</v>
+      </c>
+      <c r="BA245">
+        <v>9</v>
+      </c>
+      <c r="BB245">
+        <v>6</v>
+      </c>
+      <c r="BC245">
+        <v>15</v>
+      </c>
+      <c r="BD245">
+        <v>1.23</v>
+      </c>
+      <c r="BE245">
+        <v>8.5</v>
+      </c>
+      <c r="BF245">
+        <v>4.4</v>
+      </c>
+      <c r="BG245">
+        <v>1.21</v>
+      </c>
+      <c r="BH245">
+        <v>3.8</v>
+      </c>
+      <c r="BI245">
+        <v>1.38</v>
+      </c>
+      <c r="BJ245">
+        <v>2.75</v>
+      </c>
+      <c r="BK245">
+        <v>1.62</v>
+      </c>
+      <c r="BL245">
+        <v>2.12</v>
+      </c>
+      <c r="BM245">
+        <v>1.98</v>
+      </c>
+      <c r="BN245">
+        <v>1.72</v>
+      </c>
+      <c r="BO245">
+        <v>2.48</v>
+      </c>
+      <c r="BP245">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="374">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -793,6 +793,18 @@
     <t>['11', '32', '66']</t>
   </si>
   <si>
+    <t>['67', '71']</t>
+  </si>
+  <si>
+    <t>['14', '17']</t>
+  </si>
+  <si>
+    <t>['33', '84']</t>
+  </si>
+  <si>
+    <t>['32', '35', '76']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -1112,6 +1124,18 @@
   </si>
   <si>
     <t>['62', '82']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['11', '28', '88']</t>
+  </si>
+  <si>
+    <t>['24', '31']</t>
+  </si>
+  <si>
+    <t>['43', '45']</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP245"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1807,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ2">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2141,7 +2165,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2425,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ5">
         <v>1.64</v>
@@ -2553,7 +2577,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2837,10 +2861,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ7">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3046,7 +3070,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ8">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3171,7 +3195,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3249,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3455,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ10">
         <v>0.5</v>
@@ -3870,7 +3894,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ12">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4073,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ13">
         <v>1.14</v>
@@ -4279,10 +4303,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4407,7 +4431,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4485,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ15">
         <v>0.64</v>
@@ -4613,7 +4637,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4694,7 +4718,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ16">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4819,7 +4843,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4900,7 +4924,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ17">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5518,7 +5542,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ20">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR20">
         <v>1.11</v>
@@ -5643,7 +5667,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5721,10 +5745,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ21">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR21">
         <v>0.96</v>
@@ -5849,7 +5873,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5930,7 +5954,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ22">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR22">
         <v>0.79</v>
@@ -6133,7 +6157,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ23">
         <v>1.64</v>
@@ -6545,10 +6569,10 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ25">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR25">
         <v>1.08</v>
@@ -6751,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6879,7 +6903,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6957,7 +6981,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ27">
         <v>1.64</v>
@@ -7163,7 +7187,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ28">
         <v>0.64</v>
@@ -7291,7 +7315,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7372,7 +7396,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR29">
         <v>2.19</v>
@@ -7578,7 +7602,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ30">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR30">
         <v>2.4</v>
@@ -7703,7 +7727,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -8196,7 +8220,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ33">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR33">
         <v>0.7</v>
@@ -8608,7 +8632,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR35">
         <v>2.65</v>
@@ -8811,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ36">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR36">
         <v>1.72</v>
@@ -8939,7 +8963,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9017,10 +9041,10 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ37">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR37">
         <v>1.07</v>
@@ -9429,7 +9453,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ39">
         <v>0.5</v>
@@ -9557,7 +9581,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9635,7 +9659,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ40">
         <v>1.08</v>
@@ -10253,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ43">
         <v>0.5</v>
@@ -10459,7 +10483,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10587,7 +10611,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10793,7 +10817,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10999,7 +11023,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -11077,7 +11101,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ47">
         <v>1.14</v>
@@ -11205,7 +11229,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11283,7 +11307,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ48">
         <v>2.29</v>
@@ -11411,7 +11435,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11492,7 +11516,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ49">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR49">
         <v>1.18</v>
@@ -11617,7 +11641,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11823,7 +11847,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11901,7 +11925,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ51">
         <v>1.14</v>
@@ -12110,7 +12134,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ52">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR52">
         <v>2.23</v>
@@ -12235,7 +12259,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12316,7 +12340,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ53">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12647,7 +12671,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12728,7 +12752,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ55">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR55">
         <v>1.25</v>
@@ -12853,7 +12877,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -12934,7 +12958,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ56">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR56">
         <v>1.55</v>
@@ -13137,7 +13161,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13549,10 +13573,10 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ59">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR59">
         <v>2.11</v>
@@ -13755,7 +13779,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ60">
         <v>1.08</v>
@@ -13883,7 +13907,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13961,7 +13985,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ61">
         <v>2.29</v>
@@ -14089,7 +14113,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14167,10 +14191,10 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ62">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR62">
         <v>2.58</v>
@@ -14373,7 +14397,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ63">
         <v>0.86</v>
@@ -14582,7 +14606,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -14913,7 +14937,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -15119,7 +15143,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15197,10 +15221,10 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ67">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15612,7 +15636,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ69">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR69">
         <v>2.09</v>
@@ -15737,7 +15761,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15815,7 +15839,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ70">
         <v>0.64</v>
@@ -16149,7 +16173,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16227,7 +16251,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ72">
         <v>0.71</v>
@@ -16355,7 +16379,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16433,10 +16457,10 @@
         <v>3</v>
       </c>
       <c r="AP73">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ73">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR73">
         <v>2.44</v>
@@ -16845,7 +16869,7 @@
         <v>1.5</v>
       </c>
       <c r="AP75">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ75">
         <v>1.14</v>
@@ -16973,7 +16997,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17051,10 +17075,10 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ76">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR76">
         <v>1.77</v>
@@ -17463,10 +17487,10 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ78">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR78">
         <v>1.07</v>
@@ -17591,7 +17615,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17797,7 +17821,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17878,7 +17902,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ80">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR80">
         <v>1.12</v>
@@ -18081,10 +18105,10 @@
         <v>0.75</v>
       </c>
       <c r="AP81">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR81">
         <v>1.25</v>
@@ -18496,7 +18520,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ83">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR83">
         <v>2.49</v>
@@ -18621,7 +18645,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -19033,7 +19057,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19114,7 +19138,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ86">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19317,10 +19341,10 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ87">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -19523,7 +19547,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ88">
         <v>0.86</v>
@@ -19651,7 +19675,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19729,7 +19753,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ89">
         <v>1.08</v>
@@ -19857,7 +19881,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -20350,7 +20374,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ92">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR92">
         <v>1.39</v>
@@ -20475,7 +20499,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20553,10 +20577,10 @@
         <v>3</v>
       </c>
       <c r="AP93">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ93">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR93">
         <v>2.04</v>
@@ -20681,7 +20705,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -21093,7 +21117,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21171,10 +21195,10 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ96">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21505,7 +21529,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21583,10 +21607,10 @@
         <v>2.5</v>
       </c>
       <c r="AP98">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ98">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR98">
         <v>1.7</v>
@@ -21789,7 +21813,7 @@
         <v>0.5</v>
       </c>
       <c r="AP99">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ99">
         <v>0.71</v>
@@ -21998,7 +22022,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ100">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR100">
         <v>1.37</v>
@@ -22201,7 +22225,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ101">
         <v>1.14</v>
@@ -22535,7 +22559,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22616,7 +22640,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ103">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR103">
         <v>1.38</v>
@@ -22741,7 +22765,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22819,10 +22843,10 @@
         <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR104">
         <v>1.2</v>
@@ -22947,7 +22971,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -23025,10 +23049,10 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ105">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR105">
         <v>1.24</v>
@@ -23153,7 +23177,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23231,7 +23255,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ106">
         <v>2.29</v>
@@ -23565,7 +23589,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23643,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108">
         <v>0.86</v>
@@ -23849,7 +23873,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ109">
         <v>0.71</v>
@@ -24183,7 +24207,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24595,7 +24619,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24801,7 +24825,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24882,7 +24906,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ114">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -25007,7 +25031,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -25085,7 +25109,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ115">
         <v>1.64</v>
@@ -25213,7 +25237,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25294,7 +25318,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ116">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR116">
         <v>1.02</v>
@@ -25497,10 +25521,10 @@
         <v>0.5</v>
       </c>
       <c r="AP117">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ117">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR117">
         <v>2.01</v>
@@ -26115,7 +26139,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ120">
         <v>0.86</v>
@@ -26655,7 +26679,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26736,7 +26760,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ123">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR123">
         <v>1.43</v>
@@ -26861,7 +26885,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26939,7 +26963,7 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ124">
         <v>1.08</v>
@@ -27145,10 +27169,10 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ125">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR125">
         <v>1.92</v>
@@ -27273,7 +27297,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27479,7 +27503,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27557,10 +27581,10 @@
         <v>2.67</v>
       </c>
       <c r="AP127">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ127">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR127">
         <v>1.82</v>
@@ -27969,10 +27993,10 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ129">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -28097,7 +28121,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28175,10 +28199,10 @@
         <v>0.57</v>
       </c>
       <c r="AP130">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ130">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR130">
         <v>1.55</v>
@@ -28303,7 +28327,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28381,10 +28405,10 @@
         <v>2.14</v>
       </c>
       <c r="AP131">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ131">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28509,7 +28533,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28793,10 +28817,10 @@
         <v>0.43</v>
       </c>
       <c r="AP133">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ133">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR133">
         <v>1.23</v>
@@ -28921,7 +28945,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29205,7 +29229,7 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ135">
         <v>2.29</v>
@@ -29333,7 +29357,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29411,10 +29435,10 @@
         <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ136">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29826,7 +29850,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ138">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR138">
         <v>1.59</v>
@@ -29951,7 +29975,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -30157,7 +30181,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30238,7 +30262,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ140">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR140">
         <v>1.81</v>
@@ -30363,7 +30387,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30853,7 +30877,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ143">
         <v>0.64</v>
@@ -31059,7 +31083,7 @@
         <v>0.29</v>
       </c>
       <c r="AP144">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ144">
         <v>0.71</v>
@@ -31187,7 +31211,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31393,7 +31417,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31471,10 +31495,10 @@
         <v>0.5</v>
       </c>
       <c r="AP146">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ146">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR146">
         <v>1.16</v>
@@ -31677,10 +31701,10 @@
         <v>0.88</v>
       </c>
       <c r="AP147">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ147">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR147">
         <v>1.7</v>
@@ -31883,7 +31907,7 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ148">
         <v>0.5</v>
@@ -32089,7 +32113,7 @@
         <v>1.63</v>
       </c>
       <c r="AP149">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ149">
         <v>1.14</v>
@@ -32217,7 +32241,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32295,7 +32319,7 @@
         <v>1.75</v>
       </c>
       <c r="AP150">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ150">
         <v>2.29</v>
@@ -32504,7 +32528,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ151">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR151">
         <v>2.48</v>
@@ -32629,7 +32653,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32916,7 +32940,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ153">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR153">
         <v>1.13</v>
@@ -33041,7 +33065,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33531,7 +33555,7 @@
         <v>0.25</v>
       </c>
       <c r="AP156">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ156">
         <v>0.5</v>
@@ -33659,7 +33683,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33740,7 +33764,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR157">
         <v>1.23</v>
@@ -33865,7 +33889,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -34071,7 +34095,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34149,7 +34173,7 @@
         <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ159">
         <v>0.86</v>
@@ -34355,7 +34379,7 @@
         <v>0.25</v>
       </c>
       <c r="AP160">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ160">
         <v>0.71</v>
@@ -34483,7 +34507,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34564,7 +34588,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ161">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR161">
         <v>1.8</v>
@@ -34689,7 +34713,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34895,7 +34919,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -34976,7 +35000,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ163">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR163">
         <v>1.24</v>
@@ -35307,7 +35331,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35388,7 +35412,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ165">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR165">
         <v>1.19</v>
@@ -35591,7 +35615,7 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ166">
         <v>0.64</v>
@@ -35719,7 +35743,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -35925,7 +35949,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q168">
         <v>3.1</v>
@@ -36003,10 +36027,10 @@
         <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ168">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR168">
         <v>1.26</v>
@@ -36131,7 +36155,7 @@
         <v>91</v>
       </c>
       <c r="P169" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q169">
         <v>5</v>
@@ -36337,7 +36361,7 @@
         <v>205</v>
       </c>
       <c r="P170" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36621,7 +36645,7 @@
         <v>0.22</v>
       </c>
       <c r="AP171">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ171">
         <v>0.5</v>
@@ -36830,7 +36854,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ172">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR172">
         <v>1.45</v>
@@ -36955,7 +36979,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q173">
         <v>1.4</v>
@@ -37036,7 +37060,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ173">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR173">
         <v>2.35</v>
@@ -37239,7 +37263,7 @@
         <v>0.6</v>
       </c>
       <c r="AP174">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ174">
         <v>0.5</v>
@@ -37367,7 +37391,7 @@
         <v>208</v>
       </c>
       <c r="P175" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q175">
         <v>2.75</v>
@@ -37448,7 +37472,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ175">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR175">
         <v>1.34</v>
@@ -37651,7 +37675,7 @@
         <v>1.22</v>
       </c>
       <c r="AP176">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ176">
         <v>0.86</v>
@@ -37779,7 +37803,7 @@
         <v>210</v>
       </c>
       <c r="P177" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q177">
         <v>2.1</v>
@@ -37857,7 +37881,7 @@
         <v>1</v>
       </c>
       <c r="AP177">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ177">
         <v>1.14</v>
@@ -37985,7 +38009,7 @@
         <v>211</v>
       </c>
       <c r="P178" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38272,7 +38296,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ179">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR179">
         <v>1.35</v>
@@ -38397,7 +38421,7 @@
         <v>213</v>
       </c>
       <c r="P180" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q180">
         <v>3.6</v>
@@ -38478,7 +38502,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ180">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR180">
         <v>1.23</v>
@@ -38603,7 +38627,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q181">
         <v>2.75</v>
@@ -38809,7 +38833,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -38890,7 +38914,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ182">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR182">
         <v>1.6</v>
@@ -39015,7 +39039,7 @@
         <v>216</v>
       </c>
       <c r="P183" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39093,7 +39117,7 @@
         <v>0.3</v>
       </c>
       <c r="AP183">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ183">
         <v>0.5</v>
@@ -39299,10 +39323,10 @@
         <v>1.9</v>
       </c>
       <c r="AP184">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ184">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR184">
         <v>1.78</v>
@@ -39427,7 +39451,7 @@
         <v>218</v>
       </c>
       <c r="P185" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39505,7 +39529,7 @@
         <v>1.3</v>
       </c>
       <c r="AP185">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ185">
         <v>1.14</v>
@@ -39711,7 +39735,7 @@
         <v>0.5</v>
       </c>
       <c r="AP186">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ186">
         <v>0.64</v>
@@ -39839,7 +39863,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -40045,7 +40069,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40535,10 +40559,10 @@
         <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ190">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR190">
         <v>1.38</v>
@@ -41153,10 +41177,10 @@
         <v>0.7</v>
       </c>
       <c r="AP193">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ193">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR193">
         <v>1.22</v>
@@ -41281,7 +41305,7 @@
         <v>91</v>
       </c>
       <c r="P194" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q194">
         <v>5.5</v>
@@ -41565,10 +41589,10 @@
         <v>0.8</v>
       </c>
       <c r="AP195">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ195">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR195">
         <v>1.82</v>
@@ -41693,7 +41717,7 @@
         <v>225</v>
       </c>
       <c r="P196" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41977,7 +42001,7 @@
         <v>1.09</v>
       </c>
       <c r="AP197">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ197">
         <v>1.14</v>
@@ -42105,7 +42129,7 @@
         <v>226</v>
       </c>
       <c r="P198" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q198">
         <v>1.8</v>
@@ -42186,7 +42210,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ198">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR198">
         <v>2.36</v>
@@ -42392,7 +42416,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ199">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR199">
         <v>1.41</v>
@@ -42517,7 +42541,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q200">
         <v>3.25</v>
@@ -42723,7 +42747,7 @@
         <v>228</v>
       </c>
       <c r="P201" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43213,7 +43237,7 @@
         <v>0.55</v>
       </c>
       <c r="AP203">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ203">
         <v>0.5</v>
@@ -43419,10 +43443,10 @@
         <v>0.8</v>
       </c>
       <c r="AP204">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ204">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR204">
         <v>1.82</v>
@@ -43831,7 +43855,7 @@
         <v>1.1</v>
       </c>
       <c r="AP206">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ206">
         <v>1.08</v>
@@ -44037,10 +44061,10 @@
         <v>0.9</v>
       </c>
       <c r="AP207">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ207">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR207">
         <v>2.08</v>
@@ -44243,7 +44267,7 @@
         <v>1</v>
       </c>
       <c r="AP208">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ208">
         <v>1</v>
@@ -44371,7 +44395,7 @@
         <v>160</v>
       </c>
       <c r="P209" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q209">
         <v>2.6</v>
@@ -44449,7 +44473,7 @@
         <v>0.92</v>
       </c>
       <c r="AP209">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ209">
         <v>1</v>
@@ -44658,7 +44682,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ210">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR210">
         <v>1.55</v>
@@ -44783,7 +44807,7 @@
         <v>237</v>
       </c>
       <c r="P211" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q211">
         <v>4.75</v>
@@ -44861,10 +44885,10 @@
         <v>2</v>
       </c>
       <c r="AP211">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ211">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR211">
         <v>1.68</v>
@@ -44989,7 +45013,7 @@
         <v>128</v>
       </c>
       <c r="P212" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q212">
         <v>4.33</v>
@@ -45067,7 +45091,7 @@
         <v>1.25</v>
       </c>
       <c r="AP212">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ212">
         <v>1.14</v>
@@ -45276,7 +45300,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ213">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR213">
         <v>1.91</v>
@@ -45607,7 +45631,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45688,7 +45712,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ215">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR215">
         <v>1.42</v>
@@ -45891,7 +45915,7 @@
         <v>2.09</v>
       </c>
       <c r="AP216">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ216">
         <v>2.29</v>
@@ -46097,7 +46121,7 @@
         <v>1.09</v>
       </c>
       <c r="AP217">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ217">
         <v>0.86</v>
@@ -46512,7 +46536,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ219">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR219">
         <v>1.35</v>
@@ -46637,7 +46661,7 @@
         <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q220">
         <v>1.62</v>
@@ -46843,7 +46867,7 @@
         <v>242</v>
       </c>
       <c r="P221" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q221">
         <v>4.33</v>
@@ -46924,7 +46948,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ221">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AR221">
         <v>1.2</v>
@@ -47049,7 +47073,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q222">
         <v>5</v>
@@ -47255,7 +47279,7 @@
         <v>243</v>
       </c>
       <c r="P223" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q223">
         <v>2.75</v>
@@ -47539,7 +47563,7 @@
         <v>0.58</v>
       </c>
       <c r="AP224">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ224">
         <v>0.71</v>
@@ -47745,10 +47769,10 @@
         <v>0.58</v>
       </c>
       <c r="AP225">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AQ225">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR225">
         <v>1.36</v>
@@ -47954,7 +47978,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ226">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR226">
         <v>1.62</v>
@@ -48157,10 +48181,10 @@
         <v>0.67</v>
       </c>
       <c r="AP227">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ227">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR227">
         <v>1.66</v>
@@ -48285,7 +48309,7 @@
         <v>91</v>
       </c>
       <c r="P228" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q228">
         <v>8</v>
@@ -48363,10 +48387,10 @@
         <v>1.83</v>
       </c>
       <c r="AP228">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AQ228">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR228">
         <v>1.35</v>
@@ -48572,7 +48596,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ229">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR229">
         <v>1.69</v>
@@ -48775,7 +48799,7 @@
         <v>1</v>
       </c>
       <c r="AP230">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ230">
         <v>0.86</v>
@@ -48981,7 +49005,7 @@
         <v>1.08</v>
       </c>
       <c r="AP231">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ231">
         <v>1</v>
@@ -49109,7 +49133,7 @@
         <v>248</v>
       </c>
       <c r="P232" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49187,10 +49211,10 @@
         <v>1.67</v>
       </c>
       <c r="AP232">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ232">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR232">
         <v>2</v>
@@ -49315,7 +49339,7 @@
         <v>249</v>
       </c>
       <c r="P233" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q233">
         <v>2.5</v>
@@ -49393,7 +49417,7 @@
         <v>1.75</v>
       </c>
       <c r="AP233">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ233">
         <v>1.64</v>
@@ -49727,7 +49751,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q235">
         <v>2.88</v>
@@ -49933,7 +49957,7 @@
         <v>91</v>
       </c>
       <c r="P236" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q236">
         <v>3.75</v>
@@ -50345,7 +50369,7 @@
         <v>252</v>
       </c>
       <c r="P238" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q238">
         <v>3.75</v>
@@ -50757,7 +50781,7 @@
         <v>91</v>
       </c>
       <c r="P240" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51169,7 +51193,7 @@
         <v>255</v>
       </c>
       <c r="P242" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q242">
         <v>1.91</v>
@@ -51375,7 +51399,7 @@
         <v>256</v>
       </c>
       <c r="P243" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q243">
         <v>1.8</v>
@@ -51453,7 +51477,7 @@
         <v>0.46</v>
       </c>
       <c r="AP243">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ243">
         <v>0.5</v>
@@ -51944,6 +51968,1654 @@
       </c>
       <c r="BP245">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7466298</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45752.47916666666</v>
+      </c>
+      <c r="F246">
+        <v>28</v>
+      </c>
+      <c r="G246" t="s">
+        <v>82</v>
+      </c>
+      <c r="H246" t="s">
+        <v>71</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>1</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+      <c r="M246">
+        <v>1</v>
+      </c>
+      <c r="N246">
+        <v>1</v>
+      </c>
+      <c r="O246" t="s">
+        <v>91</v>
+      </c>
+      <c r="P246" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q246">
+        <v>3.1</v>
+      </c>
+      <c r="R246">
+        <v>2.2</v>
+      </c>
+      <c r="S246">
+        <v>3.25</v>
+      </c>
+      <c r="T246">
+        <v>1.36</v>
+      </c>
+      <c r="U246">
+        <v>3</v>
+      </c>
+      <c r="V246">
+        <v>2.63</v>
+      </c>
+      <c r="W246">
+        <v>1.44</v>
+      </c>
+      <c r="X246">
+        <v>7</v>
+      </c>
+      <c r="Y246">
+        <v>1.1</v>
+      </c>
+      <c r="Z246">
+        <v>2.6</v>
+      </c>
+      <c r="AA246">
+        <v>3.87</v>
+      </c>
+      <c r="AB246">
+        <v>2.55</v>
+      </c>
+      <c r="AC246">
+        <v>0</v>
+      </c>
+      <c r="AD246">
+        <v>0</v>
+      </c>
+      <c r="AE246">
+        <v>1.21</v>
+      </c>
+      <c r="AF246">
+        <v>3.74</v>
+      </c>
+      <c r="AG246">
+        <v>1.85</v>
+      </c>
+      <c r="AH246">
+        <v>1.96</v>
+      </c>
+      <c r="AI246">
+        <v>1.67</v>
+      </c>
+      <c r="AJ246">
+        <v>2.1</v>
+      </c>
+      <c r="AK246">
+        <v>1.47</v>
+      </c>
+      <c r="AL246">
+        <v>1.32</v>
+      </c>
+      <c r="AM246">
+        <v>1.57</v>
+      </c>
+      <c r="AN246">
+        <v>1.77</v>
+      </c>
+      <c r="AO246">
+        <v>1.77</v>
+      </c>
+      <c r="AP246">
+        <v>1.64</v>
+      </c>
+      <c r="AQ246">
+        <v>1.86</v>
+      </c>
+      <c r="AR246">
+        <v>1.83</v>
+      </c>
+      <c r="AS246">
+        <v>1.92</v>
+      </c>
+      <c r="AT246">
+        <v>3.75</v>
+      </c>
+      <c r="AU246">
+        <v>6</v>
+      </c>
+      <c r="AV246">
+        <v>4</v>
+      </c>
+      <c r="AW246">
+        <v>8</v>
+      </c>
+      <c r="AX246">
+        <v>6</v>
+      </c>
+      <c r="AY246">
+        <v>16</v>
+      </c>
+      <c r="AZ246">
+        <v>10</v>
+      </c>
+      <c r="BA246">
+        <v>5</v>
+      </c>
+      <c r="BB246">
+        <v>3</v>
+      </c>
+      <c r="BC246">
+        <v>8</v>
+      </c>
+      <c r="BD246">
+        <v>1.85</v>
+      </c>
+      <c r="BE246">
+        <v>6.55</v>
+      </c>
+      <c r="BF246">
+        <v>2.5</v>
+      </c>
+      <c r="BG246">
+        <v>1.25</v>
+      </c>
+      <c r="BH246">
+        <v>3.28</v>
+      </c>
+      <c r="BI246">
+        <v>1.53</v>
+      </c>
+      <c r="BJ246">
+        <v>2.38</v>
+      </c>
+      <c r="BK246">
+        <v>1.94</v>
+      </c>
+      <c r="BL246">
+        <v>1.85</v>
+      </c>
+      <c r="BM246">
+        <v>2.4</v>
+      </c>
+      <c r="BN246">
+        <v>1.52</v>
+      </c>
+      <c r="BO246">
+        <v>3.2</v>
+      </c>
+      <c r="BP246">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7466300</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45752.57291666666</v>
+      </c>
+      <c r="F247">
+        <v>28</v>
+      </c>
+      <c r="G247" t="s">
+        <v>81</v>
+      </c>
+      <c r="H247" t="s">
+        <v>79</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>1</v>
+      </c>
+      <c r="M247">
+        <v>1</v>
+      </c>
+      <c r="N247">
+        <v>2</v>
+      </c>
+      <c r="O247" t="s">
+        <v>175</v>
+      </c>
+      <c r="P247" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q247">
+        <v>1.91</v>
+      </c>
+      <c r="R247">
+        <v>2.5</v>
+      </c>
+      <c r="S247">
+        <v>7</v>
+      </c>
+      <c r="T247">
+        <v>1.3</v>
+      </c>
+      <c r="U247">
+        <v>3.4</v>
+      </c>
+      <c r="V247">
+        <v>2.5</v>
+      </c>
+      <c r="W247">
+        <v>1.5</v>
+      </c>
+      <c r="X247">
+        <v>6</v>
+      </c>
+      <c r="Y247">
+        <v>1.13</v>
+      </c>
+      <c r="Z247">
+        <v>1.32</v>
+      </c>
+      <c r="AA247">
+        <v>6</v>
+      </c>
+      <c r="AB247">
+        <v>8.9</v>
+      </c>
+      <c r="AC247">
+        <v>0</v>
+      </c>
+      <c r="AD247">
+        <v>0</v>
+      </c>
+      <c r="AE247">
+        <v>1.23</v>
+      </c>
+      <c r="AF247">
+        <v>4.4</v>
+      </c>
+      <c r="AG247">
+        <v>1.77</v>
+      </c>
+      <c r="AH247">
+        <v>1.98</v>
+      </c>
+      <c r="AI247">
+        <v>1.95</v>
+      </c>
+      <c r="AJ247">
+        <v>1.8</v>
+      </c>
+      <c r="AK247">
+        <v>1.12</v>
+      </c>
+      <c r="AL247">
+        <v>1.19</v>
+      </c>
+      <c r="AM247">
+        <v>3.08</v>
+      </c>
+      <c r="AN247">
+        <v>2.31</v>
+      </c>
+      <c r="AO247">
+        <v>1</v>
+      </c>
+      <c r="AP247">
+        <v>2.21</v>
+      </c>
+      <c r="AQ247">
+        <v>1</v>
+      </c>
+      <c r="AR247">
+        <v>1.91</v>
+      </c>
+      <c r="AS247">
+        <v>1.07</v>
+      </c>
+      <c r="AT247">
+        <v>2.98</v>
+      </c>
+      <c r="AU247">
+        <v>4</v>
+      </c>
+      <c r="AV247">
+        <v>2</v>
+      </c>
+      <c r="AW247">
+        <v>8</v>
+      </c>
+      <c r="AX247">
+        <v>7</v>
+      </c>
+      <c r="AY247">
+        <v>14</v>
+      </c>
+      <c r="AZ247">
+        <v>9</v>
+      </c>
+      <c r="BA247">
+        <v>7</v>
+      </c>
+      <c r="BB247">
+        <v>3</v>
+      </c>
+      <c r="BC247">
+        <v>10</v>
+      </c>
+      <c r="BD247">
+        <v>1.19</v>
+      </c>
+      <c r="BE247">
+        <v>11.5</v>
+      </c>
+      <c r="BF247">
+        <v>5.9</v>
+      </c>
+      <c r="BG247">
+        <v>1.26</v>
+      </c>
+      <c r="BH247">
+        <v>3.22</v>
+      </c>
+      <c r="BI247">
+        <v>1.59</v>
+      </c>
+      <c r="BJ247">
+        <v>2.26</v>
+      </c>
+      <c r="BK247">
+        <v>1.97</v>
+      </c>
+      <c r="BL247">
+        <v>1.83</v>
+      </c>
+      <c r="BM247">
+        <v>2.43</v>
+      </c>
+      <c r="BN247">
+        <v>1.51</v>
+      </c>
+      <c r="BO247">
+        <v>3.2</v>
+      </c>
+      <c r="BP247">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7466299</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45752.625</v>
+      </c>
+      <c r="F248">
+        <v>28</v>
+      </c>
+      <c r="G248" t="s">
+        <v>70</v>
+      </c>
+      <c r="H248" t="s">
+        <v>74</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248">
+        <v>2</v>
+      </c>
+      <c r="K248">
+        <v>3</v>
+      </c>
+      <c r="L248">
+        <v>1</v>
+      </c>
+      <c r="M248">
+        <v>3</v>
+      </c>
+      <c r="N248">
+        <v>4</v>
+      </c>
+      <c r="O248" t="s">
+        <v>106</v>
+      </c>
+      <c r="P248" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q248">
+        <v>6.5</v>
+      </c>
+      <c r="R248">
+        <v>2.6</v>
+      </c>
+      <c r="S248">
+        <v>1.91</v>
+      </c>
+      <c r="T248">
+        <v>1.29</v>
+      </c>
+      <c r="U248">
+        <v>3.5</v>
+      </c>
+      <c r="V248">
+        <v>2.25</v>
+      </c>
+      <c r="W248">
+        <v>1.57</v>
+      </c>
+      <c r="X248">
+        <v>5.5</v>
+      </c>
+      <c r="Y248">
+        <v>1.14</v>
+      </c>
+      <c r="Z248">
+        <v>8.4</v>
+      </c>
+      <c r="AA248">
+        <v>6.2</v>
+      </c>
+      <c r="AB248">
+        <v>1.33</v>
+      </c>
+      <c r="AC248">
+        <v>0</v>
+      </c>
+      <c r="AD248">
+        <v>0</v>
+      </c>
+      <c r="AE248">
+        <v>1.15</v>
+      </c>
+      <c r="AF248">
+        <v>4.25</v>
+      </c>
+      <c r="AG248">
+        <v>1.53</v>
+      </c>
+      <c r="AH248">
+        <v>2.4</v>
+      </c>
+      <c r="AI248">
+        <v>1.75</v>
+      </c>
+      <c r="AJ248">
+        <v>2</v>
+      </c>
+      <c r="AK248">
+        <v>2.92</v>
+      </c>
+      <c r="AL248">
+        <v>1.23</v>
+      </c>
+      <c r="AM248">
+        <v>1.11</v>
+      </c>
+      <c r="AN248">
+        <v>1.77</v>
+      </c>
+      <c r="AO248">
+        <v>1.92</v>
+      </c>
+      <c r="AP248">
+        <v>1.64</v>
+      </c>
+      <c r="AQ248">
+        <v>2</v>
+      </c>
+      <c r="AR248">
+        <v>1.41</v>
+      </c>
+      <c r="AS248">
+        <v>1.91</v>
+      </c>
+      <c r="AT248">
+        <v>3.32</v>
+      </c>
+      <c r="AU248">
+        <v>4</v>
+      </c>
+      <c r="AV248">
+        <v>6</v>
+      </c>
+      <c r="AW248">
+        <v>11</v>
+      </c>
+      <c r="AX248">
+        <v>11</v>
+      </c>
+      <c r="AY248">
+        <v>17</v>
+      </c>
+      <c r="AZ248">
+        <v>20</v>
+      </c>
+      <c r="BA248">
+        <v>4</v>
+      </c>
+      <c r="BB248">
+        <v>5</v>
+      </c>
+      <c r="BC248">
+        <v>9</v>
+      </c>
+      <c r="BD248">
+        <v>4.65</v>
+      </c>
+      <c r="BE248">
+        <v>10.25</v>
+      </c>
+      <c r="BF248">
+        <v>1.28</v>
+      </c>
+      <c r="BG248">
+        <v>1.24</v>
+      </c>
+      <c r="BH248">
+        <v>3.34</v>
+      </c>
+      <c r="BI248">
+        <v>1.5</v>
+      </c>
+      <c r="BJ248">
+        <v>2.45</v>
+      </c>
+      <c r="BK248">
+        <v>1.86</v>
+      </c>
+      <c r="BL248">
+        <v>1.93</v>
+      </c>
+      <c r="BM248">
+        <v>2.28</v>
+      </c>
+      <c r="BN248">
+        <v>1.58</v>
+      </c>
+      <c r="BO248">
+        <v>3.08</v>
+      </c>
+      <c r="BP248">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7466297</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45752.66666666666</v>
+      </c>
+      <c r="F249">
+        <v>28</v>
+      </c>
+      <c r="G249" t="s">
+        <v>73</v>
+      </c>
+      <c r="H249" t="s">
+        <v>85</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>2</v>
+      </c>
+      <c r="K249">
+        <v>2</v>
+      </c>
+      <c r="L249">
+        <v>2</v>
+      </c>
+      <c r="M249">
+        <v>2</v>
+      </c>
+      <c r="N249">
+        <v>4</v>
+      </c>
+      <c r="O249" t="s">
+        <v>259</v>
+      </c>
+      <c r="P249" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q249">
+        <v>2.88</v>
+      </c>
+      <c r="R249">
+        <v>2.1</v>
+      </c>
+      <c r="S249">
+        <v>3.75</v>
+      </c>
+      <c r="T249">
+        <v>1.4</v>
+      </c>
+      <c r="U249">
+        <v>2.75</v>
+      </c>
+      <c r="V249">
+        <v>3</v>
+      </c>
+      <c r="W249">
+        <v>1.36</v>
+      </c>
+      <c r="X249">
+        <v>8</v>
+      </c>
+      <c r="Y249">
+        <v>1.08</v>
+      </c>
+      <c r="Z249">
+        <v>2.55</v>
+      </c>
+      <c r="AA249">
+        <v>3.4</v>
+      </c>
+      <c r="AB249">
+        <v>2.87</v>
+      </c>
+      <c r="AC249">
+        <v>1.01</v>
+      </c>
+      <c r="AD249">
+        <v>8.4</v>
+      </c>
+      <c r="AE249">
+        <v>1.28</v>
+      </c>
+      <c r="AF249">
+        <v>3.2</v>
+      </c>
+      <c r="AG249">
+        <v>2.03</v>
+      </c>
+      <c r="AH249">
+        <v>1.79</v>
+      </c>
+      <c r="AI249">
+        <v>1.75</v>
+      </c>
+      <c r="AJ249">
+        <v>2</v>
+      </c>
+      <c r="AK249">
+        <v>1.4</v>
+      </c>
+      <c r="AL249">
+        <v>1.34</v>
+      </c>
+      <c r="AM249">
+        <v>1.63</v>
+      </c>
+      <c r="AN249">
+        <v>0.62</v>
+      </c>
+      <c r="AO249">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP249">
+        <v>0.64</v>
+      </c>
+      <c r="AQ249">
+        <v>0.71</v>
+      </c>
+      <c r="AR249">
+        <v>1.41</v>
+      </c>
+      <c r="AS249">
+        <v>1.03</v>
+      </c>
+      <c r="AT249">
+        <v>2.44</v>
+      </c>
+      <c r="AU249">
+        <v>6</v>
+      </c>
+      <c r="AV249">
+        <v>7</v>
+      </c>
+      <c r="AW249">
+        <v>19</v>
+      </c>
+      <c r="AX249">
+        <v>5</v>
+      </c>
+      <c r="AY249">
+        <v>29</v>
+      </c>
+      <c r="AZ249">
+        <v>12</v>
+      </c>
+      <c r="BA249">
+        <v>7</v>
+      </c>
+      <c r="BB249">
+        <v>4</v>
+      </c>
+      <c r="BC249">
+        <v>11</v>
+      </c>
+      <c r="BD249">
+        <v>1.76</v>
+      </c>
+      <c r="BE249">
+        <v>8.5</v>
+      </c>
+      <c r="BF249">
+        <v>2.45</v>
+      </c>
+      <c r="BG249">
+        <v>1.22</v>
+      </c>
+      <c r="BH249">
+        <v>3.48</v>
+      </c>
+      <c r="BI249">
+        <v>1.49</v>
+      </c>
+      <c r="BJ249">
+        <v>2.48</v>
+      </c>
+      <c r="BK249">
+        <v>1.87</v>
+      </c>
+      <c r="BL249">
+        <v>1.93</v>
+      </c>
+      <c r="BM249">
+        <v>2.3</v>
+      </c>
+      <c r="BN249">
+        <v>1.57</v>
+      </c>
+      <c r="BO249">
+        <v>3.05</v>
+      </c>
+      <c r="BP249">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7466302</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45753.30208333334</v>
+      </c>
+      <c r="F250">
+        <v>28</v>
+      </c>
+      <c r="G250" t="s">
+        <v>83</v>
+      </c>
+      <c r="H250" t="s">
+        <v>84</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>0</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>0</v>
+      </c>
+      <c r="O250" t="s">
+        <v>91</v>
+      </c>
+      <c r="P250" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q250">
+        <v>2.88</v>
+      </c>
+      <c r="R250">
+        <v>2.25</v>
+      </c>
+      <c r="S250">
+        <v>3.4</v>
+      </c>
+      <c r="T250">
+        <v>1.33</v>
+      </c>
+      <c r="U250">
+        <v>3.25</v>
+      </c>
+      <c r="V250">
+        <v>2.63</v>
+      </c>
+      <c r="W250">
+        <v>1.44</v>
+      </c>
+      <c r="X250">
+        <v>6.5</v>
+      </c>
+      <c r="Y250">
+        <v>1.11</v>
+      </c>
+      <c r="Z250">
+        <v>2.14</v>
+      </c>
+      <c r="AA250">
+        <v>3.94</v>
+      </c>
+      <c r="AB250">
+        <v>3.18</v>
+      </c>
+      <c r="AC250">
+        <v>1.04</v>
+      </c>
+      <c r="AD250">
+        <v>10</v>
+      </c>
+      <c r="AE250">
+        <v>1.22</v>
+      </c>
+      <c r="AF250">
+        <v>4</v>
+      </c>
+      <c r="AG250">
+        <v>1.6</v>
+      </c>
+      <c r="AH250">
+        <v>2.25</v>
+      </c>
+      <c r="AI250">
+        <v>1.62</v>
+      </c>
+      <c r="AJ250">
+        <v>2.2</v>
+      </c>
+      <c r="AK250">
+        <v>1.39</v>
+      </c>
+      <c r="AL250">
+        <v>1.27</v>
+      </c>
+      <c r="AM250">
+        <v>1.61</v>
+      </c>
+      <c r="AN250">
+        <v>0.85</v>
+      </c>
+      <c r="AO250">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP250">
+        <v>0.86</v>
+      </c>
+      <c r="AQ250">
+        <v>0.71</v>
+      </c>
+      <c r="AR250">
+        <v>1.3</v>
+      </c>
+      <c r="AS250">
+        <v>0.98</v>
+      </c>
+      <c r="AT250">
+        <v>2.28</v>
+      </c>
+      <c r="AU250">
+        <v>4</v>
+      </c>
+      <c r="AV250">
+        <v>2</v>
+      </c>
+      <c r="AW250">
+        <v>8</v>
+      </c>
+      <c r="AX250">
+        <v>7</v>
+      </c>
+      <c r="AY250">
+        <v>14</v>
+      </c>
+      <c r="AZ250">
+        <v>14</v>
+      </c>
+      <c r="BA250">
+        <v>6</v>
+      </c>
+      <c r="BB250">
+        <v>9</v>
+      </c>
+      <c r="BC250">
+        <v>15</v>
+      </c>
+      <c r="BD250">
+        <v>1.88</v>
+      </c>
+      <c r="BE250">
+        <v>6.75</v>
+      </c>
+      <c r="BF250">
+        <v>2.1</v>
+      </c>
+      <c r="BG250">
+        <v>1.19</v>
+      </c>
+      <c r="BH250">
+        <v>4.1</v>
+      </c>
+      <c r="BI250">
+        <v>1.34</v>
+      </c>
+      <c r="BJ250">
+        <v>2.9</v>
+      </c>
+      <c r="BK250">
+        <v>1.57</v>
+      </c>
+      <c r="BL250">
+        <v>2.23</v>
+      </c>
+      <c r="BM250">
+        <v>1.91</v>
+      </c>
+      <c r="BN250">
+        <v>1.78</v>
+      </c>
+      <c r="BO250">
+        <v>2.38</v>
+      </c>
+      <c r="BP250">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7466301</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45753.39583333334</v>
+      </c>
+      <c r="F251">
+        <v>28</v>
+      </c>
+      <c r="G251" t="s">
+        <v>77</v>
+      </c>
+      <c r="H251" t="s">
+        <v>76</v>
+      </c>
+      <c r="I251">
+        <v>2</v>
+      </c>
+      <c r="J251">
+        <v>2</v>
+      </c>
+      <c r="K251">
+        <v>4</v>
+      </c>
+      <c r="L251">
+        <v>2</v>
+      </c>
+      <c r="M251">
+        <v>2</v>
+      </c>
+      <c r="N251">
+        <v>4</v>
+      </c>
+      <c r="O251" t="s">
+        <v>260</v>
+      </c>
+      <c r="P251" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q251">
+        <v>2.63</v>
+      </c>
+      <c r="R251">
+        <v>2.3</v>
+      </c>
+      <c r="S251">
+        <v>3.75</v>
+      </c>
+      <c r="T251">
+        <v>1.3</v>
+      </c>
+      <c r="U251">
+        <v>3.4</v>
+      </c>
+      <c r="V251">
+        <v>2.5</v>
+      </c>
+      <c r="W251">
+        <v>1.5</v>
+      </c>
+      <c r="X251">
+        <v>6</v>
+      </c>
+      <c r="Y251">
+        <v>1.13</v>
+      </c>
+      <c r="Z251">
+        <v>2.09</v>
+      </c>
+      <c r="AA251">
+        <v>3.8</v>
+      </c>
+      <c r="AB251">
+        <v>3.41</v>
+      </c>
+      <c r="AC251">
+        <v>1.04</v>
+      </c>
+      <c r="AD251">
+        <v>10</v>
+      </c>
+      <c r="AE251">
+        <v>1.2</v>
+      </c>
+      <c r="AF251">
+        <v>4.33</v>
+      </c>
+      <c r="AG251">
+        <v>1.62</v>
+      </c>
+      <c r="AH251">
+        <v>2.22</v>
+      </c>
+      <c r="AI251">
+        <v>1.57</v>
+      </c>
+      <c r="AJ251">
+        <v>2.25</v>
+      </c>
+      <c r="AK251">
+        <v>1.31</v>
+      </c>
+      <c r="AL251">
+        <v>1.26</v>
+      </c>
+      <c r="AM251">
+        <v>1.75</v>
+      </c>
+      <c r="AN251">
+        <v>2.14</v>
+      </c>
+      <c r="AO251">
+        <v>2.23</v>
+      </c>
+      <c r="AP251">
+        <v>2.07</v>
+      </c>
+      <c r="AQ251">
+        <v>2.14</v>
+      </c>
+      <c r="AR251">
+        <v>1.71</v>
+      </c>
+      <c r="AS251">
+        <v>1.42</v>
+      </c>
+      <c r="AT251">
+        <v>3.13</v>
+      </c>
+      <c r="AU251">
+        <v>7</v>
+      </c>
+      <c r="AV251">
+        <v>4</v>
+      </c>
+      <c r="AW251">
+        <v>6</v>
+      </c>
+      <c r="AX251">
+        <v>10</v>
+      </c>
+      <c r="AY251">
+        <v>16</v>
+      </c>
+      <c r="AZ251">
+        <v>18</v>
+      </c>
+      <c r="BA251">
+        <v>1</v>
+      </c>
+      <c r="BB251">
+        <v>5</v>
+      </c>
+      <c r="BC251">
+        <v>6</v>
+      </c>
+      <c r="BD251">
+        <v>1.7</v>
+      </c>
+      <c r="BE251">
+        <v>6.5</v>
+      </c>
+      <c r="BF251">
+        <v>2.4</v>
+      </c>
+      <c r="BG251">
+        <v>1.21</v>
+      </c>
+      <c r="BH251">
+        <v>3.8</v>
+      </c>
+      <c r="BI251">
+        <v>1.38</v>
+      </c>
+      <c r="BJ251">
+        <v>2.75</v>
+      </c>
+      <c r="BK251">
+        <v>1.64</v>
+      </c>
+      <c r="BL251">
+        <v>2.1</v>
+      </c>
+      <c r="BM251">
+        <v>2</v>
+      </c>
+      <c r="BN251">
+        <v>1.71</v>
+      </c>
+      <c r="BO251">
+        <v>2.55</v>
+      </c>
+      <c r="BP251">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7466304</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45753.39583333334</v>
+      </c>
+      <c r="F252">
+        <v>28</v>
+      </c>
+      <c r="G252" t="s">
+        <v>75</v>
+      </c>
+      <c r="H252" t="s">
+        <v>72</v>
+      </c>
+      <c r="I252">
+        <v>1</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>2</v>
+      </c>
+      <c r="O252" t="s">
+        <v>261</v>
+      </c>
+      <c r="P252" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q252">
+        <v>2.63</v>
+      </c>
+      <c r="R252">
+        <v>2.2</v>
+      </c>
+      <c r="S252">
+        <v>4</v>
+      </c>
+      <c r="T252">
+        <v>1.4</v>
+      </c>
+      <c r="U252">
+        <v>2.75</v>
+      </c>
+      <c r="V252">
+        <v>3</v>
+      </c>
+      <c r="W252">
+        <v>1.36</v>
+      </c>
+      <c r="X252">
+        <v>8</v>
+      </c>
+      <c r="Y252">
+        <v>1.08</v>
+      </c>
+      <c r="Z252">
+        <v>2.04</v>
+      </c>
+      <c r="AA252">
+        <v>3.55</v>
+      </c>
+      <c r="AB252">
+        <v>3.82</v>
+      </c>
+      <c r="AC252">
+        <v>1.05</v>
+      </c>
+      <c r="AD252">
+        <v>9.5</v>
+      </c>
+      <c r="AE252">
+        <v>1.28</v>
+      </c>
+      <c r="AF252">
+        <v>3.55</v>
+      </c>
+      <c r="AG252">
+        <v>1.92</v>
+      </c>
+      <c r="AH252">
+        <v>1.89</v>
+      </c>
+      <c r="AI252">
+        <v>1.8</v>
+      </c>
+      <c r="AJ252">
+        <v>1.95</v>
+      </c>
+      <c r="AK252">
+        <v>1.29</v>
+      </c>
+      <c r="AL252">
+        <v>1.28</v>
+      </c>
+      <c r="AM252">
+        <v>1.75</v>
+      </c>
+      <c r="AN252">
+        <v>0.92</v>
+      </c>
+      <c r="AO252">
+        <v>1</v>
+      </c>
+      <c r="AP252">
+        <v>1.07</v>
+      </c>
+      <c r="AQ252">
+        <v>0.93</v>
+      </c>
+      <c r="AR252">
+        <v>1.63</v>
+      </c>
+      <c r="AS252">
+        <v>1.31</v>
+      </c>
+      <c r="AT252">
+        <v>2.94</v>
+      </c>
+      <c r="AU252">
+        <v>5</v>
+      </c>
+      <c r="AV252">
+        <v>2</v>
+      </c>
+      <c r="AW252">
+        <v>9</v>
+      </c>
+      <c r="AX252">
+        <v>6</v>
+      </c>
+      <c r="AY252">
+        <v>14</v>
+      </c>
+      <c r="AZ252">
+        <v>9</v>
+      </c>
+      <c r="BA252">
+        <v>3</v>
+      </c>
+      <c r="BB252">
+        <v>2</v>
+      </c>
+      <c r="BC252">
+        <v>5</v>
+      </c>
+      <c r="BD252">
+        <v>1.58</v>
+      </c>
+      <c r="BE252">
+        <v>6.75</v>
+      </c>
+      <c r="BF252">
+        <v>2.55</v>
+      </c>
+      <c r="BG252">
+        <v>1.18</v>
+      </c>
+      <c r="BH252">
+        <v>4.1</v>
+      </c>
+      <c r="BI252">
+        <v>1.33</v>
+      </c>
+      <c r="BJ252">
+        <v>3</v>
+      </c>
+      <c r="BK252">
+        <v>1.54</v>
+      </c>
+      <c r="BL252">
+        <v>2.3</v>
+      </c>
+      <c r="BM252">
+        <v>1.88</v>
+      </c>
+      <c r="BN252">
+        <v>1.81</v>
+      </c>
+      <c r="BO252">
+        <v>2.33</v>
+      </c>
+      <c r="BP252">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7466296</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45753.48958333334</v>
+      </c>
+      <c r="F253">
+        <v>28</v>
+      </c>
+      <c r="G253" t="s">
+        <v>78</v>
+      </c>
+      <c r="H253" t="s">
+        <v>87</v>
+      </c>
+      <c r="I253">
+        <v>2</v>
+      </c>
+      <c r="J253">
+        <v>1</v>
+      </c>
+      <c r="K253">
+        <v>3</v>
+      </c>
+      <c r="L253">
+        <v>3</v>
+      </c>
+      <c r="M253">
+        <v>1</v>
+      </c>
+      <c r="N253">
+        <v>4</v>
+      </c>
+      <c r="O253" t="s">
+        <v>262</v>
+      </c>
+      <c r="P253" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q253">
+        <v>1.67</v>
+      </c>
+      <c r="R253">
+        <v>2.75</v>
+      </c>
+      <c r="S253">
+        <v>8.5</v>
+      </c>
+      <c r="T253">
+        <v>1.25</v>
+      </c>
+      <c r="U253">
+        <v>3.75</v>
+      </c>
+      <c r="V253">
+        <v>2.1</v>
+      </c>
+      <c r="W253">
+        <v>1.67</v>
+      </c>
+      <c r="X253">
+        <v>4.5</v>
+      </c>
+      <c r="Y253">
+        <v>1.18</v>
+      </c>
+      <c r="Z253">
+        <v>1.28</v>
+      </c>
+      <c r="AA253">
+        <v>6.4</v>
+      </c>
+      <c r="AB253">
+        <v>10</v>
+      </c>
+      <c r="AC253">
+        <v>1.03</v>
+      </c>
+      <c r="AD253">
+        <v>11</v>
+      </c>
+      <c r="AE253">
+        <v>1.14</v>
+      </c>
+      <c r="AF253">
+        <v>5.5</v>
+      </c>
+      <c r="AG253">
+        <v>1.58</v>
+      </c>
+      <c r="AH253">
+        <v>2.18</v>
+      </c>
+      <c r="AI253">
+        <v>1.91</v>
+      </c>
+      <c r="AJ253">
+        <v>1.91</v>
+      </c>
+      <c r="AK253">
+        <v>1.05</v>
+      </c>
+      <c r="AL253">
+        <v>1.12</v>
+      </c>
+      <c r="AM253">
+        <v>3.8</v>
+      </c>
+      <c r="AN253">
+        <v>2.69</v>
+      </c>
+      <c r="AO253">
+        <v>0.62</v>
+      </c>
+      <c r="AP253">
+        <v>2.71</v>
+      </c>
+      <c r="AQ253">
+        <v>0.57</v>
+      </c>
+      <c r="AR253">
+        <v>1.82</v>
+      </c>
+      <c r="AS253">
+        <v>1.18</v>
+      </c>
+      <c r="AT253">
+        <v>3</v>
+      </c>
+      <c r="AU253">
+        <v>5</v>
+      </c>
+      <c r="AV253">
+        <v>4</v>
+      </c>
+      <c r="AW253">
+        <v>6</v>
+      </c>
+      <c r="AX253">
+        <v>5</v>
+      </c>
+      <c r="AY253">
+        <v>12</v>
+      </c>
+      <c r="AZ253">
+        <v>9</v>
+      </c>
+      <c r="BA253">
+        <v>9</v>
+      </c>
+      <c r="BB253">
+        <v>0</v>
+      </c>
+      <c r="BC253">
+        <v>9</v>
+      </c>
+      <c r="BD253">
+        <v>1.2</v>
+      </c>
+      <c r="BE253">
+        <v>8.5</v>
+      </c>
+      <c r="BF253">
+        <v>4.9</v>
+      </c>
+      <c r="BG253">
+        <v>1.26</v>
+      </c>
+      <c r="BH253">
+        <v>3.4</v>
+      </c>
+      <c r="BI253">
+        <v>1.47</v>
+      </c>
+      <c r="BJ253">
+        <v>2.48</v>
+      </c>
+      <c r="BK253">
+        <v>1.75</v>
+      </c>
+      <c r="BL253">
+        <v>1.95</v>
+      </c>
+      <c r="BM253">
+        <v>2.18</v>
+      </c>
+      <c r="BN253">
+        <v>1.58</v>
+      </c>
+      <c r="BO253">
+        <v>2.8</v>
+      </c>
+      <c r="BP253">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -52113,19 +52113,19 @@
         <v>6</v>
       </c>
       <c r="AV246">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW246">
+        <v>1</v>
+      </c>
+      <c r="AX246">
         <v>8</v>
       </c>
-      <c r="AX246">
-        <v>6</v>
-      </c>
       <c r="AY246">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ246">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA246">
         <v>5</v>
@@ -52322,16 +52322,16 @@
         <v>2</v>
       </c>
       <c r="AW247">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX247">
+        <v>4</v>
+      </c>
+      <c r="AY247">
+        <v>13</v>
+      </c>
+      <c r="AZ247">
         <v>7</v>
-      </c>
-      <c r="AY247">
-        <v>14</v>
-      </c>
-      <c r="AZ247">
-        <v>9</v>
       </c>
       <c r="BA247">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eredivisie_20242025.xlsx
@@ -2026,7 +2026,7 @@
         <v>4</v>
       </c>
       <c r="AY2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ2">
         <v>8</v>
@@ -2232,10 +2232,10 @@
         <v>0</v>
       </c>
       <c r="AY3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA3">
         <v>14</v>
@@ -2438,10 +2438,10 @@
         <v>8</v>
       </c>
       <c r="AY4">
+        <v>8</v>
+      </c>
+      <c r="AZ4">
         <v>14</v>
-      </c>
-      <c r="AZ4">
-        <v>16</v>
       </c>
       <c r="BA4">
         <v>7</v>
@@ -2644,7 +2644,7 @@
         <v>5</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ5">
         <v>10</v>
@@ -2850,10 +2850,10 @@
         <v>4</v>
       </c>
       <c r="AY6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA6">
         <v>7</v>
@@ -3056,10 +3056,10 @@
         <v>5</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA7">
         <v>3</v>
@@ -3262,10 +3262,10 @@
         <v>3</v>
       </c>
       <c r="AY8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AZ8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA8">
         <v>2</v>
@@ -3468,10 +3468,10 @@
         <v>3</v>
       </c>
       <c r="AY9">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA9">
         <v>6</v>
@@ -3674,10 +3674,10 @@
         <v>3</v>
       </c>
       <c r="AY10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3880,10 +3880,10 @@
         <v>2</v>
       </c>
       <c r="AY11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA11">
         <v>9</v>
@@ -4086,7 +4086,7 @@
         <v>2</v>
       </c>
       <c r="AY12">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ12">
         <v>7</v>
@@ -4292,10 +4292,10 @@
         <v>7</v>
       </c>
       <c r="AY13">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -4498,10 +4498,10 @@
         <v>6</v>
       </c>
       <c r="AY14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA14">
         <v>4</v>
@@ -4704,10 +4704,10 @@
         <v>3</v>
       </c>
       <c r="AY15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA15">
         <v>7</v>
@@ -4910,10 +4910,10 @@
         <v>10</v>
       </c>
       <c r="AY16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ16">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="BA16">
         <v>2</v>
@@ -5116,10 +5116,10 @@
         <v>4</v>
       </c>
       <c r="AY17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ17">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA17">
         <v>1</v>
@@ -5322,10 +5322,10 @@
         <v>9</v>
       </c>
       <c r="AY18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA18">
         <v>4</v>
@@ -5528,10 +5528,10 @@
         <v>4</v>
       </c>
       <c r="AY19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA19">
         <v>1</v>
@@ -5734,10 +5734,10 @@
         <v>4</v>
       </c>
       <c r="AY20">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA20">
         <v>6</v>
@@ -5940,10 +5940,10 @@
         <v>7</v>
       </c>
       <c r="AY21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ21">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA21">
         <v>1</v>
@@ -6146,10 +6146,10 @@
         <v>4</v>
       </c>
       <c r="AY22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA22">
         <v>4</v>
@@ -6352,10 +6352,10 @@
         <v>5</v>
       </c>
       <c r="AY23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA23">
         <v>2</v>
@@ -6558,10 +6558,10 @@
         <v>6</v>
       </c>
       <c r="AY24">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA24">
         <v>8</v>
@@ -6764,10 +6764,10 @@
         <v>8</v>
       </c>
       <c r="AY25">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ25">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA25">
         <v>6</v>
@@ -6970,10 +6970,10 @@
         <v>4</v>
       </c>
       <c r="AY26">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA26">
         <v>7</v>
@@ -7176,10 +7176,10 @@
         <v>13</v>
       </c>
       <c r="AY27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AZ27">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA27">
         <v>3</v>
@@ -7382,7 +7382,7 @@
         <v>6</v>
       </c>
       <c r="AY28">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ28">
         <v>9</v>
@@ -7588,10 +7588,10 @@
         <v>3</v>
       </c>
       <c r="AY29">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ29">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA29">
         <v>4</v>
@@ -7794,10 +7794,10 @@
         <v>7</v>
       </c>
       <c r="AY30">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ30">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA30">
         <v>3</v>
@@ -8000,10 +8000,10 @@
         <v>4</v>
       </c>
       <c r="AY31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ31">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA31">
         <v>4</v>
@@ -8206,10 +8206,10 @@
         <v>7</v>
       </c>
       <c r="AY32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ32">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA32">
         <v>5</v>
@@ -8412,10 +8412,10 @@
         <v>3</v>
       </c>
       <c r="AY33">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AZ33">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA33">
         <v>4</v>
@@ -8618,10 +8618,10 @@
         <v>2</v>
       </c>
       <c r="AY34">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA34">
         <v>5</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AY35">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AZ35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA35">
         <v>15</v>
@@ -9030,10 +9030,10 @@
         <v>1</v>
       </c>
       <c r="AY36">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ36">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA36">
         <v>8</v>
@@ -9236,10 +9236,10 @@
         <v>3</v>
       </c>
       <c r="AY37">
+        <v>10</v>
+      </c>
+      <c r="AZ37">
         <v>12</v>
-      </c>
-      <c r="AZ37">
-        <v>16</v>
       </c>
       <c r="BA37">
         <v>5</v>
@@ -9442,10 +9442,10 @@
         <v>5</v>
       </c>
       <c r="AY38">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ38">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA38">
         <v>3</v>
@@ -9648,10 +9648,10 @@
         <v>7</v>
       </c>
       <c r="AY39">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ39">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA39">
         <v>5</v>
@@ -9854,10 +9854,10 @@
         <v>9</v>
       </c>
       <c r="AY40">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ40">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA40">
         <v>5</v>
@@ -10060,10 +10060,10 @@
         <v>3</v>
       </c>
       <c r="AY41">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ41">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA41">
         <v>4</v>
@@ -10266,10 +10266,10 @@
         <v>3</v>
       </c>
       <c r="AY42">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AZ42">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA42">
         <v>10</v>
@@ -10472,10 +10472,10 @@
         <v>3</v>
       </c>
       <c r="AY43">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ43">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA43">
         <v>6</v>
@@ -10678,7 +10678,7 @@
         <v>3</v>
       </c>
       <c r="AY44">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AZ44">
         <v>5</v>
@@ -10884,10 +10884,10 @@
         <v>6</v>
       </c>
       <c r="AY45">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AZ45">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA45">
         <v>10</v>
@@ -11090,10 +11090,10 @@
         <v>3</v>
       </c>
       <c r="AY46">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AZ46">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA46">
         <v>7</v>
@@ -11296,10 +11296,10 @@
         <v>6</v>
       </c>
       <c r="AY47">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AZ47">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA47">
         <v>6</v>
@@ -11502,10 +11502,10 @@
         <v>3</v>
       </c>
       <c r="AY48">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ48">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA48">
         <v>7</v>
@@ -11708,10 +11708,10 @@
         <v>5</v>
       </c>
       <c r="AY49">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ49">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA49">
         <v>7</v>
@@ -11914,7 +11914,7 @@
         <v>1</v>
       </c>
       <c r="AY50">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ50">
         <v>3</v>
@@ -12120,10 +12120,10 @@
         <v>4</v>
       </c>
       <c r="AY51">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ51">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA51">
         <v>7</v>
@@ -12326,10 +12326,10 @@
         <v>2</v>
       </c>
       <c r="AY52">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AZ52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA52">
         <v>5</v>
@@ -12532,10 +12532,10 @@
         <v>5</v>
       </c>
       <c r="AY53">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ53">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA53">
         <v>5</v>
@@ -12738,10 +12738,10 @@
         <v>5</v>
       </c>
       <c r="AY54">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ54">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA54">
         <v>9</v>
@@ -12944,10 +12944,10 @@
         <v>6</v>
       </c>
       <c r="AY55">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ55">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA55">
         <v>3</v>
@@ -13150,10 +13150,10 @@
         <v>8</v>
       </c>
       <c r="AY56">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ56">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA56">
         <v>3</v>
@@ -13356,10 +13356,10 @@
         <v>3</v>
       </c>
       <c r="AY57">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ57">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA57">
         <v>9</v>
@@ -13562,10 +13562,10 @@
         <v>6</v>
       </c>
       <c r="AY58">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ58">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA58">
         <v>6</v>
@@ -13768,10 +13768,10 @@
         <v>5</v>
       </c>
       <c r="AY59">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ59">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="BA59">
         <v>7</v>
@@ -13974,10 +13974,10 @@
         <v>4</v>
       </c>
       <c r="AY60">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AZ60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA60">
         <v>4</v>
@@ -14180,10 +14180,10 @@
         <v>12</v>
       </c>
       <c r="AY61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ61">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="BA61">
         <v>2</v>
@@ -14386,10 +14386,10 @@
         <v>3</v>
       </c>
       <c r="AY62">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ62">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA62">
         <v>8</v>
@@ -14592,10 +14592,10 @@
         <v>1</v>
       </c>
       <c r="AY63">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA63">
         <v>6</v>
@@ -14798,10 +14798,10 @@
         <v>5</v>
       </c>
       <c r="AY64">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ64">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA64">
         <v>8</v>
@@ -15004,10 +15004,10 @@
         <v>5</v>
       </c>
       <c r="AY65">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ65">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA65">
         <v>3</v>
@@ -15210,10 +15210,10 @@
         <v>1</v>
       </c>
       <c r="AY66">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA66">
         <v>7</v>
@@ -15416,10 +15416,10 @@
         <v>3</v>
       </c>
       <c r="AY67">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ67">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA67">
         <v>3</v>
@@ -15622,10 +15622,10 @@
         <v>4</v>
       </c>
       <c r="AY68">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ68">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA68">
         <v>8</v>
@@ -16034,10 +16034,10 @@
         <v>3</v>
       </c>
       <c r="AY70">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ70">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA70">
         <v>5</v>
@@ -16240,10 +16240,10 @@
         <v>5</v>
       </c>
       <c r="AY71">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ71">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA71">
         <v>2</v>
@@ -16446,10 +16446,10 @@
         <v>4</v>
       </c>
       <c r="AY72">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ72">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA72">
         <v>5</v>
@@ -16655,7 +16655,7 @@
         <v>6</v>
       </c>
       <c r="AZ73">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BA73">
         <v>0</v>
@@ -16858,10 +16858,10 @@
         <v>2</v>
       </c>
       <c r="AY74">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ74">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA74">
         <v>4</v>
@@ -17064,10 +17064,10 @@
         <v>8</v>
       </c>
       <c r="AY75">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ75">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA75">
         <v>3</v>
@@ -17270,10 +17270,10 @@
         <v>10</v>
       </c>
       <c r="AY76">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ76">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA76">
         <v>2</v>
@@ -18506,10 +18506,10 @@
         <v>4</v>
       </c>
       <c r="AY82">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ82">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA82">
         <v>6</v>
@@ -18712,10 +18712,10 @@
         <v>1</v>
       </c>
       <c r="AY83">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA83">
         <v>9</v>
@@ -18918,10 +18918,10 @@
         <v>2</v>
       </c>
       <c r="AY84">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ84">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA84">
         <v>6</v>
@@ -19124,10 +19124,10 @@
         <v>2</v>
       </c>
       <c r="AY85">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ85">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA85">
         <v>6</v>
@@ -19333,7 +19333,7 @@
         <v>6</v>
       </c>
       <c r="AZ86">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA86">
         <v>2</v>
@@ -19536,10 +19536,10 @@
         <v>2</v>
       </c>
       <c r="AY87">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA87">
         <v>5</v>
@@ -19742,7 +19742,7 @@
         <v>1</v>
       </c>
       <c r="AY88">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ88">
         <v>4</v>
@@ -19948,10 +19948,10 @@
         <v>6</v>
       </c>
       <c r="AY89">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ89">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA89">
         <v>4</v>
@@ -20154,10 +20154,10 @@
         <v>2</v>
       </c>
       <c r="AY90">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ90">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA90">
         <v>3</v>
@@ -20360,10 +20360,10 @@
         <v>6</v>
       </c>
       <c r="AY91">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ91">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA91">
         <v>4</v>
@@ -20566,10 +20566,10 @@
         <v>4</v>
       </c>
       <c r="AY92">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ92">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA92">
         <v>2</v>
@@ -20772,10 +20772,10 @@
         <v>5</v>
       </c>
       <c r="AY93">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ93">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA93">
         <v>6</v>
@@ -20978,10 +20978,10 @@
         <v>4</v>
       </c>
       <c r="AY94">
+        <v>6</v>
+      </c>
+      <c r="AZ94">
         <v>7</v>
-      </c>
-      <c r="AZ94">
-        <v>12</v>
       </c>
       <c r="BA94">
         <v>1</v>
@@ -21184,10 +21184,10 @@
         <v>3</v>
       </c>
       <c r="AY95">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ95">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA95">
         <v>10</v>
@@ -21390,7 +21390,7 @@
         <v>2</v>
       </c>
       <c r="AY96">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ96">
         <v>7</v>
@@ -21596,10 +21596,10 @@
         <v>2</v>
       </c>
       <c r="AY97">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ97">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA97">
         <v>1</v>
@@ -21802,10 +21802,10 @@
         <v>7</v>
       </c>
       <c r="AY98">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ98">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA98">
         <v>4</v>
@@ -22008,10 +22008,10 @@
         <v>6</v>
       </c>
       <c r="AY99">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ99">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA99">
         <v>4</v>
@@ -22214,10 +22214,10 @@
         <v>4</v>
       </c>
       <c r="AY100">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AZ100">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA100">
         <v>4</v>
@@ -22420,10 +22420,10 @@
         <v>4</v>
       </c>
       <c r="AY101">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ101">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA101">
         <v>4</v>
@@ -22626,10 +22626,10 @@
         <v>6</v>
       </c>
       <c r="AY102">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ102">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA102">
         <v>5</v>
@@ -22832,10 +22832,10 @@
         <v>3</v>
       </c>
       <c r="AY103">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ103">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BA103">
         <v>5</v>
@@ -23038,10 +23038,10 @@
         <v>6</v>
       </c>
       <c r="AY104">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ104">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA104">
         <v>4</v>
@@ -23244,10 +23244,10 @@
         <v>7</v>
       </c>
       <c r="AY105">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ105">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA105">
         <v>0</v>
@@ -23450,10 +23450,10 @@
         <v>3</v>
       </c>
       <c r="AY106">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ106">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA106">
         <v>5</v>
@@ -23656,10 +23656,10 @@
         <v>5</v>
       </c>
       <c r="AY107">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AZ107">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA107">
         <v>2</v>
@@ -23862,10 +23862,10 @@
         <v>3</v>
       </c>
       <c r="AY108">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="AZ108">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA108">
         <v>10</v>
@@ -25098,10 +25098,10 @@
         <v>4</v>
       </c>
       <c r="AY114">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ114">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA114">
         <v>8</v>
@@ -25304,10 +25304,10 @@
         <v>3</v>
       </c>
       <c r="AY115">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA115">
         <v>5</v>
@@ -25510,10 +25510,10 @@
         <v>5</v>
       </c>
       <c r="AY116">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ116">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA116">
         <v>8</v>
@@ -25922,10 +25922,10 @@
         <v>5</v>
       </c>
       <c r="AY118">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ118">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BA118">
         <v>3</v>
@@ -26128,10 +26128,10 @@
         <v>5</v>
       </c>
       <c r="AY119">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ119">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA119">
         <v>5</v>
@@ -26334,10 +26334,10 @@
         <v>3</v>
       </c>
       <c r="AY120">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ120">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA120">
         <v>3</v>
@@ -26540,10 +26540,10 @@
         <v>2</v>
       </c>
       <c r="AY121">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ121">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA121">
         <v>9</v>
@@ -26746,10 +26746,10 @@
         <v>6</v>
       </c>
       <c r="AY122">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ122">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA122">
         <v>3</v>
@@ -26952,10 +26952,10 @@
         <v>3</v>
       </c>
       <c r="AY123">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ123">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA123">
         <v>4</v>
@@ -27158,10 +27158,10 @@
         <v>4</v>
       </c>
       <c r="AY124">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ124">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA124">
         <v>8</v>
@@ -27570,10 +27570,10 @@
         <v>1</v>
       </c>
       <c r="AY126">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ126">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA126">
         <v>7</v>
@@ -27776,10 +27776,10 @@
         <v>6</v>
       </c>
       <c r="AY127">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ127">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA127">
         <v>7</v>
@@ -27982,10 +27982,10 @@
         <v>3</v>
       </c>
       <c r="AY128">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ128">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA128">
         <v>9</v>
@@ -28188,10 +28188,10 @@
         <v>5</v>
       </c>
       <c r="AY129">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ129">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA129">
         <v>5</v>
@@ -28394,10 +28394,10 @@
         <v>3</v>
       </c>
       <c r="AY130">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AZ130">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA130">
         <v>9</v>
@@ -28600,10 +28600,10 @@
         <v>7</v>
       </c>
       <c r="AY131">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ131">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA131">
         <v>2</v>
@@ -28806,10 +28806,10 @@
         <v>1</v>
       </c>
       <c r="AY132">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ132">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA132">
         <v>5</v>
@@ -29012,10 +29012,10 @@
         <v>4</v>
       </c>
       <c r="AY133">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ133">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA133">
         <v>6</v>
@@ -29218,10 +29218,10 @@
         <v>3</v>
       </c>
       <c r="AY134">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ134">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA134">
         <v>6</v>
@@ -29427,7 +29427,7 @@
         <v>10</v>
       </c>
       <c r="AZ135">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BA135">
         <v>2</v>
@@ -29630,10 +29630,10 @@
         <v>2</v>
       </c>
       <c r="AY136">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ136">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA136">
         <v>4</v>
@@ -29836,7 +29836,7 @@
         <v>4</v>
       </c>
       <c r="AY137">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AZ137">
         <v>11</v>
@@ -30042,10 +30042,10 @@
         <v>6</v>
       </c>
       <c r="AY138">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ138">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA138">
         <v>7</v>
@@ -30248,10 +30248,10 @@
         <v>4</v>
       </c>
       <c r="AY139">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ139">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA139">
         <v>12</v>
@@ -30454,10 +30454,10 @@
         <v>0</v>
       </c>
       <c r="AY140">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ140">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA140">
         <v>10</v>
@@ -30660,10 +30660,10 @@
         <v>2</v>
       </c>
       <c r="AY141">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AZ141">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA141">
         <v>7</v>
@@ -30866,10 +30866,10 @@
         <v>7</v>
       </c>
       <c r="AY142">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ142">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA142">
         <v>13</v>
@@ -31072,10 +31072,10 @@
         <v>4</v>
       </c>
       <c r="AY143">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ143">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA143">
         <v>3</v>
@@ -31278,7 +31278,7 @@
         <v>5</v>
       </c>
       <c r="AY144">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ144">
         <v>5</v>
@@ -31487,7 +31487,7 @@
         <v>5</v>
       </c>
       <c r="AZ145">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA145">
         <v>1</v>
@@ -31690,10 +31690,10 @@
         <v>3</v>
       </c>
       <c r="AY146">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ146">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA146">
         <v>7</v>
@@ -31896,10 +31896,10 @@
         <v>6</v>
       </c>
       <c r="AY147">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AZ147">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA147">
         <v>11</v>
@@ -32102,10 +32102,10 @@
         <v>5</v>
       </c>
       <c r="AY148">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ148">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA148">
         <v>6</v>
@@ -32308,10 +32308,10 @@
         <v>3</v>
       </c>
       <c r="AY149">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ149">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA149">
         <v>4</v>
@@ -32514,10 +32514,10 @@
         <v>2</v>
       </c>
       <c r="AY150">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ150">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA150">
         <v>7</v>
@@ -32720,10 +32720,10 @@
         <v>5</v>
       </c>
       <c r="AY151">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ151">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA151">
         <v>4</v>
@@ -32926,10 +32926,10 @@
         <v>5</v>
       </c>
       <c r="AY152">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ152">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA152">
         <v>7</v>
@@ -33132,10 +33132,10 @@
         <v>4</v>
       </c>
       <c r="AY153">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ153">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA153">
         <v>5</v>
@@ -33338,10 +33338,10 @@
         <v>10</v>
       </c>
       <c r="AY154">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ154">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA154">
         <v>9</v>
@@ -33544,10 +33544,10 @@
         <v>11</v>
       </c>
       <c r="AY155">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ155">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA155">
         <v>8</v>
@@ -33750,10 +33750,10 @@
         <v>9</v>
       </c>
       <c r="AY156">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AZ156">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA156">
         <v>9</v>
@@ -33956,10 +33956,10 @@
         <v>7</v>
       </c>
       <c r="AY157">
+        <v>9</v>
+      </c>
+      <c r="AZ157">
         <v>11</v>
-      </c>
-      <c r="AZ157">
-        <v>12</v>
       </c>
       <c r="BA157">
         <v>6</v>
@@ -34162,10 +34162,10 @@
         <v>4</v>
       </c>
       <c r="AY158">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ158">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA158">
         <v>11</v>
@@ -34368,10 +34368,10 @@
         <v>4</v>
       </c>
       <c r="AY159">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ159">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA159">
         <v>7</v>
@@ -34574,7 +34574,7 @@
         <v>6</v>
       </c>
       <c r="AY160">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ160">
         <v>10</v>
@@ -34780,10 +34780,10 @@
         <v>4</v>
       </c>
       <c r="AY161">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ161">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA161">
         <v>15</v>
@@ -34986,10 +34986,10 @@
         <v>7</v>
       </c>
       <c r="AY162">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ162">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA162">
         <v>7</v>
@@ -35195,7 +35195,7 @@
         <v>9</v>
       </c>
       <c r="AZ163">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA163">
         <v>3</v>
@@ -35398,10 +35398,10 @@
         <v>8</v>
       </c>
       <c r="AY164">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ164">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA164">
         <v>4</v>
@@ -35604,10 +35604,10 @@
         <v>8</v>
       </c>
       <c r="AY165">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ165">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA165">
         <v>3</v>
@@ -35810,10 +35810,10 @@
         <v>17</v>
       </c>
       <c r="AY166">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ166">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BA166">
         <v>2</v>
@@ -36016,10 +36016,10 @@
         <v>19</v>
       </c>
       <c r="AY167">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ167">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BA167">
         <v>7</v>
@@ -36222,7 +36222,7 @@
         <v>6</v>
       </c>
       <c r="AY168">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ168">
         <v>10</v>
@@ -36428,10 +36428,10 @@
         <v>9</v>
       </c>
       <c r="AY169">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ169">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA169">
         <v>5</v>
@@ -36840,10 +36840,10 @@
         <v>14</v>
       </c>
       <c r="AY171">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AZ171">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BA171">
         <v>6</v>
@@ -37046,10 +37046,10 @@
         <v>12</v>
       </c>
       <c r="AY172">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ172">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA172">
         <v>4</v>
@@ -37252,10 +37252,10 @@
         <v>13</v>
       </c>
       <c r="AY173">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AZ173">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA173">
         <v>10</v>
@@ -37458,10 +37458,10 @@
         <v>7</v>
       </c>
       <c r="AY174">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ174">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA174">
         <v>5</v>
@@ -37664,7 +37664,7 @@
         <v>4</v>
       </c>
       <c r="AY175">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ175">
         <v>9</v>
@@ -37870,10 +37870,10 @@
         <v>5</v>
       </c>
       <c r="AY176">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ176">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA176">
         <v>10</v>
@@ -38076,10 +38076,10 @@
         <v>6</v>
       </c>
       <c r="AY177">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AZ177">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA177">
         <v>8</v>
@@ -38488,10 +38488,10 @@
         <v>6</v>
       </c>
       <c r="AY179">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ179">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA179">
         <v>4</v>
@@ -38694,10 +38694,10 @@
         <v>8</v>
       </c>
       <c r="AY180">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ180">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA180">
         <v>5</v>
@@ -38900,7 +38900,7 @@
         <v>2</v>
       </c>
       <c r="AY181">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AZ181">
         <v>7</v>
@@ -39106,7 +39106,7 @@
         <v>9</v>
       </c>
       <c r="AY182">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ182">
         <v>16</v>
@@ -39312,10 +39312,10 @@
         <v>14</v>
       </c>
       <c r="AY183">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ183">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BA183">
         <v>5</v>
@@ -39521,7 +39521,7 @@
         <v>18</v>
       </c>
       <c r="AZ184">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA184">
         <v>7</v>
@@ -39727,7 +39727,7 @@
         <v>10</v>
       </c>
       <c r="AZ185">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA185">
         <v>4</v>
@@ -40139,7 +40139,7 @@
         <v>4</v>
       </c>
       <c r="AZ187">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA187">
         <v>1</v>
@@ -40342,10 +40342,10 @@
         <v>6</v>
       </c>
       <c r="AY188">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AZ188">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA188">
         <v>11</v>
@@ -40551,7 +40551,7 @@
         <v>16</v>
       </c>
       <c r="AZ189">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA189">
         <v>6</v>
@@ -40754,10 +40754,10 @@
         <v>9</v>
       </c>
       <c r="AY190">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ190">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA190">
         <v>7</v>
@@ -40960,10 +40960,10 @@
         <v>10</v>
       </c>
       <c r="AY191">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ191">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA191">
         <v>6</v>
@@ -41166,10 +41166,10 @@
         <v>9</v>
       </c>
       <c r="AY192">
+        <v>16</v>
+      </c>
+      <c r="AZ192">
         <v>17</v>
-      </c>
-      <c r="AZ192">
-        <v>18</v>
       </c>
       <c r="BA192">
         <v>8</v>
@@ -41372,10 +41372,10 @@
         <v>12</v>
       </c>
       <c r="AY193">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ193">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA193">
         <v>7</v>
@@ -41581,7 +41581,7 @@
         <v>11</v>
       </c>
       <c r="AZ194">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA194">
         <v>5</v>
@@ -41787,7 +41787,7 @@
         <v>12</v>
       </c>
       <c r="AZ195">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA195">
         <v>3</v>
@@ -41990,7 +41990,7 @@
         <v>1</v>
       </c>
       <c r="AY196">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AZ196">
         <v>5</v>
@@ -42196,10 +42196,10 @@
         <v>13</v>
       </c>
       <c r="AY197">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ197">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA197">
         <v>8</v>
@@ -42402,10 +42402,10 @@
         <v>3</v>
       </c>
       <c r="AY198">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="AZ198">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA198">
         <v>9</v>
@@ -42608,10 +42608,10 @@
         <v>18</v>
       </c>
       <c r="AY199">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ199">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BA199">
         <v>6</v>
@@ -42814,10 +42814,10 @@
         <v>7</v>
       </c>
       <c r="AY200">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ200">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA200">
         <v>5</v>
@@ -43020,10 +43020,10 @@
         <v>8</v>
       </c>
       <c r="AY201">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ201">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA201">
         <v>4</v>
@@ -43226,10 +43226,10 @@
         <v>8</v>
       </c>
       <c r="AY202">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AZ202">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA202">
         <v>8</v>
@@ -43435,7 +43435,7 @@
         <v>8</v>
       </c>
       <c r="AZ203">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA203">
         <v>3</v>
@@ -43638,10 +43638,10 @@
         <v>4</v>
       </c>
       <c r="AY204">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ204">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA204">
         <v>5</v>
@@ -43844,7 +43844,7 @@
         <v>9</v>
       </c>
       <c r="AY205">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ205">
         <v>14</v>
@@ -44053,7 +44053,7 @@
         <v>12</v>
       </c>
       <c r="AZ206">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA206">
         <v>2</v>
@@ -44256,10 +44256,10 @@
         <v>5</v>
       </c>
       <c r="AY207">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AZ207">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA207">
         <v>3</v>
@@ -44462,10 +44462,10 @@
         <v>5</v>
       </c>
       <c r="AY208">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ208">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA208">
         <v>9</v>
@@ -44668,7 +44668,7 @@
         <v>4</v>
       </c>
       <c r="AY209">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ209">
         <v>7</v>
@@ -44874,7 +44874,7 @@
         <v>5</v>
       </c>
       <c r="AY210">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ210">
         <v>9</v>
@@ -45083,7 +45083,7 @@
         <v>10</v>
       </c>
       <c r="AZ211">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA211">
         <v>2</v>
@@ -45286,10 +45286,10 @@
         <v>10</v>
       </c>
       <c r="AY212">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ212">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA212">
         <v>2</v>
@@ -45492,7 +45492,7 @@
         <v>3</v>
       </c>
       <c r="AY213">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ213">
         <v>7</v>
@@ -45698,10 +45698,10 @@
         <v>9</v>
       </c>
       <c r="AY214">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ214">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA214">
         <v>3</v>
@@ -45904,7 +45904,7 @@
         <v>2</v>
       </c>
       <c r="AY215">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ215">
         <v>6</v>
@@ -46110,10 +46110,10 @@
         <v>3</v>
       </c>
       <c r="AY216">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ216">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA216">
         <v>3</v>
@@ -46316,10 +46316,10 @@
         <v>6</v>
       </c>
       <c r="AY217">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ217">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA217">
         <v>9</v>
@@ -46522,10 +46522,10 @@
         <v>13</v>
       </c>
       <c r="AY218">
+        <v>13</v>
+      </c>
+      <c r="AZ218">
         <v>17</v>
-      </c>
-      <c r="AZ218">
-        <v>25</v>
       </c>
       <c r="BA218">
         <v>5</v>
@@ -46728,10 +46728,10 @@
         <v>7</v>
       </c>
       <c r="AY219">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ219">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA219">
         <v>2</v>
@@ -46934,7 +46934,7 @@
         <v>4</v>
       </c>
       <c r="AY220">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AZ220">
         <v>8</v>
@@ -47140,10 +47140,10 @@
         <v>9</v>
       </c>
       <c r="AY221">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ221">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA221">
         <v>4</v>
@@ -47346,10 +47346,10 @@
         <v>6</v>
       </c>
       <c r="AY222">
+        <v>11</v>
+      </c>
+      <c r="AZ222">
         <v>12</v>
-      </c>
-      <c r="AZ222">
-        <v>15</v>
       </c>
       <c r="BA222">
         <v>3</v>
@@ -47552,10 +47552,10 @@
         <v>13</v>
       </c>
       <c r="AY223">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ223">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA223">
         <v>3</v>
@@ -47758,10 +47758,10 @@
         <v>6</v>
       </c>
       <c r="AY224">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ224">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA224">
         <v>4</v>
@@ -47964,7 +47964,7 @@
         <v>9</v>
       </c>
       <c r="AY225">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ225">
         <v>13</v>
@@ -48170,10 +48170,10 @@
         <v>11</v>
       </c>
       <c r="AY226">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ226">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA226">
         <v>6</v>
@@ -48376,10 +48376,10 @@
         <v>3</v>
       </c>
       <c r="AY227">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ227">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA227">
         <v>1</v>
@@ -48994,7 +48994,7 @@
         <v>2</v>
       </c>
       <c r="AY230">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AZ230">
         <v>6</v>
@@ -49200,10 +49200,10 @@
         <v>3</v>
       </c>
       <c r="AY231">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ231">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA231">
         <v>9</v>
@@ -49406,7 +49406,7 @@
         <v>3</v>
       </c>
       <c r="AY232">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ232">
         <v>10</v>
@@ -49612,7 +49612,7 @@
         <v>4</v>
       </c>
       <c r="AY233">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ233">
         <v>7</v>
@@ -49818,10 +49818,10 @@
         <v>1</v>
       </c>
       <c r="AY234">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ234">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA234">
         <v>3</v>
@@ -50024,10 +50024,10 @@
         <v>8</v>
       </c>
       <c r="AY235">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ235">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA235">
         <v>2</v>
@@ -50230,10 +50230,10 @@
         <v>15</v>
       </c>
       <c r="AY236">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ236">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA236">
         <v>8</v>
@@ -50436,10 +50436,10 @@
         <v>8</v>
       </c>
       <c r="AY237">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AZ237">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA237">
         <v>11</v>
@@ -50642,10 +50642,10 @@
         <v>4</v>
       </c>
       <c r="AY238">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ238">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA238">
         <v>5</v>
@@ -50851,7 +50851,7 @@
         <v>13</v>
       </c>
       <c r="AZ239">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA239">
         <v>4</v>
@@ -51054,10 +51054,10 @@
         <v>6</v>
       </c>
       <c r="AY240">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ240">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA240">
         <v>1</v>
@@ -51260,7 +51260,7 @@
         <v>7</v>
       </c>
       <c r="AY241">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ241">
         <v>10</v>
@@ -51466,10 +51466,10 @@
         <v>10</v>
       </c>
       <c r="AY242">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ242">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA242">
         <v>2</v>
@@ -51672,10 +51672,10 @@
         <v>4</v>
       </c>
       <c r="AY243">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AZ243">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA243">
         <v>12</v>
@@ -51878,7 +51878,7 @@
         <v>5</v>
       </c>
       <c r="AY244">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ244">
         <v>7</v>
@@ -52084,10 +52084,10 @@
         <v>8</v>
       </c>
       <c r="AY245">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AZ245">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA245">
         <v>9</v>
@@ -52290,10 +52290,10 @@
         <v>8</v>
       </c>
       <c r="AY246">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AZ246">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA246">
         <v>5</v>
@@ -52496,10 +52496,10 @@
         <v>4</v>
       </c>
       <c r="AY247">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ247">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA247">
         <v>7</v>
@@ -52702,10 +52702,10 @@
         <v>11</v>
       </c>
       <c r="AY248">
+        <v>15</v>
+      </c>
+      <c r="AZ248">
         <v>17</v>
-      </c>
-      <c r="AZ248">
-        <v>20</v>
       </c>
       <c r="BA248">
         <v>4</v>
@@ -52908,7 +52908,7 @@
         <v>5</v>
       </c>
       <c r="AY249">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AZ249">
         <v>12</v>
@@ -53114,10 +53114,10 @@
         <v>7</v>
       </c>
       <c r="AY250">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ250">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA250">
         <v>6</v>
@@ -53320,10 +53320,10 @@
         <v>10</v>
       </c>
       <c r="AY251">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ251">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA251">
         <v>1</v>
@@ -53529,7 +53529,7 @@
         <v>14</v>
       </c>
       <c r="AZ252">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA252">
         <v>3</v>
@@ -53732,7 +53732,7 @@
         <v>5</v>
       </c>
       <c r="AY253">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ253">
         <v>9</v>
@@ -53938,10 +53938,10 @@
         <v>7</v>
       </c>
       <c r="AY254">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ254">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA254">
         <v>3</v>
@@ -54144,10 +54144,10 @@
         <v>2</v>
       </c>
       <c r="AY255">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ255">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA255">
         <v>5</v>
@@ -54350,10 +54350,10 @@
         <v>6</v>
       </c>
       <c r="AY256">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ256">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA256">
         <v>4</v>
@@ -54556,7 +54556,7 @@
         <v>6</v>
       </c>
       <c r="AY257">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AZ257">
         <v>9</v>
@@ -54762,10 +54762,10 @@
         <v>6</v>
       </c>
       <c r="AY258">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AZ258">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA258">
         <v>6</v>
@@ -54968,10 +54968,10 @@
         <v>7</v>
       </c>
       <c r="AY259">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ259">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA259">
         <v>2</v>
@@ -55174,10 +55174,10 @@
         <v>9</v>
       </c>
       <c r="AY260">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ260">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA260">
         <v>4</v>
@@ -55380,10 +55380,10 @@
         <v>6</v>
       </c>
       <c r="AY261">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ261">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA261">
         <v>6</v>
@@ -55589,7 +55589,7 @@
         <v>6</v>
       </c>
       <c r="AZ262">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BA262">
         <v>1</v>
@@ -55792,7 +55792,7 @@
         <v>8</v>
       </c>
       <c r="AY263">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ263">
         <v>13</v>
@@ -55998,10 +55998,10 @@
         <v>4</v>
       </c>
       <c r="AY264">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ264">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA264">
         <v>1</v>
@@ -56204,10 +56204,10 @@
         <v>5</v>
       </c>
       <c r="AY265">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ265">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA265">
         <v>3</v>
@@ -56410,10 +56410,10 @@
         <v>5</v>
       </c>
       <c r="AY266">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ266">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA266">
         <v>10</v>
@@ -56616,10 +56616,10 @@
         <v>8</v>
       </c>
       <c r="AY267">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ267">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA267">
         <v>3</v>
@@ -56822,19 +56822,19 @@
         <v>12</v>
       </c>
       <c r="AY268">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ268">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BA268">
         <v>5</v>
       </c>
       <c r="BB268">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC268">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD268">
         <v>0</v>
@@ -57028,10 +57028,10 @@
         <v>15</v>
       </c>
       <c r="AY269">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ269">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA269">
         <v>1</v>
@@ -57234,10 +57234,10 @@
         <v>4</v>
       </c>
       <c r="AY270">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ270">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA270">
         <v>4</v>
@@ -57440,10 +57440,10 @@
         <v>8</v>
       </c>
       <c r="AY271">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AZ271">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA271">
         <v>11</v>
@@ -57646,10 +57646,10 @@
         <v>6</v>
       </c>
       <c r="AY272">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ272">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA272">
         <v>7</v>
@@ -57852,10 +57852,10 @@
         <v>4</v>
       </c>
       <c r="AY273">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AZ273">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA273">
         <v>13</v>
@@ -58058,10 +58058,10 @@
         <v>7</v>
       </c>
       <c r="AY274">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ274">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA274">
         <v>4</v>
@@ -58264,10 +58264,10 @@
         <v>7</v>
       </c>
       <c r="AY275">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ275">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA275">
         <v>5</v>
@@ -58470,10 +58470,10 @@
         <v>5</v>
       </c>
       <c r="AY276">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AZ276">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA276">
         <v>5</v>
@@ -58676,10 +58676,10 @@
         <v>3</v>
       </c>
       <c r="AY277">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA277">
         <v>5</v>
@@ -58882,7 +58882,7 @@
         <v>8</v>
       </c>
       <c r="AY278">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ278">
         <v>14</v>
@@ -59088,10 +59088,10 @@
         <v>7</v>
       </c>
       <c r="AY279">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AZ279">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA279">
         <v>5</v>
@@ -59294,10 +59294,10 @@
         <v>9</v>
       </c>
       <c r="AY280">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ280">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA280">
         <v>6</v>
@@ -59503,7 +59503,7 @@
         <v>11</v>
       </c>
       <c r="AZ281">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA281">
         <v>5</v>
@@ -59706,7 +59706,7 @@
         <v>2</v>
       </c>
       <c r="AY282">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ282">
         <v>5</v>
@@ -59912,10 +59912,10 @@
         <v>0</v>
       </c>
       <c r="AY283">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ283">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA283">
         <v>5</v>
@@ -60118,10 +60118,10 @@
         <v>4</v>
       </c>
       <c r="AY284">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AZ284">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA284">
         <v>6</v>
@@ -60324,10 +60324,10 @@
         <v>6</v>
       </c>
       <c r="AY285">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AZ285">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA285">
         <v>6</v>
@@ -60530,10 +60530,10 @@
         <v>8</v>
       </c>
       <c r="AY286">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ286">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA286">
         <v>7</v>
@@ -60736,10 +60736,10 @@
         <v>14</v>
       </c>
       <c r="AY287">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ287">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BA287">
         <v>1</v>
@@ -60945,7 +60945,7 @@
         <v>24</v>
       </c>
       <c r="AZ288">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA288">
         <v>8</v>
@@ -61148,19 +61148,19 @@
         <v>7</v>
       </c>
       <c r="AY289">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ289">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA289">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB289">
         <v>4</v>
       </c>
       <c r="BC289">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD289">
         <v>1.3</v>
@@ -61354,10 +61354,10 @@
         <v>11</v>
       </c>
       <c r="AY290">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ290">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA290">
         <v>3</v>
@@ -61560,7 +61560,7 @@
         <v>1</v>
       </c>
       <c r="AY291">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AZ291">
         <v>4</v>
@@ -61766,7 +61766,7 @@
         <v>10</v>
       </c>
       <c r="AY292">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ292">
         <v>10</v>
@@ -61972,10 +61972,10 @@
         <v>14</v>
       </c>
       <c r="AY293">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ293">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA293">
         <v>2</v>
@@ -62178,10 +62178,10 @@
         <v>5</v>
       </c>
       <c r="AY294">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AZ294">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA294">
         <v>11</v>
@@ -62384,10 +62384,10 @@
         <v>8</v>
       </c>
       <c r="AY295">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ295">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA295">
         <v>3</v>
@@ -62590,7 +62590,7 @@
         <v>9</v>
       </c>
       <c r="AY296">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ296">
         <v>14</v>
@@ -63002,10 +63002,10 @@
         <v>5</v>
       </c>
       <c r="AY298">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ298">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA298">
         <v>6</v>
@@ -63211,7 +63211,7 @@
         <v>15</v>
       </c>
       <c r="AZ299">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA299">
         <v>4</v>
@@ -63414,10 +63414,10 @@
         <v>8</v>
       </c>
       <c r="AY300">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ300">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA300">
         <v>4</v>
@@ -63620,10 +63620,10 @@
         <v>10</v>
       </c>
       <c r="AY301">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ301">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA301">
         <v>9</v>
@@ -64032,10 +64032,10 @@
         <v>5</v>
       </c>
       <c r="AY303">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ303">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA303">
         <v>4</v>
@@ -64238,10 +64238,10 @@
         <v>9</v>
       </c>
       <c r="AY304">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ304">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA304">
         <v>4</v>
@@ -64444,10 +64444,10 @@
         <v>24</v>
       </c>
       <c r="AY305">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ305">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BA305">
         <v>4</v>
@@ -64650,7 +64650,7 @@
         <v>4</v>
       </c>
       <c r="AY306">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ306">
         <v>9</v>
@@ -64859,7 +64859,7 @@
         <v>7</v>
       </c>
       <c r="AZ307">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BA307">
         <v>0</v>
@@ -65065,7 +65065,7 @@
         <v>13</v>
       </c>
       <c r="AZ308">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA308">
         <v>4</v>
@@ -65268,19 +65268,19 @@
         <v>15</v>
       </c>
       <c r="AY309">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ309">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BA309">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB309">
         <v>8</v>
       </c>
       <c r="BC309">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD309">
         <v>1.27</v>
@@ -65474,10 +65474,10 @@
         <v>7</v>
       </c>
       <c r="AY310">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ310">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA310">
         <v>3</v>
